--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -207,6 +207,27 @@
 Die vorliegende Standesinitiative des Kantons Basel-Stadt verlangt, wie der Kommissionssprecher ausgeführt hat, dass die beiden Basel zu Kantonen mit vollem Ständerecht aufgewertet werden. Im Namen der Minderheit und auch im Namen der beiden Kantone bitte ich Sie, diese Standesinitiative zu unterstützen und damit dem Grundsatz zuzustimmen, dass das Thema der Kantone mit halber Standesstimme endlich ernsthaft aufs staatspolitische Tapet gehört. 
 Das Thema beschäftigt unsere Region seit Jahrzehnten. Aufschwung bekam die Debatte aber vor allem auch wieder mit der Gründung des Kantons Jura 1979. Die Eidgenossenschaft entschied damals, nicht zwei Halbkantone, den Kanton Bern und den Kanton Jura, zu gründen und die Standesstimmen zwischen den beiden aufzuteilen, sondern den beiden Kantonen die Gleichbehandlung zu gewähren und zwei Standesstimmen zuzugestehen. Damit wurde damals auch die Zusammensetzung des Ständerates verändert. Anders war es damals bei der Gründung meines Kantons, des Kantons Basel-Landschaft. Die Ländler wehrten sich damals - eine kleine Geschichtsstunde für Sie - erfolgreich gegen die Besetzung durch die Städter. 1832 wurde per Volksabstimmung der Kanton Basel-Landschaft gegründet und dann 1833 nach einem für die Städter verlustreichen Gefecht mit einem entsprechenden Beschluss der Tagsatzung endgültig auch durchgesetzt. Die beiden ehemaligen Halbkantone erhielten dann je eine Stimme im Ständerat. Knapp 150 Jahre später wurde mit der Gründung des Kantons Jura gewissermassen das offizielle Bekenntnis zum Ende der Geschichte der Halbkantone gesetzt. Schon damals monierten die Vertretungen aus dem Kanton Basel-Landschaft, wie es sich denn nun mit ihrem Kanton verhalte, wann sie jetzt endlich gleichbehandelt würden. Der damals zuständige Bundesrat Furgler vertröstete sie, die Frage könne man dann im Rahmen der nächsten Totalrevision der Bundesverfassung diskutieren. Er wolle, sagte er verständlicherweise, jetzt die Gründung des Kantons Jura nicht gefährden. Dann wurden die Halbkantone im Rahmen der Totalrevision zwar abgeschafft und die Gleichheit der Kantone und das Gebot der Gleichbehandlung der Kantone festgehalten, aber das Relikt der sogenannt vollwertigen Kantone mit halber Standesstimme blieb bestehen. 2001 wurde der parlamentarischen Initiative Janiak 01.403, "Basel-Landschaft und Basel-Stadt. Vollberechtigte Kantone", vom Nationalrat ebenfalls keine Folge gegeben. Auch damals wurde dagegen vor allem eingewendet, dass die Verfassung des Kantons Basel-Stadt damals noch das Ziel der Wiedervereinigung beinhaltete. Basel-Land strebte bereits damals die zwei Sitze an, Basel-Stadt aber den Zusammenschluss. Mehr als zehn Jahre später wurde über eine Initiative zur Wiedervereinigung abgestimmt. Basel-Stadt nahm diese an, Basel-Land aber lehnte sie mit über 70 Prozent ab. Unterdessen wurde auch die Verfassung des Kantons Basel-Stadt angepasst. Die Wiedervereinigung ist nun kein offizielles Verfassungsziel mehr, nur die gute Zusammenarbeit. All das zeigt, dass sich seit der Debatte in den 70er-Jahren die Situation auch vor Ort geändert hat und sich beide Kantone als vollwertige und auch selbstständige Kantone verstehen. In der Region wird nicht verstanden, warum man im Unterschied zu praktisch allen anderen Kantonen nur einen Sitz im Ständerat hat und man quasi vom Nachbarkanton Jura, der uns nahe ist und den wir gut kennen, links überholt wurde. 
 Mir ist klar, dass diese Standesinitiative Schwächen hat. Sie klärt nicht, warum neue Ungleichheiten mit den anderen Kantonen mit halber Standesstimme, den Appenzeller Kantonen sowie Nid- und Obwalden, geschaffen werden sollen. Auch das Argument der wirtschaftlichen Stärke, das in der Begründung der Initiative vom Kanton Basel-Stadt genannt wird, überzeugt mich persönlich nicht. Die Standesvertretung soll bekanntlich ja nicht an Wirtschaftsleistung oder an Grösse geknüpft werden. Ich bedauere deshalb - der Kommissionssprecher hat das ebenfalls erwähnt -, dass die Kommission meinen Antrag auf ein Postulat nicht unterstützt hat. Es braucht eine ernsthafte Auslegeordnung zu Reformoptionen, wie die Gleichbehandlung der Regionen bzw. der Kantone unter Berücksichtigung des Gleichgewichts im Bundesstaat erreicht werden können. Das ist keine statische Angelegenheit, die über hundert Jahre genau das gleiche Gleichgewicht darstellt. Sie werden mit mir einverstanden sein, dass die Konfession heute zum Beispiel nicht mehr die entscheidende Konfliktlinie in unserem Bundesstaat ist. Es sind andere Unterschiedlichkeiten, die wir überwinden und über die wir als Bundesstaat zusammenhalten müssen. Es sind sprachliche und kulturelle Differenzen, die es in einem vielfältigen Land wie der Schweiz gibt. Lassen Sie uns darüber nachdenken. Diese Standesinitiative könnte dafür der Anfang sein. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosenwasser Anna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Demokratie-Initiative verlangt, dass Ausländerinnen und Ausländer nach fünf Jahren in der Schweiz das Recht auf Einbürgerung erhalten. Die Bedingung ist, dass sie nach diesen fünf Jahren eine Landessprache beherrschen, die Sicherheit nicht gefährden und nicht ins Gefängnis müssen. 
+Momentan kann ein Viertel aller Menschen, die in der Schweiz leben, weder abstimmen noch wählen, geschweige denn für ein politisches Amt kandidieren. Das heisst, über 2 Millionen Menschen in der Schweiz sind zwar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Demokratie-Initiative verlangt, dass Ausländerinnen und Ausländer nach fünf Jahren in der Schweiz das Recht auf Einbürgerung erhalten. Die Bedingung ist, dass sie nach diesen fünf Jahren eine Landessprache beherrschen, die Sicherheit nicht gefährden und nicht ins Gefängnis müssen. 
+Momentan kann ein Viertel aller Menschen, die in der Schweiz leben, weder abstimmen noch wählen, geschweige denn für ein politisches Amt kandidieren. Das heisst, über 2 Millionen Menschen in der Schweiz sind zwar von politischen Entscheiden betroffen, dürfen aber nicht mitbestimmen. Wer hier zuhause ist, ist von hier. Diese Aussage ist nicht radikal, denn es geht nicht um unsere Wurzeln. Diejenigen, über die bestimmt wird, müssen mitbestimmen können. Wenn drei Viertel unseres Landes über das andere Viertel bestimmen, ist das keine vollwertige Demokratie. 
+Das aktuell geltende Einbürgerungsrecht ist eine Lotterie. Je nach Kanton hat man ein bisschen Glück oder sehr viel Pech. Im Aargau und im Kanton St. Gallen kostet es über 2000 Franken, sich einbürgern zu lassen, im Kanton Zug nur 350 Franken. Im Kanton Jura wurde eine Person von einer Einbürgerungskommission abgelehnt, weil sie am Sonntag Rasen gemäht hat. In Zürich wurde jemand nicht angenommen, weil er den geografischen und historischen Ursprung von Raclette nicht kannte. In Arth, in Schwyz, wurde jemand abgelehnt, weil er nicht wusste, dass Wölfe und Bären sich im Tierpark Goldau ein Gehege teilen. Es braucht endlich einheitliche Regeln gegen diese Willkür. Es sagt nichts über uns aus, ob wir wissen, welche Tiere sich ein Gehege teilen, aber es sagt viel über uns aus, mit wem wir ein Land teilen. 
+Wer einen Schweizer Pass hat, kann nicht nur wählen und abstimmen, es geht um Grundrechte. Eine Staatsbürgerschaft gibt einem Menschen Sicherheit - Sicherheit, hier bleiben zu dürfen, eine Familie zu gründen, die Meinung zu äussern, sich frei zu bewegen. Ein Viertel unserer Bevölkerung kann das momentan nicht. Wenn sie einen Schweizer Pass wollen, wird es teuer, dauert ewig und ist voller Willkür und Schikane. 
+Seien wir ehrlich, der einzige Grund, weswegen wir das tolerieren, ist, dass viele dieser Ausländerinnen und Ausländer nicht weiss genug oder nicht reich genug sind. Wenn es um Ausländer geht, wird gern bis nach links argumentiert, dass diese ja schliesslich auch Steuern zahlen und hier arbeiten würden und dass wir ohne sie verloren wären, etwa auf dem Bau, im Gastgewerbe oder in der Pflege. Und das stimmt: Ohne migrantische Menschen wären wir alle aufgeschmissen. Aber das ist nicht der Grund, warum Menschen ohne Schweizer Pass einen einheitlichen Anspruch auf Einbürgerung erhalten sollen. Ausländerinnen und Ausländer müssen uns nichts nützen. 
+Ich bin für die Demokratie-Initiative, weil ich meinen Mitmenschen auf Augenhöhe begegnen will, nicht, weil ich von ihnen profitiere. Wer mit mir im gleichen Land lebt, soll mitbestimmen können, egal, ob er in Herrliberg oder in Spreitenbach wohnt, egal, ob er Thomas oder Mahmoud heisst, und egal, ob er meiner Meinung ist oder irgendeinen Gugus abstimmt. Ich respektiere nämlich nicht nur Menschen, die ähnlich sind wie ich, sondern alle. 
+Zuletzt noch dies: Wenn Ausländerinnen und Ausländer fünf Jahre lang friedlich sein müssen, um sich den Pass zu verdienen, wie es die Initiative verlangt, könnten wir Schweizerinnen und Schweizer unseren Pass eigentlich abgeben, wenn wir uns innerhalb von fünf Jahren mal menschenverachtend verhalten. Aber dann wäre unsere Demokratie wieder unvollständiger - und dieser Saal um einiges leerer. 
+Ich bitte Sie, die Demokratie-Initiative anzunehmen.
 </t>
   </si>
 </sst>
@@ -261,8 +282,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I9" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I10" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I10"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -821,6 +842,35 @@
         <v>51</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -41,209 +41,85 @@
     <t xml:space="preserve">Text</t>
   </si>
   <si>
-    <t xml:space="preserve">373559</t>
+    <t xml:space="preserve">374432</t>
   </si>
   <si>
     <t xml:space="preserve">N</t>
   </si>
   <si>
-    <t xml:space="preserve">Page Pierre-André</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR</t>
+    <t xml:space="preserve">Ryser Franziska</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SG</t>
   </si>
   <si>
     <t xml:space="preserve">DE</t>
   </si>
   <si>
-    <t xml:space="preserve">Le président (Page Pierre-André, président): La session spéciale est ouverte. Nous accueillons aujourd'hui six nouveaux membres de notre conseil. J'ai le plaisir de saluer Mme Michèle Dünki-Bättig, Mme Laura Gantenbein, Mme Miriam Locher, Mme Anna-Béatrice Schmaltz, M. Arbër Bullakaj et M. Loïc Dobler. Je donne la parole à M. Golay pour le bureau.
+    <t xml:space="preserve">Mindestlöhne wurden nicht aus einer Laune heraus eingeführt, sie sind eine Antwort auf reale Probleme im Arbeitsmarkt, auf die Tatsache, dass Menschen Vollzeit arbeiten und trotzdem zu wenig Geld zum Leben verdienen. Mit dieser Vorlage wollen Sie dieses Instrument unterlaufen. Zumindest der Ständerat hat eingesehen, dass die Übersteuerung demokratisch legitimierter Entscheidungen höchst kritisch ist. Die Ausnahme für Mindestlöhne, die bereits vor dieser Gesetzesvorlage beschlossen wurden, wie et</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mindestlöhne wurden nicht aus einer Laune heraus eingeführt, sie sind eine Antwort auf reale Probleme im Arbeitsmarkt, auf die Tatsache, dass Menschen Vollzeit arbeiten und trotzdem zu wenig Geld zum Leben verdienen. Mit dieser Vorlage wollen Sie dieses Instrument unterlaufen. Zumindest der Ständerat hat eingesehen, dass die Übersteuerung demokratisch legitimierter Entscheidungen höchst kritisch ist. Die Ausnahme für Mindestlöhne, die bereits vor dieser Gesetzesvorlage beschlossen wurden, wie etwa in den Kantonen Genf, Neuenburg, Basel-Stadt oder Jura, ist ein Kompromiss für die Vergangenheit und ein kleiner Schritt in Richtung einer demokratisch verträglichen Vorlage. Dieser Schritt muss nun aber konsequent weitergedacht werden. 
+Mit der Minderheit Amoos wird auch für die Zukunft ein solcher Kompromiss gefunden. Wird ein Mindestlohn beschlossen, so erhalten die Sozialpartner Zeit, um zu reagieren. Sie können bei der nächsten Verhandlung der GAV die Löhne anpassen. Spätestens aber nach zwei Jahren müssen die Löhne auf das Niveau der geltenden Mindestlöhne angehoben werden. Das schafft Verbindlichkeit, und es schafft Fairness. Denn ohne klare Fristen besteht die Gefahr, dass über Jahre hinweg zu tiefe Löhne bestehen bleiben. Und genau das ist aus unserer Sicht nicht akzeptabel. Mindestlöhne sind keine symbolischen Grössen, sie sind eine verbindliche Untergrenze. Sie sollen sicherstellen, dass Arbeit vor Armut schützt. Und so kommen wir auch wieder näher zurück an die Verfassung. Denn die Kantone haben gemäss Bundesverfassung das Recht, Mindestlöhne einzuführen. Eine Übersteuerung durch privatrechtliche Verträge - ein allgemeinverbindlich erklärter GAV ist nichts anderes - ist schlicht nicht verfassungskonform. Mit der Minderheit Amoos könnte man die Vorlage schon beinahe als demokratisch verträglich bezeichnen. Deshalb unterstützen wir den Antrag der Minderheit bei Artikel 1 Absatz 4 für einen Lohnschutz, der seinen Namen auch verdient.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">373560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golay Roger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M. Loïc Dobler est le premier suppléant de la liste 1 Parti socialiste jurassien (PSJ). M. Dobler est chef de service à l'Établissement cantonal des assurances sociales du canton du Jura (ECAS Jura). Le gouvernement de la République et canton du Jura l'a proclamé élu par arrêté du 24 mars 2026. Le bureau a constaté que l'élection de M. Loïc Dobler, né le 7 avril 1987, originaire de Mümliswil-Ramiswil dans le canton de Soleure, domicilié à Glovelier, a été validée. M. Dobler remplace notre ancien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M. Loïc Dobler est le premier suppléant de la liste 1 Parti socialiste jurassien (PSJ). M. Dobler est chef de service à l'Établissement cantonal des assurances sociales du canton du Jura (ECAS Jura). Le gouvernement de la République et canton du Jura l'a proclamé élu par arrêté du 24 mars 2026. Le bureau a constaté que l'élection de M. Loïc Dobler, né le 7 avril 1987, originaire de Mümliswil-Ramiswil dans le canton de Soleure, domicilié à Glovelier, a été validée. M. Dobler remplace notre ancien collègue Pierre-Alain Fridez. Sur la base des indications communiquées par M. Dobler, le bureau n'a identifié aucune activité incompatible avec l'exercice d'un mandat parlementaire au sens de l'article 144 de la Constitution fédérale et de l'article 14 de la loi sur le Parlement. Il propose dès lors de constater formellement l'élection de M. Loïc Dobler.
+    <t xml:space="preserve">374445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dobler Loïc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le canton du Jura a introduit un salaire minimum cantonal auquel les conventions collectives de travail de force obligatoire peuvent déroger. Vous avez évoqué dans votre intervention, Monsieur le conseiller national, le fait de vouloir redynamiser le partenariat social. Je peux vous dire que la réalité cantonale fait qu'il y a eu zéro convention collective de travail de plus et qu'on a dû introduire des contrats-types de travail dans le secteur de la vente ainsi que d'autres, actuellement en con</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le canton du Jura a introduit un salaire minimum cantonal auquel les conventions collectives de travail de force obligatoire peuvent déroger. Vous avez évoqué dans votre intervention, Monsieur le conseiller national, le fait de vouloir redynamiser le partenariat social. Je peux vous dire que la réalité cantonale fait qu'il y a eu zéro convention collective de travail de plus et qu'on a dû introduire des contrats-types de travail dans le secteur de la vente ainsi que d'autres, actuellement en consultation, dans celui de l'horlogerie. Pouvez-vous donc nous expliquer la notion visant à redynamiser le partenariat social en faisant fi des décisions populaires prises dans les cantons ?
 </t>
   </si>
   <si>
-    <t xml:space="preserve">373693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michaud Gigon Sophie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G</t>
+    <t xml:space="preserve">374452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feller Olivier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RL</t>
   </si>
   <si>
     <t xml:space="preserve">VD</t>
   </si>
   <si>
-    <t xml:space="preserve">Par cette initiative, le canton du Jura demande que la législation fédérale soit adaptée pour interdire les importations de denrées alimentaires dont les méthodes de production ne respecteraient pas les normes en vigueur en Suisse. On y retrouve l'esprit de l'initiative populaire "Fair-Food" : exiger la même chose des importations que de l'agriculture suisse, plus d'équité et de durabilité. "Fair-Food" voulait mettre de la justice dans nos assiettes. Un bénéfice qui vise les producteurs et l'env</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Par cette initiative, le canton du Jura demande que la législation fédérale soit adaptée pour interdire les importations de denrées alimentaires dont les méthodes de production ne respecteraient pas les normes en vigueur en Suisse. On y retrouve l'esprit de l'initiative populaire "Fair-Food" : exiger la même chose des importations que de l'agriculture suisse, plus d'équité et de durabilité. "Fair-Food" voulait mettre de la justice dans nos assiettes. Un bénéfice qui vise les producteurs et l'environnement à l'étranger, comme les familles de l'agriculture, ici en Suisse. La Suisse romande avait soutenu cette initiative en 2018, alors qu'elle était rejetée au niveau suisse.
-Depuis plusieurs années, un élément prépondérant de la politique étrangère suisse a été la multiplication des accords de libre-échange avec d'autres pays. Prenons par exemple les accords avec l'Indonésie et le Mercosur, pour les plus récents. Il s'agit d'acteurs dont les standards agricoles, que ce soit en matière de protection de l'environnement ou de bien-être animal, ne sont en aucun cas équivalents à ceux en vigueur dans notre pays, malgré certaines provisions prévues dans les accords. Cela a des conséquences non négligeables pour l'agriculture suisse. Moins compétitive, notamment en raison des coûts de production plus élevés, elle est soumise à une concurrence qui peut être déloyale vis-à-vis des produits étrangers lorsque ceux-ci ne respectent pas les mêmes normes. L'initiative du canton du Jura s'est inscrite dans le contexte de la révolte paysanne face à ces revenus et ces conditions de marché, et a été déposée en mars 2024, l'idée centrale étant l'équité économique et la défense de l'agriculture suisse.
-Face à cette situation, il faut reconnaître que les solutions déjà en place ont montré leurs limites. Ainsi, les labels et étiquetages d'aliments stigmatisant certaines pratiques sont moins complets que des règles plus contraignantes s'appliquant à tous les acteurs sur le marché suisse. Si les standards agricoles suisses sont stricts, notamment pour freiner les impacts environnementaux, les standards appliqués par certains pays peuvent causer de véritables dommages, détruisant la biodiversité ou soumettant les travailleuses et les travailleurs à des conditions de travail inacceptables. En autorisant ces importations, la Suisse cautionne ces méthodes. Refuser les denrées agricoles qui ne répondent pas à certains standards, c'est, à notre échelle, prendre nos responsabilités pour une agriculture plus écologique et humaine au niveau mondial. C'est aussi renforcer la protection des agriculteurs et des agricultrices suisses face à une concurrence déloyale.
-Pour ces deux raisons, l'impact à l'étranger comme la concurrence pour l'agriculture suisse, une minorité de votre Commission de l'économie et des redevances vous enjoint à donner suite à cette initiative du canton du Jura.
+    <t xml:space="preserve">Il existe des conventions collectives de travail dans le domaine du nettoyage. Il me semble que ces conventions, sauf erreur, sont plutôt négociées sur le plan régional ou cantonal.
+Prenons l'exemple d'une convention connue sur le plan national, celle qui concerne l'hôtellerie-restauration. Comment voulez-vous que le partenariat social puisse continuer de vivre pleinement et de jouer pleinement son rôle si, après de dures négociations entre associations d'employeurs et syndicats, et après avoir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il existe des conventions collectives de travail dans le domaine du nettoyage. Il me semble que ces conventions, sauf erreur, sont plutôt négociées sur le plan régional ou cantonal.
+Prenons l'exemple d'une convention connue sur le plan national, celle qui concerne l'hôtellerie-restauration. Comment voulez-vous que le partenariat social puisse continuer de vivre pleinement et de jouer pleinement son rôle si, après de dures négociations entre associations d'employeurs et syndicats, et après avoir demandé au Conseil fédéral de rendre la convention collective obligatoire pour toute la branche de l'hôtellerie-restauration, on introduit un salaire minimum qui contourne l'un des éléments de la convention collective de travail ?
+La convention de l'hôtellerie et de la restauration concerne aussi le canton du Jura. Selon la majorité de la commission, en acceptant notre projet vous revivifiez le partenariat social, y compris dans le canton du Jura, puisque, dans ce canton, la convention nationale pour l'hôtellerie-restauration est également appliquée.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">373698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pamini Paolo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mi esprimo a nome della Commissione dell'economia e dei tributi sull'oggetto 24.326, l'iniziativa cantonale del Canton Giura "Una politica federale 'a deforestazione zero'".
-Die Initiative fordert den Bund auf, das Bundesrecht so anzupassen, dass Rohstoffe und ihre Nebenprodukte, die auf dem Schweizer Markt in Verkehr gebracht werden oder für den Export bestimmt sind, nicht mit Entwaldung in Verbindung stehen.
-Konkret geht es darum, die EU-Verordnung für entwaldungsfreie Produkte (EU Regulation </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mi esprimo a nome della Commissione dell'economia e dei tributi sull'oggetto 24.326, l'iniziativa cantonale del Canton Giura "Una politica federale 'a deforestazione zero'".
-Die Initiative fordert den Bund auf, das Bundesrecht so anzupassen, dass Rohstoffe und ihre Nebenprodukte, die auf dem Schweizer Markt in Verkehr gebracht werden oder für den Export bestimmt sind, nicht mit Entwaldung in Verbindung stehen.
-Konkret geht es darum, die EU-Verordnung für entwaldungsfreie Produkte (EU Regulation on Deforestation-free Products - EUDR), ins Schweizer Recht zu übernehmen. Diese verbietet die Vermarktung von Produkten, die mit Entwaldung in Zusammenhang stehen, wie etwa Palmöl, Kakao, Kaffee, Rindfleisch, Kautschuk und Holz. Die Begründung des Kantons Jura ist zweifach. Einerseits sollen Wettbewerbsnachteile für Schweizer Unternehmen vermieden werden, die in die EU exportieren. Andererseits soll ein Beitrag zur globalen Bekämpfung der Entwaldung sowie zum Schutz der Biodiversität geleistet werden.
-La commission, par 16 voix contre 7 et 2 abstentions, vous propose de ne pas donner suite à l'initiative. Les principales motivations sont les suivantes. L'initiative entraînerait une incertitude réglementaire. Vu que l'application du règlement européen a déjà été reportée à plusieurs reprises, procéder dès à présent à une reprise anticipée entraînerait une incertitude quant à sa mise en oeuvre. Il y aurait aussi des problèmes au niveau des charges administratives élevées. La traçabilité de la certification "sans déforestation" impliquerait des coûts significatifs pour les entreprises, en particulier pour les PME. Finalement, l'initiative aurait une portée très large. Il ne s'agirait pas uniquement des produits suisses, mais également des matières premières, importées et transformées dans notre pays, avec des effets systématiques sur des secteurs économiques entiers.
-Une minorité de la commission vous propose en revanche de donner suite à l'initiative. Je pense que ma collègue, Mme la conseillère nationale Sophie Michaud Gigon, va vous en expliquer les motivations.
-Permettetemi tuttavia una considerazione importante che è stata sollevata anche durante i lavori commissionali. 
-Il mondo sta diventando sempre più verde. Ci sono dati satellitari della Nasa, in particolare le serie storiche Modis e precedenti, che mostrano a partire dagli anni Ottanta un continuo inverdimento della terra e un continuo aumento della massa forestale. La letteratura scientifica di alto livello è chiara su questo punto. Non abbiamo un problema di deforestazione e di diminuzione della vegetazione a livello globale. Lo studio intitolato "Greening of the earth and its drivers" pubblicato su "Nature Climate Change" nel 2016 da Zhu e altri coautori, evidenzia che nel periodo dal 1982 al 2009 tra il 25 per cento e il 50 per cento delle superfici vegetate del pianeta mostra un aumento della copertura fogliare, mentre solo una minima parte registra un declino. Lo stesso studio attribuisce circa il 70 per cento di questo inverdimento all'aumento della concentrazione di anidride carbonica, che agisce come fertilizzante, aumentando la fotosintesi. Forse non tutti ne sono coscienti, ma l'anidride carbonica è il miglior fertilizzante delle piante perché è quello che le piante mangiano. 
-Ulteriori studi su riviste come "Nature Sustainability", "Nature Reviews Earth and Environment", nonché "Nature Climate Change" confermano con dati dal 1981 fino al 2020 e paper pubblicati pochi anni fa, che il fenomeno è reale. I fattori principali sono l'aumento di anidride carbonica, la gestione del territorio e i cambiamenti climatici. In altre parole, la CO2 non è solo un fattore climatico, ma è un input fondamentale per la crescita vegetale, perché è il cibo delle piante. La CO2, alla prova dei fatti, è uno dei migliori fertilizzanti. Questo non vuol dire negare il problema della deforestazione, ma va messo in una chiara prospettiva.
-Vor diesem Hintergrund beantragt Ihnen die Kommission, der Initiative keine Folge zu geben. Sie erachtet eine einseitige Übernahme der europäischen Regelung zum jetzigen Zeitpunkt als verfrüht und mit erheblichen Belastungen verbunden.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cette initiative vise à adapter la législation en vigueur pour garantir que les matières premières et produits mis sur le marché suisse ne soient pas issus de la déforestation. Elle vise à lutter contre la déforestation importée. Certains produits, comme le cacao, le soja, le café, la viande bovine ou l'huile de palme, peuvent occasionner à large échelle une déforestation de forêts tropicales. Celles-ci sont pourtant essentielles pour les populations et pays concernés, mais aussi pour l'humanité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cette initiative vise à adapter la législation en vigueur pour garantir que les matières premières et produits mis sur le marché suisse ne soient pas issus de la déforestation. Elle vise à lutter contre la déforestation importée. Certains produits, comme le cacao, le soja, le café, la viande bovine ou l'huile de palme, peuvent occasionner à large échelle une déforestation de forêts tropicales. Celles-ci sont pourtant essentielles pour les populations et pays concernés, mais aussi pour l'humanité comme puits de carbone. Cette initiative du canton du Jura a trait non seulement à la responsabilité des entreprises, mais aussi à la mise en conformité des entreprises suisses aux normes du marché européen.
-Elle s'inscrit en particulier dans le contexte de la mise en oeuvre prochaine du règlement européen sur la déforestation adopté par les instances de l'Union européenne en 2023. Ce règlement prévoit de nouvelles mesures de diligence pour les opérateurs du marché européen utilisant des matières premières telles que cacao, caoutchouc ou bois. Ces nouvelles obligations toucheront principalement les grandes entreprises et consisteront à prouver systématiquement, notamment par la communication de leurs origines géographiques, que les matières premières utilisées ne sont pas issues de la déforestation. Ces dispositions, qui vont plus loin que celles prévues actuellement par le droit suisse, s'appliqueront aussi aux acteurs d'États tiers qui souhaitent exporter vers l'Union européenne. Se pose donc la question fondamentale de la continuité de l'accès au marché européen pour les entreprises suisses. Le Conseil fédéral se repose sur l'absence actuelle de reconnaissance mutuelle pour éviter de devoir adapter les règles en vigueur. Pourtant, l'expérience nous a montré qu'une position attentiste contient des risques non négligeables.
-Nous nous souvenons de la situation de certains secteurs économiques, comme le secteur biomédical, lors de l'arrêt des négociations sur l'accord-cadre avec l'Union européenne. L'absence de reconnaissance mutuelle dans le domaine médical et celui des biotechnologies a fait capoter de nombreux projets et mis en péril des entreprises suisses pourtant florissantes jusqu'alors. La minorité de la Commission de l'économie et des redevances veut éviter qu'une telle situation ne se répète. En entamant dès maintenant le processus législatif en ce sens, nous pourrons disposer d'une base solide lorsque le moment sera venu de négocier une reconnaissance mutuelle avec l'Union européenne. Même de grandes entreprises suisses, qui seraient pourtant les plus touchées par une telle réglementation, s'y sont déclarées favorables. La proactivité est donc de mise pour obtenir à terme une reconnaissance mutuelle et la garantie de l'accès au marché européen.
-Enfin, donner suite à cette initiative ne permettrait pas seulement de faciliter l'accès des entreprises au marché européen, mais aussi de renforcer significativement la protection de l'environnement. La gestion et la diminution de l'impact environnemental de la Suisse en dehors de ses frontières restent aujourd'hui encore le parent pauvre de notre politique environnementale. Reprendre à notre compte les dispositifs mis en place par l'Union européenne nous permettrait de réaliser des progrès significatifs dans ce domaine sans contraintes disproportionnées. Je le rappelle, les forêts primaires représentent une richesse en biodiversité inestimable ainsi que des puits de carbone plus efficaces. Une politique suisse "Zéro déforestation" est donc un pas vers une prise de responsabilité environnementale allant de la production de matières premières à la consommation finale. C'est un engagement de notre pays en faveur du climat et de la biodiversité.
-Ainsi, je vous enjoins, au nom de la minorité de la Commission de l'économie et des redevances, de donner suite à cette initiative du canton du Jura.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hübscher Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Standesinitiative des Kantons Jura wurde am 14. November 2024 eingereicht. Sie verlangt, den Import von Lebensmitteln, deren Herstellung nicht den Schweizer Vorschriften entspricht, zu verbieten. Die Kommission für Wirtschaft und Abgaben des Nationalrates hat an ihrer Sitzung vom 10. Februar 2026 die vom Kanton Jura eingereichte Standesinitiative vorgeprüft. Der Nationalrat ist Zweitrat. Der Ständerat hat der Standesinitiative am 18. Dezember 2025 auf Antrag seiner Kommission mit 32 zu 10 St</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Standesinitiative des Kantons Jura wurde am 14. November 2024 eingereicht. Sie verlangt, den Import von Lebensmitteln, deren Herstellung nicht den Schweizer Vorschriften entspricht, zu verbieten. Die Kommission für Wirtschaft und Abgaben des Nationalrates hat an ihrer Sitzung vom 10. Februar 2026 die vom Kanton Jura eingereichte Standesinitiative vorgeprüft. Der Nationalrat ist Zweitrat. Der Ständerat hat der Standesinitiative am 18. Dezember 2025 auf Antrag seiner Kommission mit 32 zu 10 Stimmen bei 1 Enthaltung keine Folge gegeben. 
-Die Kommissionsmehrheit hält die Forderung der Standesinitiative aus mehreren Gründen für problematisch. Eine Regelung, wonach nur noch nach Schweizer Vorschriften produzierte Lebensmittel importiert werden dürften, stünde nicht nur im Widerspruch zum WTO-Recht, sondern hätte auch eine deutliche Senkung der Versorgung in der Schweiz zur Folge. Verschiedene, auch pflanzliche Produkte wären in der Schweiz kaum in ausreichender Menge verfügbar. Dies würde den Einkaufstourismus verstärken. Zudem wären die Umsetzung und die Kontrolle eines Importverbots sehr schwierig und kaum realisierbar. 
-Auch importierte Lebensmittel müssen dem Schweizer Recht entsprechen; das ist in Artikel 2 des Lebensmittelgesetzes geregelt. Ausgenommen sind jedoch Verfahren und Produktionsmethoden, die sich nicht in den physischen Eigenschaften des Produkts niederschlagen. Deshalb dürfen z. B. Eier aus Batteriehaltung gemäss geltendem Recht importiert werden. Das ist in der Tat ein bisschen störend, aber die Schweiz verfolgt bereits heute eine andere Strategie. Wir setzen auf Deklaration statt auf Verbote. Das hat sich im Grundsatz bewährt. Die Konsumentinnen und Konsumenten haben dadurch die Wahlfreiheit. Neben der Deklaration ist auch die Einführung von Schweizer Nachhaltigkeitsstandards möglich, wie wir das z. B. bei verschiedenen Labels bereits kennen - sei das Bio Suisse, IP-Suisse oder der Branchenstandard Swissmilk Green bei der Milch. Der Weg über die Deklarationspflicht ist richtig. Er ist zwar nicht umfassend, aber er führt indirekt in gewisser Weise auch dazu, dass das Anliegen der Initiative erfüllt werden kann. Das sehen wir beispielsweise beim Kaninchenfleisch oder bei den Eiern.
-Ein komplettes Importverbot von Lebensmitteln, die nicht Schweizer Standards entsprechen, wäre nicht umsetzbar und würde, wie bereits erwähnt, bei etlichen Produkten zu Versorgungslücken führen.
-Eine Kommissionsminderheit will der Standesinitiative Folge geben, um die Bedeutung der Lebensmittelsicherheit und des fairen Wettbewerbs zwischen der Schweizer und der ausländischen Landwirtschaft zu unterstreichen. Beides würde gerade im Zusammenhang mit neuen Handelsabkommen der Schweiz - z. B. mit den USA oder den Mercosur-Staaten - in Zukunft an Aktualität gewinnen.
-Die Kommission beantragt Ihnen mit 15 zu 6 Stimmen bei 3 Enthaltungen, der Standesinitiative keine Folge zu geben. Eine Minderheit beantragt, ihr Folge zu geben. Dieser Antrag wird jetzt gleich durch Frau Michaud Gigon begründet. Herzlichen Dank, wenn Sie der Initiative keine Folge geben.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pfister Gerhard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M-E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es gibt zwei gleichlautende Standesinitiativen aus Basel-Landschaft und Basel-Stadt. Im Kanton Basel-Landschaft ist in der Verfassung verankert, dass sich alle politischen Behörden dafür einzusetzen haben, dass der Kanton Basel-Landschaft zwei Standesstimmen erhalten soll.
-Im Ständerat wurde die Standesinitiative am 16. Juni 2025 ohne Gegenantrag abgelehnt, nachdem die SPK-S einstimmig den Antrag gestellt hatte, ihr keine Folge zu geben. Die SPK Ihres Rates hat die Initiative am 23. Oktober 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es gibt zwei gleichlautende Standesinitiativen aus Basel-Landschaft und Basel-Stadt. Im Kanton Basel-Landschaft ist in der Verfassung verankert, dass sich alle politischen Behörden dafür einzusetzen haben, dass der Kanton Basel-Landschaft zwei Standesstimmen erhalten soll.
-Im Ständerat wurde die Standesinitiative am 16. Juni 2025 ohne Gegenantrag abgelehnt, nachdem die SPK-S einstimmig den Antrag gestellt hatte, ihr keine Folge zu geben. Die SPK Ihres Rates hat die Initiative am 23. Oktober 2025 beraten. Sie hat Kenntnis von der Debatte im Ständerat wie auch von der Diskussion in der SPK-S genommen, in der eine Vertretung des Kantons Basel-Stadt angehört worden war.
-Der Aufbau des Schweizer Staats und die föderalistische Struktur sind das Resultat von Entscheiden in einer geschichtlichen Epoche und der Entwicklung innerhalb der Geschichte. Insofern ist es selbstverständlich absolut legitim, diese historisch gewachsene Ordnung immer wieder darauf hin zu prüfen, ob sie weiter wachsen und anders gestaltet werden soll. Schliesslich hat der neu geschaffene Kanton Jura selbstverständlich zwei Standesstimmen erhalten. Damals wurde den Halbkantonen auf ihr Begehren hin, ebenfalls eine volle Standesstimme zu erhalten, seitens des Bundesrates beschieden, die Totalrevision der Bundesverfassung abzuwarten. Diese Revision schaffte dann zwar den Status der Halbkantone ab, änderte aber nichts daran, dass den historischen Halbkantonen im Ständerat nur je ein Sitz zugestanden wird.
-Insofern ist der Wunsch aus den Kantonen mit einer Standesstimme eine Art Perpetuum mobile der Vergeblichkeit. Beschränkt sich der Wunsch, wie bei dieser Initiative, auf gewisse Kantone wie Basel-Landschaft und Basel-Stadt, wird er mehrheitlich mit dem Argument abgelehnt, wenn schon müsste er für alle Kantone mit einer Standesstimme gelten. Die Minderheitssprecherin aus dem Kanton Basel-Landschaft hat denn auch ein Kommissionspostulat mit diesem Inhalt beantragt. Dieser Antrag wurde mit 15 zu 7 Stimmen bei 1 Enthaltung abgelehnt. Gibt es aber diese Forderung, wird sie abgelehnt, da ihre Annahme faktisch eine Stärkung der eher konservativen, ländlich geprägten Kantone und eine Stärkung der Deutschschweiz gegenüber der Romandie zur Folge hätte, was wiederum das Gleichgewicht in der Schweizer Eidgenossenschaft stören würde.
-Diese beiden Argumente waren dann auch in der SPK Ihres Rates und im Ständerat die zentralen, warum auch diese Standesinitiative abgelehnt wurde. Unabhängig davon, ob man zwei Standesstimmen für eine begrenzte Anzahl von Kantonen oder für alle will, die Mehrheit im Ständerat sowie in der SPK des Nationalrates erachtet es jetzt als nicht opportun, an dieser historisch gewachsenen Ordnung etwas zu ändern - auch in der vermutlich sehr realistischen Erwartung, dass eine solche Änderung keine Mehrheit im Volk, ganz sicher aber nicht bei den Ständen finden würde. Wer das anders sieht, kann mit einer Volksinitiative versuchen, die Probe aufs Exempel zu machen. Das alles ist nicht zynisch gemeint, sondern einfach realpolitisch. Vermutlich sehen alle hier, die von der Bevölkerung aus den Kantonen Basel-Stadt oder Basel-Landschaft gewählt sind, die Sache anders - mit der vollen politischen Legitimität.
-Die Staatspolitische Kommission Ihres Rates beantragt Ihnen mit 18 zu 4 Stimmen bei 1 Enthaltung, der Initiative keine Folge zu geben.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marti Samira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitte entschuldigen Sie meine Stimmlage. Ich bin etwas erkältet; darum habe ich mir auch erlaubt, einen Becher für den Notfall mitzunehmen. 
-Die vorliegende Standesinitiative des Kantons Basel-Stadt verlangt, wie der Kommissionssprecher ausgeführt hat, dass die beiden Basel zu Kantonen mit vollem Ständerecht aufgewertet werden. Im Namen der Minderheit und auch im Namen der beiden Kantone bitte ich Sie, diese Standesinitiative zu unterstützen und damit dem Grundsatz zuzustimmen, dass das Thema de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitte entschuldigen Sie meine Stimmlage. Ich bin etwas erkältet; darum habe ich mir auch erlaubt, einen Becher für den Notfall mitzunehmen. 
-Die vorliegende Standesinitiative des Kantons Basel-Stadt verlangt, wie der Kommissionssprecher ausgeführt hat, dass die beiden Basel zu Kantonen mit vollem Ständerecht aufgewertet werden. Im Namen der Minderheit und auch im Namen der beiden Kantone bitte ich Sie, diese Standesinitiative zu unterstützen und damit dem Grundsatz zuzustimmen, dass das Thema der Kantone mit halber Standesstimme endlich ernsthaft aufs staatspolitische Tapet gehört. 
-Das Thema beschäftigt unsere Region seit Jahrzehnten. Aufschwung bekam die Debatte aber vor allem auch wieder mit der Gründung des Kantons Jura 1979. Die Eidgenossenschaft entschied damals, nicht zwei Halbkantone, den Kanton Bern und den Kanton Jura, zu gründen und die Standesstimmen zwischen den beiden aufzuteilen, sondern den beiden Kantonen die Gleichbehandlung zu gewähren und zwei Standesstimmen zuzugestehen. Damit wurde damals auch die Zusammensetzung des Ständerates verändert. Anders war es damals bei der Gründung meines Kantons, des Kantons Basel-Landschaft. Die Ländler wehrten sich damals - eine kleine Geschichtsstunde für Sie - erfolgreich gegen die Besetzung durch die Städter. 1832 wurde per Volksabstimmung der Kanton Basel-Landschaft gegründet und dann 1833 nach einem für die Städter verlustreichen Gefecht mit einem entsprechenden Beschluss der Tagsatzung endgültig auch durchgesetzt. Die beiden ehemaligen Halbkantone erhielten dann je eine Stimme im Ständerat. Knapp 150 Jahre später wurde mit der Gründung des Kantons Jura gewissermassen das offizielle Bekenntnis zum Ende der Geschichte der Halbkantone gesetzt. Schon damals monierten die Vertretungen aus dem Kanton Basel-Landschaft, wie es sich denn nun mit ihrem Kanton verhalte, wann sie jetzt endlich gleichbehandelt würden. Der damals zuständige Bundesrat Furgler vertröstete sie, die Frage könne man dann im Rahmen der nächsten Totalrevision der Bundesverfassung diskutieren. Er wolle, sagte er verständlicherweise, jetzt die Gründung des Kantons Jura nicht gefährden. Dann wurden die Halbkantone im Rahmen der Totalrevision zwar abgeschafft und die Gleichheit der Kantone und das Gebot der Gleichbehandlung der Kantone festgehalten, aber das Relikt der sogenannt vollwertigen Kantone mit halber Standesstimme blieb bestehen. 2001 wurde der parlamentarischen Initiative Janiak 01.403, "Basel-Landschaft und Basel-Stadt. Vollberechtigte Kantone", vom Nationalrat ebenfalls keine Folge gegeben. Auch damals wurde dagegen vor allem eingewendet, dass die Verfassung des Kantons Basel-Stadt damals noch das Ziel der Wiedervereinigung beinhaltete. Basel-Land strebte bereits damals die zwei Sitze an, Basel-Stadt aber den Zusammenschluss. Mehr als zehn Jahre später wurde über eine Initiative zur Wiedervereinigung abgestimmt. Basel-Stadt nahm diese an, Basel-Land aber lehnte sie mit über 70 Prozent ab. Unterdessen wurde auch die Verfassung des Kantons Basel-Stadt angepasst. Die Wiedervereinigung ist nun kein offizielles Verfassungsziel mehr, nur die gute Zusammenarbeit. All das zeigt, dass sich seit der Debatte in den 70er-Jahren die Situation auch vor Ort geändert hat und sich beide Kantone als vollwertige und auch selbstständige Kantone verstehen. In der Region wird nicht verstanden, warum man im Unterschied zu praktisch allen anderen Kantonen nur einen Sitz im Ständerat hat und man quasi vom Nachbarkanton Jura, der uns nahe ist und den wir gut kennen, links überholt wurde. 
-Mir ist klar, dass diese Standesinitiative Schwächen hat. Sie klärt nicht, warum neue Ungleichheiten mit den anderen Kantonen mit halber Standesstimme, den Appenzeller Kantonen sowie Nid- und Obwalden, geschaffen werden sollen. Auch das Argument der wirtschaftlichen Stärke, das in der Begründung der Initiative vom Kanton Basel-Stadt genannt wird, überzeugt mich persönlich nicht. Die Standesvertretung soll bekanntlich ja nicht an Wirtschaftsleistung oder an Grösse geknüpft werden. Ich bedauere deshalb - der Kommissionssprecher hat das ebenfalls erwähnt -, dass die Kommission meinen Antrag auf ein Postulat nicht unterstützt hat. Es braucht eine ernsthafte Auslegeordnung zu Reformoptionen, wie die Gleichbehandlung der Regionen bzw. der Kantone unter Berücksichtigung des Gleichgewichts im Bundesstaat erreicht werden können. Das ist keine statische Angelegenheit, die über hundert Jahre genau das gleiche Gleichgewicht darstellt. Sie werden mit mir einverstanden sein, dass die Konfession heute zum Beispiel nicht mehr die entscheidende Konfliktlinie in unserem Bundesstaat ist. Es sind andere Unterschiedlichkeiten, die wir überwinden und über die wir als Bundesstaat zusammenhalten müssen. Es sind sprachliche und kulturelle Differenzen, die es in einem vielfältigen Land wie der Schweiz gibt. Lassen Sie uns darüber nachdenken. Diese Standesinitiative könnte dafür der Anfang sein. 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">374283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosenwasser Anna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Demokratie-Initiative verlangt, dass Ausländerinnen und Ausländer nach fünf Jahren in der Schweiz das Recht auf Einbürgerung erhalten. Die Bedingung ist, dass sie nach diesen fünf Jahren eine Landessprache beherrschen, die Sicherheit nicht gefährden und nicht ins Gefängnis müssen. 
-Momentan kann ein Viertel aller Menschen, die in der Schweiz leben, weder abstimmen noch wählen, geschweige denn für ein politisches Amt kandidieren. Das heisst, über 2 Millionen Menschen in der Schweiz sind zwar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Demokratie-Initiative verlangt, dass Ausländerinnen und Ausländer nach fünf Jahren in der Schweiz das Recht auf Einbürgerung erhalten. Die Bedingung ist, dass sie nach diesen fünf Jahren eine Landessprache beherrschen, die Sicherheit nicht gefährden und nicht ins Gefängnis müssen. 
-Momentan kann ein Viertel aller Menschen, die in der Schweiz leben, weder abstimmen noch wählen, geschweige denn für ein politisches Amt kandidieren. Das heisst, über 2 Millionen Menschen in der Schweiz sind zwar von politischen Entscheiden betroffen, dürfen aber nicht mitbestimmen. Wer hier zuhause ist, ist von hier. Diese Aussage ist nicht radikal, denn es geht nicht um unsere Wurzeln. Diejenigen, über die bestimmt wird, müssen mitbestimmen können. Wenn drei Viertel unseres Landes über das andere Viertel bestimmen, ist das keine vollwertige Demokratie. 
-Das aktuell geltende Einbürgerungsrecht ist eine Lotterie. Je nach Kanton hat man ein bisschen Glück oder sehr viel Pech. Im Aargau und im Kanton St. Gallen kostet es über 2000 Franken, sich einbürgern zu lassen, im Kanton Zug nur 350 Franken. Im Kanton Jura wurde eine Person von einer Einbürgerungskommission abgelehnt, weil sie am Sonntag Rasen gemäht hat. In Zürich wurde jemand nicht angenommen, weil er den geografischen und historischen Ursprung von Raclette nicht kannte. In Arth, in Schwyz, wurde jemand abgelehnt, weil er nicht wusste, dass Wölfe und Bären sich im Tierpark Goldau ein Gehege teilen. Es braucht endlich einheitliche Regeln gegen diese Willkür. Es sagt nichts über uns aus, ob wir wissen, welche Tiere sich ein Gehege teilen, aber es sagt viel über uns aus, mit wem wir ein Land teilen. 
-Wer einen Schweizer Pass hat, kann nicht nur wählen und abstimmen, es geht um Grundrechte. Eine Staatsbürgerschaft gibt einem Menschen Sicherheit - Sicherheit, hier bleiben zu dürfen, eine Familie zu gründen, die Meinung zu äussern, sich frei zu bewegen. Ein Viertel unserer Bevölkerung kann das momentan nicht. Wenn sie einen Schweizer Pass wollen, wird es teuer, dauert ewig und ist voller Willkür und Schikane. 
-Seien wir ehrlich, der einzige Grund, weswegen wir das tolerieren, ist, dass viele dieser Ausländerinnen und Ausländer nicht weiss genug oder nicht reich genug sind. Wenn es um Ausländer geht, wird gern bis nach links argumentiert, dass diese ja schliesslich auch Steuern zahlen und hier arbeiten würden und dass wir ohne sie verloren wären, etwa auf dem Bau, im Gastgewerbe oder in der Pflege. Und das stimmt: Ohne migrantische Menschen wären wir alle aufgeschmissen. Aber das ist nicht der Grund, warum Menschen ohne Schweizer Pass einen einheitlichen Anspruch auf Einbürgerung erhalten sollen. Ausländerinnen und Ausländer müssen uns nichts nützen. 
-Ich bin für die Demokratie-Initiative, weil ich meinen Mitmenschen auf Augenhöhe begegnen will, nicht, weil ich von ihnen profitiere. Wer mit mir im gleichen Land lebt, soll mitbestimmen können, egal, ob er in Herrliberg oder in Spreitenbach wohnt, egal, ob er Thomas oder Mahmoud heisst, und egal, ob er meiner Meinung ist oder irgendeinen Gugus abstimmt. Ich respektiere nämlich nicht nur Menschen, die ähnlich sind wie ich, sondern alle. 
-Zuletzt noch dies: Wenn Ausländerinnen und Ausländer fünf Jahre lang friedlich sein müssen, um sich den Pass zu verdienen, wie es die Initiative verlangt, könnten wir Schweizerinnen und Schweizer unseren Pass eigentlich abgeben, wenn wir uns innerhalb von fünf Jahren mal menschenverachtend verhalten. Aber dann wäre unsere Demokratie wieder unvollständiger - und dieser Saal um einiges leerer. 
-Ich bitte Sie, die Demokratie-Initiative anzunehmen.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">374382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuosto Brenda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Suisse romande refuse de payer le prix d'une planification défaillante des CFF et de l'Office fédéral des transports (OFT) pendant une décennie. L'horaire 2025 n'est pas une simple mise à jour technique, c'est un choix politique. Un choix politique de priorisation entre les différentes régions, entre les différentes vitesses, entre transport de voyageurs et transport de marchandises. Il est inadmissible qu'une partie du pays soit contrainte de porter seule le poids de choix politiques de refo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Suisse romande refuse de payer le prix d'une planification défaillante des CFF et de l'Office fédéral des transports (OFT) pendant une décennie. L'horaire 2025 n'est pas une simple mise à jour technique, c'est un choix politique. Un choix politique de priorisation entre les différentes régions, entre les différentes vitesses, entre transport de voyageurs et transport de marchandises. Il est inadmissible qu'une partie du pays soit contrainte de porter seule le poids de choix politiques de refonte de l'horaire. Si les CFF invoquent des problèmes de ponctualité pour justifier ces mesures, ces désagréments ne se justifient absolument pas et ne sauraient être absorbés au seul profit du poumon économique alémanique indûment épargné. En interrompant la liaison IC5 entre Genève et Olten, l'OFT impose aux habitantes et habitants du nord de la Suisse jusqu'à l'ouest du pays une accessibilité au rail dégradée pour la décennie à venir. On ne peut exiger de la Suisse occidentale qu'elle sacrifie sa connectivité pour compenser des retards d'infrastructures qui ne lui incombent pas. L'introduction de l'horaire 2025 marque une régression pour les habitantes et habitants de la ligne du Pied-du-Jura. L'allongement des trajets d'environ 8 pour cent sur toutes les lignes romandes d'importance nationale et la fin des liaisons directes contredisent les objectifs de neutralité carbone de l'Office fédéral de l'environnement. La complexification des parcours est un frein majeur à l'attractivité du rail.
-Le Département fédéral de l'environnement, des transports, de l'énergie et de la communication (DETEC) tente de nous rassurer en parlant de la mise en service du tunnel de Gléresse et de la remise en place du train circulant via le by-pass comme d'une révolution de l'horaire 2030. Restons lucides face à ces éléments de communication qui masquent la réalité du terrain. Le projet de by-pass existait déjà dans Rail 2000. Présenter un simple retour à la normale après travaux comme une avancée stratégique est une lecture un peu trop sélective de la réalité. D'autant plus que l'horaire 2030 ne prévoit aucun rétablissement des correspondances entre la ligne du Pied-du-Jura et celle du Valais, laissant la rupture de charge inchangée à Lausanne. La situation reste donc problématique pour les déplacements de l'Arc jurassien au-delà de Martigny. L'axe du Pied-du-Jura doit être connecté avec des noeuds de correspondance à Zurich, à Bâle et à Lausanne. Les régions d'Argovie, de Soleure, du Jura bernois, du Jura, des deux Bâle, de Neuchâtel et du Nord vaudois doivent rester connectées avec le reste de la Suisse.
-Avec ce postulat, je demande formellement le rétablissement des correspondances entre l'IC5 et l'IR90. Un réseau national n'a de sens que si ses noeuds fonctionnent. Il faut corriger cette erreur de planification maintenant. Le Conseil fédéral nous promet des solutions pour 2030, mais elles sont insuffisantes. Aujourd'hui, l'inertie administrative du DETEC bloque les projets déjà approuvés comme ceux liés à la redondance Lausanne-Genève, à la halte d'Y-Parc ou aux mesures de compensation des 100 millions de francs qui ont été votées ces dernières années et qui pourraient améliorer rapidement la situation. Si nous attendons une nouvelle décision des chambres en 2027 voire 2028, ces études deviendront caduques. Nous allons gaspiller l'argent public en refaisant de nouvelles études déjà payées. Je demande au Conseil fédéral de débloquer ces mesures immédiatement pour sauver ce qui peut l'être.
-En conclusion, nous ne demandons pas de faveur. Nous demandons le respect des engagements pris envers la Suisse occidentale et la Suisse alémanique. L'horaire 2025 est une situation qui, sans intervention politique, deviendra la norme : des liaisons nationales interrompues et des durées de trajet rallongées. Il ne s'agit pas d'exiger des offres ou des investissements supplémentaires, mais simplement de revenir à la normale. La situation d'avant 2025 doit être remise en place totalement et maintenant. Soutenir ce postulat, c'est répondre à l'appel de l'Alliance des villes et des milieux économiques situés sur l'ensemble de l'axe du Pied-du-Jura. La cohésion nationale ne saurait se maintenir si l'on consent à l'isolement d'une grande partie du pays. Je vous remercie pour votre soutien.
+    <t xml:space="preserve">374592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crevoisier Crelier Mathilde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique : à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36 108 francs contre 52 488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre femmes et</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique : à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36 108 francs contre 52 488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre femmes et hommes dans l'AVS est quasiment nulle. Cet écart ne diminue pas depuis plusieurs années. En comparaison internationale, la Suisse pointe à un peu reluisant cinquième rang des pays européens présentant les plus fortes différences de retraite entre les femmes et les hommes.
+Afin de combler ce fossé, la présente motion visait donc à tenir compte des lacunes de rente découlant des tâches éducatives et d'assistance, qui sont assumées majoritairement par les femmes au détriment de leur épargne-vieillesse, et d'introduire dans la loi sur la prévoyance professionnelle vieillesse, survivants et invalidité (LPP) le principe de la bonification ; principe bien connu et reconnu puisqu'il existe déjà dans l'AVS, comme l'a rapporté le rapporteur de commission. Comme cela a été dit, cette motion s'inscrivait dans la série d'interventions déposées dans le sillage du refus de la révision de la LPP en 2024 ; interventions qui avaient toutes été renvoyées à la commission compétente et qui ont été retirées, que ce soit en commission ou aujourd'hui au conseil, au profit du postulat 26.3521 de la CSSS, que nous avons accepté tout à l'heure.
+Ainsi, au vu des considérations avancées dans le postulat de la commission, qui refuse une approche isolée au profit d'une réflexion globale sur les améliorations possibles dans la LPP, et au vu des arguments du Conseil fédéral, qui oeuvre d'ores et déjà à la nouvelle révision de la LPP et cherche lui aussi des solutions pour améliorer la prévoyance professionnelle des personnes travaillant un temps partiel ou ayant de faibles revenus, parmi lesquels les femmes sont justement surreprésentées, je me rallie au mouvement initié par les autres auteurs de motion et retire la présente motion, dans l'espoir toutefois que les mesures de la prochaine réforme permettent enfin d'infléchir cet écart important, qui n'a plus lieu d'être dans le système de rente moderne d'un pays prospère comme le nôtre.
 </t>
   </si>
 </sst>
@@ -298,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I11" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I5" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I5"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -631,7 +507,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46139</v>
+        <v>46174</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -652,268 +528,94 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46139</v>
+        <v>46174</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46140</v>
+        <v>46174</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
         <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46140</v>
+        <v>46174</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
         <v>32</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -118,8 +118,8 @@
   </si>
   <si>
     <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique : à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36 108 francs contre 52 488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre femmes et hommes dans l'AVS est quasiment nulle. Cet écart ne diminue pas depuis plusieurs années. En comparaison internationale, la Suisse pointe à un peu reluisant cinquième rang des pays européens présentant les plus fortes différences de retraite entre les femmes et les hommes.
-Afin de combler ce fossé, la présente motion visait donc à tenir compte des lacunes de rente découlant des tâches éducatives et d'assistance, qui sont assumées majoritairement par les femmes au détriment de leur épargne-vieillesse, et d'introduire dans la loi sur la prévoyance professionnelle vieillesse, survivants et invalidité (LPP) le principe de la bonification ; principe bien connu et reconnu puisqu'il existe déjà dans l'AVS, comme l'a rapporté le rapporteur de commission. Comme cela a été dit, cette motion s'inscrivait dans la série d'interventions déposées dans le sillage du refus de la révision de la LPP en 2024 ; interventions qui avaient toutes été renvoyées à la commission compétente et qui ont été retirées, que ce soit en commission ou aujourd'hui au conseil, au profit du postulat 26.3521 de la CSSS, que nous avons accepté tout à l'heure.
-Ainsi, au vu des considérations avancées dans le postulat de la commission, qui refuse une approche isolée au profit d'une réflexion globale sur les améliorations possibles dans la LPP, et au vu des arguments du Conseil fédéral, qui oeuvre d'ores et déjà à la nouvelle révision de la LPP et cherche lui aussi des solutions pour améliorer la prévoyance professionnelle des personnes travaillant un temps partiel ou ayant de faibles revenus, parmi lesquels les femmes sont justement surreprésentées, je me rallie au mouvement initié par les autres auteurs de motion et retire la présente motion, dans l'espoir toutefois que les mesures de la prochaine réforme permettent enfin d'infléchir cet écart important, qui n'a plus lieu d'être dans le système de rente moderne d'un pays prospère comme le nôtre.
+Afin de combler ce fossé, la présente motion visait donc à tenir compte des lacunes de rente découlant des tâches éducatives et d'assistance, qui sont assumées majoritairement par les femmes au détriment de leur épargne-vieillesse, et d'introduire dans la loi sur la prévoyance professionnelle vieillesse, survivants et invalidité (LPP) le principe de la bonification ; principe bien connu et reconnu puisqu'il existe déjà dans l'AVS, comme l'a indiqué le rapporteur. Comme cela a été dit, cette motion s'inscrivait dans la série d'interventions déposées dans le sillage du refus de la révision de la LPP en 2024 ; interventions qui avaient toutes été renvoyées à la commission compétente et qui ont été retirées, que ce soit en commission ou aujourd'hui au conseil, au profit du postulat 26.3521 de la CSSS, que nous avons accepté tout à l'heure.
+Ainsi, vu les considérations avancées dans le postulat de la commission, qui refuse une approche isolée au profit d'une réflexion globale sur les améliorations possibles dans la LPP, et vu les arguments du Conseil fédéral, qui oeuvre d'ores et déjà à la nouvelle révision de la LPP et cherche, lui aussi, des solutions pour améliorer la prévoyance professionnelle des personnes travaillant à temps partiel ou ayant de faibles revenus - parmi lesquels les femmes sont justement surreprésentées -, je me rallie au mouvement initié par d'autres auteurs de motions et retire la présente motion, dans l'espoir toutefois que les mesures de la prochaine réforme permettront enfin d'infléchir cet écart important qui n'a plus lieu d'être dans le système de rente moderne d'un pays prospère comme le nôtre.
 </t>
   </si>
 </sst>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -120,6 +120,137 @@
     <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique : à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36 108 francs contre 52 488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre femmes et hommes dans l'AVS est quasiment nulle. Cet écart ne diminue pas depuis plusieurs années. En comparaison internationale, la Suisse pointe à un peu reluisant cinquième rang des pays européens présentant les plus fortes différences de retraite entre les femmes et les hommes.
 Afin de combler ce fossé, la présente motion visait donc à tenir compte des lacunes de rente découlant des tâches éducatives et d'assistance, qui sont assumées majoritairement par les femmes au détriment de leur épargne-vieillesse, et d'introduire dans la loi sur la prévoyance professionnelle vieillesse, survivants et invalidité (LPP) le principe de la bonification ; principe bien connu et reconnu puisqu'il existe déjà dans l'AVS, comme l'a indiqué le rapporteur. Comme cela a été dit, cette motion s'inscrivait dans la série d'interventions déposées dans le sillage du refus de la révision de la LPP en 2024 ; interventions qui avaient toutes été renvoyées à la commission compétente et qui ont été retirées, que ce soit en commission ou aujourd'hui au conseil, au profit du postulat 26.3521 de la CSSS, que nous avons accepté tout à l'heure.
 Ainsi, vu les considérations avancées dans le postulat de la commission, qui refuse une approche isolée au profit d'une réflexion globale sur les améliorations possibles dans la LPP, et vu les arguments du Conseil fédéral, qui oeuvre d'ores et déjà à la nouvelle révision de la LPP et cherche, lui aussi, des solutions pour améliorer la prévoyance professionnelle des personnes travaillant à temps partiel ou ayant de faibles revenus - parmi lesquels les femmes sont justement surreprésentées -, je me rallie au mouvement initié par d'autres auteurs de motions et retire la présente motion, dans l'espoir toutefois que les mesures de la prochaine réforme permettront enfin d'infléchir cet écart important qui n'a plus lieu d'être dans le système de rente moderne d'un pays prospère comme le nôtre.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keller-Sutter Karin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Sprecherinnen und der Sprecher der Kommission und der Fraktionen haben die Rechnung und auch teilweise den Nachtrag bereits ausführlich dargelegt. Ich beschränke mich darum auf die wichtigsten Punkte.
+Zunächst zum Ergebnis der Staatsrechnung: Wie Sie gehört haben, schliesst die Rechnung 2025 erstmals seit 2019 mit einem Finanzierungsüberschuss ab. Der Überschuss beläuft sich auf 259 Millionen Franken. Wie Sie wissen, unterscheidet die Schuldenbremse zwischen dem ordentlichen und dem ausseror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Sprecherinnen und der Sprecher der Kommission und der Fraktionen haben die Rechnung und auch teilweise den Nachtrag bereits ausführlich dargelegt. Ich beschränke mich darum auf die wichtigsten Punkte.
+Zunächst zum Ergebnis der Staatsrechnung: Wie Sie gehört haben, schliesst die Rechnung 2025 erstmals seit 2019 mit einem Finanzierungsüberschuss ab. Der Überschuss beläuft sich auf 259 Millionen Franken. Wie Sie wissen, unterscheidet die Schuldenbremse zwischen dem ordentlichen und dem ausserordentlichen Haushalt.
+Im ordentlichen Haushalt verzeichnet der Bund einen Überschuss von 1,2 Milliarden Franken. Die Schuldenbremse hätte konjunkturbedingt ein Defizit von 262 Millionen Franken zugelassen. Der strukturelle Saldo gemäss Schuldenbremse belief sich damit auf 1,4 Milliarden Franken. Budgetiert war ein strukturell ausgeglichener Haushalt. Die Ergebnisverbesserung ist auf die dynamische Einnahmenentwicklung zurückzuführen. Die ordentlichen Einnahmen schlossen um 1,9 Milliarden Franken über dem Budget ab. Der Hauptgrund dafür waren die Einnahmen aus der direkten Bundessteuer für die Unternehmen, also die Gewinnsteuern. Die Gewinnsteuereinnahmen lagen 1,4 Milliarden Franken über dem Budget. Diese Entwicklung ist auf die temporären Mehreinnahmen aus dem Kanton Genf zurückzuführen. Allein der Kanton Genf hat 1,5 Milliarden Franken beigesteuert. Das konnte im Budget nur summarisch abgebildet werden. Sie können sich erinnern, wir haben Sie letztes Frühjahr über die Mehreinnahmen aus dem Kanton Genf informiert. Es wurde dann aber erst zu Beginn der Budgetberatung in der Finanzkommission des Ständerates im November 2025 klar, dass eben auch provisorische Rechnungen im Kanton Genf nicht ausgestellt wurden und dass die Mehreinnahmen viel höher ausfallen würden. Wir haben aber auch unter der Ausnahme des Effekts Genf eine positive Entwicklung bei den Gewinnsteuereinnahmen, wobei sie allerdings ohne den Sondereffekt Genf leicht unter dem Budget ausgefallen wären. Gleichzeitig lagen die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden Franken relativ tief ausgefallen sind.
+Im ausserordentlichen Haushalt waren hingegen die Ausgaben grösser als die Einnahmen. Die beiden grössten ausserordentlichen Ausgaben waren diejenigen für die Schutzsuchenden aus der Ukraine sowie der einmalige Kapitalzuschuss an die SBB. Dieser war ursprünglich für das Jahr 2024 budgetiert gewesen und konnte erst 2025 ausgerichtet werden, was damals die Verbesserung der Rechnung 2024 generiert hat. Auf der Einnahmenseite wurde ein Teil der SNB-Gewinnausschüttung ausserordentlich verbucht, 333 Millionen Franken. Dazu kam die budgetierte Sonderzuweisung der SNB aus den nicht umgetauschten Banknoten der sechsten Serie.
+Noch etwas zur Ausgabenentwicklung: Verschiedene Sprecherinnen und Sprecher haben darauf hingewiesen, wie sehr man den Bundeshaushalt sozusagen auspressen würde. Ich gebe Ihnen einfach bekannt, welches Wachstum wir in den wichtigsten Positionen haben. Soziale Wohlfahrt: insgesamt 2 Prozent, allein die AHV plus 5,7 Prozent. Finanzen und Steuern: 6,3 Prozent Wachstum. Das sind natürlich die Kantonsanteile an den Einnahmen, der Finanzausgleich. Verkehr: Zunahme von 9,1 Prozent bei den Ausgaben. Bildung und Forschung: Zunahme von 5,9 Prozent. Sicherheit: Zunahme von 4,3 Prozent. Beziehung zum Ausland: minus 1,2 Prozent. Landwirtschaft und Ernährung: plus 0,1 Prozent. Und dann kommen noch die übrigen Aufgabengebiete. Dies einfach zum Thema, der Staat spare sich kaputt, man würde immer weniger für die wichtigen Bereiche ausgeben.
+Nun noch ein Ausblick: Der Bundesrat wird Ende Juni wie üblich die Zahlen zum Voranschlag 2027 und Finanzplan 2028 bis 2030 festlegen. Die Arbeiten sind noch am Laufen. Ich möchte Sie an dieser Stelle aber über den Zwischenstand dieser Arbeiten informieren, gestützt auf die inzwischen erfolgten Budgeteingaben der Departemente und gestützt auf die aktualisierte Einnahmenschätzung, nachdem uns die Kantone die Eingänge des für die Schätzung wichtigen Monats April gemeldet haben.
+Demnach dürfte sich auf der Ausgabenseite für den Voranschlag 2027 nochmals eine Verschlechterung von voraussichtlich 300 Millionen Franken ergeben, dies im Vergleich zur Standortbestimmung vom April. Grund für diese Verschlechterung sind primär Schätzkorrekturen bei den Sozialversicherungen und bei der Migration. 
+Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer, also bei der Unternehmenssteuer, für juristische Personen, eine deutliche Verbesserung ab. Neben dem Effekt Genf, den wir bereits kannten und entsprechend eingepreist haben, verzeichnen wir auch im laufenden Jahr ein starkes Einnahmenwachstum. Dies zeigt sich in unterschiedlichem Ausmass in zahlreichen Kantonen, wobei vor allem das Wachstum in den Kantonen Luzern, Zürich und Basel-Stadt ins Gewicht fällt - und dieses hohe Wachstum konzentriert sich in diesen Kantonen wiederum auf einige wenige Unternehmen. Es bestehen natürlich weiterhin grosse Unsicherheiten; unter anderem basieren die Schätzungen der Gewinnsteuer zu diesem Zeitpunkt jeweils auf provisorischen Steuerrechnungen, und es ist auch nicht in jedem Fall klar, wie nachhaltig die höheren Steuererträge sind. Einzelne Unternehmen können, ich habe es gesagt, hier grosse Effekte haben. 
+Ein weiterer Unsicherheitsfaktor ist auch die OECD-Ergänzungssteuer, wo wir frühestens im Herbst mit verlässlichen Zahlen rechnen können. Unter dem Strich erwarten wir, Stand heute, aber klar eine Entspannung im Voranschlag 2027, dies unter Einschluss der Kürzungen aus dem Entlastungsprogramm 2027, wie Sie es in der Frühjahrssession verabschiedet haben. Ohne das EP 27 wären wir weiterhin im roten Bereich. Vermutlich können wir aber darüber hinausgehende Massnahmen jetzt streichen, wir können also auf weitere Kürzungen verzichten, die wir vorsorglich im April noch beschlossen hatten, um die Schuldenbremse einzuhalten. Der Bundesrat hatte bereits damals in Aussicht gestellt, dass er die Notwendigkeit dieser zusätzlichen Bereinigungsmassnahmen nochmals überprüfen wird, falls die aktualisierte Ausgaben- und Einnahmenschätzung dies erlaubt. Der Bundesrat wird, wie gesagt, Ende Juni die Zahlen zum Budget definitiv festlegen. Bis dahin werden wir auch mehr zur Entwicklung in den Finanzplanjahren wissen. Ich kann Ihnen jedenfalls versichern, dass es unser Ziel ist, den finanzpolitischen Handlungsspielraum von Bundesrat und Parlament bestmöglich zu wahren - so viel noch zum Ausblick. 
+Der Bundesrat beantragt Ihnen, der Staatsrechnung für das Jahr 2025 zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bally Maya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mit meinem Postulat bitte ich den Bundesrat, im nächsten Wirkungsbericht zum nationalen Finanzausgleich (NFA) die Einführung einer einheitlichen Referenzgrösse für die Bewertung von Eigenheimen im Ressourcenpotenzial zu prüfen, mögliche Massnahmen aufzuzeigen und darüber Bericht zu erstatten. 
+Es geht dabei um eine Frage, die eigentlich sehr grundlegend ist. Soll der Finanzausgleich auf möglichst einheitlichen, objektiven und vergleichbaren Kriterien beruhen? Heute ist das weitgehend der Fall. F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mit meinem Postulat bitte ich den Bundesrat, im nächsten Wirkungsbericht zum nationalen Finanzausgleich (NFA) die Einführung einer einheitlichen Referenzgrösse für die Bewertung von Eigenheimen im Ressourcenpotenzial zu prüfen, mögliche Massnahmen aufzuzeigen und darüber Bericht zu erstatten. 
+Es geht dabei um eine Frage, die eigentlich sehr grundlegend ist. Soll der Finanzausgleich auf möglichst einheitlichen, objektiven und vergleichbaren Kriterien beruhen? Heute ist das weitgehend der Fall. Für die Berechnung des Ressourcenpotenzials werden grundsätzlich standardisierte Werte verwendet. Bei den Eigenheimen besteht jedoch eine Ausnahme. Hier werden die kantonalen Vermögenssteuerwerte bzw. Schätzwerte berücksichtigt. Genau diese Werte unterscheiden sich aber teilweise erheblich von Kanton zu Kanton. Der Grund dafür liegt nicht in unterschiedlichen Immobilienmärkten, sondern in unterschiedlichen kantonalen Schätzungsmethoden und Bewertungsansätzen. Damit kann dieselbe wirtschaftliche Realität je nach Kanton unterschiedlich in die Berechnung des Ressourcenpotenzials einfliessen. Aus systematischer Sicht stellt sich deshalb die Frage, ob dies noch sachgerecht ist.
+Besonders wichtig erscheint mir dabei ein weiterer Grundsatz: Die Kriterien des Finanzausgleichs sollten möglichst nicht von den Kantonen selbst beeinflusst werden können. Der nationale Finanzausgleich soll die tatsächliche Ressourcenstärke eines Kantons abbilden. Er soll aber nicht davon abhängen, mit welchen Methoden ein Kanton seine Liegenschaften bewertet oder welche Schätzungspraxis er anwendet. Wo die Ausgestaltung eines Kriteriums potenziell Auswirkungen auf die Höhe von Ausgleichszahlungen haben kann, entstehen zumindest mögliche Fehlanreize. Genau solche Fehlanreize sollten wir im Finanzausgleich vermeiden. Beim Finanzausgleich ist es evident, dass eine Beeinflussung durch die Akteure ausgeschlossen wird. Sonst wird das System ad absurdum geführt. Deshalb erscheint es sachlogisch, zu prüfen, ob auch bei Liegenschaften eine einheitliche Referenzgrösse zur Anwendung gelangen sollte. Mit dem Repartitionswert existiert ein solches Instrument bereits heute. Er wird bei interkantonalen Steuerausscheidungen verwendet und verfolgt genau das Ziel, unterschiedliche kantonale Bewertungspraktiken vergleichbar zu machen. Mein Postulat verlangt jedoch ausdrücklich nicht die Einführung einer bestimmten Lösung. Es verlangt lediglich, dass die heutige Situation analysiert und mögliche Lösungsansätze geprüft werden.
+In der Vergangenheit wurde die Verwendung einer einheitlichen Referenzgrösse mit dem Argument verworfen, die Berechnung sei mit einem zu grossen Aufwand verbunden. Dieses Argument mag zum Zeitpunkt der Einführung des NFA nachvollziehbar gewesen sein. Seither haben sich durch die Digitalisierung die technischen Möglichkeiten und die Prozesse jedoch grundlegend verändert. Deshalb ist es legitim, die damaligen Annahmen erneut zu prüfen. Selbst wenn der Aufwand weiterhin ein relevantes Argument sein sollte, müssen wir ihn den Auswirkungen gegenüberstellen. Wenn unterschiedliche Bewertungsmethoden zu Verzerrungen im Ressourcenpotenzial führen, dann sollten wir wissen, wie gross diese Verzerrungen tatsächlich sind. Und genau diese Transparenz fehlt heute.
+Der Bundesrat teilt die Einschätzung und beantragt die Annahme des Postulates.
+Es geht heute nicht um eine Reform des Finanzausgleichs. Es geht um die Frage, ob wir bereit sind zu prüfen, ob eine systematische Ungleichbehandlung besteht. Der NFA basiert auf objektiven und vergleichbaren Kriterien. Gerade deshalb sollten wir dort, wo Unterschiede zwischen den Kantonen zu Verzerrungen führen können, genau hinschauen. Wer überzeugt ist, dass das heutige System sachgerecht ist, hat keinen Grund, eine Prüfung abzulehnen. Ich bitte Sie deshalb, dem Postulat zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sie haben es gesehen: Der Bundesrat ist mit diesem Postulat einverstanden; dies einfach deshalb, weil eine umfassende Überprüfung des Lastenausgleichs im nächsten Wirksamkeitsbericht sowieso stattfindet, unabhängig von diesem Postulat. Der Lastenausgleich berechnet sich aufgrund von Indikatoren, die seit Beginn des neuen Finanzausgleichs im Jahr 2008 verwendet werden. Insbesondere die Berechnung des soziodemografischen Lastenausgleichs hat sich in den letzten Jahren etwas verändert, hat auch Sch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sie haben es gesehen: Der Bundesrat ist mit diesem Postulat einverstanden; dies einfach deshalb, weil eine umfassende Überprüfung des Lastenausgleichs im nächsten Wirksamkeitsbericht sowieso stattfindet, unabhängig von diesem Postulat. Der Lastenausgleich berechnet sich aufgrund von Indikatoren, die seit Beginn des neuen Finanzausgleichs im Jahr 2008 verwendet werden. Insbesondere die Berechnung des soziodemografischen Lastenausgleichs hat sich in den letzten Jahren etwas verändert, hat auch Schwächen gezeigt, die temporär entschärft wurden. Im letzten Wirksamkeitsbericht hat der Bundesrat bereits angekündigt, dass er im Bericht für die Jahre 2026 bis 2030 den Lastenausgleich grundsätzlich überprüfen wird. Das ist ergebnisoffen. Der Bundesrat wird das ohnehin tun. Wir sind auch hier bereits an der Arbeit.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nantermod Philippe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le postulat Bally vise à réformer la valorisation fiscale des immeubles par les cantons en Suisse et, en réalité, à l'uniformiser sur le plan fédéral. Cette proposition avait plus de sens probablement avant la votation du 28 septembre 2025 sur la valeur locative, mais, maintenant que la valeur locative a été ou va être supprimée sur décision populaire, naturellement, la question de la valeur fiscale perd de son importance. Toutefois, elle ne perd pas complètement de son importance, puisqu'il res</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le postulat Bally vise à réformer la valorisation fiscale des immeubles par les cantons en Suisse et, en réalité, à l'uniformiser sur le plan fédéral. Cette proposition avait plus de sens probablement avant la votation du 28 septembre 2025 sur la valeur locative, mais, maintenant que la valeur locative a été ou va être supprimée sur décision populaire, naturellement, la question de la valeur fiscale perd de son importance. Toutefois, elle ne perd pas complètement de son importance, puisqu'il reste quand même une valorisation fiscale, notamment au moment de taxer la fortune des citoyens.
+En Suisse, il y a une souveraineté cantonale, notamment en matière fiscale et les cantons restent libres d'imposer la méthode de calcul de la valorisation des immeubles qu'ils souhaitent. Il y a une certaine logique derrière cette approche. D'abord, on n'estime pas de la même manière un immeuble si l'on se trouve dans une région de montagne ou dans une région de plaine, en ville ou à la campagne. Finalement, il y a des choix politiques derrière ces méthodes d'évaluation. Si un franc vaut un franc partout dans le pays, un appartement n'est pas partout estimé de la même manière, son utilisation pouvant varier fortement. Puis, les cantons qui renoncent à une valorisation très haute des immeubles renoncent aussi à l'impôt qui va avec, et c'est un choix cantonal.
+En réalité le postulat qui vous est proposé ne vise naturellement pas à réduire la valorisation fiscale des immeubles ; ne vous y méprenez pas. Le postulat qui vous est proposé vise naturellement à uniformiser vers le haut la valeur des immeubles. C'est une hausse d'impôts que l'on vous propose ici ; une hausse de l'impôt sur la fortune pour tous les propriétaires de ce pays qui aboutit immanquablement à une augmentation des impôts et aussi à une diminution de l'attractivité du statut de propriétaire, que l'on devrait au contraire encourager.
+Pour toutes les familles de notre pays qui sont propriétaires, et il y en a un certain nombre, ces modifications peuvent avoir des impacts très forts sur leur fiche d'impôt, mais sur leur possibilité d'accéder notamment aux subsides des primes maladies. Il n'y a aucun besoin de faire cette réforme aujourd'hui, les cantons sont souverains et s'organisent très bien entre eux.
+On vous dit qu'il ne s'agit que d'un postulat, mais ne vous y méprenez pas. Un postulat n'est jamais anodin. Nous allons, en acceptant ce postulat, confier à l'administration le soin d'analyser la situation. Il y aura un rapport et des propositions législatives. Lors de la prochaine réforme de la RPT qui, immanquablement, reviendra, l'administration proposera forcément d'uniformiser les valeurs locatives et la valorisation des immeubles entre les cantons.
+Je vous le dis franchement : nous nous battons contre toute forme de hausse d'impôts, nous ne voulons pas de nouveaux impôts. Même si vous les trouvez justes, Madame Bally, nous préférons des impôts bas injustes à des impôts élevés justes et, dans ces circonstances, nous préférons rejeter un postulat qui introduirait de nouveaux impôts qui vous paraissent justes plutôt que de modifier la loi dans ce sens. Aussi, j'aurais compris si la gauche avait proposé cette réforme, mais venant d'un parti, le Centre, fort dans des cantons qui ont des valorisations raisonnables, proposer cette réforme, c'est en réalité mettre un grain dans la machine qui fonctionne bien aujourd'hui.
+Pour cette raison, je vous invite et je m'adresse en particulier aux élus du Centre, à rejeter cette proposition qui aboutira, qu'on le veuille ou non, à une augmentation des impôts des citoyens.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeschi Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frau Kälin hat natürlich Unrecht, wenn sie sagt, man würde hier nicht die Kantone gegeneinander ausspielen. Es geht sehr wohl um einen Verteilkampf, und man möchte gewissen Kantonen, insbesondere den Bergkantonen, Geld wegnehmen und dieses neu eher den tiefergelegenen Kantonen geben.
+Der Grund, weshalb die SVP-Fraktion das Postulat bekämpft, ist aber ein anderer. Es geht ums Grundsätzliche. Wenn Sie den NFA reformieren wollen, dann braucht es eine Gesamtreform. Dann muss man das ganze System ans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frau Kälin hat natürlich Unrecht, wenn sie sagt, man würde hier nicht die Kantone gegeneinander ausspielen. Es geht sehr wohl um einen Verteilkampf, und man möchte gewissen Kantonen, insbesondere den Bergkantonen, Geld wegnehmen und dieses neu eher den tiefergelegenen Kantonen geben.
+Der Grund, weshalb die SVP-Fraktion das Postulat bekämpft, ist aber ein anderer. Es geht ums Grundsätzliche. Wenn Sie den NFA reformieren wollen, dann braucht es eine Gesamtreform. Dann muss man das ganze System anschauen, und man muss auch die Kantone miteinbeziehen. Aber es geht sicherlich nicht, dass man nur den geografisch-topografischen Lastenausgleich anpasst, bei den anderen Indikatoren aber keine Anpassungen vornimmt.
+Es kommt hinzu, dass der soziodemografische Lastenausgleich mit 525 Millionen Franken doch um einiges grosszügiger dotiert ist als der geografisch-topografische Lastenausgleich. Wennschon, würden wir daher beantragen, dass man den soziodemografischen Lastenausgleich entsprechend kürzt, um dann beim geografisch-topografischen Lastenausgleich aufzustocken, damit bei einer allfälligen Anpassung des geografisch-topografischen Lastenausgleichs kein Kanton verliert.
+Ich bitte Sie, auf eine einseitige Anpassung des NFA zu verzichten und diesen Vorstoss entsprechend abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Commission des finances recommande l'adoption des comptes 2025. Le groupe socialiste s'y associe sans réserve. Nous tenons en préambule à remercier l'Administration fédérale des finances pour la qualité de ses travaux et son précieux soutien dans l'accomplissement de notre travail.
+Les comptes sont bons. Le frein à l'endettement est respecté, et même largement respecté. Le frein à l'endettement autorisait un déficit de 262 millions de francs. Le compte ordinaire boucle sur un excédent de 1,18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Commission des finances recommande l'adoption des comptes 2025. Le groupe socialiste s'y associe sans réserve. Nous tenons en préambule à remercier l'Administration fédérale des finances pour la qualité de ses travaux et son précieux soutien dans l'accomplissement de notre travail.
+Les comptes sont bons. Le frein à l'endettement est respecté, et même largement respecté. Le frein à l'endettement autorisait un déficit de 262 millions de francs. Le compte ordinaire boucle sur un excédent de 1,185 milliard de francs. Les recettes ont progressé de 4,3 pour cent, les dépenses de 2 pour cent seulement. La Confédération finance la totalité de ses investissements par ses propres moyens sans recourir à l'endettement. La dette nette recule à 16,1 pour cent du PIB et le compte de résultat dépasse largement ce qui était prévu au budget. Ce sont des chiffres solides. Ils méritent d'être posés clairement parce qu'ils contrastent singulièrement avec le tableau qui nous était brossé lors des débats budgétaires récents. Il y a, en effet, quelque chose de troublant dans la séquence que ce Parlement rejoue session après session. À l'automne, la situation financière est décrite comme tendue, contrainte, au bord du déséquilibre, voire pire. Des coupes sont décidées dans les politiques sociales, dans les services publics. Ces choix sont présentés non pas comme des choix, mais comme des nécessités, comme si la comptabilité avait décidé à la place de la politique. Et puis viennent les comptes, et les comptes racontent une autre histoire. On répondra légitimement que le résultat de cette année doit une partie de son éclat à des recettes extraordinaires non reconductibles. C'est exact et ce n'est pas contesté. Mais ce qui n'a rien d'extraordinaire, ce qui, au contraire, est d'une banalité répétitive et prévisible, c'est le schéma lui-même, les prophéties pessimistes de l'automne, les sacrifices qu'elles commandent et les comptes, quelques mois plus tard, qui en révèlent l'exagération. Lorsque l'erreur va systématiquement dans le même sens, elle cesse d'être une erreur, elle devient une méthode. Une méthode qui n'est pas sans conséquences. Derrière chaque décision budgétaire, il y a des réalités concrètes : des familles qui voient leurs prestations diminuer, des cantons qui compensent ce que la Confédération ne finance plus, des régions périphériques dont la cohésion repose sur des services publics que l'on réduit année après année. La méthode voulue par la majorité de notre conseil a un prix, et ce sont toujours les mêmes qui le payent. 
+Le groupe socialiste approuve ces comptes et il sera présent cet automne lorsque s'ouvrira le débat sur le budget 2027, lorsqu'immanquablement les mêmes voix expliqueront que la situation est tendue, que les marges sont inexistantes, qu'il n'y a pas d'autres issues que de couper encore dans les mêmes politiques, sur le dos des mêmes personnes. Ce Parlement a le droit d'assumer ses choix, mais qu'il les assume pour ce qu'ils sont, des choix politiques portés par une majorité, avec des conséquences assumées, et non pas des fatalités déguisées en équations budgétaires. Sous prétexte du "mieux d'État", c'est surtout le "moins d'État" qui est souhaité. En politique, il y a toujours le choix ; la question est de savoir qui le supporte. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commençons par un constat sans appel : la violence sexiste et sexuelle est un fléau qui n'épargne pas notre pays, comme l'a encore rappelé hier le Conseil fédéral en lançant la deuxième phase de sa campagne contre la violence domestique. En 2025, la police a enregistré 22 000 infractions dues à la violence domestique, un chiffre dont on sait qu'il ne constitue que la partie émergée de l'iceberg et cache une sombre réalité dans laquelle un nombre encore plus élevé de cas n'entrera jamais dans les</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commençons par un constat sans appel : la violence sexiste et sexuelle est un fléau qui n'épargne pas notre pays, comme l'a encore rappelé hier le Conseil fédéral en lançant la deuxième phase de sa campagne contre la violence domestique. En 2025, la police a enregistré 22 000 infractions dues à la violence domestique, un chiffre dont on sait qu'il ne constitue que la partie émergée de l'iceberg et cache une sombre réalité dans laquelle un nombre encore plus élevé de cas n'entrera jamais dans les statistiques de la criminalité. En effet, l'accès à la justice des victimes de violence sexiste, sexuelle et de violence domestique est encore semé d'embûches. Parmi celles-ci, la prise en charge des victimes par les autorités de procédure pénale, soit la police, les ministères publics et les tribunaux, est souvent pointée du doigt comme un facteur de renoncement pour les victimes à poursuivre la procédure. En cause, on peut mentionner notamment un manque de sensibilité dans l'accueil, la prise en charge et l'audition des victimes avec un risque important de victimisation secondaire pour ces dernières.
+Ainsi, la motion de la Commission des affaires juridiques du Conseil national, "Modification du code de procédure pénale concernant la formation initiale et continue des autorités pénales", vise donc à améliorer cette formation de manière à améliorer l'accès à la justice pour les victimes. Elle se base sur le rapport du Conseil fédéral de 2025, donnant suite au postulat Fehlmann Rielle 21.4215.
+Vous l'avez entendu, la majorité de la commission rejette la motion au motif de la répartition des compétences. Effectivement, les cantons sont responsables de la formation initiale et continue des autorités de poursuite pénale, mais le prétexte du fédéralisme ne saurait nous prémunir d'examiner si nous remplissons nos propres obligations. Que les cantons soient tenus d'assurer la formation continue et initiale, y compris en vertu de l'article 15 de la Convention d'Istanbul, ne signifie pas encore toutefois que celle-ci soit assurée. Or, aujourd'hui, on constate que la mise en oeuvre est, sinon lacunaire, encore inégale. Le rapport de 2022 d'évaluation du Groupe d'experts sur la lutte contre la violence à l'égard des femmes et la violence domestique (Grevio) déplore que la Suisse n'ait toujours pas de programme de formation standardisé dans le domaine de la violence sexuelle pour la police, et que celle-ci soit facultative pour les services judiciaires. Le Grevio encourage vivement les autorités suisses à prendre des mesures afin de veiller à dispenser une formation initiale et continue systématique et obligatoire aux professionnels en lien avec les victimes et les auteurs de toutes les formes de violence visées par la Convention d'Istanbul. Ainsi, si l'argument de la compétence cantonale doit évidemment être pris en compte, il doit aussi être soigneusement sous-pesé en regard de nos responsabilités à l'échelon fédéral.
+Dans le cadre de la réponse au postulat précité, la Confédération a commandé un avis de droit qui conclut que la Confédération dispose d'une marge de manoeuvre en vertu de l'article 123 de la Constitution qui règle la compétence fédérale en matière de droit pénal et de droit de procédure pénale, lorsqu'il s'agit de garantir l'exécution uniforme du droit fédéral, ainsi que la mise en oeuvre du droit international. Or, ces deux conditions sont remplies. D'une part, aujourd'hui, malgré les efforts d'uniformisation consentis par les cantons, force est de constater que la formation des autorités de poursuite pénale est encore trop fragmentée pour assurer l'égalité de traitement des victimes dans l'ensemble du pays et que si la formation initiale de la police est désormais généralisée, celle des ministères publics reste encore lacunaire. D'ailleurs, bien que le Conseil fédéral propose lui aussi de rejeter la motion, il admet qu'il reste des efforts à accomplir, par exemple dans l'audition des victimes ou encore au niveau de la coopération interdisciplinaire et de la formation initiale et continue des acteurs. D'autre part, une intervention de la Confédération au titre de l'article 123 de la Constitution se justifie également par l'obligation qui nous est faite en vertu de l'article 15 de la Convention d'Istanbul de garantir la formation des professionnels. Dès lors, rejeter la présente motion, comme le propose la majorité de la commission, ne relève pas du simple respect des compétences cantonales, mais bien d'une appréciation politique. Or, il faut admettre que la situation actuelle en matière de prise en charge des victimes ne permet ni de garantir l'exécution uniforme du droit ni de remplir nos obligations internationales. C'est également la conclusion à laquelle est parvenu le Conseil national, par 127 voix contre 63 et 1 abstention, soit l'intégralité des groupes parlementaires à une exception près.
+Il a été dit en commission que nous nous rendrions risibles en adoptant cette motion. Le ridicule ne tue pas, contrairement à la violence sexiste et sexuelle qui fait encore et toujours une victime toutes les deux semaines dans notre pays.
+Dans l'intérêt des victimes, mais aussi des autorités chargées de les accompagner dans la procédure pénale, je vous invite à suivre la minorité de la commission et à adopter la motion.
 </t>
   </si>
 </sst>
@@ -174,8 +305,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I5" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I12" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I12"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -618,6 +749,205 @@
         <v>32</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6"/>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8"/>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -251,6 +251,47 @@
 Dans le cadre de la réponse au postulat précité, la Confédération a commandé un avis de droit qui conclut que la Confédération dispose d'une marge de manoeuvre en vertu de l'article 123 de la Constitution qui règle la compétence fédérale en matière de droit pénal et de droit de procédure pénale, lorsqu'il s'agit de garantir l'exécution uniforme du droit fédéral, ainsi que la mise en oeuvre du droit international. Or, ces deux conditions sont remplies. D'une part, aujourd'hui, malgré les efforts d'uniformisation consentis par les cantons, force est de constater que la formation des autorités de poursuite pénale est encore trop fragmentée pour assurer l'égalité de traitement des victimes dans l'ensemble du pays et que si la formation initiale de la police est désormais généralisée, celle des ministères publics reste encore lacunaire. D'ailleurs, bien que le Conseil fédéral propose lui aussi de rejeter la motion, il admet qu'il reste des efforts à accomplir, par exemple dans l'audition des victimes ou encore au niveau de la coopération interdisciplinaire et de la formation initiale et continue des acteurs. D'autre part, une intervention de la Confédération au titre de l'article 123 de la Constitution se justifie également par l'obligation qui nous est faite en vertu de l'article 15 de la Convention d'Istanbul de garantir la formation des professionnels. Dès lors, rejeter la présente motion, comme le propose la majorité de la commission, ne relève pas du simple respect des compétences cantonales, mais bien d'une appréciation politique. Or, il faut admettre que la situation actuelle en matière de prise en charge des victimes ne permet ni de garantir l'exécution uniforme du droit ni de remplir nos obligations internationales. C'est également la conclusion à laquelle est parvenu le Conseil national, par 127 voix contre 63 et 1 abstention, soit l'intégralité des groupes parlementaires à une exception près.
 Il a été dit en commission que nous nous rendrions risibles en adoptant cette motion. Le ridicule ne tue pas, contrairement à la violence sexiste et sexuelle qui fait encore et toujours une victime toutes les deux semaines dans notre pays.
 Dans l'intérêt des victimes, mais aussi des autorités chargées de les accompagner dans la procédure pénale, je vous invite à suivre la minorité de la commission et à adopter la motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juillard Charles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous avez vu que je suis aussi dans la minorité. Je vous recommande donc d'accepter cette proposition de minorité. La question est de savoir si le Conseil fédéral peut ou doit. À mon avis, c'est une question plus générale sur les taxes ou les redevances. Lorsqu'il s'agit par exemple des impôts, la plupart des lois, cantonales en tout cas, prévoient des adaptations automatiques pour compenser le renchérissement afin d'éviter les taxes occultes. Il s'agit en l'occurrence de ne pas faire payer d'im</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous avez vu que je suis aussi dans la minorité. Je vous recommande donc d'accepter cette proposition de minorité. La question est de savoir si le Conseil fédéral peut ou doit. À mon avis, c'est une question plus générale sur les taxes ou les redevances. Lorsqu'il s'agit par exemple des impôts, la plupart des lois, cantonales en tout cas, prévoient des adaptations automatiques pour compenser le renchérissement afin d'éviter les taxes occultes. Il s'agit en l'occurrence de ne pas faire payer d'impôts supplémentaires au contribuable lorsque son revenu réel n'a pas changé.
+Or ici, on va dans le sens inverse. Tout augmente, sauf les taxes qui sont destinées à financer les investissements qui y sont liés. Je ne vais pas vous rappeler à quoi sert la RPLP, mais elle est surtout là pour financer des infrastructures ferroviaires et routières. Je veux citer un autre exemple : la vignette autoroutière a été introduite en 1985 et coûte encore aujourd'hui 40 francs. En 1985, ce prix de 40 francs permettait environ 350 millions de rentrées dans les caisses de la Confédération, dont 40 pour cent payés pour des véhicules étrangers, des véhicules en transit. Il vaut donc quand même la peine d'y réfléchir par rapport aux citoyens suisses. En 2025, s'il y avait eu une adaptation automatique au renchérissement, ce sont 553 millions qui seraient tombés dans les caisses de la Confédération, soit plus de 200 millions supplémentaires, et toujours 40 pour cent payés pour des véhicules étrangers qui transitent en Suisse. Pour les teneurs de la rigueur financière, je pense que cette adaptation automatique mérite quand même d'être analysée et discutée. On pourrait passer le coût de la vignette de 40 francs à 63 francs aujourd'hui, si on avait fait cette progression, soit, en moyenne, 53 centimes de plus par an depuis son introduction.
+Il ne faut donc pas peindre le diable sur la muraille en disant que cela aura des conséquences incroyables pour les entreprises. Je crois que c'est le contraire, c'est une question de philosophie. Ces taxes et redevances permettent de financer des infrastructures dont les coûts augmentent toujours par nature et pour lesquels il faudra bien trouver les moyens. On sait à quel point, aujourd'hui, nous avons des difficultés à trouver ces moyens. Je vous invite donc à introduire ce mécanisme avec cette marge de deux points d'inflation qui permet au Conseil fédéral d'avoir une toute petite marge de progression.
+Je vous invite donc à suivre la minorité de la commission.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Même si je peux tout à fait comprendre le souci des entreprises, si les adaptations sont à la hausse, les entreprises répercuteront aussi le coût sur le client final, donc ce ne sont pas les entreprises qui auront un souci réel d'amortissement de leur véhicule. En outre, fixer un délai de 7 ans voudrait dire que les tarifs aujourd'hui prévus dans la loi auraient dû être prévus par le prédécesseur de M. Rösti. Rendez-vous compte du temps qu'il faut pour adapter et tenir compte de la réalité du mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Même si je peux tout à fait comprendre le souci des entreprises, si les adaptations sont à la hausse, les entreprises répercuteront aussi le coût sur le client final, donc ce ne sont pas les entreprises qui auront un souci réel d'amortissement de leur véhicule. En outre, fixer un délai de 7 ans voudrait dire que les tarifs aujourd'hui prévus dans la loi auraient dû être prévus par le prédécesseur de M. Rösti. Rendez-vous compte du temps qu'il faut pour adapter et tenir compte de la réalité du moment. 7 ans, c'est beaucoup trop long. Regardez sur les événements qui se passent aujourd'hui. Comment voulez-vous savoir dans 7 ans quelle sera exactement la réalité, alors que vous demandez aujourd'hui de faire une projection ?
+Si le Conseil fédéral veut échelonner différemment la redevance telle qu'elle est proposée ici, avec l'ajout de ce délai de préavis de 7 ans, cela veut dire qu'aujourd'hui le Conseil fédéral devrait prévoir l'échelonnement des redevances pour 2032-2033. Ce n'est juste pas possible, ce n'est pas réaliste en matière de politique publique de faire une telle adjonction dans une loi, parce que cela ne permet pas raisonnablement de tenir compte de l'évolution de la situation économique, de la situation politique et de tout ce à quoi la Confédération notamment doit faire face. Je peux comprendre ce besoin de planification pour les entreprises, tout en sachant que, comme je l'ai dit, les entreprises au bout du compte, reporteront en grande partie cette adaptation des charges, si celles-ci sont à la hausse, sur le client final.
+Je vous invite donc à suivre ici la minorité de la commission et à suivre le projet du Conseil fédéral.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne vais pas revenir sur tous les arguments qui ont été indiqués par la rapporteuse ou le porte-parole de la minorité de la commission, mais si je soutiens l'entrée en matière, c'est parce que je pense qu'il y a nécessité d'agir. On nous dit qu'avec l'intelligence artificielle, ce projet n'est plus nécessaire, que les Gafam mettent à disposition toutes ces données. C'est possible, mais je n'en suis pas sûr. Lors du débat que nous avons eu en commission, nous avons quand même survolé passableme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne vais pas revenir sur tous les arguments qui ont été indiqués par la rapporteuse ou le porte-parole de la minorité de la commission, mais si je soutiens l'entrée en matière, c'est parce que je pense qu'il y a nécessité d'agir. On nous dit qu'avec l'intelligence artificielle, ce projet n'est plus nécessaire, que les Gafam mettent à disposition toutes ces données. C'est possible, mais je n'en suis pas sûr. Lors du débat que nous avons eu en commission, nous avons quand même survolé passablement de questions qui ont trait à ces besoins ou non-besoins. Qui fournit ou qui ne fournit pas ces données ? Combien cela coûte-t-il ? Combien faut-il mettre de moyens à disposition ? Je crois que ce projet mérite quand même notre attention parce qu'il est attendu. Vous avez vu le nombre de lettres que nous avons reçu d'instances directement concernées. Le porte-parole de la minorité en a cité un certain nombre, mais l'aménagement du territoire aussi peut être concerné. Les réflexions sur la circulation dans les villes et les communes sont aussi des éléments qui pourront être pris en compte.
+Je ne suis pas non plus un fan absolu de ce projet. J'aurais peut-être dû d'emblée dire que je suis président de l'intergroupe parlementaire Feu bleu, qui regroupe en particulier les sapeurs-pompiers, qui attendent ce genre de données actualisées au jour le jour. Actuellement, quand il y a des travaux dans les villes ou dans les grandes villes, ils doivent envoyer un de leurs membres régulièrement circuler dans leur secteur d'activité pour savoir si les chemins habituels sont disponibles ou non en fonction des travaux qu'il y a. Aujourd'hui, ce n'est pas acceptable. Ce projet mérite donc quand même un peu plus que d'être simplement abandonné sans avoir été approfondi.
+Je le répète, pour moi, il y a deux éléments qui sont absolument fondamentaux. En ce qui concerne la fourniture des informations, soit tous les acteurs doivent fournir leurs informations, soit ce n'est pas le cas. Si on laisse la possibilité de le faire ou pas, si on n'oblige pas à fournir les données, ce projet n'a pas de sens. C'est pour moi un élément assez essentiel. En ce qui concerne les moyens dont on parle pour le mettre en oeuvre, les 28 EPT et les coûts qui sont prévus sont absolument exorbitants. On n'a pas arrêté de nous dire, y compris de la part de l'administration, que l'intelligence artificielle allait nous permettre de gagner, mais qu'on ne sait pas exactement combien. Ce sont des questions qui, à mon avis, méritent d'être encore discutées en commission avant de couler ce projet. Je serai le premier à reconnaître, si on n'a pas de réponses claires et concrètes notamment sur ces deux éléments-là, lors du vote final, qu'il ne faut pas soutenir ce projet, si on n'a pas pu l'améliorer dans ces deux domaines. Cependant, aujourd'hui, je ne suis pas en mesure de vous dire ni de vous recommander s'il faut soutenir ou non ce projet parce qu'à mon avis, la commission n'est pas allée assez loin dans le travail d'examen. J'avais par exemple proposé que l'on fasse des auditions des milieux concernés. C'est vrai que si on ne veut pas entrer en matière, ce n'est pas la peine qu'on perde notre temps à faire des auditions, mais je pense que si nous avions été un peu plus loin et notamment avions procédé à ces auditions, peut-être que nous aurions un autre regard sur ce projet qui, je le répète, mérite d'être amélioré et que, sans ces améliorations, je ne soutiendrai pas non plus lors du vote final.
+Aujourd'hui, je vous invite vraiment à entrer en matière.
 </t>
   </si>
 </sst>
@@ -305,8 +346,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I12" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I15" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I15"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -948,6 +989,93 @@
         <v>62</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -292,6 +292,21 @@
 Je ne suis pas non plus un fan absolu de ce projet. J'aurais peut-être dû d'emblée dire que je suis président de l'intergroupe parlementaire Feu bleu, qui regroupe en particulier les sapeurs-pompiers, qui attendent ce genre de données actualisées au jour le jour. Actuellement, quand il y a des travaux dans les villes ou dans les grandes villes, ils doivent envoyer un de leurs membres régulièrement circuler dans leur secteur d'activité pour savoir si les chemins habituels sont disponibles ou non en fonction des travaux qu'il y a. Aujourd'hui, ce n'est pas acceptable. Ce projet mérite donc quand même un peu plus que d'être simplement abandonné sans avoir été approfondi.
 Je le répète, pour moi, il y a deux éléments qui sont absolument fondamentaux. En ce qui concerne la fourniture des informations, soit tous les acteurs doivent fournir leurs informations, soit ce n'est pas le cas. Si on laisse la possibilité de le faire ou pas, si on n'oblige pas à fournir les données, ce projet n'a pas de sens. C'est pour moi un élément assez essentiel. En ce qui concerne les moyens dont on parle pour le mettre en oeuvre, les 28 EPT et les coûts qui sont prévus sont absolument exorbitants. On n'a pas arrêté de nous dire, y compris de la part de l'administration, que l'intelligence artificielle allait nous permettre de gagner, mais qu'on ne sait pas exactement combien. Ce sont des questions qui, à mon avis, méritent d'être encore discutées en commission avant de couler ce projet. Je serai le premier à reconnaître, si on n'a pas de réponses claires et concrètes notamment sur ces deux éléments-là, lors du vote final, qu'il ne faut pas soutenir ce projet, si on n'a pas pu l'améliorer dans ces deux domaines. Cependant, aujourd'hui, je ne suis pas en mesure de vous dire ni de vous recommander s'il faut soutenir ou non ce projet parce qu'à mon avis, la commission n'est pas allée assez loin dans le travail d'examen. J'avais par exemple proposé que l'on fasse des auditions des milieux concernés. C'est vrai que si on ne veut pas entrer en matière, ce n'est pas la peine qu'on perde notre temps à faire des auditions, mais je pense que si nous avions été un peu plus loin et notamment avions procédé à ces auditions, peut-être que nous aurions un autre regard sur ce projet qui, je le répète, mérite d'être amélioré et que, sans ces améliorations, je ne soutiendrai pas non plus lors du vote final.
 Aujourd'hui, je vous invite vraiment à entrer en matière.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permettez-moi d'apporter quelques mots en français dans ce débat qui semble surtout concerné les Suisses alémaniques, alors qu'il concerne toute la Suisse, tous les cantons suisses et tous les citoyens de ce pays. Oui, personne ne conteste que le 8 mars dernier, une majorité du peuple a accepté la réforme qui lui était proposée au travers de l'imposition individuelle. Oui, le peuple a voulu mettre un terme à cette inégalité qui durait depuis bien trop longtemps. Cependant, le peuple était mis de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permettez-moi d'apporter quelques mots en français dans ce débat qui semble surtout concerné les Suisses alémaniques, alors qu'il concerne toute la Suisse, tous les cantons suisses et tous les citoyens de ce pays. Oui, personne ne conteste que le 8 mars dernier, une majorité du peuple a accepté la réforme qui lui était proposée au travers de l'imposition individuelle. Oui, le peuple a voulu mettre un terme à cette inégalité qui durait depuis bien trop longtemps. Cependant, le peuple était mis devant un choix cornélien ; vraiment cornélien. Beaucoup de gens, lors de la campagne, ont choisi cette option de peur de voir cette inégalité se poursuivre.
+Ce choix cornélien, vous le connaissez : il était d'accepter de mettre un terme à cette inégalité et d'accepter un modèle compliqué qui crée d'autres inégalités et qui conduit à des divisions, souvent antisociales, ou de refuser cette réforme et voir cette inégalité encore se poursuivre. On peut d'ailleurs se poser la question : pourquoi le texte de l'initiative dont on parle aujourd'hui n'a-t-il pas été traité simultanément à l'initiative sur l'imposition individuelle ? En effet, dans ce cas, le peuple aurait eu un vrai choix sur le modèle qu'il entend. Se contentait-il de régler une inégalité sur le plan fédéral qui dure depuis trop longtemps, ou bien voulait-il révolutionner le système fiscal, ce dont je ne suis absolument pas certain pour avoir discuté avec les gens ?
+Le peuple a tranché pour cette solution. Toutefois, aujourd'hui, soutenir l'initiative qui vous est proposée ne remet pas en cause la fin de cette inégalité entre les couples mariés et les autres, au contraire, et n'a pas d'incidence sur l'organisation familiale, contrairement à ce qu'on a pu entendre. Elle offre au peuple un véritable choix sur le modèle : régler un problème fédéral sans créer de nouvelles inégalités ou mettre en place un système bureaucratique sans amélioration claire pour une grande majorité des contribuables. Si l'initiative de rang constitutionnel est acceptée, elle rendra caduque la révision législative acceptée par le peuple. C'est assez clair pour ceux qui en douteraient ou qui auraient émis des avis contraires aujourd'hui.
+Il nous appartiendra à nous, parlementaires, de trouver une solution plus simple, plus égalitaire, comme les cantons l'ont fait, sans leur imposer, au passage, une révolution dont une majorité d'entre eux n'a pas voulu. Accepter l'initiative, ce n'est pas trahir la volonté du peuple, mais, au contraire, c'est lui donner l'occasion de choisir la méthode.
+Quant aux coûts, pour essayer de répondre à Madame Herzog, vous savez très bien que cela dépendra du modèle qui sera retenu par le Parlement. Ce coût, dans le débat sur l'imposition individuelle, a aussi évolué. Il pourra aussi évoluer dans les débats que nous aurons. Pour l'instant, la question se pose sur la méthode : comment régler cette inégalité qui dure depuis aussi longtemps ?
+Dans ce cadre-là, je vous invite à soutenir la proposition de la minorité, qui offrira un vrai choix au Parlement et à la population sur la méthode et sur le coût.
 </t>
   </si>
 </sst>
@@ -346,8 +361,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I15" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I16" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I16"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1076,6 +1091,35 @@
         <v>72</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -63,7 +63,8 @@
   </si>
   <si>
     <t xml:space="preserve">Mindestlöhne wurden nicht aus einer Laune heraus eingeführt, sie sind eine Antwort auf reale Probleme im Arbeitsmarkt, auf die Tatsache, dass Menschen Vollzeit arbeiten und trotzdem zu wenig Geld zum Leben verdienen. Mit dieser Vorlage wollen Sie dieses Instrument unterlaufen. Zumindest der Ständerat hat eingesehen, dass die Übersteuerung demokratisch legitimierter Entscheidungen höchst kritisch ist. Die Ausnahme für Mindestlöhne, die bereits vor dieser Gesetzesvorlage beschlossen wurden, wie etwa in den Kantonen Genf, Neuenburg, Basel-Stadt oder Jura, ist ein Kompromiss für die Vergangenheit und ein kleiner Schritt in Richtung einer demokratisch verträglichen Vorlage. Dieser Schritt muss nun aber konsequent weitergedacht werden. 
-Mit der Minderheit Amoos wird auch für die Zukunft ein solcher Kompromiss gefunden. Wird ein Mindestlohn beschlossen, so erhalten die Sozialpartner Zeit, um zu reagieren. Sie können bei der nächsten Verhandlung der GAV die Löhne anpassen. Spätestens aber nach zwei Jahren müssen die Löhne auf das Niveau der geltenden Mindestlöhne angehoben werden. Das schafft Verbindlichkeit, und es schafft Fairness. Denn ohne klare Fristen besteht die Gefahr, dass über Jahre hinweg zu tiefe Löhne bestehen bleiben. Und genau das ist aus unserer Sicht nicht akzeptabel. Mindestlöhne sind keine symbolischen Grössen, sie sind eine verbindliche Untergrenze. Sie sollen sicherstellen, dass Arbeit vor Armut schützt. Und so kommen wir auch wieder näher zurück an die Verfassung. Denn die Kantone haben gemäss Bundesverfassung das Recht, Mindestlöhne einzuführen. Eine Übersteuerung durch privatrechtliche Verträge - ein allgemeinverbindlich erklärter GAV ist nichts anderes - ist schlicht nicht verfassungskonform. Mit der Minderheit Amoos könnte man die Vorlage schon beinahe als demokratisch verträglich bezeichnen. Deshalb unterstützen wir den Antrag der Minderheit bei Artikel 1 Absatz 4 für einen Lohnschutz, der seinen Namen auch verdient.
+Mit der Minderheit Amoos wird auch für die Zukunft ein solcher Kompromiss gefunden. Wird ein Mindestlohn beschlossen, so erhalten die Sozialpartner Zeit, um zu reagieren. Sie können bei der nächsten Verhandlung der GAV die Löhne anpassen. Spätestens aber nach zwei Jahren müssen die Löhne auf das Niveau der geltenden Mindestlöhne angehoben werden. Das schafft Verbindlichkeit, und es schafft Fairness. Denn ohne klare Fristen besteht die Gefahr, dass über Jahre hinweg zu tiefe Löhne bestehen bleiben. Und genau das ist aus unserer Sicht nicht akzeptabel. Mindestlöhne sind keine symbolischen Grössen, sie sind eine verbindliche Untergrenze. Sie sollen sicherstellen, dass Arbeit vor Armut schützt. Und so kommen wir auch wieder näher zurück an die Verfassung. Denn die Kantone haben gemäss Bundesverfassung das Recht, Mindestlöhne einzuführen. Eine Übersteuerung durch privatrechtliche Verträge - ein allgemeinverbindlich erklärter GAV ist nichts anderes - ist schlicht nicht verfassungskonform. Mit der Minderheit Amoos könnte man die Vorlage schon beinahe als demokratisch verträglich bezeichnen.
+Deshalb unterstützen wir den Antrag der Minderheit bei Artikel 1 Absatz 4 für einen Lohnschutz, der seinen Namen auch verdient.
 </t>
   </si>
   <si>
@@ -307,6 +308,31 @@
 Il nous appartiendra à nous, parlementaires, de trouver une solution plus simple, plus égalitaire, comme les cantons l'ont fait, sans leur imposer, au passage, une révolution dont une majorité d'entre eux n'a pas voulu. Accepter l'initiative, ce n'est pas trahir la volonté du peuple, mais, au contraire, c'est lui donner l'occasion de choisir la méthode.
 Quant aux coûts, pour essayer de répondre à Madame Herzog, vous savez très bien que cela dépendra du modèle qui sera retenu par le Parlement. Ce coût, dans le débat sur l'imposition individuelle, a aussi évolué. Il pourra aussi évoluer dans les débats que nous aurons. Pour l'instant, la question se pose sur la méthode : comment régler cette inégalité qui dure depuis aussi longtemps ?
 Dans ce cadre-là, je vous invite à soutenir la proposition de la minorité, qui offrira un vrai choix au Parlement et à la population sur la méthode et sur le coût.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme l'a exposé de manière très exhaustive le rapporteur de la commission, il s'agit ici des mesures et des assainissements qui sont liés à la radioactivité d'origine naturelle. Le projet du Conseil fédéral prévoyait, par analogie aux mesures liées à la radioactivité d'origine anthropique, une base légale permettant de fixer des limites d'exposition à partir desquelles l'assainissement d'un site ou d'un bien-fonds serait obligatoire et de régler la prise en charge des coûts. Ici, on parle princ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme l'a exposé de manière très exhaustive le rapporteur de la commission, il s'agit ici des mesures et des assainissements qui sont liés à la radioactivité d'origine naturelle. Le projet du Conseil fédéral prévoyait, par analogie aux mesures liées à la radioactivité d'origine anthropique, une base légale permettant de fixer des limites d'exposition à partir desquelles l'assainissement d'un site ou d'un bien-fonds serait obligatoire et de régler la prise en charge des coûts. Ici, on parle principalement de la pollution au radon. Vous savez qu'il est présent en Suisse de manière inégale, mais assez largement dans certaines régions, notamment dans l'Arc jurassien et l'Arc alpin. Concrètement - le rapporteur a également cité plusieurs chiffres -, 10 pour cent des bâtiments en Suisse dépassent le plafond d'exposition de 300 becquerels par mètre cube.
+Quels sont les risques de ces valeurs supérieures aux limites d'exposition ? Une étude a permis d'estimer que le radon est responsable d'environ 200 à 300 décès par an imputables au cancer du poumon, soit 8,3 pour cent du total des décès liés à ce cancer ; un chiffre qui n'est qu'une moyenne, puisqu'il peut aller jusqu'à 15 pour cent dans les cantons particulièrement exposés, comme mon canton, le canton du Jura, mais également le Tessin, par exemple. Ainsi, le radon représente la deuxième cause de cancer du poumon après la consommation de tabac. L'exposition au radon constitue donc un véritable enjeu de santé publique. Dès lors, si l'on renonce à une base légale pour la radioactivité d'origine naturelle, les cantons seraient considérablement freinés dans leur possibilité d'action dans ce domaine. Je rappelle qu'on parle notamment d'assainissements dans les écoles ou dans les jardins d'enfants, à savoir pour un groupe de population qui est particulièrement vulnérable.
+Le Conseil national a estimé que l'absence de dispositions légales suffisamment précises pour assurer l'assainissement des biens-fonds pollués risque d'affaiblir la pratique actuelle en matière de radioactivité naturelle et, en particulier, de protection de la population, et constitue à cet égard un signal négatif. Il a donc adopté une solution de compromis, avec ce nouvel article 24b, qui permet au Conseil fédéral de fixer le plafond d'exposition à partir duquel des mesures sont nécessaires. Par ailleurs, cet article règle la prise en charge des frais liés aux examens et aux assainissements, ce qui correspond aussi à la volonté des cantons. Ainsi, la version adoptée par le Conseil national est plus ciblée que le projet initial, mais elle permet à la fois au Conseil fédéral de fixer des valeurs de référence et ménage la possibilité d'agir des cantons.
+Il a été fait allusion au fait que, lors du premier examen de ce projet de loi par notre conseil, il n'y avait pas eu de proposition de minorité à ce sujet. Toutefois, le Conseil national a fait preuve de la sagesse qui, il nous semble, a fait défaut à notre conseil en refusant de garantir le bon déroulement des assainissements de bien-fonds, et il a donc adopté à l'unanimité ce nouvel article 24b. Dès lors, il nous a semblé pertinent de mener cette discussion également dans notre chambre. C'est pourquoi je vous invite à suivre le Conseil national et à clore ainsi cette divergence.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ici aussi, il s'agit de la poursuite de la croisade contre l'infraction pour négligence que mène notre conseil. On sait pourtant que si elles sont commises par négligence, les infractions qui sont définies à l'article 44 n'en sont pas pour autant négligeables. En effet, il peut s'agir d'exercer sans autorisation des activités qui, justement, sont soumises au régime de l'autorisation, ou de ne pas prendre les mesures nécessaires pour respecter les limites de dose. Il peut s'agir également de se s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ici aussi, il s'agit de la poursuite de la croisade contre l'infraction pour négligence que mène notre conseil. On sait pourtant que si elles sont commises par négligence, les infractions qui sont définies à l'article 44 n'en sont pas pour autant négligeables. En effet, il peut s'agir d'exercer sans autorisation des activités qui, justement, sont soumises au régime de l'autorisation, ou de ne pas prendre les mesures nécessaires pour respecter les limites de dose. Il peut s'agir également de se soustraire à la dosimétrie qui est prescrite. On parle donc de pratiques - qu'elles soient intentionnelles ou commises par négligence - qui mettent en danger la population en raison du domaine que l'on traite, qui est, je le rappelle quand même, les doses de radioactivité qui sont admises. 
+Ainsi, la proposition du Conseil national ne vise pas seulement à biffer purement et simplement l'infraction par négligence du projet de loi. Elle vise aussi à biffer le montant de l'amende qui était prévu jusqu'à présent, à savoir 20 000 francs. Pour qu'un délit ou un crime, selon la gravité de l'infraction poursuivie, soit pénalisé d'une amende de 20 000 francs, on ne parle pas d'un cas de bagatelle. Par ailleurs, la clause de minimis qui a été prévue à l'article 44 alinéa 4 permet de donner la marge de manoeuvre nécessaire pour éviter de poursuivre et de chicaner les personnes ou les entreprises qui se seraient réellement livrées à une infraction de peu de gravité par rapport à cette négligence. Cela crée également une forte asymétrie dans le texte de loi, puisque seule l'intention serait mentionnée à l'article 44. Dès lors, le risque serait évident que l'on plaide la négligence pour se soustraire à toute poursuite en cas d'infraction commise. La proposition qui vous est faite par le Conseil des États constitue un recul par rapport au droit en vigueur et en regard des enjeux en matière de santé publique et de protection de la population. Il est primordial de ne pas donner lieu à ce recul. 
+C'est pourquoi je vous invite, comme l'a fait le Conseil national, à maintenir la version du Conseil fédéral et à éliminer ainsi cette dernière divergence.
 </t>
   </si>
 </sst>
@@ -361,8 +387,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I16" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I18" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I18"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1120,6 +1146,64 @@
         <v>75</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -119,8 +119,8 @@
   </si>
   <si>
     <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique : à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36 108 francs contre 52 488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre femmes et hommes dans l'AVS est quasiment nulle. Cet écart ne diminue pas depuis plusieurs années. En comparaison internationale, la Suisse pointe à un peu reluisant cinquième rang des pays européens présentant les plus fortes différences de retraite entre les femmes et les hommes.
-Afin de combler ce fossé, la présente motion visait donc à tenir compte des lacunes de rente découlant des tâches éducatives et d'assistance, qui sont assumées majoritairement par les femmes au détriment de leur épargne-vieillesse, et d'introduire dans la loi sur la prévoyance professionnelle vieillesse, survivants et invalidité (LPP) le principe de la bonification ; principe bien connu et reconnu puisqu'il existe déjà dans l'AVS, comme l'a indiqué le rapporteur. Comme cela a été dit, cette motion s'inscrivait dans la série d'interventions déposées dans le sillage du refus de la révision de la LPP en 2024 ; interventions qui avaient toutes été renvoyées à la commission compétente et qui ont été retirées, que ce soit en commission ou aujourd'hui au conseil, au profit du postulat 26.3521 de la CSSS, que nous avons accepté tout à l'heure.
-Ainsi, vu les considérations avancées dans le postulat de la commission, qui refuse une approche isolée au profit d'une réflexion globale sur les améliorations possibles dans la LPP, et vu les arguments du Conseil fédéral, qui oeuvre d'ores et déjà à la nouvelle révision de la LPP et cherche, lui aussi, des solutions pour améliorer la prévoyance professionnelle des personnes travaillant à temps partiel ou ayant de faibles revenus - parmi lesquels les femmes sont justement surreprésentées -, je me rallie au mouvement initié par d'autres auteurs de motions et retire la présente motion, dans l'espoir toutefois que les mesures de la prochaine réforme permettront enfin d'infléchir cet écart important qui n'a plus lieu d'être dans le système de rente moderne d'un pays prospère comme le nôtre.
+Afin de combler ce fossé, la présente motion visait donc à tenir compte des lacunes de rente découlant des tâches éducatives et d'assistance, qui sont assumées majoritairement par les femmes au détriment de leur épargne-vieillesse, et d'introduire dans la loi sur la prévoyance professionnelle vieillesse, survivants et invalidité (LPP) le principe de la bonification, principe bien connu et reconnu, puisqu'il existe déjà dans l'AVS, comme l'a indiqué le rapporteur. Comme cela a été dit, cette motion s'inscrivait dans la série d'interventions déposées dans le sillage du refus de la révision de la LPP en 2024, interventions qui avaient toutes été renvoyées à la commission compétente et qui ont été retirées, que ce soit en commission ou aujourd'hui au conseil, au profit du postulat 26.3521 de la CSSS, que nous avons accepté tout à l'heure.
+Ainsi, vu les considérations avancées dans le postulat de la commission, qui refuse une approche isolée au profit d'une réflexion globale sur les améliorations possibles dans la LPP, et vu les arguments du Conseil fédéral, qui oeuvre d'ores et déjà à la nouvelle révision de la LPP et cherche, lui aussi, des solutions pour améliorer la prévoyance professionnelle des personnes travaillant à temps partiel ou ayant de faibles revenus, parmi lesquels les femmes sont justement surreprésentées, je me rallie au mouvement initié par d'autres auteurs de motions et retire la présente motion, dans l'espoir toutefois que les mesures de la prochaine réforme permettront enfin d'infléchir cet écart important qui n'a plus lieu d'être dans le système de rente moderne d'un pays prospère comme le nôtre.
 </t>
   </si>
   <si>
@@ -311,6 +311,28 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">375987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gantenbein Laura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die sogenannte Blackout-Initiative und der Gegenvorschlag verkaufen sich als Lösung für Versorgungssicherheit. In Wahrheit sind sie aber ein gefährlicher Rückschritt in eine Technologie aus dem letzten Jahrtausend mit unabsehbaren Risiken, hohen Kosten, einer ungelösten Entsorgungsfrage und einer Abhängigkeit vom Ausland, da Uran in der Schweiz nicht abgebaut wird und auch nicht abgebaut werden soll. Ich könnte hier enden, möchte aber doch noch einige Punkte, die meinen Kanton betreffen, vertief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die sogenannte Blackout-Initiative und der Gegenvorschlag verkaufen sich als Lösung für Versorgungssicherheit. In Wahrheit sind sie aber ein gefährlicher Rückschritt in eine Technologie aus dem letzten Jahrtausend mit unabsehbaren Risiken, hohen Kosten, einer ungelösten Entsorgungsfrage und einer Abhängigkeit vom Ausland, da Uran in der Schweiz nicht abgebaut wird und auch nicht abgebaut werden soll. Ich könnte hier enden, möchte aber doch noch einige Punkte, die meinen Kanton betreffen, vertiefen. 
+Beznau 1 wurde 1961 gebaut, also in dem Jahr, als die ersten Schritte auf dem Mond gemacht wurden - wir wissen, wie lange das her ist. Beznau 1 ist das älteste AKW der Welt. Das AKW Gösgen im Kanton Solothurn, nahe der grössten Stadt des Kantons, wurde dann zehn Jahre später gebaut und war soeben mehrfach in den Medien, da es aufgrund von Sicherheitsmängeln sogar ausgeschaltet werden musste. Zudem liegt das AKW Leibstadt nur wenige Kilometer entfernt. Die Menschen in unserer Region tragen also seit Jahrzehnten das Risiko eines schweren Atomunfalls, ohne je gefragt worden zu sein, ob sie dieses Risiko überhaupt tragen wollen. Im Gegenteil, man hat sich sogar noch gewehrt und konnte immerhin dasjenige in Kaiseraugst verhindern. 
+Als Mitglied der Organisation "Nie wieder Atomkraft" (NWA) habe ich an Veranstaltungen teilgenommen, an denen Fachpersonen eindrücklich aufgezeigt haben, welche Folgen Radioaktivität für Menschen haben kann. Besonders eindrücklich war die Perspektive von Ärztinnen der Organisation "International Physicians for the Prevention of Nuclear War". Die Ärztinnen, die sich für soziale Verantwortung und zur Verhütung eines Atomkriegs einsetzen, erinnern uns daran, dass Radioaktivität kein abstraktes Risiko ist. Sie bedeutet nämlich konkret Krebs, genetische Schäden, unbewohnbare Regionen und jahrzehntelanges menschliches Leid. 
+Wer heute nach den Katastrophen in Fukushima und Tschernobyl vor 15 und vor 40 Jahren ernsthaft behauptet, Atomkraft sei eine sichere Zukunftstechnologie, blendet die Realität aus. Ein schwerer Unfall in Gösgen oder Leibstadt hätte katastrophale Folgen für die gesamte Nordwestschweiz, auch für Solothurn: kontaminierte Böden, kontaminiertes Trinkwasser, zerstörte Existenzen. Und trotzdem soll die Schweiz nun erneut Milliarden in diese Technologie investieren, die viel zu spät kommt, weil der Bau lange dauert, viel zu teuer ist und den Ausbau der erneuerbaren Energien ausbremst? 
+Neue AKW wären frühestens in Jahrzehnten betriebsbereit. Die Klimakrise und die Energiefrage lösen wir aber jetzt mit Solarenergie, Windkraft, Speichertechnologien, Effizienz, Suffizienz und einem intelligenten Stromnetz. Die Milliarden müssen wir in diese Lösungen investieren. Echte Versorgungssicherheit entsteht nicht durch zentrale Hochrisikoanlagen, sondern durch dezentrale, erneuerbare und demokratische Energieversorgung. Auch der Kanton Solothurn hat riesiges Potenzial bei Solarenergie auf Dächern, Fassaden und Infrastrukturen. Dieses Potenzial müssen wir endlich konsequent und besser nutzen und ja, auch auf Autobahnen, Herr Kollege Imark, wie das vorher genannt wurde. Die Sonne schickt nämlich keine radioaktive Rechnung an kommende Generationen. 
+Atomkraft hinterlässt indes ein Erbe für unzählige Generationen danach. Noch immer gibt es weltweit nämlich kein einziges Tiefenlager, das über Hunderttausende Jahre Sicherheit garantieren kann. Mit den Grünen durften wir einmal das Felslabor Mont Terri im Jura besichtigen, wo plastisch gezeigt wird, wie kompliziert es ist, ein solches Tiefenlager mit Opalinuston zu bauen. Es ist deshalb verantwortungslos, kommenden Generationen hochradioaktiven Abfall zu hinterlassen, weil man heute einfach diesen Weg gehen will. 
+Darum sage ich klar Nein zur Blackout-Initiative und zum Gegenvorschlag.
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">375762</t>
   </si>
   <si>
@@ -318,8 +340,8 @@
   </si>
   <si>
     <t xml:space="preserve">Comme l'a exposé de manière très exhaustive le rapporteur de la commission, il s'agit ici des mesures et des assainissements qui sont liés à la radioactivité d'origine naturelle. Le projet du Conseil fédéral prévoyait, par analogie aux mesures liées à la radioactivité d'origine anthropique, une base légale permettant de fixer des limites d'exposition à partir desquelles l'assainissement d'un site ou d'un bien-fonds serait obligatoire et de régler la prise en charge des coûts. Ici, on parle principalement de la pollution au radon. Vous savez qu'il est présent en Suisse de manière inégale, mais assez largement dans certaines régions, notamment dans l'Arc jurassien et l'Arc alpin. Concrètement - le rapporteur a également cité plusieurs chiffres -, 10 pour cent des bâtiments en Suisse dépassent le plafond d'exposition de 300 becquerels par mètre cube.
-Quels sont les risques de ces valeurs supérieures aux limites d'exposition ? Une étude a permis d'estimer que le radon est responsable d'environ 200 à 300 décès par an imputables au cancer du poumon, soit 8,3 pour cent du total des décès liés à ce cancer ; un chiffre qui n'est qu'une moyenne, puisqu'il peut aller jusqu'à 15 pour cent dans les cantons particulièrement exposés, comme mon canton, le canton du Jura, mais également le Tessin, par exemple. Ainsi, le radon représente la deuxième cause de cancer du poumon après la consommation de tabac. L'exposition au radon constitue donc un véritable enjeu de santé publique. Dès lors, si l'on renonce à une base légale pour la radioactivité d'origine naturelle, les cantons seraient considérablement freinés dans leur possibilité d'action dans ce domaine. Je rappelle qu'on parle notamment d'assainissements dans les écoles ou dans les jardins d'enfants, à savoir pour un groupe de population qui est particulièrement vulnérable.
-Le Conseil national a estimé que l'absence de dispositions légales suffisamment précises pour assurer l'assainissement des biens-fonds pollués risque d'affaiblir la pratique actuelle en matière de radioactivité naturelle et, en particulier, de protection de la population, et constitue à cet égard un signal négatif. Il a donc adopté une solution de compromis, avec ce nouvel article 24b, qui permet au Conseil fédéral de fixer le plafond d'exposition à partir duquel des mesures sont nécessaires. Par ailleurs, cet article règle la prise en charge des frais liés aux examens et aux assainissements, ce qui correspond aussi à la volonté des cantons. Ainsi, la version adoptée par le Conseil national est plus ciblée que le projet initial, mais elle permet à la fois au Conseil fédéral de fixer des valeurs de référence et ménage la possibilité d'agir des cantons.
+Quels sont les risques de ces valeurs supérieures aux limites d'exposition ? Une étude a permis d'estimer que le radon est responsable d'environ 200 à 300 décès par an imputables au cancer du poumon, soit 8,3 pour cent du total des décès liés à ce cancer ; un chiffre qui n'est qu'une moyenne, puisqu'il peut aller jusqu'à 15 pour cent dans les cantons particulièrement exposés, comme mon canton, le canton du Jura, mais également le Tessin, par exemple. Ainsi, le radon représente la deuxième cause de cancer du poumon après la consommation de tabac. L'exposition au radon constitue donc un véritable enjeu de santé publique. Dès lors, si l'on renonce à une base légale pour la radioactivité d'origine naturelle, les cantons seraient considérablement freinés dans leur possibilité d'action dans ce domaine. Je rappelle qu'on parle notamment d'assainissements dans les écoles ou dans les jardins d'enfants, à savoir pour un groupe de population particulièrement vulnérable.
+Le Conseil national a estimé que l'absence de dispositions légales suffisamment précises pour assurer l'assainissement des biens-fonds pollués risque d'affaiblir la pratique actuelle en matière de radioactivité naturelle et, en particulier, de protection de la population, et constitue à cet égard un signal négatif. Il a donc adopté une solution de compromis, avec ce nouvel article 24b, qui permet au Conseil fédéral de fixer le plafond d'exposition à partir duquel des mesures sont nécessaires. Par ailleurs, cet article règle la prise en charge des frais liés aux examens et aux assainissements, ce qui correspond aussi à la volonté des cantons. Ainsi, la version adoptée par le Conseil national est plus ciblée que le projet initial, mais elle permet au Conseil fédéral de fixer des valeurs de référence et ménage la possibilité d'agir des cantons.
 Il a été fait allusion au fait que, lors du premier examen de ce projet de loi par notre conseil, il n'y avait pas eu de proposition de minorité à ce sujet. Toutefois, le Conseil national a fait preuve de la sagesse qui, il nous semble, a fait défaut à notre conseil en refusant de garantir le bon déroulement des assainissements de bien-fonds, et il a donc adopté à l'unanimité ce nouvel article 24b. Dès lors, il nous a semblé pertinent de mener cette discussion également dans notre chambre. C'est pourquoi je vous invite à suivre le Conseil national et à clore ainsi cette divergence.
 </t>
   </si>
@@ -327,11 +349,11 @@
     <t xml:space="preserve">375759</t>
   </si>
   <si>
-    <t xml:space="preserve">Ici aussi, il s'agit de la poursuite de la croisade contre l'infraction pour négligence que mène notre conseil. On sait pourtant que si elles sont commises par négligence, les infractions qui sont définies à l'article 44 n'en sont pas pour autant négligeables. En effet, il peut s'agir d'exercer sans autorisation des activités qui, justement, sont soumises au régime de l'autorisation, ou de ne pas prendre les mesures nécessaires pour respecter les limites de dose. Il peut s'agir également de se s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ici aussi, il s'agit de la poursuite de la croisade contre l'infraction pour négligence que mène notre conseil. On sait pourtant que si elles sont commises par négligence, les infractions qui sont définies à l'article 44 n'en sont pas pour autant négligeables. En effet, il peut s'agir d'exercer sans autorisation des activités qui, justement, sont soumises au régime de l'autorisation, ou de ne pas prendre les mesures nécessaires pour respecter les limites de dose. Il peut s'agir également de se soustraire à la dosimétrie qui est prescrite. On parle donc de pratiques - qu'elles soient intentionnelles ou commises par négligence - qui mettent en danger la population en raison du domaine que l'on traite, qui est, je le rappelle quand même, les doses de radioactivité qui sont admises. 
-Ainsi, la proposition du Conseil national ne vise pas seulement à biffer purement et simplement l'infraction par négligence du projet de loi. Elle vise aussi à biffer le montant de l'amende qui était prévu jusqu'à présent, à savoir 20 000 francs. Pour qu'un délit ou un crime, selon la gravité de l'infraction poursuivie, soit pénalisé d'une amende de 20 000 francs, on ne parle pas d'un cas de bagatelle. Par ailleurs, la clause de minimis qui a été prévue à l'article 44 alinéa 4 permet de donner la marge de manoeuvre nécessaire pour éviter de poursuivre et de chicaner les personnes ou les entreprises qui se seraient réellement livrées à une infraction de peu de gravité par rapport à cette négligence. Cela crée également une forte asymétrie dans le texte de loi, puisque seule l'intention serait mentionnée à l'article 44. Dès lors, le risque serait évident que l'on plaide la négligence pour se soustraire à toute poursuite en cas d'infraction commise. La proposition qui vous est faite par le Conseil des États constitue un recul par rapport au droit en vigueur et en regard des enjeux en matière de santé publique et de protection de la population. Il est primordial de ne pas donner lieu à ce recul. 
+    <t xml:space="preserve">Ici aussi, il s'agit de la poursuite de la croisade contre l'infraction par négligence que mène notre conseil. On sait pourtant que si elles sont commises par négligence, les infractions qui sont définies à l'article 44 n'en sont pas pour autant négligeables. En effet, il peut s'agir d'exercer sans autorisation des activités qui, justement, sont soumises au régime de l'autorisation, ou de ne pas prendre les mesures nécessaires pour respecter les limites de dose. Il peut s'agir également de se so</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ici aussi, il s'agit de la poursuite de la croisade contre l'infraction par négligence que mène notre conseil. On sait pourtant que si elles sont commises par négligence, les infractions qui sont définies à l'article 44 n'en sont pas pour autant négligeables. En effet, il peut s'agir d'exercer sans autorisation des activités qui, justement, sont soumises au régime de l'autorisation, ou de ne pas prendre les mesures nécessaires pour respecter les limites de dose. Il peut s'agir également de se soustraire à la dosimétrie qui est prescrite. On parle donc de pratiques - qu'elles soient intentionnelles ou commises par négligence - qui mettent en danger la population en raison du domaine que l'on traite, qui est, je le rappelle quand même, les doses de radioactivité qui sont admises.
+Ainsi, la proposition de votre commission ne vise pas seulement à biffer purement et simplement l'infraction par négligence du projet de loi. Elle vise aussi à biffer le montant de l'amende qui était prévu jusqu'à présent, à savoir 20 000 francs. Pour qu'un délit ou un crime, selon la gravité de l'infraction poursuivie, soit pénalisé d'une amende de 20 000 francs, on ne parle pas d'un cas de bagatelle. Par ailleurs, la clause de minimis qui a été prévue à l'article 44 alinéa 4 permet de donner la marge de manoeuvre nécessaire pour éviter de poursuivre et de chicaner les personnes ou les entreprises qui auraient réellement commis une infraction de peu de gravité par négligence. Cela crée également une forte asymétrie dans le texte de loi, puisque seule l'intention serait mentionnée à l'article 44. Dès lors, le risque serait évident que l'on plaide la négligence pour se soustraire à toute poursuite en cas d'infraction commise. La proposition qui vous est faite par votre commission constitue un recul par rapport au droit en vigueur et en regard des enjeux en matière de santé publique et de protection de la population. Il est primordial de ne pas accepter ce recul.
 C'est pourquoi je vous invite, comme l'a fait le Conseil national, à maintenir la version du Conseil fédéral et à éliminer ainsi cette dernière divergence.
 </t>
   </si>
@@ -387,8 +409,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I18" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I19" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I19"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1154,30 +1176,30 @@
         <v>46181</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s">
         <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>46181</v>
@@ -1195,13 +1217,42 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Le canton du Jura a introduit un salaire minimum cantonal auquel les conventions collectives de travail de force obligatoire peuvent déroger. Vous avez évoqué dans votre intervention, Monsieur le conseiller national, le fait de vouloir redynamiser le partenariat social. Je peux vous dire que la réalité cantonale fait qu'il y a eu zéro convention collective de travail de plus et qu'on a dû introduire des contrats-types de travail dans le secteur de la vente ainsi que d'autres, actuellement en con</t>
   </si>
   <si>
-    <t xml:space="preserve">Le canton du Jura a introduit un salaire minimum cantonal auquel les conventions collectives de travail de force obligatoire peuvent déroger. Vous avez évoqué dans votre intervention, Monsieur le conseiller national, le fait de vouloir redynamiser le partenariat social. Je peux vous dire que la réalité cantonale fait qu'il y a eu zéro convention collective de travail de plus et qu'on a dû introduire des contrats-types de travail dans le secteur de la vente ainsi que d'autres, actuellement en consultation, dans celui de l'horlogerie. Pouvez-vous donc nous expliquer la notion visant à redynamiser le partenariat social en faisant fi des décisions populaires prises dans les cantons ?
+    <t xml:space="preserve">Le canton du Jura a introduit un salaire minimum cantonal auquel les conventions collectives de travail de force obligatoire peuvent déroger. Vous avez évoqué dans votre intervention, Monsieur le conseiller national, le fait de vouloir redynamiser le partenariat social. Je peux vous dire que la réalité cantonale fait qu'il y a eu zéro convention collective de travail de plus et qu'on a dû introduire des contrats-types de travail dans le secteur de la vente ainsi que d'autres, actuellement en consultation, dans celui de l'horlogerie. Pouvez-vous donc nous expliquer la notion visant à redynamiser le partenariat social en faisant fi des décisions populaires prises dans les cantons[NB]?
 </t>
   </si>
   <si>
@@ -104,7 +104,7 @@
   </si>
   <si>
     <t xml:space="preserve">Il existe des conventions collectives de travail dans le domaine du nettoyage. Il me semble que ces conventions, sauf erreur, sont plutôt négociées sur le plan régional ou cantonal.
-Prenons l'exemple d'une convention connue sur le plan national, celle qui concerne l'hôtellerie-restauration. Comment voulez-vous que le partenariat social puisse continuer de vivre pleinement et de jouer pleinement son rôle si, après de dures négociations entre associations d'employeurs et syndicats, et après avoir demandé au Conseil fédéral de rendre la convention collective obligatoire pour toute la branche de l'hôtellerie-restauration, on introduit un salaire minimum qui contourne l'un des éléments de la convention collective de travail ?
+Prenons l'exemple d'une convention connue sur le plan national, celle qui concerne l'hôtellerie-restauration. Comment voulez-vous que le partenariat social puisse continuer de vivre pleinement et de jouer pleinement son rôle si, après de dures négociations entre associations d'employeurs et syndicats, et après avoir demandé au Conseil fédéral de rendre la convention collective obligatoire pour toute la branche de l'hôtellerie-restauration, on introduit un salaire minimum qui contourne l'un des éléments de la convention collective de travail[NB]?
 La convention de l'hôtellerie et de la restauration concerne aussi le canton du Jura. Selon la majorité de la commission, en acceptant notre projet vous revivifiez le partenariat social, y compris dans le canton du Jura, puisque, dans ce canton, la convention nationale pour l'hôtellerie-restauration est également appliquée.
 </t>
   </si>
@@ -115,10 +115,10 @@
     <t xml:space="preserve">Crevoisier Crelier Mathilde</t>
   </si>
   <si>
-    <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique : à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36 108 francs contre 52 488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre femmes et</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique : à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36 108 francs contre 52 488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre femmes et hommes dans l'AVS est quasiment nulle. Cet écart ne diminue pas depuis plusieurs années. En comparaison internationale, la Suisse pointe à un peu reluisant cinquième rang des pays européens présentant les plus fortes différences de retraite entre les femmes et les hommes.
+    <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique[NB]: à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36 108 francs contre 52 488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre femmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique[NB]: à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36 108 francs contre 52 488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre femmes et hommes dans l'AVS est quasiment nulle. Cet écart ne diminue pas depuis plusieurs années. En comparaison internationale, la Suisse pointe à un peu reluisant cinquième rang des pays européens présentant les plus fortes différences de retraite entre les femmes et les hommes.
 Afin de combler ce fossé, la présente motion visait donc à tenir compte des lacunes de rente découlant des tâches éducatives et d'assistance, qui sont assumées majoritairement par les femmes au détriment de leur épargne-vieillesse, et d'introduire dans la loi sur la prévoyance professionnelle vieillesse, survivants et invalidité (LPP) le principe de la bonification, principe bien connu et reconnu, puisqu'il existe déjà dans l'AVS, comme l'a indiqué le rapporteur. Comme cela a été dit, cette motion s'inscrivait dans la série d'interventions déposées dans le sillage du refus de la révision de la LPP en 2024, interventions qui avaient toutes été renvoyées à la commission compétente et qui ont été retirées, que ce soit en commission ou aujourd'hui au conseil, au profit du postulat 26.3521 de la CSSS, que nous avons accepté tout à l'heure.
 Ainsi, vu les considérations avancées dans le postulat de la commission, qui refuse une approche isolée au profit d'une réflexion globale sur les améliorations possibles dans la LPP, et vu les arguments du Conseil fédéral, qui oeuvre d'ores et déjà à la nouvelle révision de la LPP et cherche, lui aussi, des solutions pour améliorer la prévoyance professionnelle des personnes travaillant à temps partiel ou ayant de faibles revenus, parmi lesquels les femmes sont justement surreprésentées, je me rallie au mouvement initié par d'autres auteurs de motions et retire la présente motion, dans l'espoir toutefois que les mesures de la prochaine réforme permettront enfin d'infléchir cet écart important qui n'a plus lieu d'être dans le système de rente moderne d'un pays prospère comme le nôtre.
 </t>
@@ -355,6 +355,34 @@
     <t xml:space="preserve">Ici aussi, il s'agit de la poursuite de la croisade contre l'infraction par négligence que mène notre conseil. On sait pourtant que si elles sont commises par négligence, les infractions qui sont définies à l'article 44 n'en sont pas pour autant négligeables. En effet, il peut s'agir d'exercer sans autorisation des activités qui, justement, sont soumises au régime de l'autorisation, ou de ne pas prendre les mesures nécessaires pour respecter les limites de dose. Il peut s'agir également de se soustraire à la dosimétrie qui est prescrite. On parle donc de pratiques - qu'elles soient intentionnelles ou commises par négligence - qui mettent en danger la population en raison du domaine que l'on traite, qui est, je le rappelle quand même, les doses de radioactivité qui sont admises.
 Ainsi, la proposition de votre commission ne vise pas seulement à biffer purement et simplement l'infraction par négligence du projet de loi. Elle vise aussi à biffer le montant de l'amende qui était prévu jusqu'à présent, à savoir 20 000 francs. Pour qu'un délit ou un crime, selon la gravité de l'infraction poursuivie, soit pénalisé d'une amende de 20 000 francs, on ne parle pas d'un cas de bagatelle. Par ailleurs, la clause de minimis qui a été prévue à l'article 44 alinéa 4 permet de donner la marge de manoeuvre nécessaire pour éviter de poursuivre et de chicaner les personnes ou les entreprises qui auraient réellement commis une infraction de peu de gravité par négligence. Cela crée également une forte asymétrie dans le texte de loi, puisque seule l'intention serait mentionnée à l'article 44. Dès lors, le risque serait évident que l'on plaide la négligence pour se soustraire à toute poursuite en cas d'infraction commise. La proposition qui vous est faite par votre commission constitue un recul par rapport au droit en vigueur et en regard des enjeux en matière de santé publique et de protection de la population. Il est primordial de ne pas accepter ce recul.
 C'est pourquoi je vous invite, comme l'a fait le Conseil national, à maintenir la version du Conseil fédéral et à éliminer ainsi cette dernière divergence.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il m'appartient de vous présenter un bref rapport de l'audition que la Commission de gestion a menée avec Mme la conseillère fédérale Karine Keller-Sutter, cheffe du Département fédéral des finances, lors de l'examen du rapport de gestion 2025 du Conseil fédéral. Je concentrerai mon propos sur les deux thèmes choisis par Mme la conseillère fédérale, à savoir la situation des finances fédérales et la réglementation bancaire.
+Premièrement, s'agissant des évolutions et perspectives du budget fédéra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il m'appartient de vous présenter un bref rapport de l'audition que la Commission de gestion a menée avec Mme la conseillère fédérale Karine Keller-Sutter, cheffe du Département fédéral des finances, lors de l'examen du rapport de gestion 2025 du Conseil fédéral. Je concentrerai mon propos sur les deux thèmes choisis par Mme la conseillère fédérale, à savoir la situation des finances fédérales et la réglementation bancaire.
+Premièrement, s'agissant des évolutions et perspectives du budget fédéral pour les années 2027 à 2029, il faut constater une détérioration initiale en 2027. Le budget de l'année 2027 tablait d'abord sur un équilibre, avant d'afficher un déficit structurel estimé entre 400 et 600 millions de francs. Ce recul découle des coupes parlementaires dans le programme de réexamen des tâches - ou Programme d'allègement budgétaire 2027 - ou de l'extension du programme européen Horizon par exemple. 
+Concernant les nouvelles charges, le budget de 2027 subit une aggravation supplémentaire de 400 millions de francs au niveau des dépenses, causée par des corrections d'estimations pour les assurances sociales et la migration. 
+Concernant la détente finale et la stabilisation, on relève que malgré ces hausses de dépenses, une nette embellie du côté des recettes permet d'anticiper une détente pour le budget de 2027. De plus, un équilibre structurel redevient possible pour 2028 et 2029, et l'année 2029 affiche un besoin de correction réduit à 300 millions de francs. 
+Concernant la fin du recours au compte extraordinaire, pour la première fois depuis la pandémie de COVID-19, le budget de 2027 ne sollicitera plus de dépenses extraordinaires. Les coûts liés à l'accueil des personnes en provenance d'Ukraine seront pleinement intégrés au budget ordinaire.
+Concernant la dynamique et les incertitudes du côté des recettes fiscales et la hausse marquée de l'impôt sur le bénéfice, les recettes provenant des entreprises connaissent une forte croissance à large échelle dans de nombreux cantons. L'impact du canton de Genève pèse positivement, de même qu'une forte concentration de rentrées fiscales à Lucerne, Zurich et Bâle-Ville, générées par un petit nombre de sociétés. 
+Concernant le flou autour de l'impôt complémentaire de l'OCDE - c'est un point sur lequel la Commission de gestion s'est déjà penchée plusieurs fois -, cet impôt représente une grande inconnue. La taxe nationale est perçue pour la première fois cette année, et la taxe internationale suivra en 2027.
+Toutefois, à titre de rappel, seuls 25 pour cent de ces recettes reviennent à la Confédération, le reste allant aux cantons. Les cantons prévoient des rendements inférieurs aux attentes, et aucun chiffre fiable ne sera disponible avant septembre.
+Concernant les effets différés de la valeur locative : l'abolition de la valeur locative n'entrera en vigueur qu'en 2029 et la baisse des recettes qui en découlera, d'environ 320 millions francs, ne se fera donc ressentir qu'à partir du budget 2030.
+Quant aux questions ou aux remarques qui sont parfois formulées sur la différence qu'il y a entre le budget et les comptes, Mme la conseillère fédérale nous a rappelé qu'à plusieurs reprises, notamment les trois dernières années, cette différence n'est que de l'ordre de 0,3 pour cent de l'ensemble des charges du budget de la Confédération.
+Concernant les grands défis et financements, notamment de l'armée, de l'AVS et de la recherche, j'aborde en premier lieu le financement de l'armée et de la sécurité. Pour faire progresser les dépenses militaires à 1 pour cent du PIB d'ici 2032, l'armée nécessite près de 3 milliards de francs supplémentaires par an. Le Conseil fédéral propose une hausse de la TVA, dont un tiers servira directement à combler ce besoin de financement dès 2028. Le Parlement étudie aussi d'autres pistes, comme la baisse temporaire de la part de l'impôt fédéral direct versé aux cantons. La mise en oeuvre de la 13e rente AVS, qui a été demandée par le peuple, représente une facture ouverte de 1 milliard de francs. Pour 2027, ce montant est compensé par des économies internes, mais son financement à long terme divise le Parlement, comme nous l'avons encore vu hier, entre un financement uniquement via la TVA ou combiné avec des pourcentages salariaux.
+Au sujet des pressions futures sur la recherche, des dépenses supplémentaires potentielles menacent le budget dès 2028, car la Commission européenne souhaite augmenter les budgets des programmes Horizon Europe et Erasmus.
+Concernant la marge de manoeuvre politique et les réformes structurelles, nous avons les mains liées face aux dépenses. La forte extension des dépenses restreint fortement la marge de manoeuvre de la Confédération. Pour retrouver une capacité d'action politique, le Conseil fédéral prône une stricte retenue sur les dépenses plutôt que de nouvelles hausses d'impôts. Concernant le dilemme des dépenses liées, le programme d'allègement budgétaire 2027 ciblait pour deux tiers des dépenses liées, à savoir des subventions. Pour dégager des moyens financiers massifs à l'avenir, la Suisse devra accepter des réformes structurelles profondes - relèvement de l'âge de la retraite, réduction de la part cantonale à l'impôt fédéral direct ou baisse de sa participation à la péréquation financière, soit des sujets qui risquent de fâcher, et pas seulement au Parlement.
+Concernant l'historique des mesures fiscales déjà prises, le Conseil fédéral rappelle avoir déjà sollicité la population avec la hausse de la TVA pour AVS 21, l'imposition de l'OCDE, l'augmentation de la taxe sur le tabac et la fin de l'allègement fiscal pour les voitures électriques.
+En résumé, la situation financière est en voie d'amélioration, mais un grand nombre d'inconnues ne facilitent pas la planification ni les prévisions. Toutes ces informations sont utiles à la Commission de gestion, même si celle-ci ne s'occupe pas en priorité des finances, mais bel et bien de gestion.
+Concernant la réglementation bancaire liée à la crise de Credit Suisse, les pressions des lobbies et le chantier législatif "too big to fail", le Département fédéral des finances a fait de cette réglementation sa priorité. Des travaux majeurs sont en cours, basés sur les propositions du Conseil fédéral, les motions parlementaires et les conclusions de la Commission d'enquête parlementaire , afin de combler les failles des banques d'importance systémique.
+Concernant le lobbying agressif et les pressions sur le Parlement, les parlementaires ont confié s'être sentis soumis à une pression intense et inconfortable de la part des lobbyistes craignant des sanctions financières, notamment la suppression de subventions pour leur parti s'ils soutenaient la réglementation bancaire. Ceci interpelle beaucoup la Commission de gestion.
+Concernant la tentative de déstabilisation des institutions - autre sujet extrêmement critique pour la Commission de gestion -, au-delà du cas de la presse où UBS a retiré ses publicités au journal "Finanz und Wirtschaft" en raison de sa ligne éditoriale, des manoeuvres ont été entreprises pour diviser le Conseil fédéral, à tel point que le gouvernement a exceptionnellement rendu public le fait que les choix qu'il a faits quant au projet de réglementation bancaire se sont faits à l'unanimité. Le Conseil fédéral est conscient qu'il évolue en terrain miné, mais il veut tenir le cap qu'il s'est fixé. Il transmettra bientôt ses propositions au Parlement, ce dont nous lui savons gré.
 </t>
   </si>
 </sst>
@@ -409,8 +437,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I19" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I20" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I20"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1255,6 +1283,35 @@
         <v>86</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -195,12 +195,12 @@
   </si>
   <si>
     <t xml:space="preserve">Le postulat Bally vise à réformer la valorisation fiscale des immeubles par les cantons en Suisse et, en réalité, à l'uniformiser sur le plan fédéral. Cette proposition avait plus de sens probablement avant la votation du 28 septembre 2025 sur la valeur locative, mais, maintenant que la valeur locative a été ou va être supprimée sur décision populaire, naturellement, la question de la valeur fiscale perd de son importance. Toutefois, elle ne perd pas complètement de son importance, puisqu'il reste quand même une valorisation fiscale, notamment au moment de taxer la fortune des citoyens.
-En Suisse, il y a une souveraineté cantonale, notamment en matière fiscale et les cantons restent libres d'imposer la méthode de calcul de la valorisation des immeubles qu'ils souhaitent. Il y a une certaine logique derrière cette approche. D'abord, on n'estime pas de la même manière un immeuble si l'on se trouve dans une région de montagne ou dans une région de plaine, en ville ou à la campagne. Finalement, il y a des choix politiques derrière ces méthodes d'évaluation. Si un franc vaut un franc partout dans le pays, un appartement n'est pas partout estimé de la même manière, son utilisation pouvant varier fortement. Puis, les cantons qui renoncent à une valorisation très haute des immeubles renoncent aussi à l'impôt qui va avec, et c'est un choix cantonal.
-En réalité le postulat qui vous est proposé ne vise naturellement pas à réduire la valorisation fiscale des immeubles ; ne vous y méprenez pas. Le postulat qui vous est proposé vise naturellement à uniformiser vers le haut la valeur des immeubles. C'est une hausse d'impôts que l'on vous propose ici ; une hausse de l'impôt sur la fortune pour tous les propriétaires de ce pays qui aboutit immanquablement à une augmentation des impôts et aussi à une diminution de l'attractivité du statut de propriétaire, que l'on devrait au contraire encourager.
-Pour toutes les familles de notre pays qui sont propriétaires, et il y en a un certain nombre, ces modifications peuvent avoir des impacts très forts sur leur fiche d'impôt, mais sur leur possibilité d'accéder notamment aux subsides des primes maladies. Il n'y a aucun besoin de faire cette réforme aujourd'hui, les cantons sont souverains et s'organisent très bien entre eux.
+En Suisse, il y a une souveraineté cantonale, notamment en matière fiscale, et les cantons restent libres d'imposer la méthode de calcul de la valorisation des immeubles qu'ils souhaitent. Il y a une certaine logique derrière cette approche. D'abord, on n'estime pas de la même manière un immeuble si l'on se trouve dans une région de montagne ou dans une région de plaine, en ville ou à la campagne. Finalement, il y a des choix politiques derrière ces méthodes d'évaluation. Si un franc vaut un franc partout dans le pays, un appartement n'est pas partout estimé de la même manière, son utilisation pouvant varier fortement. Puis, les cantons qui renoncent à une valorisation très haute des immeubles renoncent aussi à l'impôt qui va avec, et c'est un choix cantonal.
+En réalité, le postulat qui vous est proposé ne vise naturellement pas à réduire la valorisation fiscale des immeubles[NB]; ne vous y méprenez pas. Le postulat qui vous est proposé vise naturellement à uniformiser vers le haut la valeur des immeubles. C'est une hausse d'impôts que l'on vous propose ici[NB]; une hausse de l'impôt sur la fortune pour tous les propriétaires de ce pays, qui aboutit immanquablement à une augmentation des impôts et aussi à une diminution de l'attractivité du statut de propriétaire, que l'on devrait au contraire encourager.
+Pour toutes les familles de notre pays qui sont propriétaires, et il y en a un certain nombre, ces modifications peuvent avoir des impacts très forts sur leur fiche d'impôt, mais aussi sur leur possibilité d'accéder notamment aux subsides des primes maladies. Il n'y a aucun besoin de faire cette réforme aujourd'hui, les cantons sont souverains et s'organisent très bien entre eux.
 On vous dit qu'il ne s'agit que d'un postulat, mais ne vous y méprenez pas. Un postulat n'est jamais anodin. Nous allons, en acceptant ce postulat, confier à l'administration le soin d'analyser la situation. Il y aura un rapport et des propositions législatives. Lors de la prochaine réforme de la RPT qui, immanquablement, reviendra, l'administration proposera forcément d'uniformiser les valeurs locatives et la valorisation des immeubles entre les cantons.
-Je vous le dis franchement : nous nous battons contre toute forme de hausse d'impôts, nous ne voulons pas de nouveaux impôts. Même si vous les trouvez justes, Madame Bally, nous préférons des impôts bas injustes à des impôts élevés justes et, dans ces circonstances, nous préférons rejeter un postulat qui introduirait de nouveaux impôts qui vous paraissent justes plutôt que de modifier la loi dans ce sens. Aussi, j'aurais compris si la gauche avait proposé cette réforme, mais venant d'un parti, le Centre, fort dans des cantons qui ont des valorisations raisonnables, proposer cette réforme, c'est en réalité mettre un grain dans la machine qui fonctionne bien aujourd'hui.
-Pour cette raison, je vous invite et je m'adresse en particulier aux élus du Centre, à rejeter cette proposition qui aboutira, qu'on le veuille ou non, à une augmentation des impôts des citoyens.
+Je vous le dis franchement[NB]: nous nous battons contre toute forme de hausse d'impôts, nous ne voulons pas de nouveaux impôts. Même si vous les trouvez justes, Madame Bally, nous préférons des impôts bas injustes à des impôts élevés justes et, dans ces circonstances, nous préférons rejeter un postulat qui introduirait de nouveaux impôts qui vous paraissent justes plutôt que de modifier la loi dans ce sens. Aussi, j'aurais compris si la gauche avait proposé cette réforme, mais, venant d'un parti, le Centre, fort dans des cantons qui ont des valorisations raisonnables, proposer cette réforme, c'est en réalité mettre un grain dans la machine qui fonctionne bien aujourd'hui.
+Pour cette raison, je vous invite, et je m'adresse en particulier aux élus du Centre, à rejeter cette proposition qui aboutira, qu'on le veuille ou non, à une augmentation des impôts des citoyens.
 </t>
   </si>
   <si>
@@ -235,21 +235,21 @@
   </si>
   <si>
     <t xml:space="preserve">La Commission des finances recommande l'adoption des comptes 2025. Le groupe socialiste s'y associe sans réserve. Nous tenons en préambule à remercier l'Administration fédérale des finances pour la qualité de ses travaux et son précieux soutien dans l'accomplissement de notre travail.
-Les comptes sont bons. Le frein à l'endettement est respecté, et même largement respecté. Le frein à l'endettement autorisait un déficit de 262 millions de francs. Le compte ordinaire boucle sur un excédent de 1,185 milliard de francs. Les recettes ont progressé de 4,3 pour cent, les dépenses de 2 pour cent seulement. La Confédération finance la totalité de ses investissements par ses propres moyens sans recourir à l'endettement. La dette nette recule à 16,1 pour cent du PIB et le compte de résultat dépasse largement ce qui était prévu au budget. Ce sont des chiffres solides. Ils méritent d'être posés clairement parce qu'ils contrastent singulièrement avec le tableau qui nous était brossé lors des débats budgétaires récents. Il y a, en effet, quelque chose de troublant dans la séquence que ce Parlement rejoue session après session. À l'automne, la situation financière est décrite comme tendue, contrainte, au bord du déséquilibre, voire pire. Des coupes sont décidées dans les politiques sociales, dans les services publics. Ces choix sont présentés non pas comme des choix, mais comme des nécessités, comme si la comptabilité avait décidé à la place de la politique. Et puis viennent les comptes, et les comptes racontent une autre histoire. On répondra légitimement que le résultat de cette année doit une partie de son éclat à des recettes extraordinaires non reconductibles. C'est exact et ce n'est pas contesté. Mais ce qui n'a rien d'extraordinaire, ce qui, au contraire, est d'une banalité répétitive et prévisible, c'est le schéma lui-même, les prophéties pessimistes de l'automne, les sacrifices qu'elles commandent et les comptes, quelques mois plus tard, qui en révèlent l'exagération. Lorsque l'erreur va systématiquement dans le même sens, elle cesse d'être une erreur, elle devient une méthode. Une méthode qui n'est pas sans conséquences. Derrière chaque décision budgétaire, il y a des réalités concrètes : des familles qui voient leurs prestations diminuer, des cantons qui compensent ce que la Confédération ne finance plus, des régions périphériques dont la cohésion repose sur des services publics que l'on réduit année après année. La méthode voulue par la majorité de notre conseil a un prix, et ce sont toujours les mêmes qui le payent. 
-Le groupe socialiste approuve ces comptes et il sera présent cet automne lorsque s'ouvrira le débat sur le budget 2027, lorsqu'immanquablement les mêmes voix expliqueront que la situation est tendue, que les marges sont inexistantes, qu'il n'y a pas d'autres issues que de couper encore dans les mêmes politiques, sur le dos des mêmes personnes. Ce Parlement a le droit d'assumer ses choix, mais qu'il les assume pour ce qu'ils sont, des choix politiques portés par une majorité, avec des conséquences assumées, et non pas des fatalités déguisées en équations budgétaires. Sous prétexte du "mieux d'État", c'est surtout le "moins d'État" qui est souhaité. En politique, il y a toujours le choix ; la question est de savoir qui le supporte. 
+Les comptes sont bons. Le frein à l'endettement est respecté, et même largement respecté. Le frein à l'endettement autorisait un déficit de 262 millions de francs. Le compte ordinaire boucle sur un excédent de 1,185 milliard de francs. Les recettes ont progressé de 4,3 pour cent, les dépenses de 2 pour cent seulement. La Confédération finance la totalité de ses investissements par ses propres moyens sans recourir à l'endettement. La dette nette recule à 16,1 pour cent du PIB et le compte de résultat dépasse largement ce qui était prévu au budget. Ce sont des chiffres solides. Ils méritent d'être posés clairement, parce qu'ils contrastent singulièrement avec le tableau qui nous était brossé lors des débats budgétaires récents. Il y a, en effet, quelque chose de troublant dans la séquence que ce Parlement rejoue session après session. À l'automne, la situation financière est décrite comme tendue, contrainte, au bord du déséquilibre, voire pire. Des coupes sont décidées dans les politiques sociales, dans les services publics. Ces choix sont présentés non pas comme des choix, mais comme des nécessités, comme si la comptabilité avait décidé à la place de la politique. Et puis viennent les comptes, et les comptes racontent une autre histoire. On répondra légitimement que le résultat de cette année doit une partie de son éclat à des recettes extraordinaires non reconductibles. C'est exact et ce n'est pas contesté. Mais ce qui n'a rien d'extraordinaire, ce qui, au contraire, est d'une banalité répétitive et prévisible, c'est le schéma lui-même[NB]: les prophéties pessimistes de l'automne, les sacrifices qu'elles commandent et les comptes, quelques mois plus tard, qui en révèlent l'exagération. Lorsque l'erreur va systématiquement dans le même sens, elle cesse d'être une erreur, elle devient une méthode, une méthode qui n'est pas sans conséquences. Derrière chaque décision budgétaire, il y a des réalités concrètes[NB]: des familles qui voient leurs prestations diminuer, des cantons qui compensent ce que la Confédération ne finance plus, des régions périphériques dont la cohésion repose sur des services publics que l'on réduit année après année. La méthode voulue par la majorité de notre conseil a un prix, et ce sont toujours les mêmes qui le payent. 
+Le groupe socialiste approuve ces comptes et il sera présent cet automne lorsque s'ouvrira le débat sur le budget 2027, lorsqu'immanquablement les mêmes voix expliqueront que la situation est tendue, que les marges sont inexistantes, qu'il n'y a pas d'autre issue que de couper encore dans les mêmes politiques, sur le dos des mêmes personnes. Ce Parlement a le droit d'assumer ses choix, mais qu'il les assume pour ce qu'ils sont, des choix politiques portés par une majorité, avec des conséquences assumées, et non pas des fatalités déguisées en équations budgétaires. Sous prétexte du "mieux d'État", c'est surtout le "moins d'État" qui est souhaité. En politique, il y a toujours le choix[NB]; la question est de savoir qui le supporte. 
 </t>
   </si>
   <si>
     <t xml:space="preserve">374817</t>
   </si>
   <si>
-    <t xml:space="preserve">Commençons par un constat sans appel : la violence sexiste et sexuelle est un fléau qui n'épargne pas notre pays, comme l'a encore rappelé hier le Conseil fédéral en lançant la deuxième phase de sa campagne contre la violence domestique. En 2025, la police a enregistré 22 000 infractions dues à la violence domestique, un chiffre dont on sait qu'il ne constitue que la partie émergée de l'iceberg et cache une sombre réalité dans laquelle un nombre encore plus élevé de cas n'entrera jamais dans les</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commençons par un constat sans appel : la violence sexiste et sexuelle est un fléau qui n'épargne pas notre pays, comme l'a encore rappelé hier le Conseil fédéral en lançant la deuxième phase de sa campagne contre la violence domestique. En 2025, la police a enregistré 22 000 infractions dues à la violence domestique, un chiffre dont on sait qu'il ne constitue que la partie émergée de l'iceberg et cache une sombre réalité dans laquelle un nombre encore plus élevé de cas n'entrera jamais dans les statistiques de la criminalité. En effet, l'accès à la justice des victimes de violence sexiste, sexuelle et de violence domestique est encore semé d'embûches. Parmi celles-ci, la prise en charge des victimes par les autorités de procédure pénale, soit la police, les ministères publics et les tribunaux, est souvent pointée du doigt comme un facteur de renoncement pour les victimes à poursuivre la procédure. En cause, on peut mentionner notamment un manque de sensibilité dans l'accueil, la prise en charge et l'audition des victimes avec un risque important de victimisation secondaire pour ces dernières.
+    <t xml:space="preserve">Commençons par un constat sans appel[NB]: la violence sexiste et sexuelle est un fléau qui n'épargne pas notre pays, comme l'a encore rappelé hier le Conseil fédéral, en lançant la deuxième phase de sa campagne contre la violence domestique. En 2025, la police a enregistré 22 000 infractions dues à la violence domestique, un chiffre dont on sait qu'il ne constitue que la partie émergée de l'iceberg et cache une sombre réalité dans laquelle un nombre encore plus élevé de cas n'entrera jamais dans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commençons par un constat sans appel[NB]: la violence sexiste et sexuelle est un fléau qui n'épargne pas notre pays, comme l'a encore rappelé hier le Conseil fédéral, en lançant la deuxième phase de sa campagne contre la violence domestique. En 2025, la police a enregistré 22 000 infractions dues à la violence domestique, un chiffre dont on sait qu'il ne constitue que la partie émergée de l'iceberg et cache une sombre réalité dans laquelle un nombre encore plus élevé de cas n'entrera jamais dans les statistiques de la criminalité. En effet, l'accès à la justice des victimes de violence sexiste, sexuelle et de violence domestique est encore semé d'embûches. Parmi celles-ci, la prise en charge des victimes par les autorités de procédure pénale, soit la police, les ministères publics et les tribunaux, est souvent pointée du doigt comme un facteur de renoncement pour les victimes à poursuivre la procédure. En cause, on peut mentionner notamment un manque de sensibilité dans l'accueil, la prise en charge et l'audition des victimes, avec un risque important de victimisation secondaire pour ces dernières.
 Ainsi, la motion de la Commission des affaires juridiques du Conseil national, "Modification du code de procédure pénale concernant la formation initiale et continue des autorités pénales", vise donc à améliorer cette formation de manière à améliorer l'accès à la justice pour les victimes. Elle se base sur le rapport du Conseil fédéral de 2025, donnant suite au postulat Fehlmann Rielle 21.4215.
-Vous l'avez entendu, la majorité de la commission rejette la motion au motif de la répartition des compétences. Effectivement, les cantons sont responsables de la formation initiale et continue des autorités de poursuite pénale, mais le prétexte du fédéralisme ne saurait nous prémunir d'examiner si nous remplissons nos propres obligations. Que les cantons soient tenus d'assurer la formation continue et initiale, y compris en vertu de l'article 15 de la Convention d'Istanbul, ne signifie pas encore toutefois que celle-ci soit assurée. Or, aujourd'hui, on constate que la mise en oeuvre est, sinon lacunaire, encore inégale. Le rapport de 2022 d'évaluation du Groupe d'experts sur la lutte contre la violence à l'égard des femmes et la violence domestique (Grevio) déplore que la Suisse n'ait toujours pas de programme de formation standardisé dans le domaine de la violence sexuelle pour la police, et que celle-ci soit facultative pour les services judiciaires. Le Grevio encourage vivement les autorités suisses à prendre des mesures afin de veiller à dispenser une formation initiale et continue systématique et obligatoire aux professionnels en lien avec les victimes et les auteurs de toutes les formes de violence visées par la Convention d'Istanbul. Ainsi, si l'argument de la compétence cantonale doit évidemment être pris en compte, il doit aussi être soigneusement sous-pesé en regard de nos responsabilités à l'échelon fédéral.
-Dans le cadre de la réponse au postulat précité, la Confédération a commandé un avis de droit qui conclut que la Confédération dispose d'une marge de manoeuvre en vertu de l'article 123 de la Constitution qui règle la compétence fédérale en matière de droit pénal et de droit de procédure pénale, lorsqu'il s'agit de garantir l'exécution uniforme du droit fédéral, ainsi que la mise en oeuvre du droit international. Or, ces deux conditions sont remplies. D'une part, aujourd'hui, malgré les efforts d'uniformisation consentis par les cantons, force est de constater que la formation des autorités de poursuite pénale est encore trop fragmentée pour assurer l'égalité de traitement des victimes dans l'ensemble du pays et que si la formation initiale de la police est désormais généralisée, celle des ministères publics reste encore lacunaire. D'ailleurs, bien que le Conseil fédéral propose lui aussi de rejeter la motion, il admet qu'il reste des efforts à accomplir, par exemple dans l'audition des victimes ou encore au niveau de la coopération interdisciplinaire et de la formation initiale et continue des acteurs. D'autre part, une intervention de la Confédération au titre de l'article 123 de la Constitution se justifie également par l'obligation qui nous est faite en vertu de l'article 15 de la Convention d'Istanbul de garantir la formation des professionnels. Dès lors, rejeter la présente motion, comme le propose la majorité de la commission, ne relève pas du simple respect des compétences cantonales, mais bien d'une appréciation politique. Or, il faut admettre que la situation actuelle en matière de prise en charge des victimes ne permet ni de garantir l'exécution uniforme du droit ni de remplir nos obligations internationales. C'est également la conclusion à laquelle est parvenu le Conseil national, par 127 voix contre 63 et 1 abstention, soit l'intégralité des groupes parlementaires à une exception près.
+Vous l'avez entendu, la majorité de la commission rejette la motion au motif de la répartition des compétences. Effectivement, les cantons sont responsables de la formation initiale et continue des autorités de poursuite pénale, mais le prétexte du fédéralisme ne saurait nous prémunir d'examiner si nous remplissons nos propres obligations. Que les cantons soient tenus d'assurer la formation continue et initiale, y compris en vertu de l'article 15 de la Convention d'Istanbul, ne signifie pas encore, toutefois, que celle-ci soit assurée. Or, aujourd'hui, on constate que la mise en oeuvre est, sinon lacunaire, encore inégale. Le rapport de 2022 d'évaluation du Groupe d'experts sur la lutte contre la violence à l'égard des femmes et la violence domestique (Grevio) déplore que la Suisse n'ait toujours pas de programme de formation standardisé dans le domaine de la violence sexuelle pour la police, et que celle-ci soit facultative pour les services judiciaires. Le Grevio encourage vivement les autorités suisses à prendre des mesures afin de veiller à dispenser une formation initiale et continue systématique et obligatoire aux professionnels en lien avec les victimes et les auteurs de toutes les formes de violence visées par la Convention d'Istanbul. Ainsi, si l'argument de la compétence cantonale doit évidemment être pris en compte, il doit aussi être soigneusement sous-pesé en regard de nos responsabilités à l'échelon fédéral.
+Dans le cadre de la réponse au postulat précité, la Confédération a commandé un avis de droit qui conclut qu'elle dispose d'une marge de manoeuvre en vertu de l'article 123 de la Constitution qui règle la compétence fédérale en matière de droit pénal et de droit de procédure pénale, lorsqu'il s'agit de garantir l'exécution uniforme du droit fédéral, ainsi que la mise en oeuvre du droit international. Or, ces deux conditions sont remplies. D'une part, aujourd'hui, malgré les efforts d'uniformisation consentis par les cantons, force est de constater que la formation des autorités de poursuite pénale est encore trop fragmentée pour assurer l'égalité de traitement des victimes dans l'ensemble du pays, et que si la formation initiale de la police est désormais généralisée, celle des ministères publics reste encore lacunaire. D'ailleurs, bien que le Conseil fédéral propose lui aussi de rejeter la motion, il admet qu'il reste des efforts à accomplir, par exemple concernant l'audition des victimes ou encore au niveau de la coopération interdisciplinaire et de la formation initiale et continue des acteurs. D'autre part, une intervention de la Confédération au titre de l'article 123 de la Constitution se justifie également par l'obligation qui nous est faite, en vertu de l'article 15 de la Convention d'Istanbul, de garantir la formation des professionnels. Dès lors, rejeter la présente motion, comme le propose la majorité de la commission, ne relève pas du simple respect des compétences cantonales, mais bien d'une appréciation politique. Or, il faut admettre que la situation actuelle en matière de prise en charge des victimes ne permet ni de garantir l'exécution uniforme du droit ni de remplir nos obligations internationales. C'est également la conclusion à laquelle est parvenu le Conseil national, par 127 voix contre 63 et 1 abstention, soit l'intégralité des groupes parlementaires, à une exception près.
 Il a été dit en commission que nous nous rendrions risibles en adoptant cette motion. Le ridicule ne tue pas, contrairement à la violence sexiste et sexuelle qui fait encore et toujours une victime toutes les deux semaines dans notre pays.
 Dans l'intérêt des victimes, mais aussi des autorités chargées de les accompagner dans la procédure pénale, je vous invite à suivre la minorité de la commission et à adopter la motion.
 </t>
@@ -361,11 +361,11 @@
     <t xml:space="preserve">376044</t>
   </si>
   <si>
-    <t xml:space="preserve">Il m'appartient de vous présenter un bref rapport de l'audition que la Commission de gestion a menée avec Mme la conseillère fédérale Karine Keller-Sutter, cheffe du Département fédéral des finances, lors de l'examen du rapport de gestion 2025 du Conseil fédéral. Je concentrerai mon propos sur les deux thèmes choisis par Mme la conseillère fédérale, à savoir la situation des finances fédérales et la réglementation bancaire.
-Premièrement, s'agissant des évolutions et perspectives du budget fédéra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Il m'appartient de vous présenter un bref rapport de l'audition que la Commission de gestion a menée avec Mme la conseillère fédérale Karine Keller-Sutter, cheffe du Département fédéral des finances, lors de l'examen du rapport de gestion 2025 du Conseil fédéral. Je concentrerai mon propos sur les deux thèmes choisis par Mme la conseillère fédérale, à savoir la situation des finances fédérales et la réglementation bancaire.
+    <t xml:space="preserve">Il m'appartient de vous présenter un bref rapport de l'audition que la Commission de gestion a menée avec Mme la conseillère fédérale Karin Keller-Sutter, cheffe du Département fédéral des finances, lors de l'examen du rapport de gestion 2025 du Conseil fédéral. Je concentrerai mon propos sur les deux thèmes choisis par Mme la conseillère fédérale, à savoir la situation des finances fédérales et la réglementation bancaire.
+Premièrement, s'agissant des évolutions et perspectives du budget fédéral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il m'appartient de vous présenter un bref rapport de l'audition que la Commission de gestion a menée avec Mme la conseillère fédérale Karin Keller-Sutter, cheffe du Département fédéral des finances, lors de l'examen du rapport de gestion 2025 du Conseil fédéral. Je concentrerai mon propos sur les deux thèmes choisis par Mme la conseillère fédérale, à savoir la situation des finances fédérales et la réglementation bancaire.
 Premièrement, s'agissant des évolutions et perspectives du budget fédéral pour les années 2027 à 2029, il faut constater une détérioration initiale en 2027. Le budget de l'année 2027 tablait d'abord sur un équilibre, avant d'afficher un déficit structurel estimé entre 400 et 600 millions de francs. Ce recul découle des coupes parlementaires dans le programme de réexamen des tâches - ou Programme d'allègement budgétaire 2027 - ou de l'extension du programme européen Horizon par exemple. 
 Concernant les nouvelles charges, le budget de 2027 subit une aggravation supplémentaire de 400 millions de francs au niveau des dépenses, causée par des corrections d'estimations pour les assurances sociales et la migration. 
 Concernant la détente finale et la stabilisation, on relève que malgré ces hausses de dépenses, une nette embellie du côté des recettes permet d'anticiper une détente pour le budget de 2027. De plus, un équilibre structurel redevient possible pour 2028 et 2029, et l'année 2029 affiche un besoin de correction réduit à 300 millions de francs. 
@@ -383,6 +383,69 @@
 Concernant la réglementation bancaire liée à la crise de Credit Suisse, les pressions des lobbies et le chantier législatif "too big to fail", le Département fédéral des finances a fait de cette réglementation sa priorité. Des travaux majeurs sont en cours, basés sur les propositions du Conseil fédéral, les motions parlementaires et les conclusions de la Commission d'enquête parlementaire , afin de combler les failles des banques d'importance systémique.
 Concernant le lobbying agressif et les pressions sur le Parlement, les parlementaires ont confié s'être sentis soumis à une pression intense et inconfortable de la part des lobbyistes craignant des sanctions financières, notamment la suppression de subventions pour leur parti s'ils soutenaient la réglementation bancaire. Ceci interpelle beaucoup la Commission de gestion.
 Concernant la tentative de déstabilisation des institutions - autre sujet extrêmement critique pour la Commission de gestion -, au-delà du cas de la presse où UBS a retiré ses publicités au journal "Finanz und Wirtschaft" en raison de sa ligne éditoriale, des manoeuvres ont été entreprises pour diviser le Conseil fédéral, à tel point que le gouvernement a exceptionnellement rendu public le fait que les choix qu'il a faits quant au projet de réglementation bancaire se sont faits à l'unanimité. Le Conseil fédéral est conscient qu'il évolue en terrain miné, mais il veut tenir le cap qu'il s'est fixé. Il transmettra bientôt ses propositions au Parlement, ce dont nous lui savons gré.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amoos Emmanuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans son ensemble, le groupe socialiste accueille favorablement cette révision de la LDFR, qui renforce plusieurs principes fondamentaux que nous défendons depuis longtemps : la protection des terres agricoles contre la spéculation, la pérennisation de l'exploitation à titre personnel et une meilleure reconnaissance des réalités sociales du monde agricole. Le projet corrige certaines inégalités lors des successions, des ventes d'exploitations ou des séparations, en particulier au détriment des é</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans son ensemble, le groupe socialiste accueille favorablement cette révision de la LDFR, qui renforce plusieurs principes fondamentaux que nous défendons depuis longtemps : la protection des terres agricoles contre la spéculation, la pérennisation de l'exploitation à titre personnel et une meilleure reconnaissance des réalités sociales du monde agricole. Le projet corrige certaines inégalités lors des successions, des ventes d'exploitations ou des séparations, en particulier au détriment des épouses et des veuves.
+Cette révision répond également à une réalité qu'il ne faut pas ignorer : les femmes restent largement sous-représentées à la tête des exploitations agricoles. En Suisse, seules 7,2 pour cent des exploitations sont dirigées par des femmes, un taux parmi les plus faibles d'Europe. Cette situation n'est pas le fruit du hasard, mais le résultat de mécanismes structurels qui continuent de limiter l'accès des femmes, en particulier des filles d'agriculteurs, aux terres, aux exploitations et au patrimoine agricole. De nombreuses études ont montré que les mécanismes de transmission du patrimoine agricole, combinés à des rôles de genre encore très marqués, conduisent à une forte concentration des terres, des bâtiments et des entreprises agricoles entre les mains d'un nombre restreint d'hommes. Les filles d'agriculteurs sont encore trop souvent écartées de la reprise des exploitations ou contraintes de renoncer à une part importante de leur héritage. Toute avancée qui favorise une plus grande équité dans la transmission des exploitations mérite donc d'être saluée.
+Si nous soutenons le projet, nous estimons toutefois que certains ajustements sont encore nécessaires pour mieux atteindre les objectifs de la loi. Les minorités que nous proposons s'inscrivent dans cet esprit. Il s'agit de renforcer la protection de la propriété foncière agricole, favoriser la transmission des exploitations, tout particulièrement aux femmes, et préserver une agriculture familiale vivante, diversifiée et accessible aux générations futures.
+À l'article 9 alinéa 3, nous proposons d'ajouter que toutes les parts sociales de la société de capitaux doivent être détenues par des personnes physiques domiciliées en Suisse. Cette exigence est proportionnée et cohérente avec les objectifs mêmes de la révision. Si nous acceptons que l'exploitation à titre personnel puisse être exercée sous la forme d'une société de capitaux, nous devons également nous assurer que cette ouverture ne crée pas une voie détournée permettant une prise de contrôle, même partielle ou indirecte, de nos terres agricoles par des intérêts étrangers. Les terres agricoles constituent une ressource stratégique pour notre pays. Dans ce contexte, il est légitime d'exiger que les propriétaires des sociétés bénéficiant de ce régime particulier entretiennent un lien réel et durable avec la Suisse.
+À l'article 60 alinéa 1 lettre j, avec ma minorité, nous proposons de tenir compte de la possibilité de construire des bâtiments manquants, nécessaires à l'exploitation, ou de transformer, rénover ou remplacer ceux qui existent, lorsque l'exploitation permet d'assumer les dépenses correspondantes. La rédaction actuelle ne prend en considération que les bâtiments existants pour déterminer si une entreprise agricole peut être divisée. Cette approche est excessivement rigide et risque de freiner inutilement la transmission et le renouvellement des structures agricoles. Si nous voulons maintenir une agriculture familiale dynamique et une population paysanne forte, nous devons accepter que certaines grandes exploitations puissent être partagées entre plusieurs repreneurs lorsque cela est économiquement viable. Sans mécanisme de ce type, l'évolution se fera inévitablement vers des exploitations toujours plus grandes et toujours moins nombreuses. C'est aussi un aspect déterminant si nous voulons que plus de femmes puissent reprendre des exploitations.
+Je vous demande également de soutenir ma minorité à l'article 60 alinéa 2 lettre a. La législation actuelle prévoit déjà des exceptions à l'interdiction du partage matériel lorsqu'il s'agit d'améliorer les structures d'autres entreprises agricoles. En revanche, elle offre peu de souplesse lorsqu'une entreprise existante, notamment de grande taille, ne trouve pas de repreneur et pourrait pourtant être transmise plus facilement après une division adaptée de ses structures.
+Cette modification contribue à favoriser la transmission des exploitations, tout en maintenant des garde-fous clairs contre les partages injustifiés.
+Ma minorité propose encore d'abroger l'article 66 alinéa 2. L'un des objectifs fondamentaux du droit foncier rural est de lutter contre la hausse excessive des prix des terres agricoles et de maintenir ceux-ci à un niveau compatible avec leur exploitation. Or, aujourd'hui, la loi considère déjà qu'un prix est surfait lorsqu'il dépasse de plus de 5 pour cent les valeurs usuelles de la région. Permettre aux cantons de porter cette marge à 15 pour cent affaiblit considérablement ce garde-fou. Dans le contexte actuel, cette souplesse n'apparaît plus justifiée. Les prix du foncier agricole connaissent à nouveau une tendance à la hausse dans plusieurs régions. Dans le canton du Jura, par exemple, les prix ont progressé durant sept années consécutives jusqu'en 2023. La suppression de cette dérogation cantonale constitue une mesure simple, cohérente et efficace pour limiter les risques de spirale haussière. Elle renforce l'application uniforme de la loi et contribue à préserver l'accès à la terre pour les agricultrices et les agriculteurs qui souhaitent exploiter eux-mêmes leur domaine. Un seuil unique à l'échelle nationale évite également les distorsions entre cantons et garantit une application plus prévisible du droit.
+Le groupe socialiste soutiendra l'entrée en matière et la révision dans son ensemble, tout en vous invitant à suivre les minorités que nous avons déposées, ainsi que les minorités Bertschy et II (Michaud Gigon), afin de renforcer encore la protection du foncier agricole et les perspectives de transmission des exploitations.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je me permets de prendre la parole puisque je ne figure pas nommément dans cette minorité, mais que je la soutiens également. Je ne vais pas répéter ce qu'a dit M. Rieder. Simplement, je tiens à rappeler que le principe de ligne aérienne a été retiré du projet à la suite de la consultation. Je me permets de citer le message du Conseil fédéral : "Le principe de la ligne aérienne, contenu initialement, était particulièrement contesté et a été retiré du projet. Son maintien aurait entraîné une augm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je me permets de prendre la parole puisque je ne figure pas nommément dans cette minorité, mais que je la soutiens également. Je ne vais pas répéter ce qu'a dit M. Rieder. Simplement, je tiens à rappeler que le principe de ligne aérienne a été retiré du projet à la suite de la consultation. Je me permets de citer le message du Conseil fédéral : "Le principe de la ligne aérienne, contenu initialement, était particulièrement contesté et a été retiré du projet. Son maintien aurait entraîné une augmentation importante du nombre d'exceptions, ce qui aurait réduit à néant l'effet d'accélération recherché." Introduire cette primauté de la ligne aérienne aura donc probablement pour effet de ralentir les procédures plutôt que de les accélérer.
+Je me permets également de rappeler les risques sécuritaires qui peuvent concerner les lignes aériennes. On parle beaucoup de sécurité en ce moment. On renforce les moyens de l'armée. On parle d'attaques éventuelles. Les lignes électriques sont un point stratégique d'une infrastructure nationale. Si elles ne sont pas enterrées, elles sont évidemment plus vulnérables. C'est également un point que l'on peut prendre en considération dans les réflexions.
+La proposition vise simplement à établir ou à rétablir une forme de neutralité ou du moins à envisager sérieusement l'enterrement des lignes. Évidemment, les considérations environnementales entrent aussi en ligne de compte, mais également celles d'aménagement du territoire. Je rappelle quand même qu'on est sur un territoire petit, que des conflits d'utilisation sont nombreux et qu'une ligne à haute tension prend de la place. Cela touche évidemment les zones à bâtir, mais on peut également imaginer que cela interfère avec des infrastructures routières, par exemple. Dès lors, il peut être d'un intérêt, pour de multiples raisons très diversifiées, de considérer sérieusement l'enterrement des lignes à haute tension. 
+C'est pourquoi je vous invite à revenir sur cette décision du Conseil national en adoptant la minorité Rieder, afin d'offrir de meilleures chances aux lignes souterraines lorsqu'elles sont pertinentes.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme l'a dit le rapporteur, cet article 15bbis est un peu le coeur du projet. C'est un des vecteurs qui permettra de réaliser l'accélération des projets d'extension du réseau électrique. Dans ce sens, il s'agit de le concevoir de manière adéquate et aussi équilibrée. Vous voyez que le projet du Conseil fédéral prévoit que les projets d'assainissement ou de remplacement des lignes à haute tension égale ou supérieure à 220 kilovolts - il s'agit donc du réseau de transport à très haute tension - p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme l'a dit le rapporteur, cet article 15bbis est un peu le coeur du projet. C'est un des vecteurs qui permettra de réaliser l'accélération des projets d'extension du réseau électrique. Dans ce sens, il s'agit de le concevoir de manière adéquate et aussi équilibrée. Vous voyez que le projet du Conseil fédéral prévoit que les projets d'assainissement ou de remplacement des lignes à haute tension égale ou supérieure à 220 kilovolts - il s'agit donc du réseau de transport à très haute tension - puissent être réalisés sur le tracé existant ou dans la zone qui le jouxte immédiatement. Il s'agit donc déjà d'une amélioration, d'une accélération, puisqu'il ne serait plus nécessaire de repasser par une procédure pour opérer ces travaux. Maintenant, la commission de notre conseil vous propose à l'alinéa 1 d'élargir cette possibilité jusqu'au réseau de 36 kilovolts. Cela inclut donc le niveau de réseau 3, à savoir le réseau à haute tension. Cette disposition concerne donc, en tout, pour le réseau à très haute tension, environ 6000 kilomètres de lignes, et pour le réseau à haute tension, 16 000 kilomètres de lignes. Ce sont déjà, avec la disposition telle qu'elle est prévue à l'alinéa 1, 22 000 kilomètres de lignes qui sont concernées par cette facilitation.
+À l'alinéa 3, qui fait l'objet de ma minorité, la majorité de la commission a décidé d'élargir encore les possibilités, puisqu'elle propose de ne pas tenir compte des distances légales par rapport aux forêts et aux cours d'eau et donc de prévoir que les projets d'assainissement, d'extension ou de remplacement de lignes puissent être réalisés à des distances réduites par rapport aux forêts et aux cours d'eau. Avec cela, on franchit ce point d'équilibre qui doit être maintenu.
+Je vous rappelle que nous avons une discussion qui est similaire à celle concernant le projet de loi pour l'accélération des procédures que nous avons menée l'année passée et qui a attaqué également le droit de recours - on va y revenir. Il est important de maintenir une forme d'équilibre de manière à protéger les intérêts de l'environnement et aussi à éviter de créer une disposition qui est trop déséquilibrée et qui donnerait lieu ensuite à un référendum. Attaquer des exigences légales qui sont déjà relativement minimales dans le droit en vigueur par rapport aux distances des forêts et des cours d'eau, c'est franchir un pas de trop.
+Je vous propose donc de ne pas le faire et d'en rester à la version du Conseil fédéral à l'alinéa 3.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il s'agit là d'une autre croisade - et pas la dernière, malheureusement - de la Commission de l'environnement, de l'aménagement du territoire et de l'énergie, qui vise à limiter le droit de recours des associations.
+Je rappelle que, dans ce projet, nous avons déjà considérablement affaibli le droit de l'environnement à l'article 15bbis alinéas 3 et 4, en particulier pour ce qui est de la protection des marais. Maintenant, nous cherchons également à limiter les voies de droit. Comme l'a dit le ra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il s'agit là d'une autre croisade - et pas la dernière, malheureusement - de la Commission de l'environnement, de l'aménagement du territoire et de l'énergie, qui vise à limiter le droit de recours des associations.
+Je rappelle que, dans ce projet, nous avons déjà considérablement affaibli le droit de l'environnement à l'article 15bbis alinéas 3 et 4, en particulier pour ce qui est de la protection des marais. Maintenant, nous cherchons également à limiter les voies de droit. Comme l'a dit le rapporteur de la commission, cette limitation du droit de recours des organisations dans la loi sur le Tribunal fédéral fait écho à la restriction que nous avons déjà opérée lors du traitement du "Beschleunigungserlass", le projet d'accélération des procédures.
+Cela dit, il faut quand même savoir sur quoi cela porte : on parle ici du réseau de raccordement de ces seize centrales hydroélectriques. Si l'on enlève la possibilité de faire recours, on enlève la possibilité de contester des projets qui peuvent s'étendre tel un ruban sur plusieurs dizaines de kilomètres. Je rappelle quand même qu'on parle de centrales qui sont situées en haute montagne et dont l'infrastructure de raccordement peut s'étaler sur de très grandes surfaces, contrairement aux projets de centrales hydroélectriques à proprement parler qui, elles, sont restreintes à un site circonscrit. Donc on cherche à argumenter de l'harmonisation des procédures, mais c'est en occultant le fait que le site et l'infrastructure de raccordement ne sont pas pareils et ne peuvent pas être traités de la même manière. Effectivement, l'administration et l'Office fédéral de l'énergie saluent cette harmonisation, mais je rappelle que quand on a discuté de ces attaques contre le droit de recours dans la loi sur le Tribunal fédéral, l'administration s'y était opposée dans la mesure où c'est une attaque frontale contre le droit de recours des organisations, qui est un peu la base du droit de l'environnement.
+Je rappelle aussi - s'il faut le rappeler - que lorsque la population avait été invitée à valider ces seize projets de centrales dans la loi sur l'approvisionnement en électricité, la brochure de votation indiquait que le droit de recours des associations était garanti. C'est donc aussi dans ce cadre-là que s'inscrit cette nouvelle restriction du droit de recours.
+Enfin, j'aimerais rappeler qu'avec les décisions que nous avons prises aujourd'hui, nous restreignons déjà le droit de recours dans la loi sur les installations électriques. Il s'agit d'une part de l'article 16j alinéa 2 lettre c, dans lequel nous avons exclu de la qualité pour recourir contre l'approbation des plans, les parties ayant un intérêt juridiquement digne de protection, mais aussi, d'autre part, du nouvel ajout que nous avons validé aujourd'hui à l'alinéa 3, qui limite les griefs invocables aux seuls intérêts individuels dignes de protection. Une restriction du droit de recours est déjà opérée dans la loi sur les installations électriques.
+Je vous prie de ne pas faire un pas supplémentaire et de ne pas "en rajouter une couche" dans la loi sur le Tribunal fédéral en soutenant ma minorité.
 </t>
   </si>
 </sst>
@@ -437,8 +500,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I20" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I24" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I24"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1312,6 +1375,122 @@
         <v>89</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" t="s">
+        <v>92</v>
+      </c>
+      <c r="I21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" t="s">
+        <v>95</v>
+      </c>
+      <c r="I22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" t="s">
+        <v>98</v>
+      </c>
+      <c r="I23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" t="s">
+        <v>101</v>
+      </c>
+      <c r="I24" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -136,13 +136,13 @@
   <si>
     <t xml:space="preserve">Die Sprecherinnen und der Sprecher der Kommission und der Fraktionen haben die Rechnung und auch teilweise den Nachtrag bereits ausführlich dargelegt. Ich beschränke mich darum auf die wichtigsten Punkte.
 Zunächst zum Ergebnis der Staatsrechnung: Wie Sie gehört haben, schliesst die Rechnung 2025 erstmals seit 2019 mit einem Finanzierungsüberschuss ab. Der Überschuss beläuft sich auf 259 Millionen Franken. Wie Sie wissen, unterscheidet die Schuldenbremse zwischen dem ordentlichen und dem ausserordentlichen Haushalt.
-Im ordentlichen Haushalt verzeichnet der Bund einen Überschuss von 1,2 Milliarden Franken. Die Schuldenbremse hätte konjunkturbedingt ein Defizit von 262 Millionen Franken zugelassen. Der strukturelle Saldo gemäss Schuldenbremse belief sich damit auf 1,4 Milliarden Franken. Budgetiert war ein strukturell ausgeglichener Haushalt. Die Ergebnisverbesserung ist auf die dynamische Einnahmenentwicklung zurückzuführen. Die ordentlichen Einnahmen schlossen um 1,9 Milliarden Franken über dem Budget ab. Der Hauptgrund dafür waren die Einnahmen aus der direkten Bundessteuer für die Unternehmen, also die Gewinnsteuern. Die Gewinnsteuereinnahmen lagen 1,4 Milliarden Franken über dem Budget. Diese Entwicklung ist auf die temporären Mehreinnahmen aus dem Kanton Genf zurückzuführen. Allein der Kanton Genf hat 1,5 Milliarden Franken beigesteuert. Das konnte im Budget nur summarisch abgebildet werden. Sie können sich erinnern, wir haben Sie letztes Frühjahr über die Mehreinnahmen aus dem Kanton Genf informiert. Es wurde dann aber erst zu Beginn der Budgetberatung in der Finanzkommission des Ständerates im November 2025 klar, dass eben auch provisorische Rechnungen im Kanton Genf nicht ausgestellt wurden und dass die Mehreinnahmen viel höher ausfallen würden. Wir haben aber auch unter der Ausnahme des Effekts Genf eine positive Entwicklung bei den Gewinnsteuereinnahmen, wobei sie allerdings ohne den Sondereffekt Genf leicht unter dem Budget ausgefallen wären. Gleichzeitig lagen die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden Franken relativ tief ausgefallen sind.
+Im ordentlichen Haushalt verzeichnet der Bund einen Überschuss von 1,2 Milliarden Franken. Die Schuldenbremse hätte konjunkturbedingt ein Defizit von 262 Millionen Franken zugelassen. Der strukturelle Saldo gemäss Schuldenbremse belief sich damit auf 1,4 Milliarden Franken. Budgetiert war ein strukturell ausgeglichener Haushalt. Die Ergebnisverbesserung ist auf die dynamische Einnahmenentwicklung zurückzuführen. Die ordentlichen Einnahmen schlossen um 1,9 Milliarden Franken über dem Budget ab. Der Hauptgrund dafür waren die Einnahmen aus der direkten Bundessteuer für die Unternehmen, also die Gewinnsteuern. Die Gewinnsteuereinnahmen lagen 1,4 Milliarden Franken über dem Budget. Diese Entwicklung ist auf die temporären Mehreinnahmen aus dem Kanton Genf zurückzuführen. Allein der Kanton Genf hat 1,5 Milliarden Franken beigesteuert. Das konnte im Budget nur summarisch abgebildet werden. Sie können sich erinnern, wir haben Sie letztes Frühjahr über die Mehreinnahmen aus dem Kanton Genf informiert. Es wurde dann aber erst zu Beginn der Budgetberatung in der Finanzkommission des Ständerates im November 2025 klar, dass eben auch provisorische Rechnungen im Kanton Genf nicht ausgestellt wurden und dass die Mehreinnahmen viel höher ausfallen würden. Wir haben aber auch unter Ausnahme des Effekts Genf eine positive Entwicklung bei den Gewinnsteuereinnahmen, wobei sie allerdings ohne den Sondereffekt Genf leicht unter dem Budget ausgefallen wären. Gleichzeitig lagen die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden Franken relativ tief ausgefallen sind.
 Im ausserordentlichen Haushalt waren hingegen die Ausgaben grösser als die Einnahmen. Die beiden grössten ausserordentlichen Ausgaben waren diejenigen für die Schutzsuchenden aus der Ukraine sowie der einmalige Kapitalzuschuss an die SBB. Dieser war ursprünglich für das Jahr 2024 budgetiert gewesen und konnte erst 2025 ausgerichtet werden, was damals die Verbesserung der Rechnung 2024 generiert hat. Auf der Einnahmenseite wurde ein Teil der SNB-Gewinnausschüttung ausserordentlich verbucht, 333 Millionen Franken. Dazu kam die budgetierte Sonderzuweisung der SNB aus den nicht umgetauschten Banknoten der sechsten Serie.
-Noch etwas zur Ausgabenentwicklung: Verschiedene Sprecherinnen und Sprecher haben darauf hingewiesen, wie sehr man den Bundeshaushalt sozusagen auspressen würde. Ich gebe Ihnen einfach bekannt, welches Wachstum wir in den wichtigsten Positionen haben. Soziale Wohlfahrt: insgesamt 2 Prozent, allein die AHV plus 5,7 Prozent. Finanzen und Steuern: 6,3 Prozent Wachstum. Das sind natürlich die Kantonsanteile an den Einnahmen, der Finanzausgleich. Verkehr: Zunahme von 9,1 Prozent bei den Ausgaben. Bildung und Forschung: Zunahme von 5,9 Prozent. Sicherheit: Zunahme von 4,3 Prozent. Beziehung zum Ausland: minus 1,2 Prozent. Landwirtschaft und Ernährung: plus 0,1 Prozent. Und dann kommen noch die übrigen Aufgabengebiete. Dies einfach zum Thema, der Staat spare sich kaputt, man würde immer weniger für die wichtigen Bereiche ausgeben.
-Nun noch ein Ausblick: Der Bundesrat wird Ende Juni wie üblich die Zahlen zum Voranschlag 2027 und Finanzplan 2028 bis 2030 festlegen. Die Arbeiten sind noch am Laufen. Ich möchte Sie an dieser Stelle aber über den Zwischenstand dieser Arbeiten informieren, gestützt auf die inzwischen erfolgten Budgeteingaben der Departemente und gestützt auf die aktualisierte Einnahmenschätzung, nachdem uns die Kantone die Eingänge des für die Schätzung wichtigen Monats April gemeldet haben.
+Noch etwas zur Ausgabenentwicklung: Verschiedene Sprecherinnen und Sprecher haben darauf hingewiesen, wie sehr man den Bundeshaushalt sozusagen auspresse. Ich gebe Ihnen einfach bekannt, welches Wachstum wir in den wichtigsten Positionen haben. Soziale Wohlfahrt: insgesamt 2 Prozent, allein die AHV plus 5,7 Prozent. Finanzen und Steuern: 6,3 Prozent Wachstum. Das sind natürlich die Kantonsanteile an den Einnahmen, der Finanzausgleich. Verkehr: Zunahme von 9,1 Prozent bei den Ausgaben. Bildung und Forschung: Zunahme von 5,9 Prozent. Sicherheit: Zunahme von 4,3 Prozent. Beziehung zum Ausland: minus 1,2 Prozent. Landwirtschaft und Ernährung: plus 0,1 Prozent. Und dann kommen noch die übrigen Aufgabengebiete; dies einfach zum Thema, der Staat spare sich kaputt, man gebe immer weniger für die wichtigen Bereiche aus.
+Nun noch ein Ausblick: Der Bundesrat wird Ende Juni wie üblich die Zahlen zum Voranschlag 2027 und zum Finanzplan 2028-2030 festlegen. Die Arbeiten sind noch am Laufen. Ich möchte Sie an dieser Stelle aber über den Zwischenstand dieser Arbeiten informieren, gestützt auf die inzwischen erfolgten Budgeteingaben der Departemente und gestützt auf die aktualisierte Einnahmenschätzung, nachdem uns die Kantone die Eingänge des für die Schätzung wichtigen Monats April gemeldet haben.
 Demnach dürfte sich auf der Ausgabenseite für den Voranschlag 2027 nochmals eine Verschlechterung von voraussichtlich 300 Millionen Franken ergeben, dies im Vergleich zur Standortbestimmung vom April. Grund für diese Verschlechterung sind primär Schätzkorrekturen bei den Sozialversicherungen und bei der Migration. 
 Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer, also bei der Unternehmenssteuer, für juristische Personen, eine deutliche Verbesserung ab. Neben dem Effekt Genf, den wir bereits kannten und entsprechend eingepreist haben, verzeichnen wir auch im laufenden Jahr ein starkes Einnahmenwachstum. Dies zeigt sich in unterschiedlichem Ausmass in zahlreichen Kantonen, wobei vor allem das Wachstum in den Kantonen Luzern, Zürich und Basel-Stadt ins Gewicht fällt - und dieses hohe Wachstum konzentriert sich in diesen Kantonen wiederum auf einige wenige Unternehmen. Es bestehen natürlich weiterhin grosse Unsicherheiten; unter anderem basieren die Schätzungen der Gewinnsteuer zu diesem Zeitpunkt jeweils auf provisorischen Steuerrechnungen, und es ist auch nicht in jedem Fall klar, wie nachhaltig die höheren Steuererträge sind. Einzelne Unternehmen können, ich habe es gesagt, hier grosse Effekte haben. 
-Ein weiterer Unsicherheitsfaktor ist auch die OECD-Ergänzungssteuer, wo wir frühestens im Herbst mit verlässlichen Zahlen rechnen können. Unter dem Strich erwarten wir, Stand heute, aber klar eine Entspannung im Voranschlag 2027, dies unter Einschluss der Kürzungen aus dem Entlastungsprogramm 2027, wie Sie es in der Frühjahrssession verabschiedet haben. Ohne das EP 27 wären wir weiterhin im roten Bereich. Vermutlich können wir aber darüber hinausgehende Massnahmen jetzt streichen, wir können also auf weitere Kürzungen verzichten, die wir vorsorglich im April noch beschlossen hatten, um die Schuldenbremse einzuhalten. Der Bundesrat hatte bereits damals in Aussicht gestellt, dass er die Notwendigkeit dieser zusätzlichen Bereinigungsmassnahmen nochmals überprüfen wird, falls die aktualisierte Ausgaben- und Einnahmenschätzung dies erlaubt. Der Bundesrat wird, wie gesagt, Ende Juni die Zahlen zum Budget definitiv festlegen. Bis dahin werden wir auch mehr zur Entwicklung in den Finanzplanjahren wissen. Ich kann Ihnen jedenfalls versichern, dass es unser Ziel ist, den finanzpolitischen Handlungsspielraum von Bundesrat und Parlament bestmöglich zu wahren - so viel noch zum Ausblick. 
+Ein weiterer Unsicherheitsfaktor ist auch die OECD-Ergänzungssteuer, bei der wir frühestens im Herbst mit verlässlichen Zahlen rechnen können. Unter dem Strich erwarten wir, Stand heute, aber klar eine Entspannung im Voranschlag 2027, dies unter Einschluss der Kürzungen aus dem Entlastungspaket 2027, wie Sie es in der Frühjahrssession verabschiedet haben. Ohne das EP 27 wären wir weiterhin im roten Bereich. Vermutlich können wir aber darüber hinausgehende Massnahmen jetzt streichen, wir können also auf weitere Kürzungen verzichten, die wir vorsorglich im April noch beschlossen hatten, um die Schuldenbremse einzuhalten. Der Bundesrat hatte bereits damals in Aussicht gestellt, dass er die Notwendigkeit dieser zusätzlichen Bereinigungsmassnahmen nochmals überprüfen wird, falls die aktualisierte Ausgaben- und Einnahmenschätzung dies erlaubt. Der Bundesrat wird, wie gesagt, Ende Juni die Zahlen zum Budget definitiv festlegen. Bis dahin werden wir auch mehr zur Entwicklung in den Finanzplanjahren wissen. Ich kann Ihnen jedenfalls versichern, dass es unser Ziel ist, den finanzpolitischen Handlungsspielraum von Bundesrat und Parlament bestmöglich zu wahren - so viel noch zum Ausblick. 
 Der Bundesrat beantragt Ihnen, der Staatsrechnung für das Jahr 2025 zuzustimmen.
 </t>
   </si>
@@ -159,16 +159,17 @@
     <t xml:space="preserve">AG</t>
   </si>
   <si>
-    <t xml:space="preserve">Mit meinem Postulat bitte ich den Bundesrat, im nächsten Wirkungsbericht zum nationalen Finanzausgleich (NFA) die Einführung einer einheitlichen Referenzgrösse für die Bewertung von Eigenheimen im Ressourcenpotenzial zu prüfen, mögliche Massnahmen aufzuzeigen und darüber Bericht zu erstatten. 
-Es geht dabei um eine Frage, die eigentlich sehr grundlegend ist. Soll der Finanzausgleich auf möglichst einheitlichen, objektiven und vergleichbaren Kriterien beruhen? Heute ist das weitgehend der Fall. F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mit meinem Postulat bitte ich den Bundesrat, im nächsten Wirkungsbericht zum nationalen Finanzausgleich (NFA) die Einführung einer einheitlichen Referenzgrösse für die Bewertung von Eigenheimen im Ressourcenpotenzial zu prüfen, mögliche Massnahmen aufzuzeigen und darüber Bericht zu erstatten. 
+    <t xml:space="preserve">Mit meinem Postulat bitte ich den Bundesrat, im nächsten Wirksamkeitsbericht zum nationalen Finanzausgleich (NFA) die Einführung einer einheitlichen Referenzgrösse für die Bewertung von Eigenheimen im Ressourcenpotenzial zu prüfen, mögliche Massnahmen aufzuzeigen und darüber Bericht zu erstatten. 
+Es geht dabei um eine Frage, die eigentlich sehr grundlegend ist. Soll der Finanzausgleich auf möglichst einheitlichen, objektiven und vergleichbaren Kriterien beruhen? Heute ist das weitgehend der Fal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mit meinem Postulat bitte ich den Bundesrat, im nächsten Wirksamkeitsbericht zum nationalen Finanzausgleich (NFA) die Einführung einer einheitlichen Referenzgrösse für die Bewertung von Eigenheimen im Ressourcenpotenzial zu prüfen, mögliche Massnahmen aufzuzeigen und darüber Bericht zu erstatten. 
 Es geht dabei um eine Frage, die eigentlich sehr grundlegend ist. Soll der Finanzausgleich auf möglichst einheitlichen, objektiven und vergleichbaren Kriterien beruhen? Heute ist das weitgehend der Fall. Für die Berechnung des Ressourcenpotenzials werden grundsätzlich standardisierte Werte verwendet. Bei den Eigenheimen besteht jedoch eine Ausnahme. Hier werden die kantonalen Vermögenssteuerwerte bzw. Schätzwerte berücksichtigt. Genau diese Werte unterscheiden sich aber teilweise erheblich von Kanton zu Kanton. Der Grund dafür liegt nicht in unterschiedlichen Immobilienmärkten, sondern in unterschiedlichen kantonalen Schätzungsmethoden und Bewertungsansätzen. Damit kann dieselbe wirtschaftliche Realität je nach Kanton unterschiedlich in die Berechnung des Ressourcenpotenzials einfliessen. Aus systematischer Sicht stellt sich deshalb die Frage, ob dies noch sachgerecht ist.
 Besonders wichtig erscheint mir dabei ein weiterer Grundsatz: Die Kriterien des Finanzausgleichs sollten möglichst nicht von den Kantonen selbst beeinflusst werden können. Der nationale Finanzausgleich soll die tatsächliche Ressourcenstärke eines Kantons abbilden. Er soll aber nicht davon abhängen, mit welchen Methoden ein Kanton seine Liegenschaften bewertet oder welche Schätzungspraxis er anwendet. Wo die Ausgestaltung eines Kriteriums potenziell Auswirkungen auf die Höhe von Ausgleichszahlungen haben kann, entstehen zumindest mögliche Fehlanreize. Genau solche Fehlanreize sollten wir im Finanzausgleich vermeiden. Beim Finanzausgleich ist es evident, dass eine Beeinflussung durch die Akteure ausgeschlossen wird. Sonst wird das System ad absurdum geführt. Deshalb erscheint es sachlogisch, zu prüfen, ob auch bei Liegenschaften eine einheitliche Referenzgrösse zur Anwendung gelangen sollte. Mit dem Repartitionswert existiert ein solches Instrument bereits heute. Er wird bei interkantonalen Steuerausscheidungen verwendet und verfolgt genau das Ziel, unterschiedliche kantonale Bewertungspraktiken vergleichbar zu machen. Mein Postulat verlangt jedoch ausdrücklich nicht die Einführung einer bestimmten Lösung. Es verlangt lediglich, dass die heutige Situation analysiert und mögliche Lösungsansätze geprüft werden.
 In der Vergangenheit wurde die Verwendung einer einheitlichen Referenzgrösse mit dem Argument verworfen, die Berechnung sei mit einem zu grossen Aufwand verbunden. Dieses Argument mag zum Zeitpunkt der Einführung des NFA nachvollziehbar gewesen sein. Seither haben sich durch die Digitalisierung die technischen Möglichkeiten und die Prozesse jedoch grundlegend verändert. Deshalb ist es legitim, die damaligen Annahmen erneut zu prüfen. Selbst wenn der Aufwand weiterhin ein relevantes Argument sein sollte, müssen wir ihn den Auswirkungen gegenüberstellen. Wenn unterschiedliche Bewertungsmethoden zu Verzerrungen im Ressourcenpotenzial führen, dann sollten wir wissen, wie gross diese Verzerrungen tatsächlich sind. Und genau diese Transparenz fehlt heute.
 Der Bundesrat teilt die Einschätzung und beantragt die Annahme des Postulates.
-Es geht heute nicht um eine Reform des Finanzausgleichs. Es geht um die Frage, ob wir bereit sind zu prüfen, ob eine systematische Ungleichbehandlung besteht. Der NFA basiert auf objektiven und vergleichbaren Kriterien. Gerade deshalb sollten wir dort, wo Unterschiede zwischen den Kantonen zu Verzerrungen führen können, genau hinschauen. Wer überzeugt ist, dass das heutige System sachgerecht ist, hat keinen Grund, eine Prüfung abzulehnen. Ich bitte Sie deshalb, dem Postulat zuzustimmen.
+Es geht heute nicht um eine Reform des Finanzausgleichs. Es geht um die Frage, ob wir bereit sind, zu prüfen, ob eine systematische Ungleichbehandlung besteht. Der NFA basiert auf objektiven und vergleichbaren Kriterien. Gerade deshalb sollten wir dort, wo Unterschiede zwischen den Kantonen zu Verzerrungen führen können, genau hinschauen. Wer überzeugt ist, dass das heutige System sachgerecht ist, hat keinen Grund, eine Prüfung abzulehnen.
+Ich bitte Sie deshalb, dem Postulat zuzustimmen.
 </t>
   </si>
   <si>
@@ -178,7 +179,7 @@
     <t xml:space="preserve">Sie haben es gesehen: Der Bundesrat ist mit diesem Postulat einverstanden; dies einfach deshalb, weil eine umfassende Überprüfung des Lastenausgleichs im nächsten Wirksamkeitsbericht sowieso stattfindet, unabhängig von diesem Postulat. Der Lastenausgleich berechnet sich aufgrund von Indikatoren, die seit Beginn des neuen Finanzausgleichs im Jahr 2008 verwendet werden. Insbesondere die Berechnung des soziodemografischen Lastenausgleichs hat sich in den letzten Jahren etwas verändert, hat auch Sch</t>
   </si>
   <si>
-    <t xml:space="preserve">Sie haben es gesehen: Der Bundesrat ist mit diesem Postulat einverstanden; dies einfach deshalb, weil eine umfassende Überprüfung des Lastenausgleichs im nächsten Wirksamkeitsbericht sowieso stattfindet, unabhängig von diesem Postulat. Der Lastenausgleich berechnet sich aufgrund von Indikatoren, die seit Beginn des neuen Finanzausgleichs im Jahr 2008 verwendet werden. Insbesondere die Berechnung des soziodemografischen Lastenausgleichs hat sich in den letzten Jahren etwas verändert, hat auch Schwächen gezeigt, die temporär entschärft wurden. Im letzten Wirksamkeitsbericht hat der Bundesrat bereits angekündigt, dass er im Bericht für die Jahre 2026 bis 2030 den Lastenausgleich grundsätzlich überprüfen wird. Das ist ergebnisoffen. Der Bundesrat wird das ohnehin tun. Wir sind auch hier bereits an der Arbeit.
+    <t xml:space="preserve">Sie haben es gesehen: Der Bundesrat ist mit diesem Postulat einverstanden; dies einfach deshalb, weil eine umfassende Überprüfung des Lastenausgleichs im nächsten Wirksamkeitsbericht sowieso stattfindet, unabhängig von diesem Postulat. Der Lastenausgleich berechnet sich aufgrund von Indikatoren, die seit Beginn des neuen Finanzausgleichs im Jahr 2008 verwendet werden. Insbesondere die Berechnung des soziodemografischen Lastenausgleichs hat sich in den letzten Jahren etwas verändert, hat auch Schwächen gezeigt, die temporär entschärft wurden. Im letzten Wirksamkeitsbericht hat der Bundesrat bereits angekündigt, dass er im Bericht für die Jahre 2026 bis 2029 den Lastenausgleich grundsätzlich überprüfen wird. Das ist ergebnisoffen. Der Bundesrat wird das ohnehin tun. Wir sind auch hier bereits an der Arbeit.
 </t>
   </si>
   <si>
@@ -216,13 +217,13 @@
     <t xml:space="preserve">ZG</t>
   </si>
   <si>
-    <t xml:space="preserve">Frau Kälin hat natürlich Unrecht, wenn sie sagt, man würde hier nicht die Kantone gegeneinander ausspielen. Es geht sehr wohl um einen Verteilkampf, und man möchte gewissen Kantonen, insbesondere den Bergkantonen, Geld wegnehmen und dieses neu eher den tiefergelegenen Kantonen geben.
-Der Grund, weshalb die SVP-Fraktion das Postulat bekämpft, ist aber ein anderer. Es geht ums Grundsätzliche. Wenn Sie den NFA reformieren wollen, dann braucht es eine Gesamtreform. Dann muss man das ganze System ans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frau Kälin hat natürlich Unrecht, wenn sie sagt, man würde hier nicht die Kantone gegeneinander ausspielen. Es geht sehr wohl um einen Verteilkampf, und man möchte gewissen Kantonen, insbesondere den Bergkantonen, Geld wegnehmen und dieses neu eher den tiefergelegenen Kantonen geben.
-Der Grund, weshalb die SVP-Fraktion das Postulat bekämpft, ist aber ein anderer. Es geht ums Grundsätzliche. Wenn Sie den NFA reformieren wollen, dann braucht es eine Gesamtreform. Dann muss man das ganze System anschauen, und man muss auch die Kantone miteinbeziehen. Aber es geht sicherlich nicht, dass man nur den geografisch-topografischen Lastenausgleich anpasst, bei den anderen Indikatoren aber keine Anpassungen vornimmt.
-Es kommt hinzu, dass der soziodemografische Lastenausgleich mit 525 Millionen Franken doch um einiges grosszügiger dotiert ist als der geografisch-topografische Lastenausgleich. Wennschon, würden wir daher beantragen, dass man den soziodemografischen Lastenausgleich entsprechend kürzt, um dann beim geografisch-topografischen Lastenausgleich aufzustocken, damit bei einer allfälligen Anpassung des geografisch-topografischen Lastenausgleichs kein Kanton verliert.
+    <t xml:space="preserve">Frau Kälin hat natürlich Unrecht, wenn sie sagt, man würde hier nicht die Kantone gegeneinander ausspielen. Es geht sehr wohl um einen Verteilkampf, und man möchte gewissen Kantonen, insbesondere den Bergkantonen, Geld wegnehmen und dieses neu eher den tiefer gelegenen Kantonen geben.
+Der Grund, weshalb die SVP-Fraktion das Postulat bekämpft, ist aber ein anderer. Es geht ums Grundsätzliche. Wenn Sie den NFA reformieren wollen, dann braucht es eine Gesamtreform. Dann muss man das ganze System an</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frau Kälin hat natürlich Unrecht, wenn sie sagt, man würde hier nicht die Kantone gegeneinander ausspielen. Es geht sehr wohl um einen Verteilkampf, und man möchte gewissen Kantonen, insbesondere den Bergkantonen, Geld wegnehmen und dieses neu eher den tiefer gelegenen Kantonen geben.
+Der Grund, weshalb die SVP-Fraktion das Postulat bekämpft, ist aber ein anderer. Es geht ums Grundsätzliche. Wenn Sie den NFA reformieren wollen, dann braucht es eine Gesamtreform. Dann muss man das ganze System anschauen, und man muss auch die Kantone mit einbeziehen. Aber es geht sicherlich nicht, dass man nur den geografisch-topografischen Lastenausgleich anpasst, bei den anderen Indikatoren aber keine Anpassungen vornimmt.
+Es kommt hinzu, dass der soziodemografische Lastenausgleich mit 525 Millionen Franken doch um einiges grosszügiger dotiert ist als der geografisch-topografische Lastenausgleich. Wennschon würden wir daher beantragen, dass man den soziodemografischen Lastenausgleich entsprechend kürzt, um dann beim geografisch-topografischen Lastenausgleich aufzustocken, damit bei einer allfälligen Anpassung des geografisch-topografischen Lastenausgleichs kein Kanton verliert.
 Ich bitte Sie, auf eine einseitige Anpassung des NFA zu verzichten und diesen Vorstoss entsprechend abzulehnen.
 </t>
   </si>
@@ -446,6 +447,136 @@
 Je rappelle aussi - s'il faut le rappeler - que lorsque la population avait été invitée à valider ces seize projets de centrales dans la loi sur l'approvisionnement en électricité, la brochure de votation indiquait que le droit de recours des associations était garanti. C'est donc aussi dans ce cadre-là que s'inscrit cette nouvelle restriction du droit de recours.
 Enfin, j'aimerais rappeler qu'avec les décisions que nous avons prises aujourd'hui, nous restreignons déjà le droit de recours dans la loi sur les installations électriques. Il s'agit d'une part de l'article 16j alinéa 2 lettre c, dans lequel nous avons exclu de la qualité pour recourir contre l'approbation des plans, les parties ayant un intérêt juridiquement digne de protection, mais aussi, d'autre part, du nouvel ajout que nous avons validé aujourd'hui à l'alinéa 3, qui limite les griefs invocables aux seuls intérêts individuels dignes de protection. Une restriction du droit de recours est déjà opérée dans la loi sur les installations électriques.
 Je vous prie de ne pas faire un pas supplémentaire et de ne pas "en rajouter une couche" dans la loi sur le Tribunal fédéral en soutenant ma minorité.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aellen Cyril</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'initiative du canton du Jura part d'une bonne intention, et comme souvent, les bonnes intentions méritent d'être considérées avec respect, mais doivent aussi être examinées avec prudence. Personne n'a contesté, durant les échanges au sein de la commission, l'importance des prestations complémentaires. Elles sont une pièce maîtresse de notre système social. Elles permettent à des personnes âgées et à des personnes invalides dont les revenus ne suffisent pas de vivre plus dignement. Elles ne son</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'initiative du canton du Jura part d'une bonne intention, et comme souvent, les bonnes intentions méritent d'être considérées avec respect, mais doivent aussi être examinées avec prudence. Personne n'a contesté, durant les échanges au sein de la commission, l'importance des prestations complémentaires. Elles sont une pièce maîtresse de notre système social. Elles permettent à des personnes âgées et à des personnes invalides dont les revenus ne suffisent pas de vivre plus dignement. Elles ne sont ni une faveur ni une charité ; elles sont un droit, et lorsqu'un droit existe, il doit pouvoir être exercé. Sur ce point, la majorité de la commission pense que l'information doit être meilleure et que l'accompagnement doit être plus efficace. Lorsque c'est possible - et la marge de progression est importante dans les cantons -, les démarches doivent être plus simples. Le système ne doit pas laisser des personnes renoncer à une prestation par ignorance, ou par peur de remplir un formulaire qui ressemble parfois plus à un examen d'école qu'à une demande d'une prestation à laquelle on a droit.
+Une fois que ce droit est posé, il reste à choisir la bonne méthode pour y parvenir. Or, l'initiative qui nous est soumise propose un remède séduisant dans son premier aspect et dans son intitulé, mais beaucoup plus compliqué dans sa réalité. À lire les auteurs, les rentes complémentaires devraient être automatiques. Le mot "automatique" a quelque chose de magique : il donne l'impression qu'il suffirait d'appuyer sur un bouton, de croiser quelques données fiscales et qu'il en ressortirait immédiatement, à la façon d'un programme d'intelligence artificielle, le calcul des prestations auxquelles on a droit. Or, les prestations complémentaires ne fonctionnent pas ainsi ; c'est un peu plus compliqué. Le droit aux prestations complémentaires ne se résume pas à un seul revenu fiscal. Il dépend de la fortune, du loyer, de la situation familiale, du lieu de vie, des frais reconnus, parfois des frais de maladie, ou d'une série d'éléments très concrets, très personnels, et que l'administration ne connaît pas nécessairement - je dirais même qu'elle ne connaît pas, heureusement. Autrement dit, l'automatisme promis risque de vite devenir une machine compliquée, coûteuse et imparfaite, et, au fond, assez peu automatique : des pièces devront toujours être demandées, des situations devront toujours être vérifiées, les dossiers devront toujours être instruits et les erreurs, toujours corrigées.
+Avec un tel automatisme, la bureaucratie ne va donc pas disparaître comme par magie. La bureaucratie va être déplacée, voire augmentée, sous couvert d'une automatisation qui n'aurait d'automatique que le nom. Ce n'est pas ça, une bonne politique sociale ; une bonne politique sociale atteint directement les personnes concernées et les aide. Pour y parvenir, les cantons sont les mieux placés. Ils connaissent au mieux leurs citoyens. Ils connaissent les communes, leurs caisses AVS, les services sociaux et les associations, qui, il faut le souligner, sont des acteurs de terrain qui font un travail concret, parfois peu visible, mais toujours précieux et indispensable. L'action utile se trouve dans la proximité, pas dans l'illusion d'un automatisme fédéral issu d'une loi fédérale qui prétendrait tout résoudre depuis Berne.
+Certains cantons testent des approches plus ciblées. D'autres collaborent davantage avec les organisations spécialisées. Ces expériences constructives et souvent disparates doivent être suivies, encouragées et comparées. Les bonnes pratiques doivent circuler. Elles sont plus efficaces qu'une automatisation nécessairement partielle. Une modification de la loi fédérale est donc parfaitement inadéquate, malgré le fait qu'elle soit demandée par cette initiative. Elle est même peu opportune pour atteindre les objectifs poursuivis. La majorité de la commission ne ferme donc pas les yeux sur le problème ; elle refuse simplement une fausse bonne solution.
+Pour ces raisons, la majorité de la commission vous invite à ne pas donner suite à l'initiative du canton du Jura 24.316.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piller Carrard Valérie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le 3 mars 2024, le peuple et les cantons ont envoyé un signal clair : la précarité de nos aînés n'est pas une fatalité, c'est une urgence. En acceptant la 13e rente AVS, la population a choisi la dignité. Or, nous le savons toutes et tous dans cette salle, la 13e rente est une bouffée d'oxygène, pas un remède miracle contre la pauvreté structurelle. Aujourd'hui, le canton du Jura nous transmet une initiative pleine de bon sens, qui transcende les clivages politiques habituels et qui laisse la ma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le 3 mars 2024, le peuple et les cantons ont envoyé un signal clair : la précarité de nos aînés n'est pas une fatalité, c'est une urgence. En acceptant la 13e rente AVS, la population a choisi la dignité. Or, nous le savons toutes et tous dans cette salle, la 13e rente est une bouffée d'oxygène, pas un remède miracle contre la pauvreté structurelle. Aujourd'hui, le canton du Jura nous transmet une initiative pleine de bon sens, qui transcende les clivages politiques habituels et qui laisse la marge de manoeuvre nécessaire pour la recherche de solutions pragmatiques et efficaces.
+Selon une étude de Pro Senectute, dans notre pays, 230 000 retraités ont formellement droit aux prestations complémentaires, mais ne les touchent pas. Deux cent trente mille visages, ce ne sont pas des statistiques, ce sont des personnes à part entière. Pourquoi renoncent-elles ? Par ignorance, par honte de demander ce qu'elles considèrent à tort comme de l'aide sociale ou parce qu'elles sont terrassées par le monstre bureaucratique que sont devenues nos démarches administratives. Force est de constater que, dans les mentalités, dès qu'on parle de prestations complémentaires, l'accusation d'abus plane toujours aux alentours. Pourtant, les prestations complémentaires ne sont pas une aumône ; c'est, avec l'AVS, l'un des piliers de la prévoyance étatique et les personnes concernées y ont droit.
+L'Office fédéral des assurances sociales nous a assuré, en séance de commission, que l'information concernant les prestations complémentaires parvient à l'ensemble des retraités. Malheureusement, ce n'est que la moitié du chemin, puisque les personnes ayant reçu l'information doivent encore entreprendre les démarches administratives et que des questions de compréhension se posent souvent. L'initiative du canton du Jura a le mérite d'apporter du soutien aux retraités en situation difficile, en visant la garantie à un accès aisé, aspect central pour que les personnes saisissent leurs droits.
+Nous entendons toute la difficulté de la mise en oeuvre d'une telle initiative si on devait l'appliquer de façon automatique. Plutôt que d'un automatisme d'octroi, il s'agirait d'un automatisme d'alerte, comme c'est déjà le cas dans certains cantons pour les subsides d'assurance-maladie, où l'administration fiscale alerte les personnes qui se situent au-dessous d'une certaine tranche de revenus qu'elles y ont droit. Pourquoi ne pas accompagner les gens, les inciter à prendre contact, par exemple avec Pro Senectute, pour remplir les demandes d'aides de façon optimale ? L'enquête de Pro Senectute le montre assez clairement également : quand un service social ou un établissement médico-social apporte un soutien à une personne qui dépose une demande, cela fonctionne mieux que lorsqu'elle reçoit uniquement un simple courrier d'information.
+Par conséquent, afin de faciliter l'accès aux prestations complémentaires des rentières et rentiers et de lutter contre la précarité à la retraite, ma minorité vous invite à donner suite à cette initiative.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lohr Christian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Kommission für soziale Sicherheit und Gesundheit des Nationalrates hat an ihren Sitzungen vom Mai 2026 die vom Kanton Jura am 13. Juni 2024 eingereichte Initiative vorgeprüft.
+Die Standesinitiative verlangt, das Bundesgesetz über Ergänzungsleistungen zur Alters-, Hinterlassenen- und Invalidenversicherung dahingehend anzupassen, dass Anspruchsberechtigte leichter oder sogar automatisch Zugang zu Ergänzungsleistungen haben. Ihre Kommission beantragt Ihnen mit 16 zu 9 Stimmen, der Standesinitia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Kommission für soziale Sicherheit und Gesundheit des Nationalrates hat an ihren Sitzungen vom Mai 2026 die vom Kanton Jura am 13. Juni 2024 eingereichte Initiative vorgeprüft.
+Die Standesinitiative verlangt, das Bundesgesetz über Ergänzungsleistungen zur Alters-, Hinterlassenen- und Invalidenversicherung dahingehend anzupassen, dass Anspruchsberechtigte leichter oder sogar automatisch Zugang zu Ergänzungsleistungen haben. Ihre Kommission beantragt Ihnen mit 16 zu 9 Stimmen, der Standesinitiative keine Folge zu geben. Die Schwesterkommission des Ständerates beschloss am 16. Juni 2025 mit 24 zu 12 Stimmen bei 3 Enthaltungen ebenfalls, der Standesinitiative keine Folge zu geben.
+Erlauben Sie mir, einige Erwägungen der Kommission bekannt zu geben. Aus Sicht der Kommission sollten der schwierige Zugang zu Ergänzungsleistungen sowie die hohen Nichtbezugsquoten sorgfältig und vertieft analysiert werden. Sie begrüsst daher, dass das Bundesamt für Sozialversicherungen eine Studie zu diesem Thema in Auftrag gegeben und kürzlich veröffentlicht hat. Die Studie sollte insbesondere eine Bestandsaufnahme der kantonalen Informations- und Anmeldungspraktiken liefern sowie Good Practices und Verbesserungsmöglichkeiten aufzeigen. Aus ihr geht allgemein hervor, dass es zwar kantonale und damit auch kulturelle Unterschiede gibt, der Zugang zu Ergänzungsleistungen insgesamt aber durchaus gut funktioniert und auch der Informationsauftrag klar erfüllt wird. Obschon Verbesserungen zweifellos möglich und sogar wünschenswert sind, ist die Kommissionsmehrheit der Meinung, dass das aktuelle Recht ausreicht und insbesondere bei dessen Umsetzung durch die Kantone Handlungsspielraum besteht. Die SGK-N hält erfreut fest, dass im Rahmen der erwähnten Studie eine Liste der Good Practices erstellt wurde, und erwartet, dass diese als Grundlage für die Verbesserung der Informationen an die Anspruchsberechtigten verwendet wird.
+Mehrfach wurde in unserer Kommission die Bedeutung der Ergänzungsleistungen erwähnt und auch inhaltlich nicht in Frage gestellt. Es geht also nicht darum, ob wir Ergänzungsleistungen wollen oder nicht, sondern nur, wie wir die Informationen an die Berechtigten weiterleiten. Die Kommissionsmehrheit kommt zum Schluss, dass das in der Initiative erwähnte Problem erkannt ist und seriös angegangen wird. Sie ist ferner der Ansicht, dass es für eine automatische Gewährung von Ergänzungsleistungen eines äusserst aufwendigen Mechanismus bedürfte und dies derzeit nicht notwendig ist.
+Die Kommissionsminderheit beantragt, der Initiative Folge zu geben, um so einen vereinfachten und unbürokratischen Zugang zu Ergänzungsleistungen sicherzustellen und die Nichtbezugsquote zu reduzieren. Aus ihrer Sicht handelt es sich um eine vernünftige Initiative, die den für pragmatische und wirksame Lösungen erforderlichen Handlungsspielraum belässt.
+Ich wiederhole zum Schluss noch einmal: Ihre Kommission beantragt mit 16 zu 9 Stimmen, der Standesinitiative keine Folge zu geben.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si je peux suivre un bon bout la commission sur les précisions qui sont apportées à l'article 27, notamment à l'alinéa 2, j'ai quand même une question de compréhension à la lettre a. Il est dit : "L'autorisation est délivrée : si le requérant est titulaire d'une autorisation visée à l'article 30 concernant la direction d'une pharmacie publique, la direction d'une droguerie publique ou la remise de médicaments". Comment faut-il comprendre ce terme de "publique" ? Parce que cela peut porter à conf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si je peux suivre un bon bout la commission sur les précisions qui sont apportées à l'article 27, notamment à l'alinéa 2, j'ai quand même une question de compréhension à la lettre a. Il est dit : "L'autorisation est délivrée : si le requérant est titulaire d'une autorisation visée à l'article 30 concernant la direction d'une pharmacie publique, la direction d'une droguerie publique ou la remise de médicaments". Comment faut-il comprendre ce terme de "publique" ? Parce que cela peut porter à confusion. Cela peut porter à interprétation. Est-ce qu'il faut comprendre "publique" comme n'étant pas des pharmacies privées, qui sont quand même celles qui sont le plus largement répandues dans notre pays. En tout cas dans mon canton, je ne connais pas de pharmacie publique, si ce n'est celle de l'hôpital, mais elle ne délivre pas de médicaments au public, justement.
+Je pense que, dans tous les cas, ce terme mériterait d'être précisé dans la loi, parce que j'y vois un souci d'interprétation et de compréhension, notamment pour les cantons qui - comme le mien, je le répète - ne connaissent pas de pharmacies publiques, mais que des officines privées. Il en va de même pour les drogueries.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nous examinons donc toujours les questions de réglementation de la radioactivité d'origine naturelle, principalement du radon. Le Conseil national a fait tellement de pas dans notre direction qu'il est bientôt assis sur nos genoux, et qu'il est temps maintenant de faire un pas dans la sienne. 
+La version du Conseil national est actuellement débarrassée de l'obligation d'assainir pour les propriétaires ; c'est là une des préoccupations majeures qui avait été exprimée par la majorité de la commiss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nous examinons donc toujours les questions de réglementation de la radioactivité d'origine naturelle, principalement du radon. Le Conseil national a fait tellement de pas dans notre direction qu'il est bientôt assis sur nos genoux, et qu'il est temps maintenant de faire un pas dans la sienne. 
+La version du Conseil national est actuellement débarrassée de l'obligation d'assainir pour les propriétaires ; c'est là une des préoccupations majeures qui avait été exprimée par la majorité de la commission. Désormais, les propriétaires de biens-fonds touchés par la radioactivité d'origine naturelle ne seront plus tenus d'assainir leurs biens. En revanche, la version du Conseil national maintient dans la loi les prescriptions selon lesquelles le Conseil fédéral peut fixer des valeurs de référence à partir desquelles il faut prendre des mesures et peut régler les modalités de prise en charge des frais relatifs à ces mesures.
+Certes, on nous dit que la situation actuelle est satisfaisante, que ce qu'on demande peut déjà être fait à partir de la situation actuelle et de la réglementation de l'ordonnance. Toutefois, à partir du moment où le Conseil fédéral et le Conseil national, suivis par tous les participants à la consultation - dont les cantons, que nous représentons -, approuvent et saluent une inscription dans la loi, nous devons quand même nous demander pourquoi nous nous entêtons à continuer le "powerplay" auquel nous sommes en train de nous livrer.
+Je vous invite donc à suivre la minorité et à vous rallier à la décision du Conseil national pour pouvoir enfin clore élégamment ce dossier.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moi aussi, tout comme le rapporteur, j'arrive gentiment au bout de mes arguments. Je vais donc répéter ce que j'ai déjà avancé plusieurs fois. Au-delà du fait que, certes, au niveau pénal, la négligence reste punissable, il y a aussi un intérêt dissuasif à coordonner les infractions par négligence.
+Je rappelle qu'actuellement le droit précise que c'est à hauteur de 20 000 francs que les infractions peuvent être punies. Il ne s'agit donc pas de cas qui sont négligeables ou qui ne mettraient pas e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moi aussi, tout comme le rapporteur, j'arrive gentiment au bout de mes arguments. Je vais donc répéter ce que j'ai déjà avancé plusieurs fois. Au-delà du fait que, certes, au niveau pénal, la négligence reste punissable, il y a aussi un intérêt dissuasif à coordonner les infractions par négligence.
+Je rappelle qu'actuellement le droit précise que c'est à hauteur de 20 000 francs que les infractions peuvent être punies. Il ne s'agit donc pas de cas qui sont négligeables ou qui ne mettraient pas en danger la santé publique.
+Enfin, il est difficile parfois de distinguer l'intention de la négligence, particulièrement dans les cas qui nous occupent, par exemple le fait de se débarrasser dans la nature de déchets qui, a posteriori, s'avèrent radioactifs. Dès lors, si on enlève toute mention de l'infraction par négligence dans la loi, le risque est qu'il soit impossible de faire la part des choses entre intention et négligence.
+C'est pourquoi je vous invite, là aussi, à vous aligner sur la décision du Conseil national afin de clore également la question.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présente motion fait suite au scandale des laits infantiles contaminés qui secoue notre pays depuis quelques mois. Début 2026, la Suisse a en effet découvert qu'elle n'était toujours pas immunisée contre les scandales alimentaires. Bref rappel des faits : la toxine céréulide est une substance bactérienne provoquant diarrhées et vomissements potentiellement mortels pour les nourrissons. En raison d'une contamination par cette toxine, des milliers de boîtes de lait infantile ont été rappelées d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présente motion fait suite au scandale des laits infantiles contaminés qui secoue notre pays depuis quelques mois. Début 2026, la Suisse a en effet découvert qu'elle n'était toujours pas immunisée contre les scandales alimentaires. Bref rappel des faits : la toxine céréulide est une substance bactérienne provoquant diarrhées et vomissements potentiellement mortels pour les nourrissons. En raison d'une contamination par cette toxine, des milliers de boîtes de lait infantile ont été rappelées dans notre pays. L'affaire avait éclaté fin novembre 2025 aux Pays-Bas et rapidement pris une ampleur mondiale : 800 références de produits rappelées dans plus de 60 pays, et de nombreux cas suspects de maladie voire de décès. En cause : une société chinoise produisant de l'huile arachidonique (ARA), ingrédient entrant fréquemment dans la composition des laits infantiles.
+La Suisse a dû attendre plusieurs semaines avant que les marques concernées lancent le rappel de produits, d'abord Nestlé le 5 janvier 2026, puis Danone et Hochdorf. Depuis ce premier rappel, le scandale n'en finit pas de rebondir. Plusieurs semaines après le rappel public, des lots contaminés étaient encore disponibles à la vente alors que la situation était annoncée comme sous contrôle. En France, un rapport parlementaire publié mi-mai a révélé des lacunes de l'État et de l'industrie alimentaire. Une enquête a également révélé que, plusieurs jours avant le rappel public, Nestlé et Danone avaient déjà retiré des produits de la vente en Allemagne et en Autriche sans en informer le public. Hier encore, on pouvait lire dans la presse belge qu'un lot contaminé interdit en février se trouvait toujours dans les rayons dans ce pays. Ainsi, au vu de la gravité des faits, aux risques qu'elle fait courir à une catégorie de la population particulièrement vulnérable, à savoir les nourrissons, cette affaire suscite évidemment de nombreuses questions, la principale étant : qu'est-ce qui n'a pas fonctionné ?
+Le cadre légal est clair. La loi sur les denrées alimentaires (LDAI) contient quatre articles, rassemblés dans la section relative aux obligations de l'entreprise, qui disposent que ces dernières sont soumises à une obligation d'autocontrôle et doivent donc veiller à ce que les exigences fixées par la loi soient respectées, mais également une obligation de garantir la protection de la santé lorsque les entreprises constatent que des aliments mis sur le marché peuvent présenter un danger pour la santé. Elles sont également soumises à une obligation de traçabilité : les aliments et toute substance entrant dans la composition des aliments doivent être traçables à toutes les étapes de la production, de la transformation et de la distribution. Les entreprises doivent aussi mettre en place des systèmes et des procédures qui permettent de fournir les informations sur leurs fournisseurs et sur les entreprises auxquelles elles ont livré des produits, afin de pouvoir les transmettre aux autorités qui en font la demande. Et, enfin - c'est l'article 29 de la LDAI -, les entreprises ont un devoir d'assistance et une obligation de renseigner : elles doivent à cet effet assister les autorités d'exécution et fournir sur demande les échantillons des produits en question.
+Malgré ce cadre légal clair, l'affaire a mis en lumière un certain nombre de failles dans le système de sécurité alimentaire, concernant l'information et les garanties de la sécurité alimentaire et sanitaire. Le délai de plusieurs semaines entre la découverte de la contamination et le début du rappel de produits en Suisse interpelle en regard de l'obligation d'informer et de garantir la protection de la santé. L'information, tant des autorités que du public, laisse à désirer. Ainsi, l'Office fédéral de la sécurité alimentaire et des affaires vétérinaires (OSAV) n'a été informé que tardivement et au compte-goutte de la situation et des risques sanitaires encourus. L'information du public a été également tardive. La Société suisse de pédiatrie a du reste déploré un manque de transparence et une communication tardive envers les professionnels de la santé. Aucun chiffre exact n'a été livré quant à la quantité de produits concernés par le rappel. Par ailleurs, les autorités disposent de très peu d'informations sur l'origine des ingrédients. La présence de lots contaminés dans les rayons plusieurs semaines après les rappels publics suscite aussi des interrogations. Il y a donc lieu de vérifier si les procédures de retrait et de contrôle permettent d'assurer correctement l'exécution de ces retraits. Enfin, les maladies liées à la céréulide ne font pas l'objet d'une déclaration obligatoire. Les médecins ne se sont donc pas tenus d'informer les autorités compétentes, en l'occurrence l'Office fédéral de la santé publique (OFSP). Dès lors, faute de données, il est difficile d'évaluer la situation à l'échelle nationale, de suivre l'évolution du nombre de cas et d'ordonner, le cas échéant, les mesures d'analyse qui s'imposent.
+Dès lors, la présente motion charge le Conseil fédéral d'examiner si les dispositions de la LDAI ont été respectées dans cette affaire des laits infantiles contaminés et de prendre les mesures nécessaires afin d'assurer la sécurité alimentaire et sanitaire ainsi que l'information complète et immédiate des autorités compétentes et du public.
+Aucun parent ne devrait se demander s'il empoisonne son bébé lorsqu'il le nourrit. Je remercie dès lors le Conseil fédéral de son avis favorable quant à cette motion et vous invite à la soutenir, car la sécurité alimentaire et sanitaire ne doit pas être une option dans notre pays.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La motion qu'on traite aujourd'hui est une motion similaire à celle que nous avons déjà traitée le 2 juin de cette session. C'était la motion 26.3000, qui nous venait de la Commission des affaires juridiques du Conseil national. Cette motion vise à ce que des formations continues soient proposées de façon obligatoire aux autorités de poursuite judiciaire, à savoir la police ainsi que les ministères publics. Pourquoi cette demande et quelles sont les limites de la répartition des compétences du f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La motion qu'on traite aujourd'hui est une motion similaire à celle que nous avons déjà traitée le 2 juin de cette session. C'était la motion 26.3000, qui nous venait de la Commission des affaires juridiques du Conseil national. Cette motion vise à ce que des formations continues soient proposées de façon obligatoire aux autorités de poursuite judiciaire, à savoir la police ainsi que les ministères publics. Pourquoi cette demande et quelles sont les limites de la répartition des compétences du fédéralisme en la matière ? À l'heure actuelle, comme le rapporteur l'a dit, des formations continues sont proposées dans toutes les régions de Suisse. Cela dit, dans la grande majorité des cantons, elles ne sont pas obligatoires. Seuls quelques ministères publics l'exigent. Pour ce qui concerne les offres facultatives, ce sont les personnes les plus engagées, les plus intéressées par la question et qui possèdent déjà certaines connaissances en la matière qui y participent.
+Bien évidemment, en matière de violences sexistes et sexuelles - et c'est l'objet de la présente motion -, toutes les personnes qui sont amenées à engager, à accueillir et à recueillir la parole des victimes de ces violences doivent être formées à le faire correctement. Il y a notamment un risque réel de victimisation secondaire, à savoir, au travers des procédures, de faire passer aux victimes - dans la très grande majorité des femmes, voire des enfants - de multiples auditions qui les obligent à chaque fois à répéter les faits et agressions subis, et donc à prolonger le traumatisme dont elles ont fait l'objet. C'est ce qu'on appelle la victimisation secondaire.
+Certes, les formations existent, mais il n'y a pas d'uniformité en la matière, il n'y a pas de systématisme et, surtout, il n'y a pas d'obligation. De ce point de vue, seule une réglementation à l'échelle fédérale permet d'assurer cette uniformité des formations des autorités de poursuite judiciaire. En outre, un avis de droit a été demandé par le Bureau fédéral de l'égalité entre femmes et hommes pour évaluer la marge de manoeuvre de la Confédération, puisque le fédéralisme est effectivement l'un des obstacles, ou l'argument majeur, s'opposant à l'adoption de cette motion. 
+Cet avis de droit conclut qu'en vertu de l'article 123 de la Constitution, qui règle la compétence fédérale en matière de droit pénal et de droit de procédure pénale, lorsqu'il s'agit d'exécuter ou de garantir l'exécution uniforme du droit fédéral, ainsi que la mise en oeuvre du droit international, la Confédération peut intervenir. Or, tant la première que la deuxième condition sont remplies. D'une part, aujourd'hui, l'exécution n'est pas uniforme et reste lacunaire à l'échelle nationale. D'autre part, nos obligations internationales relèvent de la Convention d'Istanbul contre les violences à l'égard des femmes et de l'article 15 de cette convention, qui impose de garantir la formation des professionnels. Alors, si les cantons sont obligés d'agir en vertu de cette convention, la Confédération l'est aussi, ce qui justifierait dès lors de réglementer la formation des autorités de poursuite judiciaire à l'échelle nationale.
+Je rappelle que cette motion, tout comme celle de sa Commission des affaires juridiques, a été adoptée par le Conseil national. Je vous invite, non seulement dans l'intérêt des victimes, mais aussi des autorités qui sont chargées de les accompagner et de recueillir leurs paroles, à suivre la minorité de la commission et à adopter cette motion.
 </t>
   </si>
 </sst>
@@ -500,8 +631,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I24" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I32" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I32"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1491,6 +1622,238 @@
         <v>102</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s">
+        <v>106</v>
+      </c>
+      <c r="I25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" t="s">
+        <v>111</v>
+      </c>
+      <c r="I26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" t="s">
+        <v>116</v>
+      </c>
+      <c r="I27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" t="s">
+        <v>119</v>
+      </c>
+      <c r="I28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" t="s">
+        <v>122</v>
+      </c>
+      <c r="I29" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" t="s">
+        <v>125</v>
+      </c>
+      <c r="I30" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I31" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" t="s">
+        <v>131</v>
+      </c>
+      <c r="I32" t="s">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -115,10 +115,10 @@
     <t xml:space="preserve">Crevoisier Crelier Mathilde</t>
   </si>
   <si>
-    <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique[NB]: à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36 108 francs contre 52 488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre femmes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique[NB]: à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36 108 francs contre 52 488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre femmes et hommes dans l'AVS est quasiment nulle. Cet écart ne diminue pas depuis plusieurs années. En comparaison internationale, la Suisse pointe à un peu reluisant cinquième rang des pays européens présentant les plus fortes différences de retraite entre les femmes et les hommes.
+    <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique[NB]: à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36[NB]108 francs contre 52[NB]488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présente motion part d'un constat aussi simple que dramatique[NB]: à la retraite, l'écart de revenu moyen entre femmes et hommes double d'un seul coup pour passer de 16 pour cent d'inégalité salariale à 31 pour cent d'écart de rente. Ainsi, les femmes retraitées perçoivent en moyenne un tiers de moins que les hommes, soit 36[NB]108 francs contre 52[NB]488 francs, selon les chiffres de 2023. Cet écart important est entièrement imputable à la prévoyance professionnelle, car la différence entre femmes et hommes dans l'AVS est quasiment nulle. Cet écart ne diminue pas depuis plusieurs années. En comparaison internationale, la Suisse pointe à un peu reluisant cinquième rang des pays européens présentant les plus fortes différences de retraite entre les femmes et les hommes.
 Afin de combler ce fossé, la présente motion visait donc à tenir compte des lacunes de rente découlant des tâches éducatives et d'assistance, qui sont assumées majoritairement par les femmes au détriment de leur épargne-vieillesse, et d'introduire dans la loi sur la prévoyance professionnelle vieillesse, survivants et invalidité (LPP) le principe de la bonification, principe bien connu et reconnu, puisqu'il existe déjà dans l'AVS, comme l'a indiqué le rapporteur. Comme cela a été dit, cette motion s'inscrivait dans la série d'interventions déposées dans le sillage du refus de la révision de la LPP en 2024, interventions qui avaient toutes été renvoyées à la commission compétente et qui ont été retirées, que ce soit en commission ou aujourd'hui au conseil, au profit du postulat 26.3521 de la CSSS, que nous avons accepté tout à l'heure.
 Ainsi, vu les considérations avancées dans le postulat de la commission, qui refuse une approche isolée au profit d'une réflexion globale sur les améliorations possibles dans la LPP, et vu les arguments du Conseil fédéral, qui oeuvre d'ores et déjà à la nouvelle révision de la LPP et cherche, lui aussi, des solutions pour améliorer la prévoyance professionnelle des personnes travaillant à temps partiel ou ayant de faibles revenus, parmi lesquels les femmes sont justement surreprésentées, je me rallie au mouvement initié par d'autres auteurs de motions et retire la présente motion, dans l'espoir toutefois que les mesures de la prochaine réforme permettront enfin d'infléchir cet écart important qui n'a plus lieu d'être dans le système de rente moderne d'un pays prospère comme le nôtre.
 </t>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -63,7 +63,8 @@
   </si>
   <si>
     <t xml:space="preserve">Mindestlöhne wurden nicht aus einer Laune heraus eingeführt, sie sind eine Antwort auf reale Probleme im Arbeitsmarkt, auf die Tatsache, dass Menschen Vollzeit arbeiten und trotzdem zu wenig Geld zum Leben verdienen. Mit dieser Vorlage wollen Sie dieses Instrument unterlaufen. Zumindest der Ständerat hat eingesehen, dass die Übersteuerung demokratisch legitimierter Entscheidungen höchst kritisch ist. Die Ausnahme für Mindestlöhne, die bereits vor dieser Gesetzesvorlage beschlossen wurden, wie etwa in den Kantonen Genf, Neuenburg, Basel-Stadt oder Jura, ist ein Kompromiss für die Vergangenheit und ein kleiner Schritt in Richtung einer demokratisch verträglichen Vorlage. Dieser Schritt muss nun aber konsequent weitergedacht werden. 
-Mit der Minderheit Amoos wird auch für die Zukunft ein solcher Kompromiss gefunden. Wird ein Mindestlohn beschlossen, so erhalten die Sozialpartner Zeit, um zu reagieren. Sie können bei der nächsten Verhandlung der GAV die Löhne anpassen. Spätestens aber nach zwei Jahren müssen die Löhne auf das Niveau der geltenden Mindestlöhne angehoben werden. Das schafft Verbindlichkeit, und es schafft Fairness. Denn ohne klare Fristen besteht die Gefahr, dass über Jahre hinweg zu tiefe Löhne bestehen bleiben. Und genau das ist aus unserer Sicht nicht akzeptabel. Mindestlöhne sind keine symbolischen Grössen, sie sind eine verbindliche Untergrenze. Sie sollen sicherstellen, dass Arbeit vor Armut schützt. Und so kommen wir auch wieder näher zurück an die Verfassung. Denn die Kantone haben gemäss Bundesverfassung das Recht, Mindestlöhne einzuführen. Eine Übersteuerung durch privatrechtliche Verträge - ein allgemeinverbindlich erklärter GAV ist nichts anderes - ist schlicht nicht verfassungskonform. Mit der Minderheit Amoos könnte man die Vorlage schon beinahe als demokratisch verträglich bezeichnen.
+Mit der Minderheit Amoos wird auch für die Zukunft ein solcher Kompromiss gefunden. Wird ein Mindestlohn beschlossen, so erhalten die Sozialpartner Zeit, um zu reagieren. Sie können bei der nächsten Verhandlung der GAV die Löhne anpassen. Spätestens aber nach zwei Jahren müssen die Löhne auf das Niveau der geltenden Mindestlöhne angehoben werden. Das schafft Verbindlichkeit, und es schafft Fairness. Denn ohne klare Fristen besteht die Gefahr, dass über Jahre hinweg zu tiefe Löhne bestehen bleiben. Und genau das ist aus unserer Sicht nicht akzeptabel. 
+Mindestlöhne sind keine symbolischen Grössen, sie sind eine verbindliche Untergrenze. Sie sollen sicherstellen, dass Arbeit vor Armut schützt. Und so kommen wir auch wieder näher zurück an die Verfassung. Denn die Kantone haben gemäss Bundesverfassung das Recht, Mindestlöhne einzuführen. Eine Übersteuerung durch privatrechtliche Verträge - ein allgemeinverbindlich erklärter GAV ist nichts anderes - ist schlicht nicht verfassungskonform. Mit der Minderheit Amoos könnte man die Vorlage schon beinahe als demokratisch verträglich bezeichnen.
 Deshalb unterstützen wir den Antrag der Minderheit bei Artikel 1 Absatz 4 für einen Lohnschutz, der seinen Namen auch verdient.
 </t>
   </si>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -131,19 +131,23 @@
     <t xml:space="preserve">Keller-Sutter Karin</t>
   </si>
   <si>
-    <t xml:space="preserve">Die Sprecherinnen und der Sprecher der Kommission und der Fraktionen haben die Rechnung und auch teilweise den Nachtrag bereits ausführlich dargelegt. Ich beschränke mich darum auf die wichtigsten Punkte.
-Zunächst zum Ergebnis der Staatsrechnung: Wie Sie gehört haben, schliesst die Rechnung 2025 erstmals seit 2019 mit einem Finanzierungsüberschuss ab. Der Überschuss beläuft sich auf 259 Millionen Franken. Wie Sie wissen, unterscheidet die Schuldenbremse zwischen dem ordentlichen und dem ausseror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Sprecherinnen und der Sprecher der Kommission und der Fraktionen haben die Rechnung und auch teilweise den Nachtrag bereits ausführlich dargelegt. Ich beschränke mich darum auf die wichtigsten Punkte.
+    <t xml:space="preserve">Die Sprecherinnen und Sprecher der Kommission und der Fraktionen haben die Rechnung und auch teilweise den Nachtrag bereits ausführlich dargelegt. Ich beschränke mich darum auf die wichtigsten Punkte.
+Zunächst zum Ergebnis der Staatsrechnung: Wie Sie gehört haben, schliesst die Rechnung 2025 erstmals seit 2019 mit einem Finanzierungsüberschuss ab. Der Überschuss beläuft sich auf 259 Millionen Franken. Wie Sie wissen, unterscheidet die Schuldenbremse zwischen dem ordentlichen und dem ausserordent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Sprecherinnen und Sprecher der Kommission und der Fraktionen haben die Rechnung und auch teilweise den Nachtrag bereits ausführlich dargelegt. Ich beschränke mich darum auf die wichtigsten Punkte.
 Zunächst zum Ergebnis der Staatsrechnung: Wie Sie gehört haben, schliesst die Rechnung 2025 erstmals seit 2019 mit einem Finanzierungsüberschuss ab. Der Überschuss beläuft sich auf 259 Millionen Franken. Wie Sie wissen, unterscheidet die Schuldenbremse zwischen dem ordentlichen und dem ausserordentlichen Haushalt.
-Im ordentlichen Haushalt verzeichnet der Bund einen Überschuss von 1,2 Milliarden Franken. Die Schuldenbremse hätte konjunkturbedingt ein Defizit von 262 Millionen Franken zugelassen. Der strukturelle Saldo gemäss Schuldenbremse belief sich damit auf 1,4 Milliarden Franken. Budgetiert war ein strukturell ausgeglichener Haushalt. Die Ergebnisverbesserung ist auf die dynamische Einnahmenentwicklung zurückzuführen. Die ordentlichen Einnahmen schlossen um 1,9 Milliarden Franken über dem Budget ab. Der Hauptgrund dafür waren die Einnahmen aus der direkten Bundessteuer für die Unternehmen, also die Gewinnsteuern. Die Gewinnsteuereinnahmen lagen 1,4 Milliarden Franken über dem Budget. Diese Entwicklung ist auf die temporären Mehreinnahmen aus dem Kanton Genf zurückzuführen. Allein der Kanton Genf hat 1,5 Milliarden Franken beigesteuert. Das konnte im Budget nur summarisch abgebildet werden. Sie können sich erinnern, wir haben Sie letztes Frühjahr über die Mehreinnahmen aus dem Kanton Genf informiert. Es wurde dann aber erst zu Beginn der Budgetberatung in der Finanzkommission des Ständerates im November 2025 klar, dass eben auch provisorische Rechnungen im Kanton Genf nicht ausgestellt wurden und dass die Mehreinnahmen viel höher ausfallen würden. Wir haben aber auch unter Ausnahme des Effekts Genf eine positive Entwicklung bei den Gewinnsteuereinnahmen, wobei sie allerdings ohne den Sondereffekt Genf leicht unter dem Budget ausgefallen wären. Gleichzeitig lagen die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden Franken relativ tief ausgefallen sind.
+Im ordentlichen Haushalt verzeichnet der Bund einen Überschuss von 1,2 Milliarden Franken. Die Schuldenbremse hätte konjunkturbedingt ein Defizit von 262 Millionen Franken zugelassen. Der strukturelle Saldo gemäss Schuldenbremse belief sich damit auf 1,4 Milliarden Franken. Budgetiert war ein strukturell ausgeglichener Haushalt. Die Ergebnisverbesserung ist auf die dynamische Einnahmenentwicklung zurückzuführen. 
+Die ordentlichen Einnahmen schlossen um 1,9 Milliarden Franken über dem Budget ab. Der Hauptgrund dafür waren die Einnahmen aus der direkten Bundessteuer für die Unternehmen, also die Gewinnsteuern. Die Gewinnsteuereinnahmen lagen 1,4 Milliarden Franken über dem Budget. Diese Entwicklung ist auf die temporären Mehreinnahmen aus dem Kanton Genf zurückzuführen. Allein der Kanton Genf hat 1,5 Milliarden Franken beigesteuert. Das konnte im Budget nur summarisch abgebildet werden. Sie können sich erinnern, wir haben Sie letztes Frühjahr über die Mehreinnahmen aus dem Kanton Genf informiert. Es wurde dann aber erst zu Beginn der Budgetberatung in der Finanzkommission des Ständerates im November 2025 klar, dass eben auch provisorische Rechnungen im Kanton Genf nicht ausgestellt wurden und dass die Mehreinnahmen viel höher ausfallen würden. Wir haben aber auch unter Ausnahme des Effekts Genf eine positive Entwicklung bei den Gewinnsteuereinnahmen, wobei sie allerdings ohne den Sondereffekt Genf leicht unter dem Budget ausgefallen wären. 
+Gleichzeitig lagen die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden Franken relativ tief ausgefallen sind.
 Im ausserordentlichen Haushalt waren hingegen die Ausgaben grösser als die Einnahmen. Die beiden grössten ausserordentlichen Ausgaben waren diejenigen für die Schutzsuchenden aus der Ukraine sowie der einmalige Kapitalzuschuss an die SBB. Dieser war ursprünglich für das Jahr 2024 budgetiert gewesen und konnte erst 2025 ausgerichtet werden, was damals die Verbesserung der Rechnung 2024 generiert hat. Auf der Einnahmenseite wurde ein Teil der SNB-Gewinnausschüttung ausserordentlich verbucht, 333 Millionen Franken. Dazu kam die budgetierte Sonderzuweisung der SNB aus den nicht umgetauschten Banknoten der sechsten Serie.
-Noch etwas zur Ausgabenentwicklung: Verschiedene Sprecherinnen und Sprecher haben darauf hingewiesen, wie sehr man den Bundeshaushalt sozusagen auspresse. Ich gebe Ihnen einfach bekannt, welches Wachstum wir in den wichtigsten Positionen haben. Soziale Wohlfahrt: insgesamt 2 Prozent, allein die AHV plus 5,7 Prozent. Finanzen und Steuern: 6,3 Prozent Wachstum. Das sind natürlich die Kantonsanteile an den Einnahmen, der Finanzausgleich. Verkehr: Zunahme von 9,1 Prozent bei den Ausgaben. Bildung und Forschung: Zunahme von 5,9 Prozent. Sicherheit: Zunahme von 4,3 Prozent. Beziehung zum Ausland: minus 1,2 Prozent. Landwirtschaft und Ernährung: plus 0,1 Prozent. Und dann kommen noch die übrigen Aufgabengebiete; dies einfach zum Thema, der Staat spare sich kaputt, man gebe immer weniger für die wichtigen Bereiche aus.
+Noch etwas zur Ausgabenentwicklung: Verschiedene Sprecherinnen und Sprecher haben darauf hingewiesen, wie sehr man den Bundeshaushalt sozusagen auspresse. Ich gebe Ihnen einfach bekannt, welches Wachstum wir in den wichtigsten Positionen haben. Soziale Wohlfahrt: insgesamt 2 Prozent, allein die AHV plus 5,7 Prozent. Finanzen und Steuern: 6,3 Prozent Wachstum. Das sind natürlich die Kantonsanteile an den Einnahmen, der Finanzausgleich. Verkehr: Zunahme von 9,1 Prozent bei den Ausgaben. Bildung und Forschung: Zunahme von 5,9 Prozent. Sicherheit: Zunahme von 4,3 Prozent. Beziehung zum Ausland: minus 1,2 Prozent. Landwirtschaft und Ernährung: plus 0,1 Prozent. Und dann kommen noch die übrigen Aufgabengebiete. Dies einfach zum Thema, der Staat spare sich kaputt, man gebe immer weniger für die wichtigen Bereiche aus.
 Nun noch ein Ausblick: Der Bundesrat wird Ende Juni wie üblich die Zahlen zum Voranschlag 2027 und zum Finanzplan 2028-2030 festlegen. Die Arbeiten sind noch am Laufen. Ich möchte Sie an dieser Stelle aber über den Zwischenstand dieser Arbeiten informieren, gestützt auf die inzwischen erfolgten Budgeteingaben der Departemente und gestützt auf die aktualisierte Einnahmenschätzung, nachdem uns die Kantone die Eingänge des für die Schätzung wichtigen Monats April gemeldet haben.
 Demnach dürfte sich auf der Ausgabenseite für den Voranschlag 2027 nochmals eine Verschlechterung von voraussichtlich 300 Millionen Franken ergeben, dies im Vergleich zur Standortbestimmung vom April. Grund für diese Verschlechterung sind primär Schätzkorrekturen bei den Sozialversicherungen und bei der Migration. 
-Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer, also bei der Unternehmenssteuer, für juristische Personen, eine deutliche Verbesserung ab. Neben dem Effekt Genf, den wir bereits kannten und entsprechend eingepreist haben, verzeichnen wir auch im laufenden Jahr ein starkes Einnahmenwachstum. Dies zeigt sich in unterschiedlichem Ausmass in zahlreichen Kantonen, wobei vor allem das Wachstum in den Kantonen Luzern, Zürich und Basel-Stadt ins Gewicht fällt - und dieses hohe Wachstum konzentriert sich in diesen Kantonen wiederum auf einige wenige Unternehmen. Es bestehen natürlich weiterhin grosse Unsicherheiten; unter anderem basieren die Schätzungen der Gewinnsteuer zu diesem Zeitpunkt jeweils auf provisorischen Steuerrechnungen, und es ist auch nicht in jedem Fall klar, wie nachhaltig die höheren Steuererträge sind. Einzelne Unternehmen können, ich habe es gesagt, hier grosse Effekte haben. 
-Ein weiterer Unsicherheitsfaktor ist auch die OECD-Ergänzungssteuer, bei der wir frühestens im Herbst mit verlässlichen Zahlen rechnen können. Unter dem Strich erwarten wir, Stand heute, aber klar eine Entspannung im Voranschlag 2027, dies unter Einschluss der Kürzungen aus dem Entlastungspaket 2027, wie Sie es in der Frühjahrssession verabschiedet haben. Ohne das EP 27 wären wir weiterhin im roten Bereich. Vermutlich können wir aber darüber hinausgehende Massnahmen jetzt streichen, wir können also auf weitere Kürzungen verzichten, die wir vorsorglich im April noch beschlossen hatten, um die Schuldenbremse einzuhalten. Der Bundesrat hatte bereits damals in Aussicht gestellt, dass er die Notwendigkeit dieser zusätzlichen Bereinigungsmassnahmen nochmals überprüfen wird, falls die aktualisierte Ausgaben- und Einnahmenschätzung dies erlaubt. Der Bundesrat wird, wie gesagt, Ende Juni die Zahlen zum Budget definitiv festlegen. Bis dahin werden wir auch mehr zur Entwicklung in den Finanzplanjahren wissen. Ich kann Ihnen jedenfalls versichern, dass es unser Ziel ist, den finanzpolitischen Handlungsspielraum von Bundesrat und Parlament bestmöglich zu wahren - so viel noch zum Ausblick. 
+Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer, also bei der Unternehmenssteuer, für juristische Personen eine deutliche Verbesserung ab. Neben dem Effekt Genf, den wir bereits kannten und entsprechend eingepreist haben, verzeichnen wir auch im laufenden Jahr ein starkes Einnahmenwachstum. Dies zeigt sich in unterschiedlichem Ausmass in zahlreichen Kantonen, wobei vor allem das Wachstum in den Kantonen Luzern, Zürich und Basel-Stadt ins Gewicht fällt. Das hohe Wachstum konzentriert sich in diesen Kantonen wiederum auf einige wenige Unternehmen. Es bestehen natürlich weiterhin grosse Unsicherheiten; unter anderem basieren die Schätzungen der Gewinnsteuer zu diesem Zeitpunkt jeweils auf provisorischen Steuerrechnungen, und es ist auch nicht in jedem Fall klar, wie nachhaltig die höheren Steuererträge sind. Einzelne Unternehmen können, ich habe es gesagt, hier grosse Effekte haben. 
+Ein weiterer Unsicherheitsfaktor ist auch die OECD-Ergänzungssteuer, bei der wir frühestens im Herbst mit verlässlichen Zahlen rechnen können. 
+Unter dem Strich erwarten wir, Stand heute, aber klar eine Entspannung im Voranschlag 2027, dies unter Einschluss der Kürzungen aus dem Entlastungspaket 2027, wie Sie es in der Frühjahrssession verabschiedet haben. Ohne das EP 27 wären wir weiterhin im roten Bereich. Vermutlich können wir aber darüber hinausgehende Massnahmen jetzt streichen; wir können also auf weitere Kürzungen verzichten, die wir vorsorglich im April noch beschlossen hatten, um die Schuldenbremse einzuhalten. Der Bundesrat hatte bereits damals in Aussicht gestellt, dass er die Notwendigkeit dieser zusätzlichen Bereinigungsmassnahmen nochmals überprüfen wird, falls die aktualisierte Ausgaben- und Einnahmenschätzung dies erlaubt. 
+Der Bundesrat wird, wie gesagt, Ende Juni die Zahlen zum Budget definitiv festlegen. Bis dahin werden wir auch mehr zur Entwicklung in den Finanzplanjahren wissen. Ich kann Ihnen jedenfalls versichern, dass es unser Ziel ist, den finanzpolitischen Handlungsspielraum von Bundesrat und Parlament bestmöglich zu wahren - so viel noch zum Ausblick. 
 Der Bundesrat beantragt Ihnen, der Staatsrechnung für das Jahr 2025 zuzustimmen.
 </t>
   </si>
@@ -245,10 +249,10 @@
     <t xml:space="preserve">374817</t>
   </si>
   <si>
-    <t xml:space="preserve">Commençons par un constat sans appel[NB]: la violence sexiste et sexuelle est un fléau qui n'épargne pas notre pays, comme l'a encore rappelé hier le Conseil fédéral, en lançant la deuxième phase de sa campagne contre la violence domestique. En 2025, la police a enregistré 22 000 infractions dues à la violence domestique, un chiffre dont on sait qu'il ne constitue que la partie émergée de l'iceberg et cache une sombre réalité dans laquelle un nombre encore plus élevé de cas n'entrera jamais dans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commençons par un constat sans appel[NB]: la violence sexiste et sexuelle est un fléau qui n'épargne pas notre pays, comme l'a encore rappelé hier le Conseil fédéral, en lançant la deuxième phase de sa campagne contre la violence domestique. En 2025, la police a enregistré 22 000 infractions dues à la violence domestique, un chiffre dont on sait qu'il ne constitue que la partie émergée de l'iceberg et cache une sombre réalité dans laquelle un nombre encore plus élevé de cas n'entrera jamais dans les statistiques de la criminalité. En effet, l'accès à la justice des victimes de violence sexiste, sexuelle et de violence domestique est encore semé d'embûches. Parmi celles-ci, la prise en charge des victimes par les autorités de procédure pénale, soit la police, les ministères publics et les tribunaux, est souvent pointée du doigt comme un facteur de renoncement pour les victimes à poursuivre la procédure. En cause, on peut mentionner notamment un manque de sensibilité dans l'accueil, la prise en charge et l'audition des victimes, avec un risque important de victimisation secondaire pour ces dernières.
+    <t xml:space="preserve">Commençons par un constat sans appel[NB]: la violence sexiste et sexuelle est un fléau qui n'épargne pas notre pays, comme l'a encore rappelé hier le Conseil fédéral, en lançant la deuxième phase de sa campagne contre la violence domestique. En 2025, la police a enregistré 22[NB]000 infractions dues à la violence domestique, un chiffre dont on sait qu'il ne constitue que la partie émergée de l'iceberg et cache une sombre réalité dans laquelle un nombre encore plus élevé de cas n'entrera jamais d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commençons par un constat sans appel[NB]: la violence sexiste et sexuelle est un fléau qui n'épargne pas notre pays, comme l'a encore rappelé hier le Conseil fédéral, en lançant la deuxième phase de sa campagne contre la violence domestique. En 2025, la police a enregistré 22[NB]000 infractions dues à la violence domestique, un chiffre dont on sait qu'il ne constitue que la partie émergée de l'iceberg et cache une sombre réalité dans laquelle un nombre encore plus élevé de cas n'entrera jamais dans les statistiques de la criminalité. En effet, l'accès à la justice des victimes de violence sexiste, sexuelle et de violence domestique est encore semé d'embûches. Parmi celles-ci, la prise en charge des victimes par les autorités de procédure pénale, soit la police, les ministères publics et les tribunaux, est souvent pointée du doigt comme un facteur de renoncement pour les victimes à poursuivre la procédure. En cause, on peut mentionner notamment un manque de sensibilité dans l'accueil, la prise en charge et l'audition des victimes, avec un risque important de victimisation secondaire pour ces dernières.
 Ainsi, la motion de la Commission des affaires juridiques du Conseil national, "Modification du code de procédure pénale concernant la formation initiale et continue des autorités pénales", vise donc à améliorer cette formation de manière à améliorer l'accès à la justice pour les victimes. Elle se base sur le rapport du Conseil fédéral de 2025, donnant suite au postulat Fehlmann Rielle 21.4215.
 Vous l'avez entendu, la majorité de la commission rejette la motion au motif de la répartition des compétences. Effectivement, les cantons sont responsables de la formation initiale et continue des autorités de poursuite pénale, mais le prétexte du fédéralisme ne saurait nous prémunir d'examiner si nous remplissons nos propres obligations. Que les cantons soient tenus d'assurer la formation continue et initiale, y compris en vertu de l'article 15 de la Convention d'Istanbul, ne signifie pas encore, toutefois, que celle-ci soit assurée. Or, aujourd'hui, on constate que la mise en oeuvre est, sinon lacunaire, encore inégale. Le rapport de 2022 d'évaluation du Groupe d'experts sur la lutte contre la violence à l'égard des femmes et la violence domestique (Grevio) déplore que la Suisse n'ait toujours pas de programme de formation standardisé dans le domaine de la violence sexuelle pour la police, et que celle-ci soit facultative pour les services judiciaires. Le Grevio encourage vivement les autorités suisses à prendre des mesures afin de veiller à dispenser une formation initiale et continue systématique et obligatoire aux professionnels en lien avec les victimes et les auteurs de toutes les formes de violence visées par la Convention d'Istanbul. Ainsi, si l'argument de la compétence cantonale doit évidemment être pris en compte, il doit aussi être soigneusement sous-pesé en regard de nos responsabilités à l'échelon fédéral.
 Dans le cadre de la réponse au postulat précité, la Confédération a commandé un avis de droit qui conclut qu'elle dispose d'une marge de manoeuvre en vertu de l'article 123 de la Constitution qui règle la compétence fédérale en matière de droit pénal et de droit de procédure pénale, lorsqu'il s'agit de garantir l'exécution uniforme du droit fédéral, ainsi que la mise en oeuvre du droit international. Or, ces deux conditions sont remplies. D'une part, aujourd'hui, malgré les efforts d'uniformisation consentis par les cantons, force est de constater que la formation des autorités de poursuite pénale est encore trop fragmentée pour assurer l'égalité de traitement des victimes dans l'ensemble du pays, et que si la formation initiale de la police est désormais généralisée, celle des ministères publics reste encore lacunaire. D'ailleurs, bien que le Conseil fédéral propose lui aussi de rejeter la motion, il admet qu'il reste des efforts à accomplir, par exemple concernant l'audition des victimes ou encore au niveau de la coopération interdisciplinaire et de la formation initiale et continue des acteurs. D'autre part, une intervention de la Confédération au titre de l'article 123 de la Constitution se justifie également par l'obligation qui nous est faite, en vertu de l'article 15 de la Convention d'Istanbul, de garantir la formation des professionnels. Dès lors, rejeter la présente motion, comme le propose la majorité de la commission, ne relève pas du simple respect des compétences cantonales, mais bien d'une appréciation politique. Or, il faut admettre que la situation actuelle en matière de prise en charge des victimes ne permet ni de garantir l'exécution uniforme du droit ni de remplir nos obligations internationales. C'est également la conclusion à laquelle est parvenu le Conseil national, par 127 voix contre 63 et 1 abstention, soit l'intégralité des groupes parlementaires, à une exception près.

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -144,7 +144,7 @@
 Noch etwas zur Ausgabenentwicklung: Verschiedene Sprecherinnen und Sprecher haben darauf hingewiesen, wie sehr man den Bundeshaushalt sozusagen auspresse. Ich gebe Ihnen einfach bekannt, welches Wachstum wir in den wichtigsten Positionen haben. Soziale Wohlfahrt: insgesamt 2 Prozent, allein die AHV plus 5,7 Prozent. Finanzen und Steuern: 6,3 Prozent Wachstum. Das sind natürlich die Kantonsanteile an den Einnahmen, der Finanzausgleich. Verkehr: Zunahme von 9,1 Prozent bei den Ausgaben. Bildung und Forschung: Zunahme von 5,9 Prozent. Sicherheit: Zunahme von 4,3 Prozent. Beziehung zum Ausland: minus 1,2 Prozent. Landwirtschaft und Ernährung: plus 0,1 Prozent. Und dann kommen noch die übrigen Aufgabengebiete. Dies einfach zum Thema, der Staat spare sich kaputt, man gebe immer weniger für die wichtigen Bereiche aus.
 Nun noch ein Ausblick: Der Bundesrat wird Ende Juni wie üblich die Zahlen zum Voranschlag 2027 und zum Finanzplan 2028-2030 festlegen. Die Arbeiten sind noch am Laufen. Ich möchte Sie an dieser Stelle aber über den Zwischenstand dieser Arbeiten informieren, gestützt auf die inzwischen erfolgten Budgeteingaben der Departemente und gestützt auf die aktualisierte Einnahmenschätzung, nachdem uns die Kantone die Eingänge des für die Schätzung wichtigen Monats April gemeldet haben.
 Demnach dürfte sich auf der Ausgabenseite für den Voranschlag 2027 nochmals eine Verschlechterung von voraussichtlich 300 Millionen Franken ergeben, dies im Vergleich zur Standortbestimmung vom April. Grund für diese Verschlechterung sind primär Schätzkorrekturen bei den Sozialversicherungen und bei der Migration. 
-Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer, also bei der Unternehmenssteuer, für juristische Personen eine deutliche Verbesserung ab. Neben dem Effekt Genf, den wir bereits kannten und entsprechend eingepreist haben, verzeichnen wir auch im laufenden Jahr ein starkes Einnahmenwachstum. Dies zeigt sich in unterschiedlichem Ausmass in zahlreichen Kantonen, wobei vor allem das Wachstum in den Kantonen Luzern, Zürich und Basel-Stadt ins Gewicht fällt. Das hohe Wachstum konzentriert sich in diesen Kantonen wiederum auf einige wenige Unternehmen. Es bestehen natürlich weiterhin grosse Unsicherheiten; unter anderem basieren die Schätzungen der Gewinnsteuer zu diesem Zeitpunkt jeweils auf provisorischen Steuerrechnungen, und es ist auch nicht in jedem Fall klar, wie nachhaltig die höheren Steuererträge sind. Einzelne Unternehmen können, ich habe es gesagt, hier grosse Effekte haben. 
+Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer, also bei der Unternehmenssteuer, eine deutliche Verbesserung ab. Neben dem Effekt Genf, den wir bereits kannten und entsprechend eingepreist haben, verzeichnen wir auch im laufenden Jahr ein starkes Einnahmenwachstum. Dies zeigt sich in unterschiedlichem Ausmass in zahlreichen Kantonen, wobei vor allem das Wachstum in den Kantonen Luzern, Zürich und Basel-Stadt ins Gewicht fällt. Das hohe Wachstum konzentriert sich in diesen Kantonen wiederum auf einige wenige Unternehmen. Es bestehen natürlich weiterhin grosse Unsicherheiten; unter anderem basieren die Schätzungen der Gewinnsteuer zu diesem Zeitpunkt jeweils auf provisorischen Steuerrechnungen, und es ist auch nicht in jedem Fall klar, wie nachhaltig die höheren Steuererträge sind. Einzelne Unternehmen können, ich habe es gesagt, hier grosse Effekte haben. 
 Ein weiterer Unsicherheitsfaktor ist auch die OECD-Ergänzungssteuer, bei der wir frühestens im Herbst mit verlässlichen Zahlen rechnen können. 
 Unter dem Strich erwarten wir, Stand heute, aber klar eine Entspannung im Voranschlag 2027, dies unter Einschluss der Kürzungen aus dem Entlastungspaket 2027, wie Sie es in der Frühjahrssession verabschiedet haben. Ohne das EP 27 wären wir weiterhin im roten Bereich. Vermutlich können wir aber darüber hinausgehende Massnahmen jetzt streichen; wir können also auf weitere Kürzungen verzichten, die wir vorsorglich im April noch beschlossen hatten, um die Schuldenbremse einzuhalten. Der Bundesrat hatte bereits damals in Aussicht gestellt, dass er die Notwendigkeit dieser zusätzlichen Bereinigungsmassnahmen nochmals überprüfen wird, falls die aktualisierte Ausgaben- und Einnahmenschätzung dies erlaubt. 
 Der Bundesrat wird, wie gesagt, Ende Juni die Zahlen zum Budget definitiv festlegen. Bis dahin werden wir auch mehr zur Entwicklung in den Finanzplanjahren wissen. Ich kann Ihnen jedenfalls versichern, dass es unser Ziel ist, den finanzpolitischen Handlungsspielraum von Bundesrat und Parlament bestmöglich zu wahren - so viel noch zum Ausblick. 
@@ -170,7 +170,8 @@
   <si>
     <t xml:space="preserve">Mit meinem Postulat bitte ich den Bundesrat, im nächsten Wirksamkeitsbericht zum nationalen Finanzausgleich (NFA) die Einführung einer einheitlichen Referenzgrösse für die Bewertung von Eigenheimen im Ressourcenpotenzial zu prüfen, mögliche Massnahmen aufzuzeigen und darüber Bericht zu erstatten. 
 Es geht dabei um eine Frage, die eigentlich sehr grundlegend ist. Soll der Finanzausgleich auf möglichst einheitlichen, objektiven und vergleichbaren Kriterien beruhen? Heute ist das weitgehend der Fall. Für die Berechnung des Ressourcenpotenzials werden grundsätzlich standardisierte Werte verwendet. Bei den Eigenheimen besteht jedoch eine Ausnahme. Hier werden die kantonalen Vermögenssteuerwerte bzw. Schätzwerte berücksichtigt. Genau diese Werte unterscheiden sich aber teilweise erheblich von Kanton zu Kanton. Der Grund dafür liegt nicht in unterschiedlichen Immobilienmärkten, sondern in unterschiedlichen kantonalen Schätzungsmethoden und Bewertungsansätzen. Damit kann dieselbe wirtschaftliche Realität je nach Kanton unterschiedlich in die Berechnung des Ressourcenpotenzials einfliessen. Aus systematischer Sicht stellt sich deshalb die Frage, ob dies noch sachgerecht ist.
-Besonders wichtig erscheint mir dabei ein weiterer Grundsatz: Die Kriterien des Finanzausgleichs sollten möglichst nicht von den Kantonen selbst beeinflusst werden können. Der nationale Finanzausgleich soll die tatsächliche Ressourcenstärke eines Kantons abbilden. Er soll aber nicht davon abhängen, mit welchen Methoden ein Kanton seine Liegenschaften bewertet oder welche Schätzungspraxis er anwendet. Wo die Ausgestaltung eines Kriteriums potenziell Auswirkungen auf die Höhe von Ausgleichszahlungen haben kann, entstehen zumindest mögliche Fehlanreize. Genau solche Fehlanreize sollten wir im Finanzausgleich vermeiden. Beim Finanzausgleich ist es evident, dass eine Beeinflussung durch die Akteure ausgeschlossen wird. Sonst wird das System ad absurdum geführt. Deshalb erscheint es sachlogisch, zu prüfen, ob auch bei Liegenschaften eine einheitliche Referenzgrösse zur Anwendung gelangen sollte. Mit dem Repartitionswert existiert ein solches Instrument bereits heute. Er wird bei interkantonalen Steuerausscheidungen verwendet und verfolgt genau das Ziel, unterschiedliche kantonale Bewertungspraktiken vergleichbar zu machen. Mein Postulat verlangt jedoch ausdrücklich nicht die Einführung einer bestimmten Lösung. Es verlangt lediglich, dass die heutige Situation analysiert und mögliche Lösungsansätze geprüft werden.
+Besonders wichtig erscheint mir dabei ein weiterer Grundsatz: Die Kriterien des Finanzausgleichs sollten möglichst nicht von den Kantonen selbst beeinflusst werden können. Der nationale Finanzausgleich soll die tatsächliche Ressourcenstärke eines Kantons abbilden. Er soll aber nicht davon abhängen, mit welchen Methoden ein Kanton seine Liegenschaften bewertet oder welche Schätzungspraxis er anwendet. Wo die Ausgestaltung eines Kriteriums potenziell Auswirkungen auf die Höhe von Ausgleichszahlungen haben kann, entstehen zumindest mögliche Fehlanreize. Genau solche Fehlanreize sollten wir im Finanzausgleich vermeiden. Beim Finanzausgleich ist es evident, dass eine Beeinflussung durch die Akteure ausgeschlossen wird. Sonst wird das System ad absurdum geführt. 
+Deshalb erscheint es sachlogisch, zu prüfen, ob auch bei Liegenschaften eine einheitliche Referenzgrösse zur Anwendung gelangen sollte. Mit dem Repartitionswert existiert ein solches Instrument bereits heute. Er wird bei interkantonalen Steuerausscheidungen verwendet und verfolgt genau das Ziel, unterschiedliche kantonale Bewertungspraktiken vergleichbar zu machen. Mein Postulat verlangt jedoch ausdrücklich nicht die Einführung einer bestimmten Lösung. Es verlangt lediglich, dass die heutige Situation analysiert und mögliche Lösungsansätze geprüft werden.
 In der Vergangenheit wurde die Verwendung einer einheitlichen Referenzgrösse mit dem Argument verworfen, die Berechnung sei mit einem zu grossen Aufwand verbunden. Dieses Argument mag zum Zeitpunkt der Einführung des NFA nachvollziehbar gewesen sein. Seither haben sich durch die Digitalisierung die technischen Möglichkeiten und die Prozesse jedoch grundlegend verändert. Deshalb ist es legitim, die damaligen Annahmen erneut zu prüfen. Selbst wenn der Aufwand weiterhin ein relevantes Argument sein sollte, müssen wir ihn den Auswirkungen gegenüberstellen. Wenn unterschiedliche Bewertungsmethoden zu Verzerrungen im Ressourcenpotenzial führen, dann sollten wir wissen, wie gross diese Verzerrungen tatsächlich sind. Und genau diese Transparenz fehlt heute.
 Der Bundesrat teilt die Einschätzung und beantragt die Annahme des Postulates.
 Es geht heute nicht um eine Reform des Finanzausgleichs. Es geht um die Frage, ob wir bereit sind, zu prüfen, ob eine systematische Ungleichbehandlung besteht. Der NFA basiert auf objektiven und vergleichbaren Kriterien. Gerade deshalb sollten wir dort, wo Unterschiede zwischen den Kantonen zu Verzerrungen führen können, genau hinschauen. Wer überzeugt ist, dass das heutige System sachgerecht ist, hat keinen Grund, eine Prüfung abzulehnen.
@@ -181,10 +182,10 @@
     <t xml:space="preserve">374756</t>
   </si>
   <si>
-    <t xml:space="preserve">Sie haben es gesehen: Der Bundesrat ist mit diesem Postulat einverstanden; dies einfach deshalb, weil eine umfassende Überprüfung des Lastenausgleichs im nächsten Wirksamkeitsbericht sowieso stattfindet, unabhängig von diesem Postulat. Der Lastenausgleich berechnet sich aufgrund von Indikatoren, die seit Beginn des neuen Finanzausgleichs im Jahr 2008 verwendet werden. Insbesondere die Berechnung des soziodemografischen Lastenausgleichs hat sich in den letzten Jahren etwas verändert, hat auch Sch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sie haben es gesehen: Der Bundesrat ist mit diesem Postulat einverstanden; dies einfach deshalb, weil eine umfassende Überprüfung des Lastenausgleichs im nächsten Wirksamkeitsbericht sowieso stattfindet, unabhängig von diesem Postulat. Der Lastenausgleich berechnet sich aufgrund von Indikatoren, die seit Beginn des neuen Finanzausgleichs im Jahr 2008 verwendet werden. Insbesondere die Berechnung des soziodemografischen Lastenausgleichs hat sich in den letzten Jahren etwas verändert, hat auch Schwächen gezeigt, die temporär entschärft wurden. Im letzten Wirksamkeitsbericht hat der Bundesrat bereits angekündigt, dass er im Bericht für die Jahre 2026 bis 2029 den Lastenausgleich grundsätzlich überprüfen wird. Das ist ergebnisoffen. Der Bundesrat wird das ohnehin tun. Wir sind auch hier bereits an der Arbeit.
+    <t xml:space="preserve">Sie haben es gesehen: Der Bundesrat ist mit diesem Postulat einverstanden, einfach deshalb, weil eine umfassende Überprüfung des Lastenausgleichs im nächsten Wirksamkeitsbericht sowieso stattfindet, unabhängig von diesem Postulat. Der Lastenausgleich berechnet sich aufgrund von Indikatoren, die seit Beginn des neuen Finanzausgleichs im Jahr 2008 verwendet werden. Insbesondere die Berechnung des soziodemografischen Lastenausgleichs hat sich in den letzten Jahren etwas verändert, hat auch Schwäche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sie haben es gesehen: Der Bundesrat ist mit diesem Postulat einverstanden, einfach deshalb, weil eine umfassende Überprüfung des Lastenausgleichs im nächsten Wirksamkeitsbericht sowieso stattfindet, unabhängig von diesem Postulat. Der Lastenausgleich berechnet sich aufgrund von Indikatoren, die seit Beginn des neuen Finanzausgleichs im Jahr 2008 verwendet werden. Insbesondere die Berechnung des soziodemografischen Lastenausgleichs hat sich in den letzten Jahren etwas verändert, hat auch Schwächen gezeigt, die temporär entschärft wurden. Im letzten Wirksamkeitsbericht hat der Bundesrat bereits angekündigt, dass er im Bericht für die Jahre 2026 bis 2029 den Lastenausgleich grundsätzlich überprüfen wird. Das ist ergebnisoffen. Der Bundesrat wird das ohnehin tun. Wir sind auch hier bereits an der Arbeit.
 </t>
   </si>
   <si>
@@ -222,13 +223,13 @@
     <t xml:space="preserve">ZG</t>
   </si>
   <si>
-    <t xml:space="preserve">Frau Kälin hat natürlich Unrecht, wenn sie sagt, man würde hier nicht die Kantone gegeneinander ausspielen. Es geht sehr wohl um einen Verteilkampf, und man möchte gewissen Kantonen, insbesondere den Bergkantonen, Geld wegnehmen und dieses neu eher den tiefer gelegenen Kantonen geben.
+    <t xml:space="preserve">Frau Kälin hat natürlich unrecht, wenn sie sagt, man würde hier nicht die Kantone gegeneinander ausspielen. Es geht sehr wohl um einen Verteilkampf, und man möchte gewissen Kantonen, insbesondere den Bergkantonen, Geld wegnehmen und dieses neu eher den tiefer gelegenen Kantonen geben.
 Der Grund, weshalb die SVP-Fraktion das Postulat bekämpft, ist aber ein anderer. Es geht ums Grundsätzliche. Wenn Sie den NFA reformieren wollen, dann braucht es eine Gesamtreform. Dann muss man das ganze System an</t>
   </si>
   <si>
-    <t xml:space="preserve">Frau Kälin hat natürlich Unrecht, wenn sie sagt, man würde hier nicht die Kantone gegeneinander ausspielen. Es geht sehr wohl um einen Verteilkampf, und man möchte gewissen Kantonen, insbesondere den Bergkantonen, Geld wegnehmen und dieses neu eher den tiefer gelegenen Kantonen geben.
+    <t xml:space="preserve">Frau Kälin hat natürlich unrecht, wenn sie sagt, man würde hier nicht die Kantone gegeneinander ausspielen. Es geht sehr wohl um einen Verteilkampf, und man möchte gewissen Kantonen, insbesondere den Bergkantonen, Geld wegnehmen und dieses neu eher den tiefer gelegenen Kantonen geben.
 Der Grund, weshalb die SVP-Fraktion das Postulat bekämpft, ist aber ein anderer. Es geht ums Grundsätzliche. Wenn Sie den NFA reformieren wollen, dann braucht es eine Gesamtreform. Dann muss man das ganze System anschauen, und man muss auch die Kantone mit einbeziehen. Aber es geht sicherlich nicht, dass man nur den geografisch-topografischen Lastenausgleich anpasst, bei den anderen Indikatoren aber keine Anpassungen vornimmt.
-Es kommt hinzu, dass der soziodemografische Lastenausgleich mit 525 Millionen Franken doch um einiges grosszügiger dotiert ist als der geografisch-topografische Lastenausgleich. Wennschon würden wir daher beantragen, dass man den soziodemografischen Lastenausgleich entsprechend kürzt, um dann beim geografisch-topografischen Lastenausgleich aufzustocken, damit bei einer allfälligen Anpassung des geografisch-topografischen Lastenausgleichs kein Kanton verliert.
+Es kommt hinzu, dass der soziodemografische Lastenausgleich mit 525 Millionen Franken doch um einiges grosszügiger dotiert ist als der geografisch-topografische Lastenausgleich. Wenn schon, würden wir daher beantragen, dass man den soziodemografischen Lastenausgleich entsprechend kürzt, um dann beim geografisch-topografischen Lastenausgleich aufzustocken, damit bei einer allfälligen Anpassung des geografisch-topografischen Lastenausgleichs kein Kanton verliert.
 Ich bitte Sie, auf eine einseitige Anpassung des NFA zu verzichten und diesen Vorstoss entsprechend abzulehnen.
 </t>
   </si>
@@ -271,7 +272,7 @@
   </si>
   <si>
     <t xml:space="preserve">Vous avez vu que je suis aussi dans la minorité. Je vous recommande donc d'accepter cette proposition de minorité. La question est de savoir si le Conseil fédéral peut ou doit. À mon avis, c'est une question plus générale sur les taxes ou les redevances. Lorsqu'il s'agit par exemple des impôts, la plupart des lois, cantonales en tout cas, prévoient des adaptations automatiques pour compenser le renchérissement afin d'éviter les taxes occultes. Il s'agit en l'occurrence de ne pas faire payer d'impôts supplémentaires au contribuable lorsque son revenu réel n'a pas changé.
-Or ici, on va dans le sens inverse. Tout augmente, sauf les taxes qui sont destinées à financer les investissements qui y sont liés. Je ne vais pas vous rappeler à quoi sert la RPLP, mais elle est surtout là pour financer des infrastructures ferroviaires et routières. Je veux citer un autre exemple : la vignette autoroutière a été introduite en 1985 et coûte encore aujourd'hui 40 francs. En 1985, ce prix de 40 francs permettait environ 350 millions de rentrées dans les caisses de la Confédération, dont 40 pour cent payés pour des véhicules étrangers, des véhicules en transit. Il vaut donc quand même la peine d'y réfléchir par rapport aux citoyens suisses. En 2025, s'il y avait eu une adaptation automatique au renchérissement, ce sont 553 millions qui seraient tombés dans les caisses de la Confédération, soit plus de 200 millions supplémentaires, et toujours 40 pour cent payés pour des véhicules étrangers qui transitent en Suisse. Pour les teneurs de la rigueur financière, je pense que cette adaptation automatique mérite quand même d'être analysée et discutée. On pourrait passer le coût de la vignette de 40 francs à 63 francs aujourd'hui, si on avait fait cette progression, soit, en moyenne, 53 centimes de plus par an depuis son introduction.
+Or, ici, on va dans le sens inverse. Tout augmente, sauf les taxes qui sont destinées à financer les investissements qui y sont liés. Je ne vais pas vous rappeler à quoi sert la RPLP, mais elle est surtout là pour financer des infrastructures ferroviaires et routières. Je veux citer un autre exemple[NB]: la vignette autoroutière a été introduite en 1985 et coûte encore aujourd'hui 40 francs. En 1985, ce prix de 40 francs permettait environ 350 millions de rentrées dans les caisses de la Confédération, dont 40 pour cent payés pour des véhicules étrangers, des véhicules en transit. Il vaut donc quand même la peine d'y réfléchir par rapport aux citoyens suisses. En 2025, s'il y avait eu une adaptation automatique au renchérissement, ce sont 553 millions qui seraient tombés dans les caisses de la Confédération, soit plus de 200 millions supplémentaires, et toujours 40 pour cent payés pour des véhicules étrangers qui transitent en Suisse. Pour les tenants de la rigueur financière, je pense que cette adaptation automatique mérite quand même d'être analysée et discutée. On pourrait passer le coût de la vignette de 40 francs à 63 francs aujourd'hui, si on avait fait cette progression, soit, en moyenne, 53 centimes de plus par an depuis son introduction.
 Il ne faut donc pas peindre le diable sur la muraille en disant que cela aura des conséquences incroyables pour les entreprises. Je crois que c'est le contraire, c'est une question de philosophie. Ces taxes et redevances permettent de financer des infrastructures dont les coûts augmentent toujours par nature et pour lesquels il faudra bien trouver les moyens. On sait à quel point, aujourd'hui, nous avons des difficultés à trouver ces moyens. Je vous invite donc à introduire ce mécanisme avec cette marge de deux points d'inflation qui permet au Conseil fédéral d'avoir une toute petite marge de progression.
 Je vous invite donc à suivre la minorité de la commission.
 </t>
@@ -280,11 +281,11 @@
     <t xml:space="preserve">374945</t>
   </si>
   <si>
-    <t xml:space="preserve">Même si je peux tout à fait comprendre le souci des entreprises, si les adaptations sont à la hausse, les entreprises répercuteront aussi le coût sur le client final, donc ce ne sont pas les entreprises qui auront un souci réel d'amortissement de leur véhicule. En outre, fixer un délai de 7 ans voudrait dire que les tarifs aujourd'hui prévus dans la loi auraient dû être prévus par le prédécesseur de M. Rösti. Rendez-vous compte du temps qu'il faut pour adapter et tenir compte de la réalité du mo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Même si je peux tout à fait comprendre le souci des entreprises, si les adaptations sont à la hausse, les entreprises répercuteront aussi le coût sur le client final, donc ce ne sont pas les entreprises qui auront un souci réel d'amortissement de leur véhicule. En outre, fixer un délai de 7 ans voudrait dire que les tarifs aujourd'hui prévus dans la loi auraient dû être prévus par le prédécesseur de M. Rösti. Rendez-vous compte du temps qu'il faut pour adapter et tenir compte de la réalité du moment. 7 ans, c'est beaucoup trop long. Regardez sur les événements qui se passent aujourd'hui. Comment voulez-vous savoir dans 7 ans quelle sera exactement la réalité, alors que vous demandez aujourd'hui de faire une projection ?
-Si le Conseil fédéral veut échelonner différemment la redevance telle qu'elle est proposée ici, avec l'ajout de ce délai de préavis de 7 ans, cela veut dire qu'aujourd'hui le Conseil fédéral devrait prévoir l'échelonnement des redevances pour 2032-2033. Ce n'est juste pas possible, ce n'est pas réaliste en matière de politique publique de faire une telle adjonction dans une loi, parce que cela ne permet pas raisonnablement de tenir compte de l'évolution de la situation économique, de la situation politique et de tout ce à quoi la Confédération notamment doit faire face. Je peux comprendre ce besoin de planification pour les entreprises, tout en sachant que, comme je l'ai dit, les entreprises au bout du compte, reporteront en grande partie cette adaptation des charges, si celles-ci sont à la hausse, sur le client final.
+    <t xml:space="preserve">Même si je peux tout à fait comprendre le souci des entreprises, si les adaptations sont à la hausse, les entreprises répercuteront aussi le coût sur le client final[NB]; donc, ce ne sont pas les entreprises qui auront un souci réel d'amortissement de leurs véhicules. En outre, fixer un délai de sept ans voudrait dire que les tarifs aujourd'hui prévus dans la loi auraient dû être prévus par le prédécesseur de M.[NB]Rösti. Rendez-vous compte du temps qu'il faut pour adapter et tenir compte de la </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Même si je peux tout à fait comprendre le souci des entreprises, si les adaptations sont à la hausse, les entreprises répercuteront aussi le coût sur le client final[NB]; donc, ce ne sont pas les entreprises qui auront un souci réel d'amortissement de leurs véhicules. En outre, fixer un délai de sept ans voudrait dire que les tarifs aujourd'hui prévus dans la loi auraient dû être prévus par le prédécesseur de M.[NB]Rösti. Rendez-vous compte du temps qu'il faut pour adapter et tenir compte de la réalité du moment[NB]; sept ans, c'est beaucoup trop long. Regardez les événements qui se passent aujourd'hui. Comment voulez-vous savoir dans sept ans quelle sera exactement la réalité, alors que vous demandez aujourd'hui de faire une projection[NB]?
+Si le Conseil fédéral veut échelonner différemment la redevance telle qu'elle est proposée ici, avec l'ajout de ce délai de préavis de sept ans, cela veut dire qu'aujourd'hui le Conseil fédéral devrait prévoir l'échelonnement des redevances pour 2032-2033. Ce n'est juste pas possible, ce n'est pas réaliste en matière de politique publique de faire une telle adjonction dans une loi, parce que cela ne permet pas de tenir raisonnablement compte de l'évolution de la situation économique, de la situation politique et de tout ce à quoi la Confédération, notamment, doit faire face. Je peux comprendre ce besoin de planification pour les entreprises, tout en sachant que, comme je l'ai dit, les entreprises, au bout du compte, reporteront en grande partie cette adaptation des charges, si celles-ci sont à la hausse, sur le client final.
 Je vous invite donc à suivre ici la minorité de la commission et à suivre le projet du Conseil fédéral.
 </t>
   </si>
@@ -292,12 +293,12 @@
     <t xml:space="preserve">374985</t>
   </si>
   <si>
-    <t xml:space="preserve">Je ne vais pas revenir sur tous les arguments qui ont été indiqués par la rapporteuse ou le porte-parole de la minorité de la commission, mais si je soutiens l'entrée en matière, c'est parce que je pense qu'il y a nécessité d'agir. On nous dit qu'avec l'intelligence artificielle, ce projet n'est plus nécessaire, que les Gafam mettent à disposition toutes ces données. C'est possible, mais je n'en suis pas sûr. Lors du débat que nous avons eu en commission, nous avons quand même survolé passableme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je ne vais pas revenir sur tous les arguments qui ont été indiqués par la rapporteuse ou le porte-parole de la minorité de la commission, mais si je soutiens l'entrée en matière, c'est parce que je pense qu'il y a nécessité d'agir. On nous dit qu'avec l'intelligence artificielle, ce projet n'est plus nécessaire, que les Gafam mettent à disposition toutes ces données. C'est possible, mais je n'en suis pas sûr. Lors du débat que nous avons eu en commission, nous avons quand même survolé passablement de questions qui ont trait à ces besoins ou non-besoins. Qui fournit ou qui ne fournit pas ces données ? Combien cela coûte-t-il ? Combien faut-il mettre de moyens à disposition ? Je crois que ce projet mérite quand même notre attention parce qu'il est attendu. Vous avez vu le nombre de lettres que nous avons reçu d'instances directement concernées. Le porte-parole de la minorité en a cité un certain nombre, mais l'aménagement du territoire aussi peut être concerné. Les réflexions sur la circulation dans les villes et les communes sont aussi des éléments qui pourront être pris en compte.
+    <t xml:space="preserve">Je ne vais pas revenir sur tous les arguments qui ont été indiqués par la rapporteuse ou le porte-parole de la minorité de la commission, mais si je soutiens l'entrée en matière, c'est parce que je pense qu'il y a nécessité d'agir. On nous dit qu'avec l'intelligence artificielle ce projet n'est plus nécessaire, que les Gafam mettent à disposition toutes ces données. C'est possible, mais je n'en suis pas sûr. Lors du débat que nous avons eu en commission, nous avons quand même survolé passablemen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne vais pas revenir sur tous les arguments qui ont été indiqués par la rapporteuse ou le porte-parole de la minorité de la commission, mais si je soutiens l'entrée en matière, c'est parce que je pense qu'il y a nécessité d'agir. On nous dit qu'avec l'intelligence artificielle ce projet n'est plus nécessaire, que les Gafam mettent à disposition toutes ces données. C'est possible, mais je n'en suis pas sûr. Lors du débat que nous avons eu en commission, nous avons quand même survolé passablement de questions qui ont trait à ces besoins ou non-besoins. Qui fournit ou qui ne fournit pas ces données[NB]? Combien cela coûte-t-il[NB]? Combien faut-il mettre de moyens à disposition[NB]? Je crois que ce projet mérite quand même notre attention, parce qu'il est attendu. Vous avez vu le nombre de lettres que nous avons reçues d'instances directement concernées. Le porte-parole de la minorité en a cité un certain nombre, mais l'aménagement du territoire aussi peut être concerné. Les réflexions sur la circulation dans les villes et les communes sont aussi des éléments qui pourront être pris en compte.
 Je ne suis pas non plus un fan absolu de ce projet. J'aurais peut-être dû d'emblée dire que je suis président de l'intergroupe parlementaire Feu bleu, qui regroupe en particulier les sapeurs-pompiers, qui attendent ce genre de données actualisées au jour le jour. Actuellement, quand il y a des travaux dans les villes ou dans les grandes villes, ils doivent envoyer un de leurs membres régulièrement circuler dans leur secteur d'activité pour savoir si les chemins habituels sont disponibles ou non en fonction des travaux qu'il y a. Aujourd'hui, ce n'est pas acceptable. Ce projet mérite donc quand même un peu plus que d'être simplement abandonné sans avoir été approfondi.
-Je le répète, pour moi, il y a deux éléments qui sont absolument fondamentaux. En ce qui concerne la fourniture des informations, soit tous les acteurs doivent fournir leurs informations, soit ce n'est pas le cas. Si on laisse la possibilité de le faire ou pas, si on n'oblige pas à fournir les données, ce projet n'a pas de sens. C'est pour moi un élément assez essentiel. En ce qui concerne les moyens dont on parle pour le mettre en oeuvre, les 28 EPT et les coûts qui sont prévus sont absolument exorbitants. On n'a pas arrêté de nous dire, y compris de la part de l'administration, que l'intelligence artificielle allait nous permettre de gagner, mais qu'on ne sait pas exactement combien. Ce sont des questions qui, à mon avis, méritent d'être encore discutées en commission avant de couler ce projet. Je serai le premier à reconnaître, si on n'a pas de réponses claires et concrètes notamment sur ces deux éléments-là, lors du vote final, qu'il ne faut pas soutenir ce projet, si on n'a pas pu l'améliorer dans ces deux domaines. Cependant, aujourd'hui, je ne suis pas en mesure de vous dire ni de vous recommander s'il faut soutenir ou non ce projet parce qu'à mon avis, la commission n'est pas allée assez loin dans le travail d'examen. J'avais par exemple proposé que l'on fasse des auditions des milieux concernés. C'est vrai que si on ne veut pas entrer en matière, ce n'est pas la peine qu'on perde notre temps à faire des auditions, mais je pense que si nous avions été un peu plus loin et notamment avions procédé à ces auditions, peut-être que nous aurions un autre regard sur ce projet qui, je le répète, mérite d'être amélioré et que, sans ces améliorations, je ne soutiendrai pas non plus lors du vote final.
+Je le répète, pour moi, il y a deux éléments qui sont absolument fondamentaux. En ce qui concerne la fourniture des informations, soit tous les acteurs doivent fournir leurs informations, soit ce n'est pas le cas. Si on laisse la possibilité de le faire ou pas, si on n'oblige pas à fournir les données, ce projet n'a pas de sens. C'est pour moi un élément assez essentiel. En ce qui concerne les moyens dont on parle pour le mettre en oeuvre, les 28 EPT et les coûts qui sont prévus sont absolument exorbitants. On n'a pas arrêté de nous dire, y compris de la part de l'administration, que l'intelligence artificielle allait nous permettre de gagner, mais qu'on ne sait pas exactement combien. Ce sont des questions qui, à mon avis, méritent d'être encore discutées en commission avant de couler ce projet. Je serai le premier à reconnaître, si on n'a pas de réponses claires et concrètes notamment sur ces deux éléments-là, lors du vote final, qu'il ne faut pas soutenir ce projet, si on n'a pas pu l'améliorer dans ces deux domaines. Cependant, aujourd'hui, je ne suis pas en mesure de vous dire ni de vous recommander s'il faut soutenir ou non ce projet, parce qu'à mon avis, la commission n'est pas allée assez loin dans le travail d'examen. J'avais par exemple proposé que l'on fasse des auditions des milieux concernés. C'est vrai que si on ne veut pas entrer en matière, ce n'est pas la peine qu'on perde notre temps à faire des auditions, mais je pense que, si nous avions été un peu plus loin et notamment avions procédé à ces auditions, peut-être que nous aurions un autre regard sur ce projet qui, je le répète, mérite d'être amélioré et que, sans ces améliorations, je ne soutiendrai pas non plus lors du vote final.
 Aujourd'hui, je vous invite vraiment à entrer en matière.
 </t>
   </si>
@@ -582,6 +583,160 @@
 Certes, les formations existent, mais il n'y a pas d'uniformité en la matière, il n'y a pas de systématisme et, surtout, il n'y a pas d'obligation. De ce point de vue, seule une réglementation à l'échelle fédérale permet d'assurer cette uniformité des formations des autorités de poursuite judiciaire. En outre, un avis de droit a été demandé par le Bureau fédéral de l'égalité entre femmes et hommes pour évaluer la marge de manoeuvre de la Confédération, puisque le fédéralisme est effectivement l'un des obstacles, ou l'argument majeur, s'opposant à l'adoption de cette motion. 
 Cet avis de droit conclut qu'en vertu de l'article 123 de la Constitution, qui règle la compétence fédérale en matière de droit pénal et de droit de procédure pénale, lorsqu'il s'agit d'exécuter ou de garantir l'exécution uniforme du droit fédéral, ainsi que la mise en oeuvre du droit international, la Confédération peut intervenir. Or, tant la première que la deuxième condition sont remplies. D'une part, aujourd'hui, l'exécution n'est pas uniforme et reste lacunaire à l'échelle nationale. D'autre part, nos obligations internationales relèvent de la Convention d'Istanbul contre les violences à l'égard des femmes et de l'article 15 de cette convention, qui impose de garantir la formation des professionnels. Alors, si les cantons sont obligés d'agir en vertu de cette convention, la Confédération l'est aussi, ce qui justifierait dès lors de réglementer la formation des autorités de poursuite judiciaire à l'échelle nationale.
 Je rappelle que cette motion, tout comme celle de sa Commission des affaires juridiques, a été adoptée par le Conseil national. Je vous invite, non seulement dans l'intérêt des victimes, mais aussi des autorités qui sont chargées de les accompagner et de recueillir leurs paroles, à suivre la minorité de la commission et à adopter cette motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzog Eva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Staatsrechnung 2025 des Bundes schliesst mit einem Finanzierungsüberschuss von 259 Millionen Franken. Sie fällt damit deutlich besser aus als erwartet; veranschlagt war ein Defizit von 815 Millionen Franken. Der negative ausserordentliche Finanzierungssaldo von 926 Millionen Franken wurde durch den positiven ordentlichen Finanzierungssaldo von 1,185 Milliarden Franken mehr als ausgeglichen. Dies ist vor allem auf temporär höhere Gewinnsteuereinnahmen aus dem Kanton Genf im Umfang von 1,5 Mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Staatsrechnung 2025 des Bundes schliesst mit einem Finanzierungsüberschuss von 259 Millionen Franken. Sie fällt damit deutlich besser aus als erwartet; veranschlagt war ein Defizit von 815 Millionen Franken. Der negative ausserordentliche Finanzierungssaldo von 926 Millionen Franken wurde durch den positiven ordentlichen Finanzierungssaldo von 1,185 Milliarden Franken mehr als ausgeglichen. Dies ist vor allem auf temporär höhere Gewinnsteuereinnahmen aus dem Kanton Genf im Umfang von 1,5 Milliarden Franken zurückzuführen. 
+Die ordentlichen Einnahmen fielen insgesamt um 1,9 Milliarden Franken bzw. 2,2 Prozent höher aus als budgetiert und um 3,3 Milliarden Franken höher als im Vorjahr. Zugleich lagen die ordentlichen Ausgaben des Bundes 2025 erstmals seit der Einführung der Schuldenbremse im Jahr 2003 über dem Budgetwert. Dies ist unter anderem auf den Nachtragskredit für Horizon Europe zurückzuführen. Der ordentliche Finanzierungssaldo war positiv. Aus der Differenz ergibt sich ein struktureller Überschuss von 1,4 Milliarden Franken. In diesem Umfang war der ordentliche Finanzierungssaldo höher als von der Schuldenbremse vorgegeben. 
+Nennenswert sind im ausserordentlichen Haushalt die Mehreinnahmen aus der Zusatzausschüttung der Schweizerischen Nationalbank von 333 Millionen Franken und die budgetierte Sonderzuweisung der SNB aus den nicht ausgetauschten Banknoten der sechsten Serie von 237 Millionen Franken. Die beiden grössten Posten auf der Ausgabenseite sind die ausserordentlichen Ausgaben für die Schutzsuchenden aus der Ukraine sowie der einmalige Kapitalzuschuss an die SBB von 850 Millionen Franken, die ursprünglich für 2024 budgetiert waren.
+Weitere wichtige Kennzahlen: Erstmals seit der Corona-Pandemie konnte der Fehlbetrag des Amortisationskontos um 500 Millionen Franken reduziert werden. Neu beläuft sich der Fehlbetrag auf 26,3 Milliarden Franken. Das Ausgleichskonto hat unverändert einen positiven Stand von rund 20 Milliarden Franken. Die Nettoverschuldung hat 2025 leicht abgenommen und beträgt neu 140,1 Milliarden Franken. Die Nettoschuldenquote ging ebenfalls zurück, und zwar auf 16,1 Prozent des BIP. 
+Die Finanzkommission erhielt an ihrer Sitzung vom 26. Februar 2026 erste Informationen zum Ergebnis der Staatsrechnung. Anschliessend tagten die Subkommissionen. An der Sitzung vom 18. Mai 2026 hat die Finanzkommission die Rechnung 2025 und den Nachtrag I zum Voranschlag 2026 beraten. Im Gegensatz zur Einnahmenseite gab es auf der Ausgabenseite keine ausserordentlichen Vorkommnisse. Die Departemente sind daran, die beschlossenen Sparmassnahmen umzusetzen. Die Kommission hat zur Kenntnis genommen, dass die Digitalisierung allgemein vorangeht, aber nicht so schnell wie gewünscht, was auch an den Budgetkürzungen seitens des Parlamentes liegt. Weiter wurde berichtet, dass die erstinstanzlich hängigen Asylgesuche rückläufig sind. Ein Abbau der Gesuche war möglich, die Zahlen beim Bundesverwaltungsgericht sind aber weiter angestiegen. Die Verfahrensdauer ist nach wie vor weit weg von der ursprünglichen Zielsetzung im Rahmen der letzten Asylreform.
+Berichtet wurde über die ersten Gespräche mit dem neuen Leiter des Nachrichtendienstes des Bundes und über die höheren Ausgaben beim NDB.
+Thematisiert wurden ebenfalls die Probleme mit dem neuen Auszahlungssystem der Arbeitslosenkasse, Asalfutur. Die Kommission wurde darüber informiert, dass auf Ende März die Rückstände aufgeholt und alles ausbezahlt worden sei.
+Angesprochen wurde auch die Thematik, dass der Kapitalbezug der zweiten Säule nicht in den nationalen Finanzausgleich integriert ist. Die FK-S wird das Thema weiterverfolgen. 
+Informationen hat die Kommission auch erbeten bezüglich der Verhandlungen über die neue Vereinbarung mit der Schweizerischen Nationalbank. Auslöser waren die Aussagen des SNB-Präsidenten von Ende April in den Medien. Er sagte, dass für die SNB eine Eigenkapitalquote von 15 bis 20 Prozent zu tief sei. Aktuell sind es 19 Prozent. Eine Erhöhung würde bedeuten, dass statt einer Verbesserung sogar eine Verschlechterung gegenüber der heutigen Ausschüttungsvereinbarung drohen könnte, was in der Kommission kritisch gesehen wurde. Die Eidgenössische Finanzverwaltung erläuterte der Kommission die Rückstellungspolitik der SNB und bestätigte, dass sich die SNB eine Eigenkapitalquote zwischen 20 und 30 Prozent vorstelle, während andere Zentralbanken viel tiefere Werte hätten; so hätten beispielsweise die Fed oder die Bank of England eine Eigenkapitalquote von 1 Prozent, in Australien und Schweden sei das Eigenkapital negativ, in Singapur liege die Eigenkapitalquote bei 10 Prozent. Wenn die SNB mit ihrer Rückstellungspolitik tatsächlich dieses Ziel verfolge, müssten sich Bund und Kantone keine Hoffnungen auf höhere Ausschüttungen machen. Die Kommission wird das Thema weiterverfolgen, im Wissen, dass die Entscheide beim Bankrat angesiedelt sind. 
+Die Finanzministerin gab der Kommission auch einen Ausblick auf den Voranschlag 2027 und die kommenden Jahre.
+Nach Verabschiedung des EP 27 in beiden Räten ging der Bundesrat am 15. April noch von einem strukturellen Finanzierungsdefizit von 600 Millionen Franken aus und schlug erste mögliche Massnahmen zu dessen Bereinigung vor. An der Sitzung der FK-S vom 18. Mai konnte Bundesrätin Karin Keller-Sutter Entwarnung geben für den Voranschlag 2027, obwohl das Finanzdepartement für 2027 nochmals mit einer Verschlechterung um voraussichtlich rund 400 Millionen Franken rechnet, insbesondere aufgrund von Schätzkorrekturen bei den Sozialversicherungen und der Migration. Grund dafür sind deutliche Verbesserungen bei der Gewinnsteuer für juristische Personen, auch in anderen Kantonen als Genf. Zwar wies die Finanzministerin darauf hin, dass sich dieses ausserordentliche Wachstum auf einige wenige Unternehmen konzentriere. Sie sagte aber auch, dass die positive Entwicklung der Gewinnsteuern über diese Effekte hinaus breit abgestützt sei. Eine Mehrheit der Kantone habe Anfang Mai gemeldet, dass sie höhere Gewinnsteuereinnahmen hätten.
+Die Mehreinnahmen aus Genf waren hier ja schon mehrfach ein Thema, deshalb lediglich noch ein Wort zu ihrer Verbuchung. Die Eidgenössische Finanzkontrolle (EFK) hat verlangt, dass 1,5 Milliarden Franken schon im Jahr 2025 verbucht werden, ich habe diese eingangs erwähnt. 2026 sind es dann 1,3 Milliarden und 2027 noch 400 Millionen Franken. Es wäre auch denkbar gewesen, die Einnahmen über die Jahre zu glätten und kommende Budgets zu entlasten, doch die EFK bot nicht Hand dazu. So warnte die Finanzministerin auch bereits davor, dass die Lage angesichts der weiterhin bestehenden Herausforderungen, insbesondere bei der Armeefinanzierung und der AHV, ab 2028 wieder schwierig werden dürfte.
+Wenn keine zusätzlichen Einnahmen erschlossen werden könnten, würden ab 2028 beträchtliche strukturelle Defizite drohen. Ein Drittel der vom Bundesrat vorgesehenen Erhöhung der Mehrwertsteuer von 0,8 Prozent soll allein das bereits beschlossene Wachstum der Armee finanzieren, also den Aufwuchs auf 1 Prozent des BIP bis 2032. Der Bundesrat wird die Botschaft zur Armeefinanzierung nach der Sommerpause verabschieden. Neben der federführenden SiK wird sich auch die Finanzkommission in einem Mitbericht mit dem Geschäft befassen.
+Die Kommission tagte stets in Anwesenheit von Bundesrätin Karin Keller-Sutter und der Direktorin der Eidgenössischen Finanzverwaltung Sabine D'Amelio-Favez sowie weiteren Mitarbeiterinnen und Mitarbeitern des EFD, und sie tagte teilweise in Anwesenheit des Leiters der Finanzkontrolle Pascal Stirnimann und der zuständigen Mitarbeiterin. Ich danke den Beteiligten für ihre Begleitung unserer Diskussionen und für die guten Auskünfte.
+Nach Kenntnisnahme der Revisionsberichte der Eidgenössischen Finanzkontrolle sowie der Erwägungen und Schlussfolgerungen der Subkommissionen der FK-S beantragt die Kommission einstimmig, die Staatsrechnung 2025, die Sonderrechnungen für den Bahninfrastrukturfonds sowie den Nationalstrassen- und Agglomerationsverkehrsfonds, die Kreditüberschreitungen von 1,86 Milliarden Franken und die Bildung neuer Reserven in Höhe von 569 Millionen Franken zu genehmigen. Zum Schluss geht mein Dank an das Sekretariat der Finanzkommission für die umsichtige Vorbereitung, Organisation und Begleitung der Sitzungen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jans Beat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich danke dem Berichterstatter für seine sorgfältige und genaue Berichterstattung und beantrage namens des Bundesrates, Ihrer Kommission zu folgen und dem Entwurf eines Bundesbeschlusses über die Gewährleistung der geänderten Verfassungen der Kantone Bern, Glarus, Neuenburg, Genf und Jura zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zopfi Mathias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die genannten Kantone haben Änderungen ihrer Verfassungen beschlossen, welche durch die Bundesversammlung zu gewährleisten sind. Die Staatspolitische Kommission hat dieses Geschäft anhand der Botschaft des Bundesrates an der Sitzung vom 26. und 27. März 2026 beraten und beantragt in allen Fällen, dass Gewährleistung zu erteilen sei.
+Im Falle des Kantons Bern werden die Amtsbezirke, die schon seit 2021 keine Funktion mehr haben, aus der Verfassung gestrichen. Diese Änderung betrifft die innere Or</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die genannten Kantone haben Änderungen ihrer Verfassungen beschlossen, welche durch die Bundesversammlung zu gewährleisten sind. Die Staatspolitische Kommission hat dieses Geschäft anhand der Botschaft des Bundesrates an der Sitzung vom 26. und 27. März 2026 beraten und beantragt in allen Fällen, dass Gewährleistung zu erteilen sei.
+Im Falle des Kantons Bern werden die Amtsbezirke, die schon seit 2021 keine Funktion mehr haben, aus der Verfassung gestrichen. Diese Änderung betrifft die innere Organisation des Kantons und ist bundesrechtskonform.
+Im Falle des Kantons Glarus werden diverse Verfassungsbestimmungen zur politischen Partizipation geändert. So sind beispielsweise Personen, die wegen Geisteskrankheit oder Geistesschwäche entmündigt sind, nicht mehr vom Stimmrecht ausgeschlossen, und der Regierungsrat ergreift Massnahmen, damit auch stimmen kann, wer wegen einer Behinderung nicht in der Lage ist, die für die Stimmabgabe nötigen Handlungen selbst vorzunehmen.
+Zu einer weiteren Änderung der Glarner Verfassung schreibt der Bundesrat in der Botschaft: "Sodann wird das Landsgemeindememorial nicht mehr verteilt, sondern auf der Website des Kantons zugänglich gemacht." Diese Bestimmung hat in der Kommission Diskussionen ausgelöst. Es wurde angemerkt, dass es der politischen Partizipation nicht förderlich sei, wenn sich der Zugang zu den nötigen Unterlagen für alle ohne Internetzugang verschlechtert. Allerdings ist das Zitat aus der Botschaft etwas zu absolut formuliert. Richtig müsste es heissen, dass das Landsgemeindememorial nicht mehr zwingend abgegeben werden müsse. Mit der Verfassungsänderung hat die Landsgemeinde des Kantons Glarus nämlich auch Artikel 59a des Gesetzes über die politischen Rechte geändert, in welchem in Absatz 3 festgehalten ist, dass das Landsgemeindememorial den Stimmberechtigten weiterhin mindestens in einem Exemplar pro Haushalt in physischer Form zuzustellen ist.
+Da der Kanton für jede Gesetzesänderung das obligatorische Referendum kennt, ist diese Bestimmung gleich geschützt, wie es die Verfassungsbestimmung ist. Artikel 59a Absatz 4 des genannten Gesetzes sieht allerdings vor, dass der Regierungsrat nach der Genehmigung durch den Landrat beschliessen kann, das Landsgemeindememorial nur noch auf Verlangen physisch zuzustellen. Auch wenn dies den Schutz wieder etwas relativiert, bleibt die Aussage in der Botschaft zu absolut, und die Kommission sieht keinen Anlass, die Gewährleistung aus diesem Grund nicht zu erteilen. Die zuständigen Behörden des Kantons Glarus werden sicher sorgfältig und mit der gebotenen Rücksicht von dieser Kompetenz Gebrauch machen, da der einfache Zugang zu den Unterlagen wichtig und sogar unentbehrlich für die politische Partizipation ist.
+Im Übrigen hat der Kanton Glarus die Bestimmungen zu den Gemeinden in der Verfassung geändert und damit insbesondere die Stellung der Gemeindeparlamente gestärkt, sofern die Gemeinden sich entscheiden würden, solche zu schaffen. Auch diese Änderung ist bundesrechtskonform und zu gewährleisten.
+Im Falle des Kantons Neuenburg wurde mit dem neuen Artikel 10a der Verfassung eine Bestimmung zum Schutz der digitalen Integrität eingefügt. In diesem Bereich ist durch das Datenschutzgesetz des Bundes die Bearbeitung von Personendaten natürlicher Personen bereits umfassend geregelt. Die Kantone haben aber Spielraum, die Bearbeitung von Personendaten durch kantonale und kommunale Behörden zu regeln. Die neue Bestimmung der Kantonsverfassung kann somit nur den Bereich betreffen, wo das Verhältnis zwischen dem Kanton Neuenburg und seinen Bürgerinnen und Bürgern betroffen ist. Mit dieser Einschränkung ist die Änderung der Neuenburger Verfassung bundesrechtskonform und zu gewährleisten.
+Im Kanton Genf wurden verschiedene Änderungen vorgenommen, die die Organisation der kantonalen Behörden bzw. Abläufe und z. B. die Unterschriftenzahl für kommunale Initiativ- und Referendumsbegehren betreffen. Sie sind allesamt bundesrechtskonform und zu gewährleisten.
+Schliesslich hat der Kanton Jura seine Verfassung nach dem Kantonswechsel von Moutier zum 1. Januar 2026 angepasst. Es ging darum, die Bestimmung zur Wahl des 60 Abgeordnete zählenden Kantonsparlamentes aufgrund dieses Wechsels anzupassen. Dem Wahlkreis Moutier werden neu 7 Sitze zugeteilt. Dies ist eine Frage der kantonalen Organisationsautonomie. Allerdings ist hier erwähnenswert, weshalb der Wahlkreis mit 7 Sitzen nicht gegen die bundesgerichtliche Rechtsprechung verstossen dürfte. Im Moment ist der Wahlkreis Moutier nach dieser Rechtsprechung mit 7 Sitzen eigentlich zu klein. Das sogenannte natürliche Quorum beträgt aufgrund der 7 Sitze 12,5 Prozent, was über der bundesgerichtlichen Limite von 10 Prozent und entsprechend 9 Sitzen liegt. Allerdings lässt das Bundesgericht Ausnahmen zu, wenn ein Wahlkreis nicht deutlich zu klein ist und historische, föderalistische, kulturelle, sprachliche oder religiöse Gründe vorliegen. Im vorliegenden Fall ist das Quorum nur leicht überschritten, und es gibt mit dem Kantonswechsel klarerweise Gründe für diese Ausnahme. Der Kanton Jura hat zudem in Aussicht gestellt, in der Legislatur ab 2031 eine Anpassung der Wahlkreise unter Berücksichtigung der bundesgerichtlichen Rechtsprechung vorzunehmen.
+Von Interesse könnte hier noch sein, dass sich die Kommission aufzeigen liess, in wie vielen Kantonen mit Verhältniswahlrecht Wahlkreise mit weniger als neun Sitzen bestehen, ohne dass ein doppelt proportionales Zuteilungsverfahren oder Wahlkreisverbünde zur Anwendung kommen. Betroffen sind die Kantone Luzern, Obwalden, Basel-Stadt, Waadt und Jura. 
+Der Kanton Jura nimmt zudem Änderungen an der kantonalen Schuldenbremse vor - auch dies im Rahmen des Kantonswechsels von Moutier. 
+Beide Änderungen sind bundesrechtskonform und zu gewährleisten. 
+Ich ersuche Sie deshalb, der Kommission zu folgen und sämtlichen Verfassungsänderungen die Gewährleistung zu erteilen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engler Stefan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eintreten ist obligatorisch [GZ]
+L'entrée en matière est acquise de plein droit
+[VS]
+[VS]
+Bundesbeschluss über die Gewährleistung der geänderten Verfassungen der Kantone Bern, Glarus, Neuenburg, Genf und Jura[GZ]
+Arrêté fédéral concernant la garantie des constitutions révisées des cantons de Berne, de Glaris, de Neuchâtel, de Genève et du Jura[GZ]
+[VS][GZ]
+Detailberatung - Discussion par article [GZ]
+[VS][GZ]
+Titel und Ingress, Art. 1-6[GZ]
+Antrag der Kommission [GZ]
+Zustimmung zum Entwurf des B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eintreten ist obligatorisch [GZ]
+L'entrée en matière est acquise de plein droit
+[VS]
+[VS]
+Bundesbeschluss über die Gewährleistung der geänderten Verfassungen der Kantone Bern, Glarus, Neuenburg, Genf und Jura[GZ]
+Arrêté fédéral concernant la garantie des constitutions révisées des cantons de Berne, de Glaris, de Neuchâtel, de Genève et du Jura[GZ]
+[VS][GZ]
+Detailberatung - Discussion par article [GZ]
+[VS][GZ]
+Titel und Ingress, Art. 1-6[GZ]
+Antrag der Kommission [GZ]
+Zustimmung zum Entwurf des Bundesrates
+[VS]
+Titre et préambule, art. 1-6[GZ]
+Proposition de la commission [GZ]
+Adhérer au projet du Conseil fédéral[GZ]
+[VS][GZ]
+Angenommen - Adopté
+[VS]
+Präsident (Engler Stefan, Präsident): Da Eintreten obligatorisch ist, findet keine Gesamtabstimmung statt. Das Geschäft geht an den Nationalrat.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fässler Daniel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir hatten fast genau vor zwei Jahren über die Gewährleistung der geänderten Verfassungen von vier Kantonen beraten. Während die Verfassungsrevisionen der Kantone Bern, Waadt und Jura zu keinen besonderen Bemerkungen Anlass gaben und demzufolge von beiden Räten die Gewährleistung erhielten, wurden die drei in einer Volksabstimmung vom 18. Juni 2023 angenommenen Änderungen der Verfassung der Republik und des Kantons Genf nur teilweise gewährleistet. Unproblematisch war das in einem neuen Artikel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir hatten fast genau vor zwei Jahren über die Gewährleistung der geänderten Verfassungen von vier Kantonen beraten. Während die Verfassungsrevisionen der Kantone Bern, Waadt und Jura zu keinen besonderen Bemerkungen Anlass gaben und demzufolge von beiden Räten die Gewährleistung erhielten, wurden die drei in einer Volksabstimmung vom 18. Juni 2023 angenommenen Änderungen der Verfassung der Republik und des Kantons Genf nur teilweise gewährleistet. Unproblematisch war das in einem neuen Artikel 38A festgeschriebene kantonale Grundrecht auf Ernährung. Mit einem einschränkenden Hinweis wurde das in Artikel 21A der Genfer Verfassung festgeschriebene Recht auf digitale Integrität gewährleistet.
+Zum dritten Punkt der Verfassungsrevision vom 18. Juni 2023 entschieden sich die eidgenössischen Räte für ein besonderes Vorgehen: Auf Antrag unserer Kommission wurde die damalige Vorlage aufgeteilt. Jener Teil, der gemäss Botschaft des Bundesrates vom 22. Mai 2024 höchstens teilweise hätte gewährleistet werden können, wurde aus dem Bundesbeschluss gestrichen und in einen folgenden Entwurf II verschoben.
+Es ging dabei um den durch die Stimmberechtigten des Kantons Genf neu gefassten Artikel 205. Dieser sieht im neuen Absatz 3 vor, dass der Kanton Genf in Ergänzung zur Bundesgesetzgebung eine durch paritätische Beiträge der Arbeitgeber und der Arbeitnehmenden finanzierte Versicherung von mindestens sechzehn Wochen bei Mutterschaft und von mindestens acht Wochen für den anderen Elternteil gewährleistet. Dies soll gemäss Absatz 4 bei Adoptionen und bei der Aufnahme zur dauerhaften Unterbringung, auf französisch "accueil avec hébergement à caractère permanent", analog gelten.
+Was waren die Gründe, weshalb diese Verfassungsbestimmung vor zwei Jahren nicht gewährleistet wurde? Nach Artikel 116 Absatz 3 der Bundesverfassung richtet der Bund eine Mutterschaftsversicherung ein. Der Bund verfügt somit diesbezüglich über einen umfassenden und konkurrenzierenden Gesetzgebungsauftrag. Der Bundesgesetzgeber hat gestützt darauf auch die Vaterschaftsentschädigung und die Adoptionsentschädigung eingerichtet. Einen Vorbehalt zugunsten der Kantone für eine weitergehende Regelung enthielt das Erwerbsersatzgesetz nur im Bereich der Mutterschafts- und der Adoptionsentschädigung. Einen Vorbehalt zugunsten der Kantone auch im Bereich des Vaterschaftsurlaubs hatten die eidgenössischen Räte 2019 abgelehnt. 2021 lehnten es zudem beide Räte ab, einer Standesinitiative des Kantons Jura Folge zu geben, die den Kantonen auch im Bereich des Vaterschaftsurlaubs bzw. für einen Elternurlaub eigene Kompetenzen einräumen wollte.
+Regierung und Parlament des Kantons Genf wurden daher vom Bund wiederholt darauf hingewiesen, dass es in diesem Bereich keinen kantonalen Spielraum gibt - leider ohne Erfolg. Es war daher folgerichtig, dass der Bundesrat mit der Botschaft vom 22. Mai 2024 beantragte, den bundesrechtswidrigen Teil der Verfassungsrevision nicht zu gewährleisten. Dass die eidgenössischen Räte diesem Antrag nicht folgten, sondern die Entscheidung auf später verschoben, hatte einen einfachen Grund: Der Bundesrat hatte 2023 eine Änderung des Erwerbsersatzgesetzes in die Vernehmlassung gegeben, die es den Kantonen erlauben würde, einen verlängerten Vaterschaftsurlaub zu gewähren und z. B. mit einem kantonalen Zuschlag auf die EO-Beiträge zu finanzieren. Das Parlament wollte daher mit der Frage der Gewährleistung zuwarten, bis klar ist, ob bzw. in welchen Bereichen für die Kantone ein zusätzlicher Spielraum geschaffen wird.
+Mit Beschlüssen vom 19. Dezember des letzten Jahres haben die beiden Räte das Bundesgesetz über den Erwerbsersatz revidiert. Die Referendumsfrist lief am 17. April 2026 unbenützt ab. Das EOG sieht nun in Artikel 16mbis explizit vor, dass die Kantone bei der Versicherung für den anderen Elternteil weitergehen können als der Bund. Diese Regelung gilt gemäss Artikel 16x auch bei den Adoptionen, e contrario aber nicht für die dauerhafte Unterbringung von Pflegekindern.
+Dazu enthält das EOG gar keine Bestimmungen. Die Genfer Verfassung sieht demgegenüber vor, dass die Arbeitgebenden und die Arbeitnehmenden auch für solche Fälle eine Versicherung finanzieren müssen, aus der für Pflegemütter eine Entschädigung für mindestens 16 Wochen auszurichten ist, für Pflegeväter für mindestens 8 Wochen. Für diesen Teil der im strittigen Verfassungsartikel des Kantons Genf vorgesehenen Versicherung fehlt es somit weiterhin an einer entsprechenden Grundlage im Bundesrecht beziehungsweise an einer den Kantonen eingeräumten Kompetenz. Absatz 4 von Artikel 205 der Verfassung des Kantons Genf ist daher in diesem Sinne und in diesem Bereich bundesrechtswidrig. 
+Gemäss Artikel 51 Absatz 2 der Bundesverfassung bedürfen die Kantonsverfassungen und somit auch deren Änderungen der Gewährleistung des Bundes. Die Gewährleistung ist zu erteilen, wenn die Kantonsverfassung beziehungsweise deren Änderung im Einklang mit dem Bundesrecht steht. Der Bundesrat beantragt nun, die kantonale Versicherung für den anderen Elternteil zu gewährleisten, dies auch bei Adoptionen, nicht aber bei der Aufnahme zur dauerhaften Unterbringung. Dies kommt mit Absatz 2 von Artikel 1 des zum Entwurf 2 vorliegenden Entwurfs des Bundesbeschlusses über die Gewährleistung der geänderten Verfassung des Kantons Genf zum Ausdruck. Die Textelemente "ou d'accueil avec hébergement à caractère permanent" und "ou accueillant" sollen gemäss Antrag des Bundesrates nicht gewährleistet werden. 
+Ihre Kommission hat sich am 27. März 2026 mit der Angelegenheit befasst. Sie beantragt Ihnen mit 11 zu 1 Stimmen bei 1 Enthaltung, Artikel 205 Absätze 3 und 4 der in der Volksabstimmung vom 18. Juni 2023 revidierten Verfassung der Republik und des Kantons Genf die Gewährleistung aus den dargelegten Gründen nur teilweise zu erteilen. 
+Ständerat Maillard beantragt Ihnen mit seiner Minderheit, die Gewährleistung ohne Vorbehalt zu erteilen. Die Minderheit widersprach der juristischen Analyse nicht. Sie ist jedoch der Auffassung, dass dem Antrag der Kommissionsmehrheit eine übertriebene, unverhältnismässige Spitzfindigkeit zugrunde liege, die den Volksrechten und dem Föderalismus zu wenig Rechnung trage. Die Minderheit bezeichnete es zudem als heikel, dass man nun der Einschätzung des Bundesamtes für Justiz folge, vor Kurzem aber einen Hinweis desselben Bundesamtes übergangen habe, als es um einen Eingriff des Bundes bei den kantonalen Mindestlöhnen ging. 
+Abschliessend beantrage ich Ihnen namens der Kommission, Entwurf 2 des Bundesbeschlusses über die Gewährleistung der geänderten Verfassung des Kantons Genf gemäss vorliegendem Entwurf gutzuheissen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme vous le savez, le développement rapide des technologies d'intelligence artificielle offre des opportunités inédites aux autorités de sécurité pour anticiper, détecter ou élucider des infractions. L'analyse prédictive, la reconnaissance automatisée ou le traitement de données de masse permettent de cibler la criminalité organisée et transfrontalière tout en optimisant les ressources policières face à des flux d'informations exponentiels. Cependant, le déploiement de ces outils dans le domai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme vous le savez, le développement rapide des technologies d'intelligence artificielle offre des opportunités inédites aux autorités de sécurité pour anticiper, détecter ou élucider des infractions. L'analyse prédictive, la reconnaissance automatisée ou le traitement de données de masse permettent de cibler la criminalité organisée et transfrontalière tout en optimisant les ressources policières face à des flux d'informations exponentiels. Cependant, le déploiement de ces outils dans le domaine régalien de la sécurité présente des risques majeurs pour l'état de droit. L'usage d'algorithmes peut induire des biais discriminatoires, menacer la présomption d'innocence et porter des atteintes potentiellement irréversibles à la protection de la vie privée et à l'autodétermination des citoyens. Le domaine de la sécurité intérieure exige donc des garde-fous plus stricts que les secteurs commerciaux. Une réglementation transparente, éthique et juridiquement solide est indispensable pour garantir l'acceptabilité sociale de ces technologies.
+Le Conseil fédéral a déjà initié une réflexion transversale. Après l'adoption du postulat Dobler 23.3201, il a chargé le Département fédéral de justice et police de préparer un projet de réglementation générale de l'intelligence artificielle d'ici fin 2026. Toutefois, ce cadre horizontal ne saurait suffire. La police et la poursuite pénale se distinguent par leur capacité à déployer la contrainte étatique. Cette spécificité exige une analyse ciblée et sectorielle. De plus, l'architecture fédéraliste de la Suisse impose une approche coordonnée. La souveraineté des cantons en matière de police doit être rigoureusement articulée avec les compétences fédérales de procédure pénale. Le rapport que je demande devra poser les bases d'un cadre national harmonisé, évitant la fragmentation juridique entre les cantons tout en respectant leurs prérogatives.
+Enfin, l'intégration de l'intelligence artificielle soulève la question critique de la souveraineté numérique. Le recours à des prestataires externes, souvent basés hors de Suisse, expose nos infrastructures de sécurité à des risques de dépendance technologique, de perte de contrôle des algorithmes et de fuite de données sensibles. Face à l'importance stratégique de la capacité d'action de l'État, la Suisse doit fixer des critères d'acquisition stricts. Le rapport devra définir des exigences claires en matière d'auditabilité, d'explicabilité des codes sources et d'hébergement sécurisé des données pour garantir une autonomie stratégique durable.
+Je remercie le Conseil fédéral de proposer l'acceptation de mon postulat, signe qu'il est conscient des problèmes soulevés. Je vous invite à en faire de même.
 </t>
   </si>
 </sst>
@@ -636,8 +791,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I32" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I38" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I38"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1859,6 +2014,178 @@
         <v>132</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" t="s">
+        <v>136</v>
+      </c>
+      <c r="I33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>138</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34"/>
+      <c r="F34" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" t="s">
+        <v>140</v>
+      </c>
+      <c r="I34" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>141</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>142</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>143</v>
+      </c>
+      <c r="G35" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" t="s">
+        <v>144</v>
+      </c>
+      <c r="I35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>146</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
+        <v>147</v>
+      </c>
+      <c r="E36" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36" t="s">
+        <v>148</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" t="s">
+        <v>149</v>
+      </c>
+      <c r="I36" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>152</v>
+      </c>
+      <c r="E37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" t="s">
+        <v>153</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" t="s">
+        <v>154</v>
+      </c>
+      <c r="I37" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>156</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" t="s">
+        <v>157</v>
+      </c>
+      <c r="I38" t="s">
+        <v>158</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -306,15 +306,15 @@
     <t xml:space="preserve">375342</t>
   </si>
   <si>
-    <t xml:space="preserve">Permettez-moi d'apporter quelques mots en français dans ce débat qui semble surtout concerné les Suisses alémaniques, alors qu'il concerne toute la Suisse, tous les cantons suisses et tous les citoyens de ce pays. Oui, personne ne conteste que le 8 mars dernier, une majorité du peuple a accepté la réforme qui lui était proposée au travers de l'imposition individuelle. Oui, le peuple a voulu mettre un terme à cette inégalité qui durait depuis bien trop longtemps. Cependant, le peuple était mis de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permettez-moi d'apporter quelques mots en français dans ce débat qui semble surtout concerné les Suisses alémaniques, alors qu'il concerne toute la Suisse, tous les cantons suisses et tous les citoyens de ce pays. Oui, personne ne conteste que le 8 mars dernier, une majorité du peuple a accepté la réforme qui lui était proposée au travers de l'imposition individuelle. Oui, le peuple a voulu mettre un terme à cette inégalité qui durait depuis bien trop longtemps. Cependant, le peuple était mis devant un choix cornélien ; vraiment cornélien. Beaucoup de gens, lors de la campagne, ont choisi cette option de peur de voir cette inégalité se poursuivre.
-Ce choix cornélien, vous le connaissez : il était d'accepter de mettre un terme à cette inégalité et d'accepter un modèle compliqué qui crée d'autres inégalités et qui conduit à des divisions, souvent antisociales, ou de refuser cette réforme et voir cette inégalité encore se poursuivre. On peut d'ailleurs se poser la question : pourquoi le texte de l'initiative dont on parle aujourd'hui n'a-t-il pas été traité simultanément à l'initiative sur l'imposition individuelle ? En effet, dans ce cas, le peuple aurait eu un vrai choix sur le modèle qu'il entend. Se contentait-il de régler une inégalité sur le plan fédéral qui dure depuis trop longtemps, ou bien voulait-il révolutionner le système fiscal, ce dont je ne suis absolument pas certain pour avoir discuté avec les gens ?
-Le peuple a tranché pour cette solution. Toutefois, aujourd'hui, soutenir l'initiative qui vous est proposée ne remet pas en cause la fin de cette inégalité entre les couples mariés et les autres, au contraire, et n'a pas d'incidence sur l'organisation familiale, contrairement à ce qu'on a pu entendre. Elle offre au peuple un véritable choix sur le modèle : régler un problème fédéral sans créer de nouvelles inégalités ou mettre en place un système bureaucratique sans amélioration claire pour une grande majorité des contribuables. Si l'initiative de rang constitutionnel est acceptée, elle rendra caduque la révision législative acceptée par le peuple. C'est assez clair pour ceux qui en douteraient ou qui auraient émis des avis contraires aujourd'hui.
+    <t xml:space="preserve">Permettez-moi d'apporter quelques mots en français à ce débat qui semble surtout concerner les Suisses alémaniques, alors qu'il concerne toute la Suisse, tous les cantons suisses et tous les citoyens de ce pays. Oui, personne ne conteste que le 8 mars dernier, la majorité du peuple a accepté la réforme qui lui était proposée au travers de l'imposition individuelle. Oui, le peuple a voulu mettre un terme à cette inégalité qui durait depuis bien trop longtemps. Cependant, le peuple était mis devan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permettez-moi d'apporter quelques mots en français à ce débat qui semble surtout concerner les Suisses alémaniques, alors qu'il concerne toute la Suisse, tous les cantons suisses et tous les citoyens de ce pays. Oui, personne ne conteste que le 8 mars dernier, la majorité du peuple a accepté la réforme qui lui était proposée au travers de l'imposition individuelle. Oui, le peuple a voulu mettre un terme à cette inégalité qui durait depuis bien trop longtemps. Cependant, le peuple était mis devant un choix cornélien, vraiment cornélien. Beaucoup de gens, lors de la campagne, ont choisi cette option de peur de voir cette inégalité se poursuivre.
+Ce choix cornélien, vous le connaissez : accepter de mettre un terme à cette inégalité et accepter un modèle compliqué qui crée d'autres inégalités et qui conduit à des divisions, souvent antisociales, ou refuser cette réforme et voir cette inégalité se poursuivre. On peut d'ailleurs se poser la question : pourquoi le texte de l'initiative dont on parle aujourd'hui n'a-t-il pas été traité simultanément à l'initiative sur l'imposition individuelle ? En effet, dans ce cas, le peuple aurait eu un vrai choix sur le modèle. Se contentait-il de régler une inégalité sur le plan fédéral qui dure depuis trop longtemps ou bien voulait-il révolutionner le système fiscal, ce dont je ne suis absolument pas certain pour avoir discuté avec les gens ?
+Le peuple a tranché pour cette solution. Toutefois, aujourd'hui, soutenir l'initiative qui vous est proposée ne remet pas en cause la fin de cette inégalité entre les couples mariés et les autres, au contraire, et n'a pas d'incidence sur l'organisation familiale, contrairement à ce qu'on a pu entendre. Elle offre au peuple un véritable choix de modèle : régler un problème fédéral sans créer de nouvelles inégalités ou mettre en place un système bureaucratique sans amélioration claire pour une grande majorité des contribuables. Si l'initiative de rang constitutionnel est acceptée, elle rendra caduque la révision législative acceptée par le peuple. C'est assez clair pour ceux qui en douteraient ou qui auraient émis des avis contraires.
 Il nous appartiendra à nous, parlementaires, de trouver une solution plus simple, plus égalitaire, comme les cantons l'ont fait, sans leur imposer, au passage, une révolution dont une majorité d'entre eux n'a pas voulu. Accepter l'initiative, ce n'est pas trahir la volonté du peuple, mais, au contraire, c'est lui donner l'occasion de choisir la méthode.
-Quant aux coûts, pour essayer de répondre à Madame Herzog, vous savez très bien que cela dépendra du modèle qui sera retenu par le Parlement. Ce coût, dans le débat sur l'imposition individuelle, a aussi évolué. Il pourra aussi évoluer dans les débats que nous aurons. Pour l'instant, la question se pose sur la méthode : comment régler cette inégalité qui dure depuis aussi longtemps ?
-Dans ce cadre-là, je vous invite à soutenir la proposition de la minorité, qui offrira un vrai choix au Parlement et à la population sur la méthode et sur le coût.
+Quant aux coûts, pour essayer de répondre à Madame Herzog, vous savez très bien que cela dépendra du modèle qui sera retenu par le Parlement. Ces coûts, dans le débat sur l'imposition individuelle, ont aussi évolué. Ils pourront aussi évoluer dans les débats que nous aurons. Pour l'instant, la question se pose sur la méthode : comment régler cette inégalité qui dure depuis aussi longtemps ?
+Dans ce cadre-là, je vous invite à soutenir la proposition de la minorité, qui offrira un vrai choix au Parlement et à la population sur la méthode et sur les coûts.
 </t>
   </si>
   <si>
@@ -343,13 +343,13 @@
     <t xml:space="preserve">375762</t>
   </si>
   <si>
-    <t xml:space="preserve">Comme l'a exposé de manière très exhaustive le rapporteur de la commission, il s'agit ici des mesures et des assainissements qui sont liés à la radioactivité d'origine naturelle. Le projet du Conseil fédéral prévoyait, par analogie aux mesures liées à la radioactivité d'origine anthropique, une base légale permettant de fixer des limites d'exposition à partir desquelles l'assainissement d'un site ou d'un bien-fonds serait obligatoire et de régler la prise en charge des coûts. Ici, on parle princ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comme l'a exposé de manière très exhaustive le rapporteur de la commission, il s'agit ici des mesures et des assainissements qui sont liés à la radioactivité d'origine naturelle. Le projet du Conseil fédéral prévoyait, par analogie aux mesures liées à la radioactivité d'origine anthropique, une base légale permettant de fixer des limites d'exposition à partir desquelles l'assainissement d'un site ou d'un bien-fonds serait obligatoire et de régler la prise en charge des coûts. Ici, on parle principalement de la pollution au radon. Vous savez qu'il est présent en Suisse de manière inégale, mais assez largement dans certaines régions, notamment dans l'Arc jurassien et l'Arc alpin. Concrètement - le rapporteur a également cité plusieurs chiffres -, 10 pour cent des bâtiments en Suisse dépassent le plafond d'exposition de 300 becquerels par mètre cube.
-Quels sont les risques de ces valeurs supérieures aux limites d'exposition ? Une étude a permis d'estimer que le radon est responsable d'environ 200 à 300 décès par an imputables au cancer du poumon, soit 8,3 pour cent du total des décès liés à ce cancer ; un chiffre qui n'est qu'une moyenne, puisqu'il peut aller jusqu'à 15 pour cent dans les cantons particulièrement exposés, comme mon canton, le canton du Jura, mais également le Tessin, par exemple. Ainsi, le radon représente la deuxième cause de cancer du poumon après la consommation de tabac. L'exposition au radon constitue donc un véritable enjeu de santé publique. Dès lors, si l'on renonce à une base légale pour la radioactivité d'origine naturelle, les cantons seraient considérablement freinés dans leur possibilité d'action dans ce domaine. Je rappelle qu'on parle notamment d'assainissements dans les écoles ou dans les jardins d'enfants, à savoir pour un groupe de population particulièrement vulnérable.
-Le Conseil national a estimé que l'absence de dispositions légales suffisamment précises pour assurer l'assainissement des biens-fonds pollués risque d'affaiblir la pratique actuelle en matière de radioactivité naturelle et, en particulier, de protection de la population, et constitue à cet égard un signal négatif. Il a donc adopté une solution de compromis, avec ce nouvel article 24b, qui permet au Conseil fédéral de fixer le plafond d'exposition à partir duquel des mesures sont nécessaires. Par ailleurs, cet article règle la prise en charge des frais liés aux examens et aux assainissements, ce qui correspond aussi à la volonté des cantons. Ainsi, la version adoptée par le Conseil national est plus ciblée que le projet initial, mais elle permet au Conseil fédéral de fixer des valeurs de référence et ménage la possibilité d'agir des cantons.
-Il a été fait allusion au fait que, lors du premier examen de ce projet de loi par notre conseil, il n'y avait pas eu de proposition de minorité à ce sujet. Toutefois, le Conseil national a fait preuve de la sagesse qui, il nous semble, a fait défaut à notre conseil en refusant de garantir le bon déroulement des assainissements de bien-fonds, et il a donc adopté à l'unanimité ce nouvel article 24b. Dès lors, il nous a semblé pertinent de mener cette discussion également dans notre chambre. C'est pourquoi je vous invite à suivre le Conseil national et à clore ainsi cette divergence.
+    <t xml:space="preserve">Comme l'a exposé de manière très exhaustive le rapporteur de la commission, il s'agit ici des mesures et des assainissements qui sont liés à la radioactivité d'origine naturelle. Le projet du Conseil fédéral prévoyait, par analogie aux mesures liées à la radioactivité d'origine anthropique, une base légale permettant de fixer des limites d'exposition à partir desquelles l'assainissement d'un site ou d'un bien-fonds serait obligatoire, et de régler la prise en charge des coûts. Ici, on parle prin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme l'a exposé de manière très exhaustive le rapporteur de la commission, il s'agit ici des mesures et des assainissements qui sont liés à la radioactivité d'origine naturelle. Le projet du Conseil fédéral prévoyait, par analogie aux mesures liées à la radioactivité d'origine anthropique, une base légale permettant de fixer des limites d'exposition à partir desquelles l'assainissement d'un site ou d'un bien-fonds serait obligatoire, et de régler la prise en charge des coûts. Ici, on parle principalement de la pollution au radon. Vous savez que ce dernier est présent en Suisse de manière inégale, mais assez largement dans certaines régions, notamment dans l'Arc jurassien et l'Arc alpin. Concrètement - le rapporteur a également cité plusieurs chiffres -, 10 pour cent des bâtiments en Suisse dépassent le plafond d'exposition de 300 becquerels par mètre cube.
+Quels sont les risques de ces valeurs supérieures aux limites d'exposition[NB]? Une étude a permis d'estimer que le radon était responsable d'environ 200 à 300 décès par an imputables au cancer du poumon, soit 8,3 pour cent du total des décès liés à ce cancer[NB]; un chiffre qui n'est qu'une moyenne, puisqu'il peut aller jusqu'à 15 pour cent dans les cantons particulièrement exposés, comme mon canton, le canton du Jura, mais également le Tessin, par exemple. Ainsi, le radon représente la deuxième cause de cancer du poumon après la consommation de tabac. L'exposition au radon constitue donc un véritable enjeu de santé publique. Dès lors, si l'on renonçait à une base légale pour la radioactivité d'origine naturelle, les cantons seraient considérablement freinés dans leur possibilité d'action dans ce domaine. Je rappelle qu'on parle notamment d'assainissements dans les écoles ou dans les jardins d'enfants, à savoir concernant un groupe de population particulièrement vulnérable.
+Le Conseil national a estimé que l'absence de dispositions légales suffisamment précises pour assurer l'assainissement des biens-fonds pollués risquait d'affaiblir la pratique actuelle en matière de radioactivité naturelle et, en particulier, de protection de la population, et constituait à cet égard un signal négatif. Il a donc adopté une solution de compromis, avec ce nouvel article 24b, qui permet au Conseil fédéral de fixer le plafond d'exposition à partir duquel des mesures sont nécessaires. Par ailleurs, cet article règle la prise en charge des frais liés aux examens et aux assainissements, ce qui correspond aussi à la volonté des cantons. Ainsi, la version adoptée par le Conseil national est plus ciblée que le projet initial, mais elle permet au Conseil fédéral de fixer des valeurs de référence et ménage la possibilité d'agir des cantons.
+Il a été fait allusion au fait que, lors du premier examen de ce projet de loi par notre conseil, il n'y avait pas eu de proposition de minorité à ce sujet. Toutefois, le Conseil national a fait preuve de la sagesse qui, il nous semble, a fait défaut à notre conseil, en refusant de garantir le bon déroulement des assainissements de bien-fonds, et il a donc adopté à l'unanimité ce nouvel article 24b. Dès lors, il nous a semblé pertinent de mener cette discussion également dans notre chambre. C'est pourquoi je vous invite à suivre le Conseil national et à clore ainsi cette divergence.
 </t>
   </si>
   <si>
@@ -359,8 +359,8 @@
     <t xml:space="preserve">Ici aussi, il s'agit de la poursuite de la croisade contre l'infraction par négligence que mène notre conseil. On sait pourtant que si elles sont commises par négligence, les infractions qui sont définies à l'article 44 n'en sont pas pour autant négligeables. En effet, il peut s'agir d'exercer sans autorisation des activités qui, justement, sont soumises au régime de l'autorisation, ou de ne pas prendre les mesures nécessaires pour respecter les limites de dose. Il peut s'agir également de se so</t>
   </si>
   <si>
-    <t xml:space="preserve">Ici aussi, il s'agit de la poursuite de la croisade contre l'infraction par négligence que mène notre conseil. On sait pourtant que si elles sont commises par négligence, les infractions qui sont définies à l'article 44 n'en sont pas pour autant négligeables. En effet, il peut s'agir d'exercer sans autorisation des activités qui, justement, sont soumises au régime de l'autorisation, ou de ne pas prendre les mesures nécessaires pour respecter les limites de dose. Il peut s'agir également de se soustraire à la dosimétrie qui est prescrite. On parle donc de pratiques - qu'elles soient intentionnelles ou commises par négligence - qui mettent en danger la population en raison du domaine que l'on traite, qui est, je le rappelle quand même, les doses de radioactivité qui sont admises.
-Ainsi, la proposition de votre commission ne vise pas seulement à biffer purement et simplement l'infraction par négligence du projet de loi. Elle vise aussi à biffer le montant de l'amende qui était prévu jusqu'à présent, à savoir 20 000 francs. Pour qu'un délit ou un crime, selon la gravité de l'infraction poursuivie, soit pénalisé d'une amende de 20 000 francs, on ne parle pas d'un cas de bagatelle. Par ailleurs, la clause de minimis qui a été prévue à l'article 44 alinéa 4 permet de donner la marge de manoeuvre nécessaire pour éviter de poursuivre et de chicaner les personnes ou les entreprises qui auraient réellement commis une infraction de peu de gravité par négligence. Cela crée également une forte asymétrie dans le texte de loi, puisque seule l'intention serait mentionnée à l'article 44. Dès lors, le risque serait évident que l'on plaide la négligence pour se soustraire à toute poursuite en cas d'infraction commise. La proposition qui vous est faite par votre commission constitue un recul par rapport au droit en vigueur et en regard des enjeux en matière de santé publique et de protection de la population. Il est primordial de ne pas accepter ce recul.
+    <t xml:space="preserve">Ici aussi, il s'agit de la poursuite de la croisade contre l'infraction par négligence que mène notre conseil. On sait pourtant que si elles sont commises par négligence, les infractions qui sont définies à l'article 44 n'en sont pas pour autant négligeables. En effet, il peut s'agir d'exercer sans autorisation des activités qui, justement, sont soumises au régime de l'autorisation, ou de ne pas prendre les mesures nécessaires pour respecter les limites de dose. Il peut s'agir également de se soustraire à la dosimétrie qui est prescrite. On parle donc de pratiques - qu'elles soient intentionnelles ou commises par négligence - qui mettent en danger la population en raison du domaine que l'on traite, qui concerne, je le rappelle quand même, les doses de radioactivité qui sont admises.
+Ainsi, la proposition de votre commission ne vise pas seulement à biffer purement et simplement l'infraction par négligence du projet de loi. Elle vise aussi à biffer le montant de l'amende qui était prévu jusqu'à présent, à savoir 20 000 francs. Pour qu'un délit ou un crime, selon la gravité de l'infraction poursuivie, soit pénalisé d'une amende de 20 000 francs, on ne parle pas d'un cas de bagatelle. Par ailleurs, la clause de minimis qui a été prévue à l'article 44 alinéa 4 permet de donner la marge de manoeuvre nécessaire pour éviter de poursuivre et de chicaner les personnes ou les entreprises qui auraient réellement commis par négligence une infraction de peu de gravité. Cela crée également une forte asymétrie dans le texte de loi, puisque seule l'intention serait mentionnée à l'article 44. Dès lors, le risque serait évident que l'on plaide la négligence pour se soustraire à toute poursuite en cas d'infraction commise. La proposition qui vous est faite par votre commission constitue un retour en arrière par rapport au droit en vigueur et en regard des enjeux en matière de santé publique et de protection de la population. Il est primordial de ne pas accepter ce recul.
 C'est pourquoi je vous invite, comme l'a fait le Conseil national, à maintenir la version du Conseil fédéral et à éliminer ainsi cette dernière divergence.
 </t>
   </si>
@@ -373,23 +373,23 @@
   </si>
   <si>
     <t xml:space="preserve">Il m'appartient de vous présenter un bref rapport de l'audition que la Commission de gestion a menée avec Mme la conseillère fédérale Karin Keller-Sutter, cheffe du Département fédéral des finances, lors de l'examen du rapport de gestion 2025 du Conseil fédéral. Je concentrerai mon propos sur les deux thèmes choisis par Mme la conseillère fédérale, à savoir la situation des finances fédérales et la réglementation bancaire.
-Premièrement, s'agissant des évolutions et perspectives du budget fédéral pour les années 2027 à 2029, il faut constater une détérioration initiale en 2027. Le budget de l'année 2027 tablait d'abord sur un équilibre, avant d'afficher un déficit structurel estimé entre 400 et 600 millions de francs. Ce recul découle des coupes parlementaires dans le programme de réexamen des tâches - ou Programme d'allègement budgétaire 2027 - ou de l'extension du programme européen Horizon par exemple. 
-Concernant les nouvelles charges, le budget de 2027 subit une aggravation supplémentaire de 400 millions de francs au niveau des dépenses, causée par des corrections d'estimations pour les assurances sociales et la migration. 
-Concernant la détente finale et la stabilisation, on relève que malgré ces hausses de dépenses, une nette embellie du côté des recettes permet d'anticiper une détente pour le budget de 2027. De plus, un équilibre structurel redevient possible pour 2028 et 2029, et l'année 2029 affiche un besoin de correction réduit à 300 millions de francs. 
+Premièrement, s'agissant des évolutions et perspectives du budget fédéral pour les années 2027 à 2029, il faut constater une détérioration initiale en 2027. Le budget de l'année 2027 tablait d'abord sur un équilibre, avant d'afficher un déficit structurel estimé entre 400 et 600 millions de francs. Ce recul découle des coupes parlementaires dans le programme de réexamen des tâches - ou Programme d'allègement budgétaire 2027 - ou de l'extension du programme européen Horizon, par exemple. 
+Concernant les nouvelles charges, le budget de 2027 subit une aggravation supplémentaire de 400 millions de francs au niveau des dépenses causée par des corrections d'estimations pour les assurances sociales et la migration. 
+Concernant la détente finale et la stabilisation, on relève que, malgré ces hausses de dépenses, une nette embellie du côté des recettes permet d'anticiper une détente pour le budget de 2027. De plus, un équilibre structurel redevient possible pour 2028 et 2029, et l'année 2029 affiche un besoin de correction réduit à 300 millions de francs. 
 Concernant la fin du recours au compte extraordinaire, pour la première fois depuis la pandémie de COVID-19, le budget de 2027 ne sollicitera plus de dépenses extraordinaires. Les coûts liés à l'accueil des personnes en provenance d'Ukraine seront pleinement intégrés au budget ordinaire.
 Concernant la dynamique et les incertitudes du côté des recettes fiscales et la hausse marquée de l'impôt sur le bénéfice, les recettes provenant des entreprises connaissent une forte croissance à large échelle dans de nombreux cantons. L'impact du canton de Genève pèse positivement, de même qu'une forte concentration de rentrées fiscales à Lucerne, Zurich et Bâle-Ville, générées par un petit nombre de sociétés. 
 Concernant le flou autour de l'impôt complémentaire de l'OCDE - c'est un point sur lequel la Commission de gestion s'est déjà penchée plusieurs fois -, cet impôt représente une grande inconnue. La taxe nationale est perçue pour la première fois cette année, et la taxe internationale suivra en 2027.
 Toutefois, à titre de rappel, seuls 25 pour cent de ces recettes reviennent à la Confédération, le reste allant aux cantons. Les cantons prévoient des rendements inférieurs aux attentes, et aucun chiffre fiable ne sera disponible avant septembre.
-Concernant les effets différés de la valeur locative : l'abolition de la valeur locative n'entrera en vigueur qu'en 2029 et la baisse des recettes qui en découlera, d'environ 320 millions francs, ne se fera donc ressentir qu'à partir du budget 2030.
+Concernant les effets différés de la valeur locative, l'abolition de la valeur locative n'entrera en vigueur qu'en 2029 et la baisse des recettes qui en découlera, d'environ 320 millions francs, ne se fera donc ressentir qu'à partir du budget 2030.
 Quant aux questions ou aux remarques qui sont parfois formulées sur la différence qu'il y a entre le budget et les comptes, Mme la conseillère fédérale nous a rappelé qu'à plusieurs reprises, notamment les trois dernières années, cette différence n'est que de l'ordre de 0,3 pour cent de l'ensemble des charges du budget de la Confédération.
 Concernant les grands défis et financements, notamment de l'armée, de l'AVS et de la recherche, j'aborde en premier lieu le financement de l'armée et de la sécurité. Pour faire progresser les dépenses militaires à 1 pour cent du PIB d'ici 2032, l'armée nécessite près de 3 milliards de francs supplémentaires par an. Le Conseil fédéral propose une hausse de la TVA, dont un tiers servira directement à combler ce besoin de financement dès 2028. Le Parlement étudie aussi d'autres pistes, comme la baisse temporaire de la part de l'impôt fédéral direct versé aux cantons. La mise en oeuvre de la 13e rente AVS, qui a été demandée par le peuple, représente une facture ouverte de 1 milliard de francs. Pour 2027, ce montant est compensé par des économies internes, mais son financement à long terme divise le Parlement, comme nous l'avons encore vu hier, entre un financement uniquement via la TVA ou combiné avec des pourcentages salariaux.
 Au sujet des pressions futures sur la recherche, des dépenses supplémentaires potentielles menacent le budget dès 2028, car la Commission européenne souhaite augmenter les budgets des programmes Horizon Europe et Erasmus.
-Concernant la marge de manoeuvre politique et les réformes structurelles, nous avons les mains liées face aux dépenses. La forte extension des dépenses restreint fortement la marge de manoeuvre de la Confédération. Pour retrouver une capacité d'action politique, le Conseil fédéral prône une stricte retenue sur les dépenses plutôt que de nouvelles hausses d'impôts. Concernant le dilemme des dépenses liées, le programme d'allègement budgétaire 2027 ciblait pour deux tiers des dépenses liées, à savoir des subventions. Pour dégager des moyens financiers massifs à l'avenir, la Suisse devra accepter des réformes structurelles profondes - relèvement de l'âge de la retraite, réduction de la part cantonale à l'impôt fédéral direct ou baisse de sa participation à la péréquation financière, soit des sujets qui risquent de fâcher, et pas seulement au Parlement.
+Concernant la marge de manoeuvre politique et les réformes structurelles, nous avons les mains liées face aux dépenses. La forte expansion des dépenses restreint fortement la marge de manoeuvre de la Confédération. Pour retrouver une capacité d'action politique, le Conseil fédéral prône une stricte retenue sur les dépenses plutôt que de nouvelles hausses d'impôts. Concernant le dilemme des dépenses liées, le programme d'allègement budgétaire 2027 ciblait pour deux tiers des dépenses liées, à savoir des subventions. Pour dégager des moyens financiers massifs à l'avenir, la Suisse devra accepter des réformes structurelles profondes[NB]: relèvement de l'âge de la retraite, réduction de la part cantonale à l'impôt fédéral direct ou baisse de sa participation à la péréquation financière, soit des sujets qui risquent de fâcher, et pas seulement au Parlement.
 Concernant l'historique des mesures fiscales déjà prises, le Conseil fédéral rappelle avoir déjà sollicité la population avec la hausse de la TVA pour AVS 21, l'imposition de l'OCDE, l'augmentation de la taxe sur le tabac et la fin de l'allègement fiscal pour les voitures électriques.
 En résumé, la situation financière est en voie d'amélioration, mais un grand nombre d'inconnues ne facilitent pas la planification ni les prévisions. Toutes ces informations sont utiles à la Commission de gestion, même si celle-ci ne s'occupe pas en priorité des finances, mais bel et bien de gestion.
-Concernant la réglementation bancaire liée à la crise de Credit Suisse, les pressions des lobbies et le chantier législatif "too big to fail", le Département fédéral des finances a fait de cette réglementation sa priorité. Des travaux majeurs sont en cours, basés sur les propositions du Conseil fédéral, les motions parlementaires et les conclusions de la Commission d'enquête parlementaire , afin de combler les failles des banques d'importance systémique.
-Concernant le lobbying agressif et les pressions sur le Parlement, les parlementaires ont confié s'être sentis soumis à une pression intense et inconfortable de la part des lobbyistes craignant des sanctions financières, notamment la suppression de subventions pour leur parti s'ils soutenaient la réglementation bancaire. Ceci interpelle beaucoup la Commission de gestion.
-Concernant la tentative de déstabilisation des institutions - autre sujet extrêmement critique pour la Commission de gestion -, au-delà du cas de la presse où UBS a retiré ses publicités au journal "Finanz und Wirtschaft" en raison de sa ligne éditoriale, des manoeuvres ont été entreprises pour diviser le Conseil fédéral, à tel point que le gouvernement a exceptionnellement rendu public le fait que les choix qu'il a faits quant au projet de réglementation bancaire se sont faits à l'unanimité. Le Conseil fédéral est conscient qu'il évolue en terrain miné, mais il veut tenir le cap qu'il s'est fixé. Il transmettra bientôt ses propositions au Parlement, ce dont nous lui savons gré.
+Concernant la réglementation bancaire liée à la crise de Credit Suisse, les pressions des lobbies et le chantier législatif "too big to fail", le Département fédéral des finances a fait de cette réglementation sa priorité. Des travaux majeurs sont en cours, basés sur les propositions du Conseil fédéral, les motions parlementaires et les conclusions de la Commission d'enquête parlementaire, afin de combler les failles des banques d'importance systémique.
+Concernant le lobbying agressif et les pressions sur le Parlement, les parlementaires ont confié s'être sentis soumis à une pression intense et inconfortable de la part des lobbyistes, craignant des sanctions financières, notamment la suppression de subventions pour leur parti s'ils soutenaient la réglementation bancaire. Ceci interpelle beaucoup la Commission de gestion.
+Concernant la tentative de déstabilisation des institutions, autre sujet extrêmement critique pour la Commission de gestion, au-delà du cas de la presse où UBS a retiré ses publicités au journal "Finanz und Wirtschaft" en raison de sa ligne éditoriale, des manoeuvres ont été entreprises pour diviser le Conseil fédéral, à tel point que le gouvernement a exceptionnellement rendu public le fait que les choix qu'il a faits quant au projet de réglementation bancaire se sont faits à l'unanimité. Le Conseil fédéral est conscient qu'il évolue en terrain miné, mais il veut tenir le cap qu'il s'est fixé. Il transmettra bientôt ses propositions au Parlement, ce dont nous lui savons gré.
 </t>
   </si>
   <si>
@@ -737,6 +737,66 @@
 Le Conseil fédéral a déjà initié une réflexion transversale. Après l'adoption du postulat Dobler 23.3201, il a chargé le Département fédéral de justice et police de préparer un projet de réglementation générale de l'intelligence artificielle d'ici fin 2026. Toutefois, ce cadre horizontal ne saurait suffire. La police et la poursuite pénale se distinguent par leur capacité à déployer la contrainte étatique. Cette spécificité exige une analyse ciblée et sectorielle. De plus, l'architecture fédéraliste de la Suisse impose une approche coordonnée. La souveraineté des cantons en matière de police doit être rigoureusement articulée avec les compétences fédérales de procédure pénale. Le rapport que je demande devra poser les bases d'un cadre national harmonisé, évitant la fragmentation juridique entre les cantons tout en respectant leurs prérogatives.
 Enfin, l'intégration de l'intelligence artificielle soulève la question critique de la souveraineté numérique. Le recours à des prestataires externes, souvent basés hors de Suisse, expose nos infrastructures de sécurité à des risques de dépendance technologique, de perte de contrôle des algorithmes et de fuite de données sensibles. Face à l'importance stratégique de la capacité d'action de l'État, la Suisse doit fixer des critères d'acquisition stricts. Le rapport devra définir des exigences claires en matière d'auditabilité, d'explicabilité des codes sources et d'hébergement sécurisé des données pour garantir une autonomie stratégique durable.
 Je remercie le Conseil fédéral de proposer l'acceptation de mon postulat, signe qu'il est conscient des problèmes soulevés. Je vous invite à en faire de même.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page Pierre-André</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eintreten ist obligatorisch [GZ]
+L'entrée en matière est acquise de plein droit
+[VS]
+[VS]
+Bundesbeschluss über die Gewährleistung der geänderten Verfassungen der Kantone Bern, Glarus, Neuenburg, Genf und Jura[GZ]
+Arrêté fédéral concernant la garantie des constitutions révisées des cantons de Berne, de Glaris, de Neuchâtel, de Genève et du Jura[GZ]
+[VS][GZ]
+Detailberatung - Discussion par article [GZ]
+[VS][GZ]
+Titel und Ingress, Art. 1-6[GZ]
+Antrag der Kommission [GZ]
+Zustimmung zum Entwurf des Bundesrates
+[VS]
+Titre et préambule, art. 1-6[GZ]
+Proposition de la commission [GZ]
+Adhérer au projet du Conseil fédéral [GZ]
+[VS][GZ]
+Angenommen - Adopté
+[VS]
+Le président (Page Pierre-André, président): L'entrée en matière étant acquise de plein droit, il n'y a pas de vote sur l'ensemble. Le deux conseils ayant pris des décisions concordantes, l'objet est définitivement adopté. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nous en sommes donc au deuxième tour de la discussion visant à revenir sur l'interdiction de construire de nouvelles centrales nucléaires et donc sur la décision du peuple de sortir du nucléaire, ainsi que sur l'héritage relativement courageux en matière de politique énergétique qui avait débouché sur l'acceptation de la stratégie énergétique 2050, qui donnait une trajectoire claire à la Suisse, misant résolument sur les énergies renouvelables.
+Le Conseil national a donné à cet objet le débat sé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nous en sommes donc au deuxième tour de la discussion visant à revenir sur l'interdiction de construire de nouvelles centrales nucléaires et donc sur la décision du peuple de sortir du nucléaire, ainsi que sur l'héritage relativement courageux en matière de politique énergétique qui avait débouché sur l'acceptation de la stratégie énergétique 2050, qui donnait une trajectoire claire à la Suisse, misant résolument sur les énergies renouvelables.
+Le Conseil national a donné à cet objet le débat sérieux qu'il méritait en regard des lacunes du contre-projet que nous présente le Conseil fédéral. On vous a parlé de la courte majorité que le renvoi au Conseil fédéral a obtenue au Conseil national. Je rappelle que cette courte majorité fait écho à des majorités beaucoup plus larges : celle des cantons, qui ont majoritairement rejeté le contre-projet, mais aussi la majorité des partis, qui, lors de la consultation, ont également rejeté le contre-projet à l'initiative Stop au blackout dans le rapport de consultation.
+En renvoyant le Conseil fédéral à sa copie, le Conseil national a tout simplement donné du crédit aux préoccupations légitimes qui se sont fait jour en lien avec les modalités de financement d'éventuelles centrales notamment, puisqu'on nous demande de donner une sorte de chèque en blanc - une décision de principe, comme cela a été dit - en faisant confiance à l'avenir et au fait qu'ultérieurement viendraient les prochaines étapes. Il a également donné du crédit au risque que ce rétropédalage en matière de nucléaire ferait courir à la priorisation des énergies renouvelables. Enfin, il a donné du crédit au fait que la question des déchets générés par les centrales nucléaires actuelles n'est toujours pas résolue, sans même parler des déchets supplémentaires que de nouvelles centrales viendraient à produire.
+Je ne vais pas revenir sur le fond et sur la raison pour laquelle nous devrions rouvrir la voie au nucléaire. J'aimerais simplement souligner que, quand bien même nous serions partisans de ce contre-projet, nous ne pourrions pas venir devant le peuple en lui disant : "Donnez-nous cette possibilité, et si l'occasion doit se présenter un jour, nous ferons les changements de loi nécessaires et vous présenterons à ce moment-là les demandes de crédit correspondantes." Vu l'importance du débat et le scepticisme qui s'est fait jour lors de la consultation, nous devons fournir un peu plus de matière à la population et au Parlement. C'est ce qu'a décidé le Conseil national.
+J'ajouterai que nous sommes à la veille d'entamer les discussions de fond sur l'accord sur l'électricité avec l'Union européenne. Le moment est quand même relativement mal choisi pour envoyer un signal un peu confus en faveur d'un revirement de notre politique énergétique, d'une réouverture aux centrales nucléaires qui nous garantirait une sécurité d'approvisionnement, alors même que ce sont des questions dont nous serons amenés à discuter dans le cadre de ces discussions sur l'accord sur l'électricité avec l'Union européenne. Dans ce contexte, c'est un signal mixte et un peu confus que nous envoyons, à un moment extrêmement mal choisi.
+C'est pourquoi je vous invite à suivre le Conseil national, à renvoyer le projet au Conseil fédéral, en le chargeant de revenir avec des informations plus étayées et fournies, de manière à ce que nous puissions, dans ce dossier si important, prendre une décision qui serait enfin éclairée.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Conseil des États, qui était le conseil prioritaire dans ce dossier, a examiné cet objet au premier trimestre 2026 et a recommandé de l'approuver, ce qui a été fait, par 37 voix contre 2 et 4 abstentions. Le Conseil national a examiné le dossier la semaine dernière et a créé une divergence à l'article 2, lettre c. Concrètement, il souhaite augmenter le contingent de l'armée jusqu'à 85 militaires pour répondre à des besoins supplémentaires de la KFOR, par 127 voix contre 62.
+Après le premier e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Conseil des États, qui était le conseil prioritaire dans ce dossier, a examiné cet objet au premier trimestre 2026 et a recommandé de l'approuver, ce qui a été fait, par 37 voix contre 2 et 4 abstentions. Le Conseil national a examiné le dossier la semaine dernière et a créé une divergence à l'article 2, lettre c. Concrètement, il souhaite augmenter le contingent de l'armée jusqu'à 85 militaires pour répondre à des besoins supplémentaires de la KFOR, par 127 voix contre 62.
+Après le premier examen sur le plan formel et après le premier examen dans chaque conseil, la suite de la discussion se limite exclusivement aux questions des divergences. C'est ainsi que nous en avons une à l'article 2 lettre c, puisque le Conseil national souhaite donner plus de latitude au Conseil fédéral en augmentant le nombre de militaires de 30 à 85.
+Quels sont les éléments centraux de cette décision ? Lors des débats, le Conseil national a approuvé la prolongation de la participation suisse à la KFOR pour la période 2027 à 2029. S'il s'accorde sur le maintien d'un effectif de base maximal de 215 militaires, il a choisi de modifier la marge de manoeuvre accordée au Conseil fédéral en cas de crise et de besoin. Le Conseil national veut donner au Conseil fédéral la compétence d'augmenter cet effectif à 85 militaires supplémentaires. Les principaux arguments sont les suivants. Premièrement, une situation sécuritaire volatile : la dynamique sur le terrain, notamment dans le nord du Kosovo, reste très fragile et instable. Les événements des dernières années ont prouvé que les tensions peuvent s'aggraver de manière soudaine. Deuxièmement, un besoin de flexibilité accrue : en cas de dégradation rapide, la KFOR peut requérir un renfort urgent de ses effectifs. Porter la réserve d'engagement à 85 personnes permet à la Suisse de réagir de façon autonome et dans un délai raisonnable, sans devoir solliciter une nouvelle approbation parlementaire d'urgence. Enfin, troisièmement, une contribution à la stabilité régionale : les partisans de cette hausse rappellent que la stabilité des Balkans occidentaux demeure un intérêt direct pour la politique de sécurité de la Suisse.
+La Commission de la politique de sécurité de notre conseil a examiné cette divergence hier matin. Après de brèves discussions, la commission vous propose de vous rallier à la proposition du Conseil national de porter l'effectif du renfort potentiel à maximum 85 militaires au lieu des 30 prévus initialement par le Conseil fédéral et le Conseil des États. Dans la mesure où la disposition est formulée de façon potestative - "peut" et non "doit" -, votre commission est convaincue que le Conseil fédéral fera un usage mesuré de cette marge de manoeuvre.
+Elle vous recommande donc à l'unanimité de soutenir la décision du Conseil national, soit un maximum de 85 militaires.
 </t>
   </si>
 </sst>
@@ -791,8 +851,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I38" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I41" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I41"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -2186,6 +2246,93 @@
         <v>158</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39" t="s">
+        <v>110</v>
+      </c>
+      <c r="G39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" t="s">
+        <v>149</v>
+      </c>
+      <c r="I39" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" t="s">
+        <v>163</v>
+      </c>
+      <c r="I40" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>165</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" t="s">
+        <v>39</v>
+      </c>
+      <c r="F41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" t="s">
+        <v>166</v>
+      </c>
+      <c r="I41" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -310,10 +310,10 @@
   </si>
   <si>
     <t xml:space="preserve">Permettez-moi d'apporter quelques mots en français à ce débat qui semble surtout concerner les Suisses alémaniques, alors qu'il concerne toute la Suisse, tous les cantons suisses et tous les citoyens de ce pays. Oui, personne ne conteste que le 8 mars dernier, la majorité du peuple a accepté la réforme qui lui était proposée au travers de l'imposition individuelle. Oui, le peuple a voulu mettre un terme à cette inégalité qui durait depuis bien trop longtemps. Cependant, le peuple était mis devant un choix cornélien, vraiment cornélien. Beaucoup de gens, lors de la campagne, ont choisi cette option de peur de voir cette inégalité se poursuivre.
-Ce choix cornélien, vous le connaissez : accepter de mettre un terme à cette inégalité et accepter un modèle compliqué qui crée d'autres inégalités et qui conduit à des divisions, souvent antisociales, ou refuser cette réforme et voir cette inégalité se poursuivre. On peut d'ailleurs se poser la question : pourquoi le texte de l'initiative dont on parle aujourd'hui n'a-t-il pas été traité simultanément à l'initiative sur l'imposition individuelle ? En effet, dans ce cas, le peuple aurait eu un vrai choix sur le modèle. Se contentait-il de régler une inégalité sur le plan fédéral qui dure depuis trop longtemps ou bien voulait-il révolutionner le système fiscal, ce dont je ne suis absolument pas certain pour avoir discuté avec les gens ?
-Le peuple a tranché pour cette solution. Toutefois, aujourd'hui, soutenir l'initiative qui vous est proposée ne remet pas en cause la fin de cette inégalité entre les couples mariés et les autres, au contraire, et n'a pas d'incidence sur l'organisation familiale, contrairement à ce qu'on a pu entendre. Elle offre au peuple un véritable choix de modèle : régler un problème fédéral sans créer de nouvelles inégalités ou mettre en place un système bureaucratique sans amélioration claire pour une grande majorité des contribuables. Si l'initiative de rang constitutionnel est acceptée, elle rendra caduque la révision législative acceptée par le peuple. C'est assez clair pour ceux qui en douteraient ou qui auraient émis des avis contraires.
+Ce choix cornélien, vous le connaissez[NB]: accepter de mettre un terme à cette inégalité et accepter un modèle compliqué qui crée d'autres inégalités et qui conduit à des divisions, souvent antisociales, ou refuser cette réforme et voir cette inégalité se poursuivre. On peut d'ailleurs se poser la question[NB]: pourquoi le texte de l'initiative dont on parle aujourd'hui n'a-t-il pas été traité simultanément à l'initiative sur l'imposition individuelle[NB]? En effet, dans ce cas, le peuple aurait eu un vrai choix sur le modèle. Se contentait-il de régler une inégalité sur le plan fédéral qui dure depuis trop longtemps ou bien voulait-il révolutionner le système fiscal, ce dont je ne suis absolument pas certain pour avoir discuté avec les gens[NB]?
+Le peuple a tranché pour cette solution. Toutefois, aujourd'hui, soutenir l'initiative qui vous est proposée ne remet pas en cause la fin de cette inégalité entre les couples mariés et les autres, au contraire, et n'a pas d'incidence sur l'organisation familiale, contrairement à ce qu'on a pu entendre. Elle offre au peuple un véritable choix de modèle[NB]: régler un problème fédéral sans créer de nouvelles inégalités ou mettre en place un système bureaucratique sans amélioration claire pour une grande majorité des contribuables. Si l'initiative de rang constitutionnel est acceptée, elle rendra caduque la révision législative acceptée par le peuple. C'est assez clair pour ceux qui en douteraient ou qui auraient émis des avis contraires.
 Il nous appartiendra à nous, parlementaires, de trouver une solution plus simple, plus égalitaire, comme les cantons l'ont fait, sans leur imposer, au passage, une révolution dont une majorité d'entre eux n'a pas voulu. Accepter l'initiative, ce n'est pas trahir la volonté du peuple, mais, au contraire, c'est lui donner l'occasion de choisir la méthode.
-Quant aux coûts, pour essayer de répondre à Madame Herzog, vous savez très bien que cela dépendra du modèle qui sera retenu par le Parlement. Ces coûts, dans le débat sur l'imposition individuelle, ont aussi évolué. Ils pourront aussi évoluer dans les débats que nous aurons. Pour l'instant, la question se pose sur la méthode : comment régler cette inégalité qui dure depuis aussi longtemps ?
+Quant aux coûts, pour essayer de répondre à Madame Herzog, vous savez très bien que cela dépendra du modèle qui sera retenu par le Parlement. Ces coûts, dans le débat sur l'imposition individuelle, ont aussi évolué. Ils pourront aussi évoluer dans les débats que nous aurons. Pour l'instant, la question se pose sur la méthode[NB]: comment régler cette inégalité qui dure depuis aussi longtemps[NB]?
 Dans ce cadre-là, je vous invite à soutenir la proposition de la minorité, qui offrira un vrai choix au Parlement et à la population sur la méthode et sur les coûts.
 </t>
   </si>
@@ -713,13 +713,7 @@
     <t xml:space="preserve">Wir hatten fast genau vor zwei Jahren über die Gewährleistung der geänderten Verfassungen von vier Kantonen beraten. Während die Verfassungsrevisionen der Kantone Bern, Waadt und Jura zu keinen besonderen Bemerkungen Anlass gaben und demzufolge von beiden Räten die Gewährleistung erhielten, wurden die drei in einer Volksabstimmung vom 18. Juni 2023 angenommenen Änderungen der Verfassung der Republik und des Kantons Genf nur teilweise gewährleistet. Unproblematisch war das in einem neuen Artikel </t>
   </si>
   <si>
-    <t xml:space="preserve">Wir hatten fast genau vor zwei Jahren über die Gewährleistung der geänderten Verfassungen von vier Kantonen beraten. Während die Verfassungsrevisionen der Kantone Bern, Waadt und Jura zu keinen besonderen Bemerkungen Anlass gaben und demzufolge von beiden Räten die Gewährleistung erhielten, wurden die drei in einer Volksabstimmung vom 18. Juni 2023 angenommenen Änderungen der Verfassung der Republik und des Kantons Genf nur teilweise gewährleistet. Unproblematisch war das in einem neuen Artikel 38A festgeschriebene kantonale Grundrecht auf Ernährung. Mit einem einschränkenden Hinweis wurde das in Artikel 21A der Genfer Verfassung festgeschriebene Recht auf digitale Integrität gewährleistet.
-Zum dritten Punkt der Verfassungsrevision vom 18. Juni 2023 entschieden sich die eidgenössischen Räte für ein besonderes Vorgehen: Auf Antrag unserer Kommission wurde die damalige Vorlage aufgeteilt. Jener Teil, der gemäss Botschaft des Bundesrates vom 22. Mai 2024 höchstens teilweise hätte gewährleistet werden können, wurde aus dem Bundesbeschluss gestrichen und in einen folgenden Entwurf II verschoben.
-Es ging dabei um den durch die Stimmberechtigten des Kantons Genf neu gefassten Artikel 205. Dieser sieht im neuen Absatz 3 vor, dass der Kanton Genf in Ergänzung zur Bundesgesetzgebung eine durch paritätische Beiträge der Arbeitgeber und der Arbeitnehmenden finanzierte Versicherung von mindestens sechzehn Wochen bei Mutterschaft und von mindestens acht Wochen für den anderen Elternteil gewährleistet. Dies soll gemäss Absatz 4 bei Adoptionen und bei der Aufnahme zur dauerhaften Unterbringung, auf französisch "accueil avec hébergement à caractère permanent", analog gelten.
-Was waren die Gründe, weshalb diese Verfassungsbestimmung vor zwei Jahren nicht gewährleistet wurde? Nach Artikel 116 Absatz 3 der Bundesverfassung richtet der Bund eine Mutterschaftsversicherung ein. Der Bund verfügt somit diesbezüglich über einen umfassenden und konkurrenzierenden Gesetzgebungsauftrag. Der Bundesgesetzgeber hat gestützt darauf auch die Vaterschaftsentschädigung und die Adoptionsentschädigung eingerichtet. Einen Vorbehalt zugunsten der Kantone für eine weitergehende Regelung enthielt das Erwerbsersatzgesetz nur im Bereich der Mutterschafts- und der Adoptionsentschädigung. Einen Vorbehalt zugunsten der Kantone auch im Bereich des Vaterschaftsurlaubs hatten die eidgenössischen Räte 2019 abgelehnt. 2021 lehnten es zudem beide Räte ab, einer Standesinitiative des Kantons Jura Folge zu geben, die den Kantonen auch im Bereich des Vaterschaftsurlaubs bzw. für einen Elternurlaub eigene Kompetenzen einräumen wollte.
-Regierung und Parlament des Kantons Genf wurden daher vom Bund wiederholt darauf hingewiesen, dass es in diesem Bereich keinen kantonalen Spielraum gibt - leider ohne Erfolg. Es war daher folgerichtig, dass der Bundesrat mit der Botschaft vom 22. Mai 2024 beantragte, den bundesrechtswidrigen Teil der Verfassungsrevision nicht zu gewährleisten. Dass die eidgenössischen Räte diesem Antrag nicht folgten, sondern die Entscheidung auf später verschoben, hatte einen einfachen Grund: Der Bundesrat hatte 2023 eine Änderung des Erwerbsersatzgesetzes in die Vernehmlassung gegeben, die es den Kantonen erlauben würde, einen verlängerten Vaterschaftsurlaub zu gewähren und z. B. mit einem kantonalen Zuschlag auf die EO-Beiträge zu finanzieren. Das Parlament wollte daher mit der Frage der Gewährleistung zuwarten, bis klar ist, ob bzw. in welchen Bereichen für die Kantone ein zusätzlicher Spielraum geschaffen wird.
-Mit Beschlüssen vom 19. Dezember des letzten Jahres haben die beiden Räte das Bundesgesetz über den Erwerbsersatz revidiert. Die Referendumsfrist lief am 17. April 2026 unbenützt ab. Das EOG sieht nun in Artikel 16mbis explizit vor, dass die Kantone bei der Versicherung für den anderen Elternteil weitergehen können als der Bund. Diese Regelung gilt gemäss Artikel 16x auch bei den Adoptionen, e contrario aber nicht für die dauerhafte Unterbringung von Pflegekindern.
-Dazu enthält das EOG gar keine Bestimmungen. Die Genfer Verfassung sieht demgegenüber vor, dass die Arbeitgebenden und die Arbeitnehmenden auch für solche Fälle eine Versicherung finanzieren müssen, aus der für Pflegemütter eine Entschädigung für mindestens 16 Wochen auszurichten ist, für Pflegeväter für mindestens 8 Wochen. Für diesen Teil der im strittigen Verfassungsartikel des Kantons Genf vorgesehenen Versicherung fehlt es somit weiterhin an einer entsprechenden Grundlage im Bundesrecht beziehungsweise an einer den Kantonen eingeräumten Kompetenz. Absatz 4 von Artikel 205 der Verfassung des Kantons Genf ist daher in diesem Sinne und in diesem Bereich bundesrechtswidrig. 
+    <t xml:space="preserve">Wir hatten fast genau vor zwei Jahren über die Gewährleistung der geänderten Verfassungen von vier Kantonen beraten. Während die Verfassungsrevisionen der Kantone Bern, Waadt und Jura zu keinen besonderen Bemerkungen Anlass gaben und demzufolge von beiden Räten die Gewährleistung erhielten, wurden die drei in einer Volksabstimmung vom 18. Juni 2023 angenommenen Änderungen der Verfassung der Republik und des Kantons Genf nur teilweise gewährleistet. Unproblematisch war das in einem neuen Artikel 38A festgeschriebene kantonale Grundrecht auf Ernährung. Mit einem einschränkenden Hinweis wurde das in Artikel 21A der Genfer Verfassung festgeschriebene Recht auf digitale Integrität gewährleistet.Zum dritten Punkt der Verfassungsrevision vom 18. Juni 2023 entschieden sich die eidgenössischen Räte für ein besonderes Vorgehen: Auf Antrag unserer Kommission wurde die damalige Vorlage aufgeteilt. Jener Teil, der gemäss Botschaft des Bundesrates vom 22. Mai 2024 höchstens teilweise hätte gewährleistet werden können, wurde aus dem Bundesbeschluss gestrichen und in eine folgende Vorlage 2 verschoben.Es ging dabei um den durch die Stimmberechtigten des Kantons Genf neu gefassten Artikel 205. Dieser sieht im neuen Absatz 3 vor, dass der Kanton Genf in Ergänzung zur Bundesgesetzgebung eine durch paritätische Beiträge der Arbeitgeber und der Arbeitnehmenden finanzierte Versicherung von mindestens sechzehn Wochen bei Mutterschaft und von mindestens acht Wochen für den anderen Elternteil gewährleistet. Dies soll gemäss Absatz 4 bei Adoptionen und bei der Aufnahme zur dauerhaften Unterbringung, auf französisch "accueil avec hébergement à caractère permanent", analog gelten.Was waren die Gründe, weshalb diese Verfassungsbestimmung vor zwei Jahren nicht gewährleistet wurde? Nach Artikel 116 Absatz 3 der Bundesverfassung richtet der Bund eine Mutterschaftsversicherung ein. Der Bund verfügt somit diesbezüglich über einen umfassenden und konkurrenzierenden Gesetzgebungsauftrag. Der Bundesgesetzgeber hat gestützt darauf auch die Vaterschaftsentschädigung und die Adoptionsentschädigung eingerichtet. Einen Vorbehalt zugunsten der Kantone für eine weitergehende Regelung enthielt das Erwerbsersatzgesetz nur im Bereich der Mutterschafts- und der Adoptionsentschädigung. Einen Vorbehalt zugunsten der Kantone auch im Bereich des Vaterschaftsurlaubs hatten die eidgenössischen Räte 2019 abgelehnt. 2021 lehnten es zudem beide Räte ab, einer Standesinitiative des Kantons Jura Folge zu geben, die den Kantonen auch im Bereich des Vaterschaftsurlaubs bzw. für einen Elternurlaub eigene Kompetenzen einräumen wollte.Regierung und Parlament des Kantons Genf wurden daher vom Bund wiederholt darauf hingewiesen, dass es in diesem Bereich keinen kantonalen Spielraum gibt - leider ohne Erfolg. Es war daher folgerichtig, dass der Bundesrat mit der Botschaft vom 22. Mai 2024 beantragte, den bundesrechtswidrigen Teil der Verfassungsrevision nicht zu gewährleisten. Dass die eidgenössischen Räte diesem Antrag nicht folgten, sondern die Entscheidung auf später verschoben, hatte einen einfachen Grund: Der Bundesrat hatte 2023 eine Änderung des Erwerbsersatzgesetzes in die Vernehmlassung gegeben, die es den Kantonen erlauben würde, einen verlängerten Vaterschaftsurlaub zu gewähren und z. B. mit einem kantonalen Zuschlag auf die EO-Beiträge zu finanzieren. Das Parlament wollte daher mit der Frage der Gewährleistung zuwarten, bis klar ist, ob bzw. in welchen Bereichen für die Kantone ein zusätzlicher Spielraum geschaffen wird.Mit Beschlüssen vom 19. Dezember des letzten Jahres haben die beiden Räte das Bundesgesetz über den Erwerbsersatz revidiert. Die Referendumsfrist lief am 17. April 2026 unbenützt ab. Das EOG sieht nun in Artikel 16mbis explizit vor, dass die Kantone bei der Versicherung für den anderen Elternteil weitergehen können als der Bund. Diese Regelung gilt gemäss Artikel 16x auch bei den Adoptionen, e contrario aber nicht für die dauerhafte Unterbringung von Pflegekindern.Dazu enthält das EOG gar keine Bestimmungen. Die Genfer Verfassung sieht demgegenüber vor, dass die Arbeitgebenden und die Arbeitnehmenden auch für solche Fälle eine Versicherung finanzieren müssen, aus der für Pflegemütter eine Entschädigung für mindestens 16 Wochen auszurichten ist, für Pflegeväter für mindestens 8 Wochen. Für diesen Teil der im strittigen Verfassungsartikel des Kantons Genf vorgesehenen Versicherung fehlt es somit weiterhin an einer entsprechenden Grundlage im Bundesrecht beziehungsweise an einer den Kantonen eingeräumten Kompetenz. Absatz 4 von Artikel 205 der Verfassung des Kantons Genf ist daher in diesem Sinne und in diesem Bereich bundesrechtswidrig. 
 Gemäss Artikel 51 Absatz 2 der Bundesverfassung bedürfen die Kantonsverfassungen und somit auch deren Änderungen der Gewährleistung des Bundes. Die Gewährleistung ist zu erteilen, wenn die Kantonsverfassung beziehungsweise deren Änderung im Einklang mit dem Bundesrecht steht. Der Bundesrat beantragt nun, die kantonale Versicherung für den anderen Elternteil zu gewährleisten, dies auch bei Adoptionen, nicht aber bei der Aufnahme zur dauerhaften Unterbringung. Dies kommt mit Absatz 2 von Artikel 1 des zum Entwurf 2 vorliegenden Entwurfs des Bundesbeschlusses über die Gewährleistung der geänderten Verfassung des Kantons Genf zum Ausdruck. Die Textelemente "ou d'accueil avec hébergement à caractère permanent" und "ou accueillant" sollen gemäss Antrag des Bundesrates nicht gewährleistet werden. 
 Ihre Kommission hat sich am 27. März 2026 mit der Angelegenheit befasst. Sie beantragt Ihnen mit 11 zu 1 Stimmen bei 1 Enthaltung, Artikel 205 Absätze 3 und 4 der in der Volksabstimmung vom 18. Juni 2023 revidierten Verfassung der Republik und des Kantons Genf die Gewährleistung aus den dargelegten Gründen nur teilweise zu erteilen. 
 Ständerat Maillard beantragt Ihnen mit seiner Minderheit, die Gewährleistung ohne Vorbehalt zu erteilen. Die Minderheit widersprach der juristischen Analyse nicht. Sie ist jedoch der Auffassung, dass dem Antrag der Kommissionsmehrheit eine übertriebene, unverhältnismässige Spitzfindigkeit zugrunde liege, die den Volksrechten und dem Föderalismus zu wenig Rechnung trage. Die Minderheit bezeichnete es zudem als heikel, dass man nun der Einschätzung des Bundesamtes für Justiz folge, vor Kurzem aber einen Hinweis desselben Bundesamtes übergangen habe, als es um einen Eingriff des Bundes bei den kantonalen Mindestlöhnen ging. 
@@ -757,11 +751,25 @@
 [VS][GZ]
 Titel und Ingress, Art. 1-6[GZ]
 Antrag der Kommission [GZ]
-Zustimmung zum Entwurf des Bundesrates
+Zustimmung zum Beschluss des</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eintreten ist obligatorisch [GZ]
+L'entrée en matière est acquise de plein droit
+[VS]
+[VS]
+Bundesbeschluss über die Gewährleistung der geänderten Verfassungen der Kantone Bern, Glarus, Neuenburg, Genf und Jura[GZ]
+Arrêté fédéral concernant la garantie des constitutions révisées des cantons de Berne, de Glaris, de Neuchâtel, de Genève et du Jura[GZ]
+[VS][GZ]
+Detailberatung - Discussion par article [GZ]
+[VS][GZ]
+Titel und Ingress, Art. 1-6[GZ]
+Antrag der Kommission [GZ]
+Zustimmung zum Beschluss des Ständerates
 [VS]
 Titre et préambule, art. 1-6[GZ]
 Proposition de la commission [GZ]
-Adhérer au projet du Conseil fédéral [GZ]
+Adhérer à la décision du Conseil des États[GZ]
 [VS][GZ]
 Angenommen - Adopté
 [VS]
@@ -797,6 +805,93 @@
 Quels sont les éléments centraux de cette décision ? Lors des débats, le Conseil national a approuvé la prolongation de la participation suisse à la KFOR pour la période 2027 à 2029. S'il s'accorde sur le maintien d'un effectif de base maximal de 215 militaires, il a choisi de modifier la marge de manoeuvre accordée au Conseil fédéral en cas de crise et de besoin. Le Conseil national veut donner au Conseil fédéral la compétence d'augmenter cet effectif à 85 militaires supplémentaires. Les principaux arguments sont les suivants. Premièrement, une situation sécuritaire volatile : la dynamique sur le terrain, notamment dans le nord du Kosovo, reste très fragile et instable. Les événements des dernières années ont prouvé que les tensions peuvent s'aggraver de manière soudaine. Deuxièmement, un besoin de flexibilité accrue : en cas de dégradation rapide, la KFOR peut requérir un renfort urgent de ses effectifs. Porter la réserve d'engagement à 85 personnes permet à la Suisse de réagir de façon autonome et dans un délai raisonnable, sans devoir solliciter une nouvelle approbation parlementaire d'urgence. Enfin, troisièmement, une contribution à la stabilité régionale : les partisans de cette hausse rappellent que la stabilité des Balkans occidentaux demeure un intérêt direct pour la politique de sécurité de la Suisse.
 La Commission de la politique de sécurité de notre conseil a examiné cette divergence hier matin. Après de brèves discussions, la commission vous propose de vous rallier à la proposition du Conseil national de porter l'effectif du renfort potentiel à maximum 85 militaires au lieu des 30 prévus initialement par le Conseil fédéral et le Conseil des États. Dans la mesure où la disposition est formulée de façon potestative - "peut" et non "doit" -, votre commission est convaincue que le Conseil fédéral fera un usage mesuré de cette marge de manoeuvre.
 Elle vous recommande donc à l'unanimité de soutenir la décision du Conseil national, soit un maximum de 85 militaires.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Büchel Roland Rino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Das Freihandelsabkommen zwischen den EFTA-Staaten und den Mercosur-Staaten ist kein Luxus und ist auch nichts Böses, auch wenn es die Sprecherin der Grünen Fraktion soeben so dargelegt hat. Es ist eine absolute Notwendigkeit für die Schweizer Exportwirtschaft, für unsere KMU, für den Wohlstand der Menschen im Land, für unsere Arbeitsplätze. Es geht hier um einen riesigen Markt von 270 Millionen Konsumentinnen und Konsumenten. Dieser Markt ist derzeit durch massive bürokratische Hürden behindert.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Das Freihandelsabkommen zwischen den EFTA-Staaten und den Mercosur-Staaten ist kein Luxus und ist auch nichts Böses, auch wenn es die Sprecherin der Grünen Fraktion soeben so dargelegt hat. Es ist eine absolute Notwendigkeit für die Schweizer Exportwirtschaft, für unsere KMU, für den Wohlstand der Menschen im Land, für unsere Arbeitsplätze. Es geht hier um einen riesigen Markt von 270 Millionen Konsumentinnen und Konsumenten. Dieser Markt ist derzeit durch massive bürokratische Hürden behindert. Unsere exportorientierten Unternehmen, von der Hightech-Firma bei mir im Rheintal bis zur Uhrenmanufaktur bei Bundesrätin Baume-Schneider oben im Jura, zahlen jedes Jahr Millionen Franken an Zöllen. Dieses Geld fehlt den Betrieben für Investitionen, für Forschung und vor allem für die Sicherung von Schweizer Arbeitsplätzen. Das scheint auf linker Seite nicht auf grosses Interesse zu stossen. Mit diesem Abkommen fallen künftig 95 Prozent der Zölle für Schweizer Ausfuhren weg. Das bedeutet konkret über 150 Millionen Franken Zolleinsparungen pro Jahr.
+Geschätzte Kolleginnen und Kollegen von der linken Ratsseite, wenn ich Ihre Anträge lese, kann ich nur denken, dass Sie die ganze Welt retten wollen. Was tun Sie wirklich? Sie untergraben die Existenzgrundlage unserer eigenen Bevölkerung - und vor allem diejenige der Menschen im Amazonasgebiet,die Sie schützen wollen. Ich werde es Ihnen nachher noch erklären. 
+Unsere Unternehmer und ihre Angestellten brauchen gleich lange Spiesse - nein, lieber noch längere als die Konkurrenz. Ich begrüsse es, dass Bundesrat, Bundespräsident und Wirtschaftsminister Guy Parmelin durch Freihandelsabkommen Handelsbeziehungen dort unterstützt, wo Potenzial vorhanden ist und wo Wachstum stattfindet.
+Zu unserer Landwirtschaft: Diesbezüglich bitte ich Sie, beim Antrag der Minderheit Haab gut zuzuhören. Dazu von meiner Seite, gerade nach den Voten, die wir gehört haben, noch zwei, drei Sätze. Jedes Freihandelsabkommen ist ein Kompromiss. Die SVP-Fraktion wird dem Antrag der Minderheit Haab geschlossen zustimmen. Kollege Portmann, ich glaube, Herr Haab wird es schaffen, Ihnen den Fonds de Roulement zu erklären und Ihnen zu erklären, dass das nicht Geld ist, das zum Fenster hinausgeschmissen wird, wie bei den Anträgen von der linken Seite, sondern dass es eine sinnvolle Investition in den Nachwuchs in der Landwirtschaft ist. Ich sage es Ihnen, Herr Haab: Haben Sie Geduld mit Herrn Portmann und erklären Sie es ihm locker und leicht.
+Unsere Landwirtschaft wird mit diesem Abkommen eben genau nicht überrollt. Wir schützen die Landwirtschaft, während wir gleichzeitig der Industrie neue Tore öffnen. Das ist eine ausgewogene, eine typisch schweizerische Lösung.
+Ich bitte Sie, nachher auch bei der Begründung meines Minderheitsantrags gut zuzuhören. Dazu ein paar Worte vorweg: Unser Wohlstand basiert zu grossen Teilen darauf, dass wir hochwertige Güter exportieren. Wir dürfen uns nicht von ideologischen Argumenten lähmen lassen, wie wir sie von der linken Seite jetzt schon gehört haben und - ich bin ziemlich sicher, ich bin sogar ganz sicher - noch viel stärker hören werden, wenn dann die Anträge an die Reihe kommen.
+Dieses Abkommen sichert Arbeitsplätze. Es entlastet unsere Betriebe vor unnötiger Bürokratie und stärkt die Unabhängigkeit unserer Wirtschaft. Wir können das natürlich auch aufs Spiel setzen, wenn Sie wollen. Zum Beispiel, indem wir den Inhalt der EU-Entwaldungsverordnung in das Abkommen aufnehmen; wie gesagt, ich werde nachher bei der Begründung meines Minderheitsantrags ein bisschen mehr dazu sagen. Wir können aber auch dafür sorgen, dass dieses gute Abkommen ein gutes Abkommen bleibt. Wie? Eben, indem Sie meinem Minderheitsantrag zustimmen und den Minderheitsanträgen von links nicht zustimmen.
+Stimmen wir für den Arbeitsplatz Schweiz, stimmen wir für die KMU. Die SVP-Fraktion bittet Sie daher, auf die Vorlage einzutreten und diesem zukunftsweisenden Abkommen zuzustimmen, insbesondere dann, wenn die Minderheit Haab dank Ihnen noch zur Mehrheit wird.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tschopp Jean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La forêt amazonienne est un écosystème indispensable pour notre planète. Aujourd'hui, elle est gravement menacée. L'évaluation d'impact environnemental du Secrétariat d'État à l'économie (SECO) nous apprend que le risque de défrichement est de 900 km2. C'est plus que la superficie du canton du Jura. Comment évaluez-vous ce risque considérable, sans garantie dans l'accord du Mercosur ?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le président de la Confédération, je profite de ce débat d'entrée en matière pour vous poser une question en lien avec les différences que nous pouvons constater entre l'accord conclu avec le Mercosur et celui conclu, par exemple, avec l'Indonésie. Ce dernier contient des approches axées sur les processus et les méthodes de production qui lient les avantages tarifaires à des conditions de production durables qui ne sont pas du tout présentes dans l'accord avec le Mercosur. Pourquoi le C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le président de la Confédération, je profite de ce débat d'entrée en matière pour vous poser une question en lien avec les différences que nous pouvons constater entre l'accord conclu avec le Mercosur et celui conclu, par exemple, avec l'Indonésie. Ce dernier contient des approches axées sur les processus et les méthodes de production qui lient les avantages tarifaires à des conditions de production durables qui ne sont pas du tout présentes dans l'accord avec le Mercosur. Pourquoi le Conseil fédéral a-t-il renoncé à cet instrument, alors que des baisses des droits de douane sont prévues pour des produits particulièrement sensibles tels que les dérivés du soja et la viande bovine ?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'objet que nous traitons aujourd'hui est complexe et sensible, mais il mérite toute notre attention tant il impacte le quotidien et la vie de centaines de familles. De quoi parle-t-on ? 
+La plupart du temps, un enfant vient au monde avec deux parents juridiques. Le lien de filiation est établi automatiquement pour la personne qui a porté l'enfant, qui devient mère à la naissance - c'est l'article 252 du code civil. Si le couple est marié, l'automatisme s'étend à la ou au partenaire en vertu de </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'objet que nous traitons aujourd'hui est complexe et sensible, mais il mérite toute notre attention tant il impacte le quotidien et la vie de centaines de familles. De quoi parle-t-on ? 
+La plupart du temps, un enfant vient au monde avec deux parents juridiques. Le lien de filiation est établi automatiquement pour la personne qui a porté l'enfant, qui devient mère à la naissance - c'est l'article 252 du code civil. Si le couple est marié, l'automatisme s'étend à la ou au partenaire en vertu de la présomption de parentalité. Ce sont les articles 255 et 255a du code civil. Cette présomption s'applique également aux couples mariés homosexuels, depuis l'introduction du mariage pour toutes et tous en 2020, qui ont recours aux méthodes de procréation prévues dans la loi fédérale sur la procréation médicalement assistée (LPMA), à savoir, par exemple, l'insémination clinique ou la fécondation in vitro. Mais il reste toutefois une lacune dans ce système d'établissement de la filiation qui concerne les enfants issus de méthodes qui ne sont pas couvertes par la LPMA, soit le don de sperme privé en Suisse ou à l'étranger, et d'autres procédures de procréation médicalement assistée à l'étranger. Dans ces cas de figure, si les couples hétérosexuels jouissent des mêmes droits que si l'enfant avait été conçu selon une méthode couverte par la LPMA, à savoir présomption de parentalité ou reconnaissance par le père, les couples homosexuels doivent, quant à eux - et il s'agit en l'occurrence de femmes -, passer par l'adoption de l'enfant de leur conjointe.
+Cette procédure d'adoption est actuellement longue, compliquée et très coûteuse. On parle de deux à trois ans après la naissance de l'enfant et de plusieurs milliers de francs en frais de procédure et d'avocat. Cette durée est due notamment à une année obligatoire de lien nourricier, obligeant la famille à vivre un an avec l'enfant, qui faisait de toute façon partie du projet parental. C'est cette année de lien nourricier que la présente révision prévoit d'abroger. Cette durée est également due à la longueur des procédures administratives jusqu'au rendu de la décision d'adoption. Ainsi, aujourd'hui, un enfant qui naît d'un couple homosexuel - enfant qui a pourtant été conçu comme un projet parental commun et que, pour ce faire, le couple a eu recours au don de sperme privé en Suisse ou à l'étranger, ou à une autre méthode de procréation à l'étranger - vit jusqu'à ses 2, 3, voire 4 ans avec un seul parent juridique. Cette situation engendre bien sûr une insécurité juridique qui est problématique, voire dramatique dans certains cas. On pense au cas de décès, par exemple, de la mère légale. En outre, en l'absence de toute reconnaissance du lien de filiation avec le deuxième parent, celui-ci ne possède pas, par exemple, de droit de visite en cas de séparation. Une décision du tribunal a été rendue dans ce sens, qui privait le deuxième parent d'un droit de visite après la séparation du couple, alors que l'enfant avait été conçu dans le cadre d'un projet parental commun et d'une communauté de vie.
+Ainsi, si les problèmes se font jour en cas de décès et de maladie, au-delà de ces situations extrêmes, l'insécurité juridique génère aussi de nombreuses complications au quotidien, car elles se répercutent non seulement sur les questions d'autorité parentale, d'entretien, d'assurance sociale et d'allocation familiale, mais aussi, par exemple, sur les décisions médicales.
+Ainsi, les problèmes suscités par cette situation et la nécessité d'intervenir rapidement ont été reconnus par le Parlement avec l'adoption de la motion 22.3382, "Pas d'entrave inutile à l'adoption de l'enfant du conjoint", qui a été détaillée par le rapporteur. Nous avons adopté cette motion à l'unanimité en décembre 2022, soit il y a déjà bientôt 4 ans, et donné ainsi mandat au Conseil fédéral de modifier les dispositions légales pour que, en cas d'adoption de l'enfant du conjoint, la condition portant sur le fait d'avoir fourni à ces enfants des soins pendant au moins un an soit supprimée. Le mandat que nous avons donné au Conseil fédéral était clair. Il était aussi circonscrit à ces cas particuliers. C'est exactement le projet que nous avons sur la table aujourd'hui. La suppression de cette obligation de lien nourricier nous permet d'accélérer un peu la procédure - de réduire au moins d'une année cette longue procédure d'adoption - et d'accélérer ainsi la sécurité juridique pour ces familles.
+La majorité de la commission qui se prononce pour le renvoi au Conseil fédéral fonde son argumentation sur la nécessité de clarifier les questions sensibles qui sont liées au droit de l'enfant à connaître ses origines. Elle se base aussi, pour ce faire, sur les critiques qui ont été émises lors de la consultation en lien précisément avec ces questions. Quelques remarques s'imposent sur ce point. D'une part, il n'est pas du tout question de court-circuiter la réflexion, large, à mener sur le droit des enfants à connaître leurs origines. Mais ces réflexions seront faites dans le cadre de la révision de la loi sur la procréation médicalement assistée (LPMA) et du droit de la filiation, révision qui est en cours. En l'espèce, il ne s'agit pas de cela. Il s'agit simplement d'enfants qui sont déjà là, de familles qui sont là et dont l'insécurité juridique est avérée. D'autre part, la révision de la LPMA et du droit de la filiation est en cours, mais le processus va encore prendre plusieurs années. On l'a entendu, il est prévu d'ouvrir la procédure de consultation sur le projet l'année prochaine, mais il n'en demeure pas moins que l'entier du processus va encore durer plusieurs années. Ainsi, renvoyer cette question jusqu'à la révision générale revient à contredire la décision que nous avons prise en acceptant la motion 22.3382 - à l'unanimité -, à nier le fait que nous avons reconnu la nécessité d'agir maintenant et donc, à ralentir et à reporter - peut-être pas aux calendes grecques, mais en tout cas, assurément de plusieurs années - la résolution de cette situation urgente.
+Un mot encore sur les réserves qui ont été exprimées lors de la consultation, par les cantons notamment, et qui nous ont été détaillées par le porteur de la minorité qui demandait de ne pas entrer en matière. La majorité des cantons a salué le but du projet, à savoir faciliter et accélérer la procédure d'adoption de l'enfant du conjoint. Le Conseil fédéral a tenu compte, dans le projet que nous avons aujourd'hui sur la table, des critiques qui ont été exprimées. Le Conseil fédéral a retiré certaines dispositions parmi les plus controversées, de manière à limiter les questions liées au droit de connaître ses origines.
+Enfin, le mandat inclus dans la proposition de renvoi au Conseil fédéral d'examiner la constitutionnalité des modifications a tout à fait sa place et sa légitimité, mais dans le cadre de la révision globale et non pas dans le cadre de cette révision qui est limitée, qui est circonscrite et qui, comme je l'ai déjà dit, a été débarrassée, dans la version qui est sur la table, des dispositions les plus controversées à l'origine.
+Je veux rappeler également, même si cela ne plaît pas forcément à tout le monde, qu'une large coalition soutient l'entrée en matière sur cette révision et, évidemment, son traitement maintenant et non dans deux, trois ou quatre ans. Vous avez toutes reçu des courriers, notamment de la Coalition pour l'égalité salariale et des associations faîtières de défense qui s'expriment largement en faveur d'une révision.
+La révision de la loi sur la procréation médicalement assistée et du droit de la filiation nous permettra d'examiner dans toute la profondeur requise les questions fondamentales qui sont liées à ces objets. Mais, en attendant, le bien et l'intérêt de l'enfant doivent impérativement primer dans nos considérations. L'intérêt de garantir la sécurité juridique des enfants et de leur donner en droit la situation qu'elles et ils vivent déjà dans les faits, soit deux parents légaux, ne saurait attendre encore plusieurs années.
+Je vous invite donc à refuser résolument le renvoi au Conseil fédéral, à entrer en matière également sur ce projet et, donc, à refuser la minorité Rieder. Il s'agit ainsi de nous conformer enfin à un mandat que nous avons donné il y a plusieurs années au Conseil fédéral et qu'il est désormais urgent de régler.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La motion Schilliger prévoit que les indemnités pour travail en équipe soient exclues des éléments de salaire pertinents lors de la vérification de l'analyse de l'égalité salariale. Or, cette analyse doit inclure tous les éléments de rémunération qui sont reconnus comme salaire, afin d'éviter de dissimuler des discriminations, y compris des discriminations indirectes. Ces éléments de rémunération font partie intégrante du salaire, selon la doctrine et la jurisprudence relatives, d'une part, à la</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La motion Schilliger prévoit que les indemnités pour travail en équipe soient exclues des éléments de salaire pertinents lors de la vérification de l'analyse de l'égalité salariale. Or, cette analyse doit inclure tous les éléments de rémunération qui sont reconnus comme salaire, afin d'éviter de dissimuler des discriminations, y compris des discriminations indirectes. Ces éléments de rémunération font partie intégrante du salaire, selon la doctrine et la jurisprudence relatives, d'une part, à la Constitution - l'article 8 alinéa 3 de la Constitution fédérale garantit l'égalité salariale -, ainsi qu'à l'article 3 de la loi sur l'égalité (LEg), et, d'autre part, à la doctrine et la jurisprudence correspondant au droit des assurances sociales et au droit fiscal. Comme tous les autres éléments de salaire, ils doivent être englobés dans cette analyse. Par ailleurs, les indemnités pour travail d'équipe recèlent un potentiel de discrimination salariale indirecte, ce qui est illégal. À l'inverse, il est à noter que, dans la pratique et à la connaissance des organismes qui sont chargés de suivre la mise en oeuvre de la LEg, aucune donnée ne vient confirmer que des entreprises auraient été accusées à tort de discrimination salariale.
+Par ailleurs, la motion Schilliger manque un peu sa cible, puisqu'elle vise à modifier l'ordonnance sur la vérification de l'analyse de l'égalité des salaires, mais celle-ci porte uniquement sur les analyses en application de la LEg et cette ordonnance sera, quant à elle, abrogée à la fin de 2032, de la même manière que la LEg, en vertu de la "Sunset-Klausel" ou clause d'extinction, que nous avons refusé d'abroger hier dans ce conseil.
+Ainsi, les analyses de l'égalité des salaires qui sont demandées, notamment dans les procédures de marché public, ne sont pas concernées par la modification qui est demandée par l'auteur. Les sanctions ne sont prévues également que dans le droit des marchés publics et pas dans la LEg. Enfin, si l'on modifie simplement l'ordonnance sur la vérification de l'analyse de l'égalité des salaires, on ne peut pas, sur la base de cette simple modification d'ordonnance, accéder à la demande de l'auteur de la motion, à savoir exclure ces indemnités, puisque l'obligation d'inclure ces indemnités découle directement de la définition du salaire, selon la Constitution et la LEg.
+Enfin, vous le savez, nous sommes en cours d'évaluation de l'efficacité des mesures de contrôle de l'égalité salariale en vertu de la LEg. Le rapport final est attendu pour fin 2027. En attendant, le bilan intermédiaire qui a été publié l'année dernière, en février 2025, faisait état de résultats aussi mitigés que sans appel : plus de la moitié des entreprises contrôlées ne se conformaient pas aux trois obligations qu'elles ont en vertu de la LEg. On constate donc déjà maintenant que la mise en oeuvre est problématique. Dès lors, il serait "dépiauté" déjà maintenant, avant le bilan final sur la LEg, ce qui ne ferait qu'accentuer ce phénomène. À l'inverse, nous avons refusé déjà plusieurs objets, dont l'intervention parlementaire de Maya Graf hier, plusieurs objets qui visaient à renforcer la LEg. Dès lors, ayons peut-être l'honnêteté de ne pas, à l'inverse, adopter des motions qui visent à affaiblir cette loi.
+Si nous voulons vraiment, avant d'agir plus avant pour renforcer la loi ou, le cas échéant, l'affaiblir, attendre le résultat du bilan final sur les effets de cette loi, faisons-le dans les deux sens et n'adoptons pas une politique du deux poids, deux mesures, qui n'est pas très sérieuse dans notre rôle de législateur.
+Vous l'avez vu également, cette motion Schilliger est controversée. Nous avons reçu un certain nombre de courriers nous invitant à la rejeter résolument, notamment la Coalition contre la discrimination salariale qui regroupe plus de 50 organisations et associations, dont les sections Femmes de la majorité des partis politiques qui sont représentés au Parlement, ainsi que toute une série d'associations, les Frauenzentralen, notamment des cantons d'Argovie, de Berne, Glaris, Saint-Gall, Zurich, l'Union suisse des paysannes et des femmes rurales, les syndicats évidemment, le Verband Frauenunternehmen, l'association Protection de l'enfance suisse, Alliance F. Il s'agit de toute une série d'organisations qui sont actives et qui cherchent à améliorer le problème de l'égalité salariale qui, au-delà des critiques que l'on peut apporter à la loi, reste malgré tout un problème prégnant et qui ne semble pas diminuer, en particulier pour ce qui concerne les parties inexpliquées des discriminations salariales.
+Je vous invite à rejeter cette motion Schilliger et ainsi, de la même manière que nous avons refusé d'améliorer d'ores et déjà la LEg, de refuser également par honnêteté de l'affaiblir.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne vais pas trop rallonger le débat, parce que ce que je voulais dire a été dit tant par M. Maillard que par M. Sommaruga. Aujourd'hui, j'invite vraiment M. Müller à retirer sa motion, parce qu'elle n'a plus d'objectif, puisque depuis le 12 juin, comme cela a été rappelé, l'Italie s'est engagée à reprendre les cas Dublin. J'avais de la sympathie pour le contenu de la motion lorsqu'elle a été déposée, mais, avec la réponse apportée par le Conseil fédéral, je crois qu'on a les réponses aux ques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne vais pas trop rallonger le débat, parce que ce que je voulais dire a été dit tant par M. Maillard que par M. Sommaruga. Aujourd'hui, j'invite vraiment M. Müller à retirer sa motion, parce qu'elle n'a plus d'objectif, puisque depuis le 12 juin, comme cela a été rappelé, l'Italie s'est engagée à reprendre les cas Dublin. J'avais de la sympathie pour le contenu de la motion lorsqu'elle a été déposée, mais, avec la réponse apportée par le Conseil fédéral, je crois qu'on a les réponses aux questions qui sont soulevées et qui se heurtent à d'autres réalités. C'est vrai qu'à force de vouloir faire de la cogestion, si je peux faire un ajout aux propos tenus par M. Maillard, on va arriver à la congestion, de telle sorte que l'administration ne passera plus son temps qu'à répondre aux interventions plutôt que d'agir réellement sur le terrain pour aboutir à des solutions concrètes. C'est la raison pour laquelle, si M. Müller maintient sa motion, je la rejetterai. Si les problèmes qui étaient soulevés, comme je l'ai dit, attiraient ma sympathie, avec les réponses qui sont données aujourd'hui, la motion n'a plus lieu d'être.
 </t>
   </si>
 </sst>
@@ -851,8 +946,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I41" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I47" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I47"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -2269,15 +2364,15 @@
         <v>14</v>
       </c>
       <c r="H39" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="I39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>46189</v>
@@ -2298,15 +2393,15 @@
         <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B41" s="1" t="n">
         <v>46189</v>
@@ -2327,10 +2422,184 @@
         <v>20</v>
       </c>
       <c r="H41" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I41" t="s">
-        <v>167</v>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>169</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" t="s">
+        <v>170</v>
+      </c>
+      <c r="E42" t="s">
+        <v>53</v>
+      </c>
+      <c r="F42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" t="s">
+        <v>171</v>
+      </c>
+      <c r="I42" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>173</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" t="s">
+        <v>174</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>175</v>
+      </c>
+      <c r="I43" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>176</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44" t="s">
+        <v>177</v>
+      </c>
+      <c r="I44" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>179</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" t="s">
+        <v>180</v>
+      </c>
+      <c r="I45" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>182</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" t="s">
+        <v>183</v>
+      </c>
+      <c r="I46" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>185</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" t="s">
+        <v>39</v>
+      </c>
+      <c r="F47" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I47" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -818,7 +818,7 @@
   </si>
   <si>
     <t xml:space="preserve">Das Freihandelsabkommen zwischen den EFTA-Staaten und den Mercosur-Staaten ist kein Luxus und ist auch nichts Böses, auch wenn es die Sprecherin der Grünen Fraktion soeben so dargelegt hat. Es ist eine absolute Notwendigkeit für die Schweizer Exportwirtschaft, für unsere KMU, für den Wohlstand der Menschen im Land, für unsere Arbeitsplätze. Es geht hier um einen riesigen Markt von 270 Millionen Konsumentinnen und Konsumenten. Dieser Markt ist derzeit durch massive bürokratische Hürden behindert. Unsere exportorientierten Unternehmen, von der Hightech-Firma bei mir im Rheintal bis zur Uhrenmanufaktur bei Bundesrätin Baume-Schneider oben im Jura, zahlen jedes Jahr Millionen Franken an Zöllen. Dieses Geld fehlt den Betrieben für Investitionen, für Forschung und vor allem für die Sicherung von Schweizer Arbeitsplätzen. Das scheint auf linker Seite nicht auf grosses Interesse zu stossen. Mit diesem Abkommen fallen künftig 95 Prozent der Zölle für Schweizer Ausfuhren weg. Das bedeutet konkret über 150 Millionen Franken Zolleinsparungen pro Jahr.
-Geschätzte Kolleginnen und Kollegen von der linken Ratsseite, wenn ich Ihre Anträge lese, kann ich nur denken, dass Sie die ganze Welt retten wollen. Was tun Sie wirklich? Sie untergraben die Existenzgrundlage unserer eigenen Bevölkerung - und vor allem diejenige der Menschen im Amazonasgebiet,die Sie schützen wollen. Ich werde es Ihnen nachher noch erklären. 
+Geschätzte Kolleginnen und Kollegen von der linken Ratsseite, wenn ich Ihre Anträge lese, kann ich nur denken, dass Sie die ganze Welt retten wollen. Was tun Sie wirklich? Sie untergraben die Existenzgrundlage unserer eigenen Bevölkerung - und vor allem diejenige der Menschen im Amazonasgebiet, die Sie schützen wollen. Ich werde es Ihnen nachher noch erklären.
 Unsere Unternehmer und ihre Angestellten brauchen gleich lange Spiesse - nein, lieber noch längere als die Konkurrenz. Ich begrüsse es, dass Bundesrat, Bundespräsident und Wirtschaftsminister Guy Parmelin durch Freihandelsabkommen Handelsbeziehungen dort unterstützt, wo Potenzial vorhanden ist und wo Wachstum stattfindet.
 Zu unserer Landwirtschaft: Diesbezüglich bitte ich Sie, beim Antrag der Minderheit Haab gut zuzuhören. Dazu von meiner Seite, gerade nach den Voten, die wir gehört haben, noch zwei, drei Sätze. Jedes Freihandelsabkommen ist ein Kompromiss. Die SVP-Fraktion wird dem Antrag der Minderheit Haab geschlossen zustimmen. Kollege Portmann, ich glaube, Herr Haab wird es schaffen, Ihnen den Fonds de Roulement zu erklären und Ihnen zu erklären, dass das nicht Geld ist, das zum Fenster hinausgeschmissen wird, wie bei den Anträgen von der linken Seite, sondern dass es eine sinnvolle Investition in den Nachwuchs in der Landwirtschaft ist. Ich sage es Ihnen, Herr Haab: Haben Sie Geduld mit Herrn Portmann und erklären Sie es ihm locker und leicht.
 Unsere Landwirtschaft wird mit diesem Abkommen eben genau nicht überrollt. Wir schützen die Landwirtschaft, während wir gleichzeitig der Industrie neue Tore öffnen. Das ist eine ausgewogene, eine typisch schweizerische Lösung.
@@ -841,10 +841,23 @@
     <t xml:space="preserve">377731</t>
   </si>
   <si>
-    <t xml:space="preserve">Monsieur le président de la Confédération, je profite de ce débat d'entrée en matière pour vous poser une question en lien avec les différences que nous pouvons constater entre l'accord conclu avec le Mercosur et celui conclu, par exemple, avec l'Indonésie. Ce dernier contient des approches axées sur les processus et les méthodes de production qui lient les avantages tarifaires à des conditions de production durables qui ne sont pas du tout présentes dans l'accord avec le Mercosur. Pourquoi le C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monsieur le président de la Confédération, je profite de ce débat d'entrée en matière pour vous poser une question en lien avec les différences que nous pouvons constater entre l'accord conclu avec le Mercosur et celui conclu, par exemple, avec l'Indonésie. Ce dernier contient des approches axées sur les processus et les méthodes de production qui lient les avantages tarifaires à des conditions de production durables qui ne sont pas du tout présentes dans l'accord avec le Mercosur. Pourquoi le Conseil fédéral a-t-il renoncé à cet instrument, alors que des baisses des droits de douane sont prévues pour des produits particulièrement sensibles tels que les dérivés du soja et la viande bovine ?
+    <t xml:space="preserve">Monsieur le président de la Confédération, je profite de ce débat d'entrée en matière pour vous poser une question en lien avec les différences que nous pouvons constater entre l'accord conclu avec le Mercosur et celui conclu, par exemple, avec l'Indonésie. Ce dernier contient des approches axées sur les processus et les méthodes de production qui lient les avantages tarifaires à des conditions de production durable qui ne sont pas du tout présentes dans l'accord avec le Mercosur. Pourquoi le Co</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le président de la Confédération, je profite de ce débat d'entrée en matière pour vous poser une question en lien avec les différences que nous pouvons constater entre l'accord conclu avec le Mercosur et celui conclu, par exemple, avec l'Indonésie. Ce dernier contient des approches axées sur les processus et les méthodes de production qui lient les avantages tarifaires à des conditions de production durable qui ne sont pas du tout présentes dans l'accord avec le Mercosur. Pourquoi le Conseil fédéral a-t-il renoncé à cet instrument, alors que des baisses des droits de douane sont prévues pour des produits particulièrement sensibles tels que les dérivés du soja et la viande bovine ?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stettler Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Kollege Portmann, Sie haben jetzt vor den Bauern etwas Süssholz geraspelt. Vorhin, in der Eintretensdebatte, haben Sie als Sprecher der FDP-Fraktion alle Bauern der Schweiz als ewige Jammerer, die seit 15 Jahren den Schweizer Staat melken, verunglimpft, nein, regelrecht durch den Dreck gezogen. Was für eine Ohrfeige für die Menschen, die für einen Stundenlohn, für den Sie, Herr Kollege Portmann, heute Morgen nicht einmal aufgestanden wären, jeden Tag kämpfen und nicht jammern, unsere schöne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Kollege Portmann, Sie haben jetzt vor den Bauern etwas Süssholz geraspelt. Vorhin, in der Eintretensdebatte, haben Sie als Sprecher der FDP-Fraktion alle Bauern der Schweiz als ewige Jammerer, die seit 15 Jahren den Schweizer Staat melken, verunglimpft, nein, regelrecht durch den Dreck gezogen. Was für eine Ohrfeige für die Menschen, die für einen Stundenlohn, für den Sie, Herr Kollege Portmann, heute Morgen nicht einmal aufgestanden wären, jeden Tag kämpfen und nicht jammern, unsere schöne Landschaft pflegen und die Schweiz mit hochwertigen Produkten versorgen! Deshalb meine Frage an Sie: Werden Sie sich, auch im Namen Ihrer Partei, dafür entschuldigen?
 </t>
   </si>
   <si>
@@ -946,8 +959,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I47" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I48" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I48"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -2523,13 +2536,13 @@
         <v>46190</v>
       </c>
       <c r="C45" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="F45" t="s">
         <v>20</v>
@@ -2538,15 +2551,15 @@
         <v>20</v>
       </c>
       <c r="H45" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B46" s="1" t="n">
         <v>46190</v>
@@ -2567,15 +2580,15 @@
         <v>20</v>
       </c>
       <c r="H46" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I46" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B47" s="1" t="n">
         <v>46190</v>
@@ -2584,22 +2597,51 @@
         <v>19</v>
       </c>
       <c r="D47" t="s">
+        <v>30</v>
+      </c>
+      <c r="E47" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" t="s">
+        <v>187</v>
+      </c>
+      <c r="I47" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>189</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" t="s">
         <v>64</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E48" t="s">
         <v>39</v>
       </c>
-      <c r="F47" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H47" t="s">
-        <v>186</v>
-      </c>
-      <c r="I47" t="s">
-        <v>187</v>
+      <c r="F48" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" t="s">
+        <v>190</v>
+      </c>
+      <c r="I48" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -834,7 +834,7 @@
     <t xml:space="preserve">Tschopp Jean</t>
   </si>
   <si>
-    <t xml:space="preserve">La forêt amazonienne est un écosystème indispensable pour notre planète. Aujourd'hui, elle est gravement menacée. L'évaluation d'impact environnemental du Secrétariat d'État à l'économie (SECO) nous apprend que le risque de défrichement est de 900 km2. C'est plus que la superficie du canton du Jura. Comment évaluez-vous ce risque considérable, sans garantie dans l'accord du Mercosur ?
+    <t xml:space="preserve">Monsieur le président, la forêt amazonienne est un écosystème indispensable pour notre planète. Aujourd'hui, elle est gravement menacée. L'évaluation d'impact environnemental du Secrétariat d'État à l'économie (SECO) nous apprend que le risque de défrichement est de 900 km2. C'est plus que la superficie du canton du Jura. Comment évaluez-vous ce risque considérable, sans garantie dans l'accord du Mercosur ?
 </t>
   </si>
   <si>
@@ -905,6 +905,68 @@
   </si>
   <si>
     <t xml:space="preserve">Je ne vais pas trop rallonger le débat, parce que ce que je voulais dire a été dit tant par M. Maillard que par M. Sommaruga. Aujourd'hui, j'invite vraiment M. Müller à retirer sa motion, parce qu'elle n'a plus d'objectif, puisque depuis le 12 juin, comme cela a été rappelé, l'Italie s'est engagée à reprendre les cas Dublin. J'avais de la sympathie pour le contenu de la motion lorsqu'elle a été déposée, mais, avec la réponse apportée par le Conseil fédéral, je crois qu'on a les réponses aux questions qui sont soulevées et qui se heurtent à d'autres réalités. C'est vrai qu'à force de vouloir faire de la cogestion, si je peux faire un ajout aux propos tenus par M. Maillard, on va arriver à la congestion, de telle sorte que l'administration ne passera plus son temps qu'à répondre aux interventions plutôt que d'agir réellement sur le terrain pour aboutir à des solutions concrètes. C'est la raison pour laquelle, si M. Müller maintient sa motion, je la rejetterai. Si les problèmes qui étaient soulevés, comme je l'ai dit, attiraient ma sympathie, avec les réponses qui sont données aujourd'hui, la motion n'a plus lieu d'être.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">378164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docourt Martine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette motion de la Commission de l'environnement, de l'aménagement du territoire et de l'énergie vise à clarifier les conditions d'encouragement de la géothermie dans le cadre de la loi sur le CO2 et à garantir que les moyens financiers décidés par le Parlement puissent effectivement être utilisés pour les projets que nous souhaitons voir se réaliser.
+Une interprétation restrictive de la notion d'utilisation directe de la géothermie menace aujourd'hui la réalisation d'une grande partie des proje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette motion de la Commission de l'environnement, de l'aménagement du territoire et de l'énergie vise à clarifier les conditions d'encouragement de la géothermie dans le cadre de la loi sur le CO2 et à garantir que les moyens financiers décidés par le Parlement puissent effectivement être utilisés pour les projets que nous souhaitons voir se réaliser.
+Une interprétation restrictive de la notion d'utilisation directe de la géothermie menace aujourd'hui la réalisation d'une grande partie des projets actuellement en préparation. Plus d'une vingtaine de projets géothermiques sont en cours de développement en Suisse. Nombre d'entre eux ont déjà franchi avec succès la phase d'exploration soutenue par la Confédération et s'apprêtent à entrer dans la phase de mise en oeuvre. La majorité de ces projets sont destinés à alimenter des réseaux thermiques urbains et représentent des investissements considérables de la part des collectivités publiques et des entreprises énergétiques. Or, selon l'interprétation actuellement retenue par l'Office fédéral de l'énergie et récemment confirmée par le Tribunal administratif fédéral, seule une définition très étroite de l'utilisation directe serait admissible. En pratique, la température de la ressource géothermique devrait être suffisamment élevée pour atteindre directement la température de départ du réseau de chaleur.
+Cette lecture ne correspond ni à la réalité technique des réseaux thermiques modernes ni aux pratiques courantes observées dans les pays voisins. Dans de nombreux projets, la chaleur géothermique est utilisée directement pour préchauffer le retour du réseau. Une pompe à chaleur peut ensuite compléter le système lorsque cela est nécessaire. Cette configuration permet déjà une valorisation directe de la ressource géothermique tout en limitant le recours à l'électricité. Elle est reconnue comme une solution efficace, économique, pertinente et largement répandue en Europe. Si l'interprétation actuelle devait prévaloir, une grande partie des projets situés notamment dans la région du pied du Jura, entre Genève et Bâle, deviendraient inéligibles au soutien prévu par la loi sur le CO2. Plus de la moitié des projets en développement pourraient ainsi être remis en question. Nous risquons alors de perdre des investissements déjà consentis, mais aussi de compromettre les objectifs qui ont été fixés dans la loi sur l'énergie et dans la loi sur le CO2.
+La conséquence serait également un report vers des solutions davantage dépendantes de l'électricité, alors même que nous cherchons à maîtriser la demande hivernale et à renforcer notre sécurité d'approvisionnement.
+La motion de commission ne crée pas de nouvelles subventions et ne modifie pas les montants octroyés par le Parlement. Elle vise simplement à garantir que l'intention du législateur soit respectée et que les projets géothermiques puissent bénéficier du soutien prévu lorsqu'ils contribuent effectivement à la production de chaleur renouvelable pour les réseaux thermiques.
+De plus, il est important de rappeler que le Parlement a confirmé, dans le cadre du programme d'allègement budgétaire 2027, le maintien d'un soutien annuel de 30 millions de francs à la géothermie. Nous avons ainsi affirmé notre volonté de développer cette ressource indigène, renouvelable et disponible toute l'année, afin de contribuer à la décarbonation du chauffage et au développement des réseaux thermiques.
+La commission estime qu'il appartient désormais au législateur de lever cette insécurité juridique et de corriger une interprétation qui menace le développement d'une filière importante pour la transition énergétique en Suisse.
+Pour toutes ces raisons, la CEATE du Conseil national vous invite donc à adopter la motion 26.3011. Au sein de la commission, la proposition de motion a été acceptée, par 14 voix contre 9 et 1 abstention.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">378198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klopfenstein Broggini Delphine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les agglomérations transfrontalières sont malheureusement un angle mort de notre politique des transports. Ce ne sont pas des cas particuliers, ce sont plutôt des moteurs économiques du pays, où se concentrent emplois, croissance et mobilité internationale. À Bâle, les flux quotidiens entre la Suisse, la France et l'Allemagne exercent une pression constante sur les infrastructures. Au Tessin, les axes avec l'Italie sont saturés aux heures de pointe. Dans l'arc jurassien, de Neuchâtel au canton d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les agglomérations transfrontalières sont malheureusement un angle mort de notre politique des transports. Ce ne sont pas des cas particuliers, ce sont plutôt des moteurs économiques du pays, où se concentrent emplois, croissance et mobilité internationale. À Bâle, les flux quotidiens entre la Suisse, la France et l'Allemagne exercent une pression constante sur les infrastructures. Au Tessin, les axes avec l'Italie sont saturés aux heures de pointe. Dans l'arc jurassien, de Neuchâtel au canton du Jura, les alternatives ferroviaires restent insuffisantes face à une forte dépendance à la route. Dans la vallée du Rhin saint-galloise, les déplacements transfrontaliers avec l'Autriche suivent la même dynamique. Près de 400 000 frontaliers travaillent aujourd'hui en Suisse. Ce chiffre a plus que doublé en 20 ans. Ces déplacements existent, la question maintenant est de savoir comment les organiser. Est-ce qu'on veut les organiser de manière efficace ou est-ce qu'on veut le faire à coup d'embouteillages et de pollution ?
+Prenons un exemple concret : le Grand Genève. Chaque jour, près de 300 000 véhicules franchissent la frontière. Dans le même temps, le Léman Express qui relie Genève à la Haute-Savoie montre qu'une alternative fonctionne quand l'offre est là. Là où le rail est développé, la demande suit. Là où elle ne l'est pas, la voiture et les nuisances, malheureusement, restent dominantes et, avec elles, les embouteillages. Le Conseil fédéral nous répond que les instruments existent déjà : la loi sur les chemins de fer, les programmes d'agglomération, la planification cantonale. C'est vrai sur le papier, mais, dans la réalité, cela ne suffit malheureusement pas. Pourquoi cela ne suffit-il pas ? Parce que ces instruments ont été pensés dans un cadre essentiellement national, à l'intérieur même des frontières, alors que les flux, eux, sont transfrontaliers. Le résultat est des projets qui avancent lentement, une coordination qui est complexe et surtout une absence de vision d'ensemble à l'échelle des bassins de vie.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je soutiens également le postulat Z'graggen dans le sens où les compétences et l'expérience des personnes plus âgées sont évidemment précieuses. Elles seules sont à même d'assurer le transfert d'expérience vers les plus jeunes générations ; elles représentent, à ce titre, une ressource précieuse. Je rejoins également les considérations évoquées selon lesquelles l'engagement à partir de la quarantaine - je n'avais pas conscience que c'était dès la quarantaine - devient plus compliqué pour les per</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je soutiens également le postulat Z'graggen dans le sens où les compétences et l'expérience des personnes plus âgées sont évidemment précieuses. Elles seules sont à même d'assurer le transfert d'expérience vers les plus jeunes générations ; elles représentent, à ce titre, une ressource précieuse. Je rejoins également les considérations évoquées selon lesquelles l'engagement à partir de la quarantaine - je n'avais pas conscience que c'était dès la quarantaine - devient plus compliqué pour les personnes impliquées. J'aimerais toutefois formuler deux remarques.
+Premièrement, je salue le fait que dans son postulat, l'auteure admette qu'il y a des mécanismes de discrimination, y compris cachés, dans les conditions de travail. J'aurais souhaité que, par cohérence, elle ne s'attaque pas à la protection contre les discriminations à l'égard des femmes, qui est garantie par la loi sur l'égalité (LEg) et que nous avons, à plusieurs égards, durant cette session et durant cette semaine de session, affaiblie en matière de discriminations cachées, notamment en adoptant la motion Schilliger 23.4139 hier. Autant je suis prête à soutenir la lutte contre les discriminations des travailleurs et des travailleuses âgés, autant je souhaiterais que la même chose soit faite pour les discriminations à l'égard des femmes en général. 
+Deuxièmement, les travailleurs et travailleuses âgés représentent effectivement, pour les budgets des unités administratives, un coût plus élevé - heureusement, d'ailleurs, en raison de l'évolution salariale et de la rémunération de l'expérience. Ces mêmes unités administratives sont soumises, année après année, à des coupes budgétaires qui restreignent leur budget. Dès lors, si nous souhaitons qu'une politique soit menée en faveur d'un personnel le plus adéquat et le plus expérimenté possible dans l'administration, il faut aussi lui en donner les moyens. Ainsi, ce Parlement devrait garder cette réflexion en tête lorsqu'il adopte des coupes à la hache dans tous les budgets de l'administration, qui sont généralement, vous le savez, répercutés sur le personnel, car c'est là un des leviers les plus flexibles.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J'ai cosigné ce postulat et je vous invite aussi à le soutenir, parce qu'il part d'un principe qui me paraît assez fondamental et qui consiste finalement à se poser des questions à intervalles réguliers pour voir si les décisions que nous avons prises à un moment donné sont toujours valables, sont toujours d'actualité ou permettent toujours d'atteindre les objectifs que nous nous sommes fixés. Cela implique un gros travail, c'est sûr. Cela implique peut-être aussi de remettre en cause certaines </t>
+  </si>
+  <si>
+    <t xml:space="preserve">J'ai cosigné ce postulat et je vous invite aussi à le soutenir, parce qu'il part d'un principe qui me paraît assez fondamental et qui consiste finalement à se poser des questions à intervalles réguliers pour voir si les décisions que nous avons prises à un moment donné sont toujours valables, sont toujours d'actualité ou permettent toujours d'atteindre les objectifs que nous nous sommes fixés. Cela implique un gros travail, c'est sûr. Cela implique peut-être aussi de remettre en cause certaines décisions que nous avons prises antérieurement, mais je crois qu'il faut être conscient que les choses évoluent, que le monde change et que ce qui était peut-être nécessaire à un moment donné devient moins nécessaire à un autre moment, que des priorités doivent être changées. C'est pour cela que je vous invite à soutenir ce postulat.
+Je vais même plus loin. La question qu'on devrait se poser, je l'ai déjà exprimé à quelques reprises, c'est la remise en cause des lois, des lois mêmes que nous faisons. Parce qu'on n'arrête pas de parler d'inflation législative, avec toujours plus de lois, toujours plus de réglementations qui arrivent, mais jamais d'abrogation de textes de loi qui sont en vigueur. On ne repose jamais ces questions.
+Alors, je sais que pour les docteurs en droit, ce que je vais dire est une hérésie, mais on devrait frapper chaque loi d'une date limite de réexamen pour pouvoir se poser la question de savoir si ce qu'elle contient, si les objectifs qui sont visés au travers de ces politiques publiques, sont encore d'actualité et ne mériteraient pas, peut-être, une remise en question, au même titre que celle qui nous est proposée ici par le postulat Regazzi que je vous invite vraiment à soutenir.
 </t>
   </si>
 </sst>
@@ -959,8 +1021,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I48" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I52" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I52"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -2644,6 +2706,122 @@
         <v>191</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>192</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" t="s">
+        <v>193</v>
+      </c>
+      <c r="E49" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" t="s">
+        <v>194</v>
+      </c>
+      <c r="G49" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" t="s">
+        <v>195</v>
+      </c>
+      <c r="I49" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>197</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" t="s">
+        <v>198</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>105</v>
+      </c>
+      <c r="G50" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" t="s">
+        <v>199</v>
+      </c>
+      <c r="I50" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>201</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" t="s">
+        <v>30</v>
+      </c>
+      <c r="E51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" t="s">
+        <v>202</v>
+      </c>
+      <c r="I51" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>204</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C52" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" t="s">
+        <v>39</v>
+      </c>
+      <c r="F52" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" t="s">
+        <v>205</v>
+      </c>
+      <c r="I52" t="s">
+        <v>206</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="211">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -942,7 +942,34 @@
   </si>
   <si>
     <t xml:space="preserve">Les agglomérations transfrontalières sont malheureusement un angle mort de notre politique des transports. Ce ne sont pas des cas particuliers, ce sont plutôt des moteurs économiques du pays, où se concentrent emplois, croissance et mobilité internationale. À Bâle, les flux quotidiens entre la Suisse, la France et l'Allemagne exercent une pression constante sur les infrastructures. Au Tessin, les axes avec l'Italie sont saturés aux heures de pointe. Dans l'arc jurassien, de Neuchâtel au canton du Jura, les alternatives ferroviaires restent insuffisantes face à une forte dépendance à la route. Dans la vallée du Rhin saint-galloise, les déplacements transfrontaliers avec l'Autriche suivent la même dynamique. Près de 400 000 frontaliers travaillent aujourd'hui en Suisse. Ce chiffre a plus que doublé en 20 ans. Ces déplacements existent, la question maintenant est de savoir comment les organiser. Est-ce qu'on veut les organiser de manière efficace ou est-ce qu'on veut le faire à coup d'embouteillages et de pollution ?
-Prenons un exemple concret : le Grand Genève. Chaque jour, près de 300 000 véhicules franchissent la frontière. Dans le même temps, le Léman Express qui relie Genève à la Haute-Savoie montre qu'une alternative fonctionne quand l'offre est là. Là où le rail est développé, la demande suit. Là où elle ne l'est pas, la voiture et les nuisances, malheureusement, restent dominantes et, avec elles, les embouteillages. Le Conseil fédéral nous répond que les instruments existent déjà : la loi sur les chemins de fer, les programmes d'agglomération, la planification cantonale. C'est vrai sur le papier, mais, dans la réalité, cela ne suffit malheureusement pas. Pourquoi cela ne suffit-il pas ? Parce que ces instruments ont été pensés dans un cadre essentiellement national, à l'intérieur même des frontières, alors que les flux, eux, sont transfrontaliers. Le résultat est des projets qui avancent lentement, une coordination qui est complexe et surtout une absence de vision d'ensemble à l'échelle des bassins de vie.
+Prenons un exemple concret : le Grand Genève. Chaque jour, près de 300 000 véhicules franchissent la frontière. Dans le même temps, le Léman Express qui relie Genève à la Haute-Savoie montre qu'une alternative fonctionne quand l'offre est là. Là où le rail est développé, la demande suit. Là où elle ne l'est pas, la voiture et les nuisances, malheureusement, restent dominantes et, avec elles, les embouteillages. Le Conseil fédéral nous répond que les instruments existent déjà : la loi sur les chemins de fer, les programmes d'agglomération, la planification cantonale. C'est vrai sur le papier, mais dans la réalité, cela ne suffit malheureusement pas. Pourquoi cela ne suffit-il pas ? Parce que ces instruments ont été pensés dans un cadre essentiellement national, à l'intérieur même des frontières, alors que les flux, eux, sont transfrontaliers. Le résultat est le suivant : des projets qui avancent lentement, une coordination qui est complexe et surtout une absence de vision d'ensemble à l'échelle des bassins de vie.
+Dire que les cantons doivent prendre l'initiative - c'est ce qui est écrit dans la réponse - revient à fragmenter la réponse face à un enjeu qui dépasse les frontières. Mais cet enjeu dépasse aussi les régions. À Bâle, à Genève, au Tessin, les décisions prises de l'autre côté de la frontière ont un impact direct sur notre réseau. Sans impulsion fédérale claire, on reste dans une logique réactive. La complexité ne s'arrête pas là : selon qu'on parle de rail, de bus ou de tram, les interlocuteurs ne sont pas les mêmes en face. Opérateurs nationaux, régions, départements, Länder, communes : les cadres de décision, les financements et les priorités diffèrent. Sans impulsion fédérale pour structurer aussi cette coordination, on multiplie les interfaces et malheureusement, on ralentit les projets. Par ailleurs, dans sa stratégie Perspective Rail 2050, le Conseil fédéral reconnaît le potentiel du transfert modal sur les courtes et moyennes distances, en particulier sur les fameux parcours transfrontaliers. Mais reconnaître un potentiel ne suffit pas aujourd'hui, malheureusement ; il faut le traduire en priorités opérationnelles.
+Ce que vise ce postulat est assez simple et n'est pas si exigeant que cela ; c'est faire, au fond, un état des lieux, consolider une forme d'identification des maillons faibles et des options concrètes, avec des modèles de financement adaptés, autrement dit, des bases nécessaires quand on s'intéresse un tant soit peu à nos agglomérations transfrontalières. Cela concerne au fond l'ensemble de la Suisse, les régions qui vivent sur ses frontières. Ce n'est pas une planification parallèle, mais un outil de pilotage. Dans n'importe quel domaine, quand plusieurs acteurs sont impliqués, on commence par une vision commune avant d'investir.
+Enfin, il y a une logique économique, bien sûr, parce que chaque franc investi intelligemment dans les transports publics transfrontaliers réduit des coûts ailleurs : congestion, infrastructures routières, pollution, perte de productivité. Le rapport coût-bénéfice est favorable, en particulier dans des zones qui sont particulièrement denses.
+Refuser d'effectuer cette analyse au motif que des instruments existent déjà - c'est la réponse du Conseil fédéral -, c'est malheureusement se priver d'une optimisation évidente. C'est maintenir une approche fragmentée face à un phénomène qui est pourtant structurant pour notre pays. Nous avons les données, nous avons des exemples qui fonctionnent, nous avons des besoins ; il manque maintenant une coordination à la hauteur de ces enjeux.
+Je vous remercie donc d'accepter ce postulat.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">378253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rechsteiner Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auf den ersten Blick mag die Forderung der Motion attraktiv erscheinen. Wird eine zusätzliche AHV-Rente ausbezahlt, sollen auch die daraus resultierenden entstehenden Steuererträge wieder der AHV zugeführt werden. Bei genauer Betrachtung zeigt sich jedoch, dass dieser Vorschlag erhebliche finanzielle, föderalistische und systematische Probleme schafft. 
+Aus fünf Gründen ist die Motion abzulehnen: 
+1. Die Finanzierung der AHV ist eine Bundesaufgabe. Mit der Neugestaltung des Finanzausgleichs und </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auf den ersten Blick mag die Forderung der Motion attraktiv erscheinen. Wird eine zusätzliche AHV-Rente ausbezahlt, sollen auch die daraus resultierenden entstehenden Steuererträge wieder der AHV zugeführt werden. Bei genauer Betrachtung zeigt sich jedoch, dass dieser Vorschlag erhebliche finanzielle, föderalistische und systematische Probleme schafft. 
+Aus fünf Gründen ist die Motion abzulehnen: 
+1. Die Finanzierung der AHV ist eine Bundesaufgabe. Mit der Neugestaltung des Finanzausgleichs und der Aufgabenteilung zwischen Bund und Kantonen wurde die Verantwortung für die AHV bewusst und konsequent dem Bund zugewiesen. Kantone und Gemeinden finanzieren die AHV heute nicht direkt. Genau diese Entflechtung war ein zentrales Ziel des Neuen Finanzausgleichs (NFA). Die Motion würde dieses Prinzip durchbrechen. Sie würde dazu führen, dass Kantone und Gemeinden plötzlich zur Mitfinanzierung einer Bundesaufgabe herangezogen würden, ohne dass sie auf die Ausgestaltung der Aufgabe einen entsprechenden Einfluss hätten. Damit wird ein Grundsatz unseres Föderalismus verletzt. Wer eine Aufgabe verantwortet, soll sie auch finanzieren. 
+2. Die Motion schafft einen problematischen Präzedenzfall. Wenn künftig sämtliche positiven finanziellen Auswirkungen von Bundesbeschlüssen bei Kantonen und Gemeinden abgeschöpft werden, stellt sich sofort die Gegenfrage: Müsste der Bund dann nicht umgekehrt auch sämtliche negativen Auswirkungen kompensieren? Denn genau solche negativen Effekte entstehen ebenfalls. Wer die Mehreinnahmen abschöpfen will, müsste konsequenterweise auch die Mindereinnahmen und Mehrkosten berücksichtigen. Eine einseitige Betrachtung ist weder sachgerecht noch fair. 
+3. Die Motion greift in die bestehende Steuersystematik ein. Bundesgesetze können Auswirkungen auf die Einnahmen von Kantonen und Gemeinden haben. Diese werden jedoch grundsätzlich nicht laufend über den Kantonsanteil an der direkten Bundessteuer nachkorrigiert. Anpassungen des Kantonsanteils wurden in der Vergangenheit nur bei grossen Reformen vorgenommen, beispielsweise beim NFA oder bei der Steuerreform und AHV-Finanzierung. Die vorliegende Motion würde dieses bewährte Prinzip aufgeben und einen neuen Mechanismus schaffen, bei dem künftig jede fiskalische Nebenwirkung eines Bundesentscheids nachträglich korrigiert werden müsste. 
+4. Die Umsetzung ist alles andere als einfach. Die Eidgenössische Steuerverwaltung hat aufgezeigt, dass die Abschöpfung der Steuermehreinnahmen faktisch über eine Senkung des Kantonsanteils an der direkten Bundessteuer am besten möglich wäre. Das ist aber nicht einfach so zu lösen. Zudem bestehen technische Herausforderungen. Die Steuermehreinnahmen der Kantone werden nach dem Forderungsprinzip berechnet, der Kantonsanteil an der direkten Bundessteuer hingegen nach dem Kassaprinzip ausbezahlt. Sie sehen, die Zahlungsströme laufen also zeitlich nicht parallel. Eine präzise und verursachergerechte Abschöpfung ist deshalb kaum möglich und würde zusätzlichen administrativen Aufwand verursachen. 
+5. Die Auswirkungen auf Kantone, Städte und Gemeinden wären erheblich. Viele Kantone würden einen Teil dieser Belastung zwangsläufig den Gemeinden weitergeben. Gerade Städte und Gemeinden lehnen die Motion deshalb auch entschieden ab, da diese Gemeinwesen weder für die Finanzierung der AHV verantwortlich sind noch die Möglichkeit haben, diese Ausgaben zu steuern. Gleichzeitig müssten sie die finanziellen Folgen davon tragen. Dies schwächt die finanzielle Handlungsfähigkeit von Kantonen und Gemeinden und erschwert die Erfüllung ihrer eigenen Aufgaben. 
+Die Verantwortung der Finanzierung der 13. AHV-Rente liegt beim Bund. Die Lösung kann nicht darin bestehen, den Kantonen und Gemeinden nachträglich Mittel zu entziehen und damit die klaren Aufgaben und die Finanzierungsordnung unseres Föderalismus zu verwässern. Die Motion verletzt bewährte Grundsätze der fiskalischen Äquivalenz, schafft neue Abgrenzungsprobleme, greift in die Steuerautonomie von Kantonen und Gemeinden ein und führt zu einer unnötigen Verkomplizierung unseres Finanzsystems. Aus all diesen Gründen bitte ich Sie, die Motion abzulehnen.
 </t>
   </si>
   <si>
@@ -1021,8 +1048,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I52" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I53" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I53"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -2772,30 +2799,30 @@
         <v>46191</v>
       </c>
       <c r="C51" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>30</v>
+        <v>202</v>
       </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F51" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="G51" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H51" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I51" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B52" s="1" t="n">
         <v>46191</v>
@@ -2804,22 +2831,51 @@
         <v>19</v>
       </c>
       <c r="D52" t="s">
+        <v>30</v>
+      </c>
+      <c r="E52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" t="s">
+        <v>206</v>
+      </c>
+      <c r="I52" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>208</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
         <v>64</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E53" t="s">
         <v>39</v>
       </c>
-      <c r="F52" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" t="s">
-        <v>20</v>
-      </c>
-      <c r="H52" t="s">
-        <v>205</v>
-      </c>
-      <c r="I52" t="s">
-        <v>206</v>
+      <c r="F53" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" t="s">
+        <v>209</v>
+      </c>
+      <c r="I53" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_Jura.xlsx
+++ b/Debats_Jura.xlsx
@@ -327,15 +327,16 @@
     <t xml:space="preserve">SO</t>
   </si>
   <si>
-    <t xml:space="preserve">Die sogenannte Blackout-Initiative und der Gegenvorschlag verkaufen sich als Lösung für Versorgungssicherheit. In Wahrheit sind sie aber ein gefährlicher Rückschritt in eine Technologie aus dem letzten Jahrtausend mit unabsehbaren Risiken, hohen Kosten, einer ungelösten Entsorgungsfrage und einer Abhängigkeit vom Ausland, da Uran in der Schweiz nicht abgebaut wird und auch nicht abgebaut werden soll. Ich könnte hier enden, möchte aber doch noch einige Punkte, die meinen Kanton betreffen, vertief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die sogenannte Blackout-Initiative und der Gegenvorschlag verkaufen sich als Lösung für Versorgungssicherheit. In Wahrheit sind sie aber ein gefährlicher Rückschritt in eine Technologie aus dem letzten Jahrtausend mit unabsehbaren Risiken, hohen Kosten, einer ungelösten Entsorgungsfrage und einer Abhängigkeit vom Ausland, da Uran in der Schweiz nicht abgebaut wird und auch nicht abgebaut werden soll. Ich könnte hier enden, möchte aber doch noch einige Punkte, die meinen Kanton betreffen, vertiefen. 
-Beznau 1 wurde 1961 gebaut, also in dem Jahr, als die ersten Schritte auf dem Mond gemacht wurden - wir wissen, wie lange das her ist. Beznau 1 ist das älteste AKW der Welt. Das AKW Gösgen im Kanton Solothurn, nahe der grössten Stadt des Kantons, wurde dann zehn Jahre später gebaut und war soeben mehrfach in den Medien, da es aufgrund von Sicherheitsmängeln sogar ausgeschaltet werden musste. Zudem liegt das AKW Leibstadt nur wenige Kilometer entfernt. Die Menschen in unserer Region tragen also seit Jahrzehnten das Risiko eines schweren Atomunfalls, ohne je gefragt worden zu sein, ob sie dieses Risiko überhaupt tragen wollen. Im Gegenteil, man hat sich sogar noch gewehrt und konnte immerhin dasjenige in Kaiseraugst verhindern. 
+    <t xml:space="preserve">Die sogenannte Blackout-Initiative und der Gegenvorschlag verkaufen sich als Lösung für Versorgungssicherheit. In Wahrheit sind sie ein gefährlicher Rückschritt in eine Technologie aus dem letzten Jahrtausend mit unabsehbaren Risiken, hohen Kosten, einer ungelösten Entsorgungsfrage und einer Abhängigkeit vom Ausland, da Uran in der Schweiz nicht abgebaut wird und auch nicht abgebaut werden soll. Ich könnte hier enden, möchte aber doch noch einige Punkte, die meinen Kanton betreffen, vertiefen. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die sogenannte Blackout-Initiative und der Gegenvorschlag verkaufen sich als Lösung für Versorgungssicherheit. In Wahrheit sind sie ein gefährlicher Rückschritt in eine Technologie aus dem letzten Jahrtausend mit unabsehbaren Risiken, hohen Kosten, einer ungelösten Entsorgungsfrage und einer Abhängigkeit vom Ausland, da Uran in der Schweiz nicht abgebaut wird und auch nicht abgebaut werden soll. Ich könnte hier enden, möchte aber doch noch einige Punkte, die meinen Kanton betreffen, vertiefen. 
+Beznau 1 wurde 1969 fertiggebaut, also in dem Jahr, in dem die ersten Schritte auf dem Mond gemacht wurden - wir wissen, wie lange das her ist. Beznau 1 ist das älteste AKW der Welt. Das AKW Gösgen im Kanton Solothurn, nahe der grössten Stadt des Kantons, wurde zehn Jahre später gebaut und war soeben mehrfach in den Medien, da es aufgrund von Sicherheitsmängeln sogar ausgeschaltet werden musste. Zudem liegt das AKW Leibstadt nur wenige Kilometer entfernt. Die Menschen in unserer Region tragen also seit Jahrzehnten das Risiko eines schweren Atomunfalls, ohne je gefragt worden zu sein, ob sie dieses Risiko überhaupt tragen wollen. Dabei hat man sich sogar noch gewehrt und konnte immerhin dasjenige in Kaiseraugst verhindern. 
 Als Mitglied der Organisation "Nie wieder Atomkraft" (NWA) habe ich an Veranstaltungen teilgenommen, an denen Fachpersonen eindrücklich aufgezeigt haben, welche Folgen Radioaktivität für Menschen haben kann. Besonders eindrücklich war die Perspektive von Ärztinnen der Organisation "International Physicians for the Prevention of Nuclear War". Die Ärztinnen, die sich für soziale Verantwortung und zur Verhütung eines Atomkriegs einsetzen, erinnern uns daran, dass Radioaktivität kein abstraktes Risiko ist. Sie bedeutet nämlich konkret Krebs, genetische Schäden, unbewohnbare Regionen und jahrzehntelanges menschliches Leid. 
-Wer heute nach den Katastrophen in Fukushima und Tschernobyl vor 15 und vor 40 Jahren ernsthaft behauptet, Atomkraft sei eine sichere Zukunftstechnologie, blendet die Realität aus. Ein schwerer Unfall in Gösgen oder Leibstadt hätte katastrophale Folgen für die gesamte Nordwestschweiz, auch für Solothurn: kontaminierte Böden, kontaminiertes Trinkwasser, zerstörte Existenzen. Und trotzdem soll die Schweiz nun erneut Milliarden in diese Technologie investieren, die viel zu spät kommt, weil der Bau lange dauert, viel zu teuer ist und den Ausbau der erneuerbaren Energien ausbremst? 
-Neue AKW wären frühestens in Jahrzehnten betriebsbereit. Die Klimakrise und die Energiefrage lösen wir aber jetzt mit Solarenergie, Windkraft, Speichertechnologien, Effizienz, Suffizienz und einem intelligenten Stromnetz. Die Milliarden müssen wir in diese Lösungen investieren. Echte Versorgungssicherheit entsteht nicht durch zentrale Hochrisikoanlagen, sondern durch dezentrale, erneuerbare und demokratische Energieversorgung. Auch der Kanton Solothurn hat riesiges Potenzial bei Solarenergie auf Dächern, Fassaden und Infrastrukturen. Dieses Potenzial müssen wir endlich konsequent und besser nutzen und ja, auch auf Autobahnen, Herr Kollege Imark, wie das vorher genannt wurde. Die Sonne schickt nämlich keine radioaktive Rechnung an kommende Generationen. 
-Atomkraft hinterlässt indes ein Erbe für unzählige Generationen danach. Noch immer gibt es weltweit nämlich kein einziges Tiefenlager, das über Hunderttausende Jahre Sicherheit garantieren kann. Mit den Grünen durften wir einmal das Felslabor Mont Terri im Jura besichtigen, wo plastisch gezeigt wird, wie kompliziert es ist, ein solches Tiefenlager mit Opalinuston zu bauen. Es ist deshalb verantwortungslos, kommenden Generationen hochradioaktiven Abfall zu hinterlassen, weil man heute einfach diesen Weg gehen will. 
+Wer heute, nach den Katastrophen in Fukushima und Tschernobyl vor 15 und vor 40 Jahren, ernsthaft behauptet, Atomkraft sei eine sichere Zukunftstechnologie, blendet die Realität aus. Ein schwerer Unfall in Gösgen oder Leibstadt hätte katastrophale Folgen für die gesamte Nordwestschweiz, auch für Solothurn: kontaminierte Böden, kontaminiertes Trinkwasser, zerstörte Existenzen. Trotzdem soll die Schweiz nun erneut Milliarden in diese Technologie investieren, obwohl sie viel zu spät kommt, der Bau lange dauert, viel zu teuer ist und den Ausbau der erneuerbaren Energien ausbremst? 
+Neue AKW wären frühestens in Jahrzehnten betriebsbereit. Die Klimakrise und die Energiefrage lösen wir aber jetzt mit Solarenergie, Windkraft, Speichertechnologien, Effizienz, Suffizienz und einem intelligenten Stromnetz. Die Milliarden müssen wir in diese Lösungen investieren. Echte Versorgungssicherheit entsteht nicht durch zentrale Hochrisikoanlagen, sondern durch eine dezentrale, erneuerbare und demokratische Energieversorgung. Auch der Kanton Solothurn hat riesiges Potenzial bei Solarenergie auf Dächern, Fassaden und Infrastrukturen. Dieses Potenzial müssen wir endlich konsequent und besser nutzen - ja, auch auf Autobahnen, Herr Kollege Imark, wie vorher gesagt wurde. Die Sonne schickt nämlich keine radioaktive Rechnung an kommende Generationen. 
+Atomkraft hinterlässt indes ein Erbe für unzählige nachfolgende Generationen. Noch immer gibt es weltweit nämlich kein einziges Tiefenlager, das über Hunderttausende Jahre Sicherheit garantieren kann. Wir Grünen durften einmal das Felslabor Mont Terri im Jura besichtigen, wo plastisch gezeigt wird, wie kompliziert es ist, ein solches Tiefenlager mit Opalinuston zu bauen. Es ist verantwortungslos, kommenden Generationen hochradioaktiven Abfall zu hinterlassen, weil man heute einfach diesen Weg gehen will. 
 Darum sage ich klar Nein zur Blackout-Initiative und zum Gegenvorschlag.
 </t>
   </si>
